--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7525A4-734D-C143-81EB-0560642290ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EA017D-EDC3-064C-B02E-E4E6DE022333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1573,6 +1573,9 @@
       <c r="B6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="C6" s="15">
+        <v>11</v>
+      </c>
       <c r="D6" s="33"/>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -1584,7 +1587,7 @@
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -4016,6 +4019,9 @@
       <c r="A17" s="14"/>
       <c r="B17" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>10</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="10"/>
@@ -4028,7 +4034,7 @@
       <c r="L17" s="35"/>
       <c r="M17" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="0"/>
@@ -6464,6 +6470,9 @@
       <c r="A28" s="14"/>
       <c r="B28" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C28" s="1">
+        <v>7</v>
       </c>
       <c r="D28" s="35"/>
       <c r="E28" s="10"/>
@@ -6476,7 +6485,7 @@
       <c r="L28" s="35"/>
       <c r="M28" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="0"/>
@@ -8912,6 +8921,9 @@
       <c r="A39" s="14"/>
       <c r="B39" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
       </c>
       <c r="D39" s="35"/>
       <c r="E39" s="10"/>
@@ -8924,7 +8936,7 @@
       <c r="L39" s="35"/>
       <c r="M39" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="0"/>
@@ -11361,6 +11373,9 @@
       <c r="A50" s="14"/>
       <c r="B50" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2</v>
       </c>
       <c r="D50" s="35"/>
       <c r="E50" s="10"/>
@@ -11373,7 +11388,7 @@
       <c r="L50" s="35"/>
       <c r="M50" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="0"/>
@@ -13813,7 +13828,7 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E7:G60 M5:O60 U5:W60 AC5:AE60 AJ5:AM60 AS5:AU60 BA5:BC60 BI5:BK60 BQ5:BS60 BY5:CA60 CG5:CI60 CO5:CQ60 CW5:CY60</xm:sqref>
+          <xm:sqref>M5:O60 U5:W60 AC5:AE60 AJ5:AM60 AS5:AU60 BA5:BC60 BI5:BK60 BQ5:BS60 BY5:CA60 CG5:CI60 CO5:CQ60 CW5:CY60 E7:G60</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EA017D-EDC3-064C-B02E-E4E6DE022333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31EB115-C919-0E45-A498-A6E2069C6246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="3120" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="2820" yWindow="3840" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
-    <sheet name="26Q3" sheetId="2" r:id="rId1"/>
+    <sheet name="26Q4" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="25">
   <si>
     <t>總計</t>
   </si>
@@ -149,6 +149,14 @@
   </si>
   <si>
     <t>06/28~07/04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q4W2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>07/05-07/11</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -928,7 +936,9 @@
       </c>
       <c r="B1" s="26"/>
       <c r="D1" s="25"/>
-      <c r="I1" s="26"/>
+      <c r="I1" s="26" t="s">
+        <v>23</v>
+      </c>
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
       <c r="Q1" s="26"/>
@@ -969,7 +979,9 @@
       </c>
       <c r="B2" s="22"/>
       <c r="D2" s="21"/>
-      <c r="I2" s="23"/>
+      <c r="I2" s="23" t="s">
+        <v>24</v>
+      </c>
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
@@ -1324,11 +1336,13 @@
       <c r="J5" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="40"/>
+      <c r="K5" s="40">
+        <v>4160</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="10">
         <f t="shared" ref="M5:N60" si="0">K5-C5</f>
-        <v>-6261</v>
+        <v>-2101</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
@@ -1349,7 +1363,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="10">
         <f t="shared" ref="U5:U60" si="2">S5-K5</f>
-        <v>0</v>
+        <v>-4160</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V60" si="3">T5-L5</f>
@@ -1801,18 +1815,23 @@
       <c r="J7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="K7" s="10">
+        <v>159</v>
+      </c>
+      <c r="L7" s="12">
+        <v>178482.85714225</v>
+      </c>
       <c r="M7" s="10">
         <f t="shared" si="0"/>
-        <v>-193</v>
+        <v>-34</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>-256952.38095148996</v>
+        <v>-78469.523809239967</v>
       </c>
       <c r="O7" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.30538547071900546</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="13" t="s">
@@ -1821,15 +1840,15 @@
       <c r="T7" s="12"/>
       <c r="U7" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-159</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W7" s="11" t="e">
+        <v>-178482.85714225</v>
+      </c>
+      <c r="W7" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y7" s="14"/>
       <c r="Z7" s="13"/>
@@ -2020,18 +2039,23 @@
       <c r="J8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="12"/>
+      <c r="K8" s="10">
+        <v>189</v>
+      </c>
+      <c r="L8" s="12">
+        <v>267975.23809503997</v>
+      </c>
       <c r="M8" s="10">
         <f t="shared" si="0"/>
-        <v>-234</v>
+        <v>-45</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="0"/>
-        <v>-286997.14285695989</v>
+        <v>-19021.904761919926</v>
       </c>
       <c r="O8" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-6.6279073626180629E-2</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="13" t="s">
@@ -2040,15 +2064,15 @@
       <c r="T8" s="12"/>
       <c r="U8" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-189</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="11" t="e">
+        <v>-267975.23809503997</v>
+      </c>
+      <c r="W8" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13"/>
@@ -2239,18 +2263,23 @@
       <c r="J9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="K9" s="10">
+        <v>62</v>
+      </c>
+      <c r="L9" s="12">
+        <v>412266.66666664998</v>
+      </c>
       <c r="M9" s="10">
         <f t="shared" si="0"/>
-        <v>-53</v>
+        <v>9</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="0"/>
-        <v>-343780.95238093002</v>
+        <v>68485.714285719965</v>
       </c>
       <c r="O9" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.19921323101645744</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="13" t="s">
@@ -2259,15 +2288,15 @@
       <c r="T9" s="12"/>
       <c r="U9" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="11" t="e">
+        <v>-412266.66666664998</v>
+      </c>
+      <c r="W9" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y9" s="14"/>
       <c r="Z9" s="13"/>
@@ -2458,18 +2487,23 @@
       <c r="J10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="K10" s="10">
+        <v>25</v>
+      </c>
+      <c r="L10" s="12">
+        <v>279147.61904757004</v>
+      </c>
       <c r="M10" s="10">
         <f t="shared" si="0"/>
-        <v>-48</v>
+        <v>-23</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="0"/>
-        <v>-644380.95238085999</v>
+        <v>-365233.33333328995</v>
       </c>
       <c r="O10" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.5667972214011372</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="13" t="s">
@@ -2478,15 +2512,15 @@
       <c r="T10" s="12"/>
       <c r="U10" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="11" t="e">
+        <v>-279147.61904757004</v>
+      </c>
+      <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="13"/>
@@ -2677,18 +2711,23 @@
       <c r="J11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="K11" s="10">
+        <v>8</v>
+      </c>
+      <c r="L11" s="12">
+        <v>35120</v>
+      </c>
       <c r="M11" s="10">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="0"/>
-        <v>-34820</v>
+        <v>300</v>
       </c>
       <c r="O11" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>8.6157380815623207E-3</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="13" t="s">
@@ -2697,15 +2736,15 @@
       <c r="T11" s="12"/>
       <c r="U11" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="11" t="e">
+        <v>-35120</v>
+      </c>
+      <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="13"/>
@@ -2896,18 +2935,23 @@
       <c r="J12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="K12" s="10">
+        <v>28</v>
+      </c>
+      <c r="L12" s="12">
+        <v>1034838.0952380203</v>
+      </c>
       <c r="M12" s="10">
         <f t="shared" si="0"/>
-        <v>-12</v>
+        <v>16</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
-        <v>-496161.90476184007</v>
+        <v>538676.19047618029</v>
       </c>
       <c r="O12" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>1.0856863159108261</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="13" t="s">
@@ -2916,15 +2960,15 @@
       <c r="T12" s="12"/>
       <c r="U12" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="11" t="e">
+        <v>-1034838.0952380203</v>
+      </c>
+      <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y12" s="14"/>
       <c r="Z12" s="13"/>
@@ -3115,18 +3159,23 @@
       <c r="J13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="K13" s="10">
+        <v>60</v>
+      </c>
+      <c r="L13" s="12">
+        <v>1410190.47619037</v>
+      </c>
       <c r="M13" s="10">
         <f t="shared" si="0"/>
-        <v>-33</v>
+        <v>27</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="0"/>
-        <v>-822857.14285706007</v>
+        <v>587333.33333330997</v>
       </c>
       <c r="O13" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.71377314814819159</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="13" t="s">
@@ -3135,15 +3184,15 @@
       <c r="T13" s="12"/>
       <c r="U13" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="11" t="e">
+        <v>-1410190.47619037</v>
+      </c>
+      <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y13" s="14"/>
       <c r="Z13" s="13"/>
@@ -3334,18 +3383,23 @@
       <c r="J14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="12"/>
+      <c r="K14" s="10">
+        <v>140</v>
+      </c>
+      <c r="L14" s="12">
+        <v>5139047.6190475598</v>
+      </c>
       <c r="M14" s="10">
         <f t="shared" si="0"/>
-        <v>-59</v>
+        <v>81</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="0"/>
-        <v>-2111523.8095237603</v>
+        <v>3027523.8095237995</v>
       </c>
       <c r="O14" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>1.433809931893042</v>
       </c>
       <c r="Q14" s="14"/>
       <c r="R14" s="13" t="s">
@@ -3354,15 +3408,15 @@
       <c r="T14" s="12"/>
       <c r="U14" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-140</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="11" t="e">
+        <v>-5139047.6190475598</v>
+      </c>
+      <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="13"/>
@@ -3554,19 +3608,23 @@
         <v>18</v>
       </c>
       <c r="J15" s="9"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
+      <c r="K15" s="8">
+        <v>671</v>
+      </c>
+      <c r="L15" s="7">
+        <v>8757068.5714274608</v>
+      </c>
       <c r="M15" s="27">
         <f t="shared" si="0"/>
-        <v>-640</v>
+        <v>31</v>
       </c>
       <c r="N15" s="28">
         <f t="shared" si="0"/>
-        <v>-4997474.2857129006</v>
+        <v>3759594.2857145602</v>
       </c>
       <c r="O15" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.7522988755465394</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>18</v>
@@ -3576,15 +3634,15 @@
       <c r="T15" s="7"/>
       <c r="U15" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-671</v>
       </c>
       <c r="V15" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="29" t="e">
+        <v>-8757068.5714274608</v>
+      </c>
+      <c r="W15" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y15" s="9" t="s">
         <v>18</v>
@@ -3789,10 +3847,13 @@
       <c r="J16" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="K16" s="1">
+        <v>2903</v>
+      </c>
       <c r="L16" s="35"/>
       <c r="M16" s="10">
         <f t="shared" si="0"/>
-        <v>-4406</v>
+        <v>-1503</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="0"/>
@@ -3811,7 +3872,7 @@
       <c r="T16" s="35"/>
       <c r="U16" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2903</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="3"/>
@@ -4252,18 +4313,23 @@
       <c r="J18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L18" s="12"/>
+      <c r="K18" s="10">
+        <v>99</v>
+      </c>
+      <c r="L18" s="12">
+        <v>104603.80952343997</v>
+      </c>
       <c r="M18" s="10">
         <f t="shared" si="0"/>
-        <v>-142</v>
+        <v>-43</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="0"/>
-        <v>-144453.33333267999</v>
+        <v>-39849.523809240025</v>
       </c>
       <c r="O18" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.27586434241337637</v>
       </c>
       <c r="Q18" s="14"/>
       <c r="R18" s="13" t="s">
@@ -4272,15 +4338,15 @@
       <c r="T18" s="12"/>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="11" t="e">
+        <v>-104603.80952343997</v>
+      </c>
+      <c r="W18" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y18" s="14"/>
       <c r="Z18" s="13"/>
@@ -4471,18 +4537,23 @@
       <c r="J19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L19" s="12"/>
+      <c r="K19" s="10">
+        <v>133</v>
+      </c>
+      <c r="L19" s="12">
+        <v>152373.33333323002</v>
+      </c>
       <c r="M19" s="10">
         <f t="shared" si="0"/>
-        <v>-185</v>
+        <v>-52</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="0"/>
-        <v>-198114.28571418001</v>
+        <v>-45740.952380949981</v>
       </c>
       <c r="O19" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.23088164599568842</v>
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="13" t="s">
@@ -4491,15 +4562,15 @@
       <c r="T19" s="12"/>
       <c r="U19" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-133</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="11" t="e">
+        <v>-152373.33333323002</v>
+      </c>
+      <c r="W19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="13"/>
@@ -4690,18 +4761,23 @@
       <c r="J20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="12"/>
+      <c r="K20" s="10">
+        <v>33</v>
+      </c>
+      <c r="L20" s="12">
+        <v>241114.28571425998</v>
+      </c>
       <c r="M20" s="10">
         <f t="shared" si="0"/>
-        <v>-37</v>
+        <v>-4</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="0"/>
-        <v>-225361.90476189001</v>
+        <v>15752.380952369975</v>
       </c>
       <c r="O20" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>6.9898153234964108E-2</v>
       </c>
       <c r="Q20" s="14"/>
       <c r="R20" s="13" t="s">
@@ -4710,15 +4786,15 @@
       <c r="T20" s="12"/>
       <c r="U20" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="11" t="e">
+        <v>-241114.28571425998</v>
+      </c>
+      <c r="W20" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y20" s="14"/>
       <c r="Z20" s="13"/>
@@ -4909,18 +4985,23 @@
       <c r="J21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="12"/>
+      <c r="K21" s="10">
+        <v>21</v>
+      </c>
+      <c r="L21" s="12">
+        <v>262190.47619041003</v>
+      </c>
       <c r="M21" s="10">
         <f t="shared" si="0"/>
-        <v>-22</v>
+        <v>-1</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="0"/>
-        <v>-241714.28571422998</v>
+        <v>20476.190476180054</v>
       </c>
       <c r="O21" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>8.4712371946390919E-2</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="R21" s="13" t="s">
@@ -4929,15 +5010,15 @@
       <c r="T21" s="12"/>
       <c r="U21" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="11" t="e">
+        <v>-262190.47619041003</v>
+      </c>
+      <c r="W21" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="13"/>
@@ -5128,18 +5209,23 @@
       <c r="J22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="12"/>
+      <c r="K22" s="10">
+        <v>16</v>
+      </c>
+      <c r="L22" s="12">
+        <v>43520</v>
+      </c>
       <c r="M22" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="0"/>
-        <v>-48020</v>
+        <v>-4500</v>
       </c>
       <c r="O22" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-9.3710953769262806E-2</v>
       </c>
       <c r="Q22" s="14"/>
       <c r="R22" s="13" t="s">
@@ -5148,15 +5234,15 @@
       <c r="T22" s="12"/>
       <c r="U22" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="11" t="e">
+        <v>-43520</v>
+      </c>
+      <c r="W22" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y22" s="14"/>
       <c r="Z22" s="13"/>
@@ -5347,18 +5433,23 @@
       <c r="J23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="12"/>
+      <c r="K23" s="10">
+        <v>13</v>
+      </c>
+      <c r="L23" s="12">
+        <v>544261.90476184001</v>
+      </c>
       <c r="M23" s="10">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="0"/>
-        <v>-197980.95238092</v>
+        <v>346280.95238092</v>
       </c>
       <c r="O23" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>1.74906195882252</v>
       </c>
       <c r="Q23" s="14"/>
       <c r="R23" s="13" t="s">
@@ -5367,15 +5458,15 @@
       <c r="T23" s="12"/>
       <c r="U23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="11" t="e">
+        <v>-544261.90476184001</v>
+      </c>
+      <c r="W23" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y23" s="14"/>
       <c r="Z23" s="13"/>
@@ -5566,18 +5657,23 @@
       <c r="J24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="12"/>
+      <c r="K24" s="10">
+        <v>16</v>
+      </c>
+      <c r="L24" s="12">
+        <v>381904.76190469001</v>
+      </c>
       <c r="M24" s="10">
         <f t="shared" si="0"/>
-        <v>-27</v>
+        <v>-11</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="0"/>
-        <v>-568285.71428566007</v>
+        <v>-186380.95238097006</v>
       </c>
       <c r="O24" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.32797050444115505</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="13" t="s">
@@ -5586,15 +5682,15 @@
       <c r="T24" s="12"/>
       <c r="U24" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="11" t="e">
+        <v>-381904.76190469001</v>
+      </c>
+      <c r="W24" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y24" s="14"/>
       <c r="Z24" s="13"/>
@@ -5785,18 +5881,23 @@
       <c r="J25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="12"/>
+      <c r="K25" s="10">
+        <v>28</v>
+      </c>
+      <c r="L25" s="12">
+        <v>979238.09523806989</v>
+      </c>
       <c r="M25" s="10">
         <f t="shared" si="0"/>
-        <v>-43</v>
+        <v>-15</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="0"/>
-        <v>-1540666.66666663</v>
+        <v>-561428.57142856007</v>
       </c>
       <c r="O25" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.3644062557952662</v>
       </c>
       <c r="Q25" s="14"/>
       <c r="R25" s="13" t="s">
@@ -5805,15 +5906,15 @@
       <c r="T25" s="12"/>
       <c r="U25" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="11" t="e">
+        <v>-979238.09523806989</v>
+      </c>
+      <c r="W25" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y25" s="14"/>
       <c r="Z25" s="13"/>
@@ -6005,19 +6106,23 @@
         <v>12</v>
       </c>
       <c r="J26" s="9"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
+      <c r="K26" s="8">
+        <v>359</v>
+      </c>
+      <c r="L26" s="7">
+        <v>2709206.6666659401</v>
+      </c>
       <c r="M26" s="27">
         <f t="shared" si="0"/>
-        <v>-475</v>
+        <v>-116</v>
       </c>
       <c r="N26" s="28">
         <f t="shared" si="0"/>
-        <v>-3164597.14285619</v>
+        <v>-455390.4761902499</v>
       </c>
       <c r="O26" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.14390156333745524</v>
       </c>
       <c r="Q26" s="9" t="s">
         <v>12</v>
@@ -6027,15 +6132,15 @@
       <c r="T26" s="7"/>
       <c r="U26" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-359</v>
       </c>
       <c r="V26" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="29" t="e">
+        <v>-2709206.6666659401</v>
+      </c>
+      <c r="W26" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y26" s="9" t="s">
         <v>12</v>
@@ -6240,10 +6345,13 @@
       <c r="J27" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="K27" s="1">
+        <v>2311</v>
+      </c>
       <c r="L27" s="35"/>
       <c r="M27" s="10">
         <f t="shared" si="0"/>
-        <v>-3539</v>
+        <v>-1228</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="0"/>
@@ -6262,7 +6370,7 @@
       <c r="T27" s="35"/>
       <c r="U27" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2311</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="3"/>
@@ -6703,18 +6811,23 @@
       <c r="J29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="12"/>
+      <c r="K29" s="10">
+        <v>63</v>
+      </c>
+      <c r="L29" s="12">
+        <v>74600.952380670016</v>
+      </c>
       <c r="M29" s="10">
         <f t="shared" si="0"/>
-        <v>-77</v>
+        <v>-14</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="0"/>
-        <v>-84747.619047319968</v>
+        <v>-10146.666666649951</v>
       </c>
       <c r="O29" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.11972804405259367</v>
       </c>
       <c r="Q29" s="14"/>
       <c r="R29" s="13" t="s">
@@ -6723,15 +6836,15 @@
       <c r="T29" s="12"/>
       <c r="U29" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W29" s="11" t="e">
+        <v>-74600.952380670016</v>
+      </c>
+      <c r="W29" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y29" s="14"/>
       <c r="Z29" s="13"/>
@@ -6922,18 +7035,23 @@
       <c r="J30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="12"/>
+      <c r="K30" s="10">
+        <v>44</v>
+      </c>
+      <c r="L30" s="12">
+        <v>39866.666666610006</v>
+      </c>
       <c r="M30" s="10">
         <f t="shared" si="0"/>
-        <v>-47</v>
+        <v>-3</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="0"/>
-        <v>-48895.238095150009</v>
+        <v>-9028.5714285400027</v>
       </c>
       <c r="O30" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.18465134398099106</v>
       </c>
       <c r="Q30" s="14"/>
       <c r="R30" s="13" t="s">
@@ -6942,15 +7060,15 @@
       <c r="T30" s="12"/>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="11" t="e">
+        <v>-39866.666666610006</v>
+      </c>
+      <c r="W30" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y30" s="14"/>
       <c r="Z30" s="13"/>
@@ -7141,18 +7259,23 @@
       <c r="J31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L31" s="12"/>
+      <c r="K31" s="10">
+        <v>15</v>
+      </c>
+      <c r="L31" s="12">
+        <v>96999.999999989988</v>
+      </c>
       <c r="M31" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="0"/>
-        <v>-101304.76190474999</v>
+        <v>-4304.7619047600019</v>
       </c>
       <c r="O31" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-4.2493184168454767E-2</v>
       </c>
       <c r="Q31" s="14"/>
       <c r="R31" s="13" t="s">
@@ -7161,15 +7284,15 @@
       <c r="T31" s="12"/>
       <c r="U31" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="11" t="e">
+        <v>-96999.999999989988</v>
+      </c>
+      <c r="W31" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y31" s="14"/>
       <c r="Z31" s="13"/>
@@ -7360,18 +7483,23 @@
       <c r="J32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L32" s="12"/>
+      <c r="K32" s="10">
+        <v>9</v>
+      </c>
+      <c r="L32" s="12">
+        <v>110571.4285714</v>
+      </c>
       <c r="M32" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="0"/>
-        <v>-164190.47619043002</v>
+        <v>-53619.047619030025</v>
       </c>
       <c r="O32" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.32656612529000789</v>
       </c>
       <c r="Q32" s="14"/>
       <c r="R32" s="13" t="s">
@@ -7380,15 +7508,15 @@
       <c r="T32" s="12"/>
       <c r="U32" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="11" t="e">
+        <v>-110571.4285714</v>
+      </c>
+      <c r="W32" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="13"/>
@@ -7579,18 +7707,23 @@
       <c r="J33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="12"/>
+      <c r="K33" s="10">
+        <v>2</v>
+      </c>
+      <c r="L33" s="12">
+        <v>3880</v>
+      </c>
       <c r="M33" s="10">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="0"/>
-        <v>-14760</v>
+        <v>-10880</v>
       </c>
       <c r="O33" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.73712737127371275</v>
       </c>
       <c r="Q33" s="14"/>
       <c r="R33" s="13" t="s">
@@ -7599,15 +7732,15 @@
       <c r="T33" s="12"/>
       <c r="U33" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="11" t="e">
+        <v>-3880</v>
+      </c>
+      <c r="W33" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y33" s="14"/>
       <c r="Z33" s="13"/>
@@ -7798,18 +7931,23 @@
       <c r="J34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L34" s="12"/>
+      <c r="K34" s="10">
+        <v>7</v>
+      </c>
+      <c r="L34" s="12">
+        <v>198380.95238093002</v>
+      </c>
       <c r="M34" s="10">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="0"/>
-        <v>-124759.04761904001</v>
+        <v>73621.904761890008</v>
       </c>
       <c r="O34" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.59011275067359725</v>
       </c>
       <c r="Q34" s="14"/>
       <c r="R34" s="13" t="s">
@@ -7818,15 +7956,15 @@
       <c r="T34" s="12"/>
       <c r="U34" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="11" t="e">
+        <v>-198380.95238093002</v>
+      </c>
+      <c r="W34" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y34" s="14"/>
       <c r="Z34" s="13"/>
@@ -8017,18 +8155,23 @@
       <c r="J35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="12"/>
+      <c r="K35" s="10">
+        <v>5</v>
+      </c>
+      <c r="L35" s="12">
+        <v>116190.47619044999</v>
+      </c>
       <c r="M35" s="10">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="0"/>
-        <v>-145714.28571425998</v>
+        <v>-29523.809523809992</v>
       </c>
       <c r="O35" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.20261437908500632</v>
       </c>
       <c r="Q35" s="14"/>
       <c r="R35" s="13" t="s">
@@ -8037,15 +8180,15 @@
       <c r="T35" s="12"/>
       <c r="U35" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="11" t="e">
+        <v>-116190.47619044999</v>
+      </c>
+      <c r="W35" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y35" s="14"/>
       <c r="Z35" s="13"/>
@@ -8236,18 +8379,23 @@
       <c r="J36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L36" s="12"/>
+      <c r="K36" s="10">
+        <v>13</v>
+      </c>
+      <c r="L36" s="12">
+        <v>416857.14285712998</v>
+      </c>
       <c r="M36" s="10">
         <f t="shared" si="0"/>
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="0"/>
-        <v>-506285.71428568999</v>
+        <v>-89428.571428560012</v>
       </c>
       <c r="O36" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.1766365688487444</v>
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="13" t="s">
@@ -8256,15 +8404,15 @@
       <c r="T36" s="12"/>
       <c r="U36" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="11" t="e">
+        <v>-416857.14285712998</v>
+      </c>
+      <c r="W36" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y36" s="14"/>
       <c r="Z36" s="13"/>
@@ -8456,19 +8604,23 @@
         <v>11</v>
       </c>
       <c r="J37" s="9"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="7"/>
+      <c r="K37" s="8">
+        <v>158</v>
+      </c>
+      <c r="L37" s="7">
+        <v>1057347.6190471801</v>
+      </c>
       <c r="M37" s="27">
         <f t="shared" si="0"/>
-        <v>-179</v>
+        <v>-21</v>
       </c>
       <c r="N37" s="28">
         <f t="shared" si="0"/>
-        <v>-1190657.1428566398</v>
+        <v>-133309.52380945976</v>
       </c>
       <c r="O37" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.11196298162678624</v>
       </c>
       <c r="Q37" s="9" t="s">
         <v>11</v>
@@ -8478,15 +8630,15 @@
       <c r="T37" s="7"/>
       <c r="U37" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-158</v>
       </c>
       <c r="V37" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="29" t="e">
+        <v>-1057347.6190471801</v>
+      </c>
+      <c r="W37" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y37" s="9" t="s">
         <v>11</v>
@@ -8691,10 +8843,13 @@
       <c r="J38" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="K38" s="1">
+        <v>1271</v>
+      </c>
       <c r="L38" s="35"/>
       <c r="M38" s="10">
         <f t="shared" si="0"/>
-        <v>-1818</v>
+        <v>-547</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="0"/>
@@ -8713,7 +8868,7 @@
       <c r="T38" s="35"/>
       <c r="U38" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1271</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="3"/>
@@ -9154,18 +9309,23 @@
       <c r="J40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L40" s="12"/>
+      <c r="K40" s="10">
+        <v>69</v>
+      </c>
+      <c r="L40" s="12">
+        <v>62975.238094860004</v>
+      </c>
       <c r="M40" s="10">
         <f t="shared" si="0"/>
-        <v>-86</v>
+        <v>-17</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="0"/>
-        <v>-91735.238094819957</v>
+        <v>-28759.999999959953</v>
       </c>
       <c r="O40" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.31351093208296749</v>
       </c>
       <c r="Q40" s="14"/>
       <c r="R40" s="13" t="s">
@@ -9174,15 +9334,15 @@
       <c r="T40" s="12"/>
       <c r="U40" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="11" t="e">
+        <v>-62975.238094860004</v>
+      </c>
+      <c r="W40" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y40" s="14"/>
       <c r="Z40" s="13"/>
@@ -9373,18 +9533,23 @@
       <c r="J41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="12"/>
+      <c r="K41" s="10">
+        <v>71</v>
+      </c>
+      <c r="L41" s="12">
+        <v>59047.619047520013</v>
+      </c>
       <c r="M41" s="10">
         <f t="shared" si="0"/>
-        <v>-74</v>
+        <v>-3</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="0"/>
-        <v>-92057.142857059996</v>
+        <v>-33009.523809539984</v>
       </c>
       <c r="O41" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.35857645354901901</v>
       </c>
       <c r="Q41" s="14"/>
       <c r="R41" s="13" t="s">
@@ -9393,15 +9558,15 @@
       <c r="T41" s="12"/>
       <c r="U41" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W41" s="11" t="e">
+        <v>-59047.619047520013</v>
+      </c>
+      <c r="W41" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y41" s="14"/>
       <c r="Z41" s="13"/>
@@ -9592,18 +9757,23 @@
       <c r="J42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L42" s="12"/>
+      <c r="K42" s="10">
+        <v>13</v>
+      </c>
+      <c r="L42" s="12">
+        <v>92733.333333319999</v>
+      </c>
       <c r="M42" s="10">
         <f t="shared" si="0"/>
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="0"/>
-        <v>-72458.095238089998</v>
+        <v>20275.238095230001</v>
       </c>
       <c r="O42" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.27982019163776817</v>
       </c>
       <c r="Q42" s="14"/>
       <c r="R42" s="13" t="s">
@@ -9612,15 +9782,15 @@
       <c r="T42" s="12"/>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W42" s="11" t="e">
+        <v>-92733.333333319999</v>
+      </c>
+      <c r="W42" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y42" s="14"/>
       <c r="Z42" s="13"/>
@@ -9811,18 +9981,23 @@
       <c r="J43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L43" s="12"/>
+      <c r="K43" s="10">
+        <v>10</v>
+      </c>
+      <c r="L43" s="12">
+        <v>116190.47619045002</v>
+      </c>
       <c r="M43" s="10">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="0"/>
-        <v>-103999.99999998001</v>
+        <v>12190.476190470014</v>
       </c>
       <c r="O43" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.11721611721608036</v>
       </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="13" t="s">
@@ -9831,15 +10006,15 @@
       <c r="T43" s="12"/>
       <c r="U43" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W43" s="11" t="e">
+        <v>-116190.47619045002</v>
+      </c>
+      <c r="W43" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y43" s="14"/>
       <c r="Z43" s="13"/>
@@ -10030,18 +10205,23 @@
       <c r="J44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="12"/>
+      <c r="K44" s="10">
+        <v>1</v>
+      </c>
+      <c r="L44" s="12">
+        <v>2590</v>
+      </c>
       <c r="M44" s="10">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="0"/>
-        <v>-10880</v>
+        <v>-8290</v>
       </c>
       <c r="O44" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.76194852941176472</v>
       </c>
       <c r="Q44" s="14"/>
       <c r="R44" s="13" t="s">
@@ -10050,15 +10230,15 @@
       <c r="T44" s="12"/>
       <c r="U44" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W44" s="11" t="e">
+        <v>-2590</v>
+      </c>
+      <c r="W44" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13"/>
@@ -10250,18 +10430,23 @@
       <c r="J45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="12"/>
+      <c r="K45" s="10">
+        <v>5</v>
+      </c>
+      <c r="L45" s="12">
+        <v>159523.80952377999</v>
+      </c>
       <c r="M45" s="10">
         <f t="shared" si="0"/>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="0"/>
-        <v>-173233.33333331998</v>
+        <v>-13709.523809539998</v>
       </c>
       <c r="O45" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-7.9139063745667051E-2</v>
       </c>
       <c r="Q45" s="14"/>
       <c r="R45" s="13" t="s">
@@ -10270,15 +10455,15 @@
       <c r="T45" s="12"/>
       <c r="U45" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W45" s="11" t="e">
+        <v>-159523.80952377999</v>
+      </c>
+      <c r="W45" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y45" s="14"/>
       <c r="Z45" s="13"/>
@@ -10470,18 +10655,23 @@
       <c r="J46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="12"/>
+      <c r="K46" s="10">
+        <v>10</v>
+      </c>
+      <c r="L46" s="12">
+        <v>235238.09523804</v>
+      </c>
       <c r="M46" s="10">
         <f t="shared" si="0"/>
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="0"/>
-        <v>-342666.66666660999</v>
+        <v>-107428.57142856999</v>
       </c>
       <c r="O46" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.31350750416903045</v>
       </c>
       <c r="Q46" s="14"/>
       <c r="R46" s="13" t="s">
@@ -10490,15 +10680,15 @@
       <c r="T46" s="12"/>
       <c r="U46" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W46" s="11" t="e">
+        <v>-235238.09523804</v>
+      </c>
+      <c r="W46" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y46" s="14"/>
       <c r="Z46" s="13"/>
@@ -10690,18 +10880,23 @@
       <c r="J47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L47" s="12"/>
+      <c r="K47" s="10">
+        <v>12</v>
+      </c>
+      <c r="L47" s="12">
+        <v>419809.52380949992</v>
+      </c>
       <c r="M47" s="10">
         <f t="shared" si="0"/>
-        <v>-26</v>
+        <v>-14</v>
       </c>
       <c r="N47" s="12">
         <f t="shared" si="0"/>
-        <v>-867047.61904758995</v>
+        <v>-447238.09523809003</v>
       </c>
       <c r="O47" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.51581722319860535</v>
       </c>
       <c r="Q47" s="14"/>
       <c r="R47" s="13" t="s">
@@ -10710,15 +10905,15 @@
       <c r="T47" s="12"/>
       <c r="U47" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V47" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W47" s="11" t="e">
+        <v>-419809.52380949992</v>
+      </c>
+      <c r="W47" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y47" s="14"/>
       <c r="Z47" s="13"/>
@@ -10911,19 +11106,23 @@
         <v>10</v>
       </c>
       <c r="J48" s="9"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="7"/>
+      <c r="K48" s="8">
+        <v>191</v>
+      </c>
+      <c r="L48" s="7">
+        <v>1148108.0952374698</v>
+      </c>
       <c r="M48" s="27">
         <f t="shared" si="0"/>
-        <v>-227</v>
+        <v>-36</v>
       </c>
       <c r="N48" s="28">
         <f t="shared" si="0"/>
-        <v>-1754078.0952374698</v>
+        <v>-605970</v>
       </c>
       <c r="O48" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.34546352391337676</v>
       </c>
       <c r="Q48" s="9" t="s">
         <v>10</v>
@@ -10933,15 +11132,15 @@
       <c r="T48" s="7"/>
       <c r="U48" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-191</v>
       </c>
       <c r="V48" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W48" s="29" t="e">
+        <v>-1148108.0952374698</v>
+      </c>
+      <c r="W48" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y48" s="9" t="s">
         <v>10</v>
@@ -11606,18 +11805,23 @@
       <c r="J51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L51" s="12"/>
+      <c r="K51" s="10">
+        <v>124</v>
+      </c>
+      <c r="L51" s="12">
+        <v>124930.47618994996</v>
+      </c>
       <c r="M51" s="10">
         <f t="shared" si="0"/>
-        <v>-108</v>
+        <v>16</v>
       </c>
       <c r="N51" s="12">
         <f t="shared" si="0"/>
-        <v>-114496.19047567996</v>
+        <v>10434.285714269994</v>
       </c>
       <c r="O51" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>9.1132164929857054E-2</v>
       </c>
       <c r="Q51" s="14"/>
       <c r="R51" s="13" t="s">
@@ -11626,15 +11830,15 @@
       <c r="T51" s="12"/>
       <c r="U51" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="11" t="e">
+        <v>-124930.47618994996</v>
+      </c>
+      <c r="W51" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y51" s="14"/>
       <c r="Z51" s="13"/>
@@ -11825,18 +12029,23 @@
       <c r="J52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="12"/>
+      <c r="K52" s="10">
+        <v>60</v>
+      </c>
+      <c r="L52" s="12">
+        <v>62190.476190410016</v>
+      </c>
       <c r="M52" s="10">
         <f t="shared" si="0"/>
-        <v>-53</v>
+        <v>7</v>
       </c>
       <c r="N52" s="12">
         <f t="shared" si="0"/>
-        <v>-68638.095238030015</v>
+        <v>-6447.619047619999</v>
       </c>
       <c r="O52" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-9.3936450673059974E-2</v>
       </c>
       <c r="Q52" s="14"/>
       <c r="R52" s="13" t="s">
@@ -11845,15 +12054,15 @@
       <c r="T52" s="12"/>
       <c r="U52" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="V52" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="11" t="e">
+        <v>-62190.476190410016</v>
+      </c>
+      <c r="W52" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y52" s="14"/>
       <c r="Z52" s="13"/>
@@ -12044,18 +12253,23 @@
       <c r="J53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L53" s="12"/>
+      <c r="K53" s="10">
+        <v>11</v>
+      </c>
+      <c r="L53" s="12">
+        <v>72752.380952370004</v>
+      </c>
       <c r="M53" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="N53" s="12">
         <f t="shared" si="0"/>
-        <v>-77019.047619040008</v>
+        <v>-4266.6666666700039</v>
       </c>
       <c r="O53" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-5.5397551626115329E-2</v>
       </c>
       <c r="Q53" s="14"/>
       <c r="R53" s="13" t="s">
@@ -12064,15 +12278,15 @@
       <c r="T53" s="12"/>
       <c r="U53" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="V53" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W53" s="11" t="e">
+        <v>-72752.380952370004</v>
+      </c>
+      <c r="W53" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y53" s="14"/>
       <c r="Z53" s="13"/>
@@ -12263,18 +12477,23 @@
       <c r="J54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L54" s="12"/>
+      <c r="K54" s="10">
+        <v>7</v>
+      </c>
+      <c r="L54" s="12">
+        <v>89809.52380950001</v>
+      </c>
       <c r="M54" s="10">
         <f t="shared" si="0"/>
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="0"/>
-        <v>-154857.14285710998</v>
+        <v>-65047.619047609973</v>
       </c>
       <c r="O54" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.42004920049203548</v>
       </c>
       <c r="Q54" s="14"/>
       <c r="R54" s="13" t="s">
@@ -12283,15 +12502,15 @@
       <c r="T54" s="12"/>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W54" s="11" t="e">
+        <v>-89809.52380950001</v>
+      </c>
+      <c r="W54" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y54" s="14"/>
       <c r="Z54" s="13"/>
@@ -12482,18 +12701,23 @@
       <c r="J55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L55" s="12"/>
+      <c r="K55" s="10">
+        <v>6</v>
+      </c>
+      <c r="L55" s="12">
+        <v>25140</v>
+      </c>
       <c r="M55" s="10">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="N55" s="12">
         <f t="shared" si="0"/>
-        <v>-17130</v>
+        <v>8010</v>
       </c>
       <c r="O55" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.46760070052539404</v>
       </c>
       <c r="Q55" s="14"/>
       <c r="R55" s="13" t="s">
@@ -12502,15 +12726,15 @@
       <c r="T55" s="12"/>
       <c r="U55" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W55" s="11" t="e">
+        <v>-25140</v>
+      </c>
+      <c r="W55" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y55" s="14"/>
       <c r="Z55" s="13"/>
@@ -12702,18 +12926,23 @@
       <c r="J56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L56" s="12"/>
+      <c r="K56" s="10">
+        <v>5</v>
+      </c>
+      <c r="L56" s="12">
+        <v>156057.14285710998</v>
+      </c>
       <c r="M56" s="10">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="N56" s="12">
         <f t="shared" si="0"/>
-        <v>-163523.80952379</v>
+        <v>-7466.6666666800156</v>
       </c>
       <c r="O56" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-4.566103669199157E-2</v>
       </c>
       <c r="Q56" s="14"/>
       <c r="R56" s="13" t="s">
@@ -12722,15 +12951,15 @@
       <c r="T56" s="12"/>
       <c r="U56" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W56" s="11" t="e">
+        <v>-156057.14285710998</v>
+      </c>
+      <c r="W56" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y56" s="14"/>
       <c r="Z56" s="13"/>
@@ -12922,18 +13151,23 @@
       <c r="J57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="12"/>
+      <c r="K57" s="10">
+        <v>5</v>
+      </c>
+      <c r="L57" s="12">
+        <v>114761.90476188999</v>
+      </c>
       <c r="M57" s="10">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="N57" s="12">
         <f t="shared" si="0"/>
-        <v>-325428.57142852002</v>
+        <v>-210666.66666663002</v>
       </c>
       <c r="O57" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.64735147790458436</v>
       </c>
       <c r="Q57" s="14"/>
       <c r="R57" s="13" t="s">
@@ -12942,15 +13176,15 @@
       <c r="T57" s="12"/>
       <c r="U57" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W57" s="11" t="e">
+        <v>-114761.90476188999</v>
+      </c>
+      <c r="W57" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y57" s="14"/>
       <c r="Z57" s="13"/>
@@ -13142,18 +13376,23 @@
       <c r="J58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L58" s="12"/>
+      <c r="K58" s="10">
+        <v>20</v>
+      </c>
+      <c r="L58" s="12">
+        <v>658095.23809521995</v>
+      </c>
       <c r="M58" s="10">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>13</v>
       </c>
       <c r="N58" s="12">
         <f t="shared" si="0"/>
-        <v>-248857.14285712998</v>
+        <v>409238.09523808997</v>
       </c>
       <c r="O58" s="11">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>1.6444699579028577</v>
       </c>
       <c r="Q58" s="14"/>
       <c r="R58" s="13" t="s">
@@ -13162,15 +13401,15 @@
       <c r="T58" s="12"/>
       <c r="U58" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W58" s="11" t="e">
+        <v>-658095.23809521995</v>
+      </c>
+      <c r="W58" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y58" s="14"/>
       <c r="Z58" s="13"/>
@@ -13363,19 +13602,23 @@
         <v>1</v>
       </c>
       <c r="J59" s="9"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="7"/>
+      <c r="K59" s="8">
+        <v>238</v>
+      </c>
+      <c r="L59" s="7">
+        <v>1303737.1428564498</v>
+      </c>
       <c r="M59" s="27">
         <f t="shared" si="0"/>
-        <v>-218</v>
+        <v>20</v>
       </c>
       <c r="N59" s="28">
         <f t="shared" si="0"/>
-        <v>-1169949.9999992999</v>
+        <v>133787.14285714994</v>
       </c>
       <c r="O59" s="29">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.11435287222294116</v>
       </c>
       <c r="Q59" s="9" t="s">
         <v>1</v>
@@ -13385,15 +13628,15 @@
       <c r="T59" s="7"/>
       <c r="U59" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-238</v>
       </c>
       <c r="V59" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W59" s="29" t="e">
+        <v>-1303737.1428564498</v>
+      </c>
+      <c r="W59" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y59" s="9" t="s">
         <v>1</v>
@@ -13596,19 +13839,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="4"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="2"/>
+      <c r="K60" s="3">
+        <v>1617</v>
+      </c>
+      <c r="L60" s="2">
+        <v>14975468.095234502</v>
+      </c>
       <c r="M60" s="6">
         <f t="shared" si="0"/>
-        <v>-1739</v>
+        <v>-122</v>
       </c>
       <c r="N60" s="5">
         <f t="shared" si="0"/>
-        <v>-12276756.666662497</v>
+        <v>2698711.4285720047</v>
       </c>
       <c r="O60" s="30">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>0.21982283284153942</v>
       </c>
       <c r="Q60" s="4" t="s">
         <v>0</v>
@@ -13618,15 +13865,15 @@
       <c r="T60" s="2"/>
       <c r="U60" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1617</v>
       </c>
       <c r="V60" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W60" s="30" t="e">
+        <v>-14975468.095234502</v>
+      </c>
+      <c r="W60" s="30">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31EB115-C919-0E45-A498-A6E2069C6246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B11812E-5A81-1649-81F2-BC0EEF98AC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2820" yWindow="3840" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1598,10 +1598,13 @@
       <c r="J6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K6" s="15">
+        <v>8</v>
+      </c>
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -1618,7 +1621,7 @@
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -4092,10 +4095,13 @@
       <c r="J17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K17" s="1">
+        <v>6</v>
+      </c>
       <c r="L17" s="35"/>
       <c r="M17" s="10">
         <f t="shared" si="0"/>
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="0"/>
@@ -4112,7 +4118,7 @@
       <c r="T17" s="35"/>
       <c r="U17" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="3"/>
@@ -6590,10 +6596,13 @@
       <c r="J28" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
       <c r="L28" s="35"/>
       <c r="M28" s="10">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="0"/>
@@ -6610,7 +6619,7 @@
       <c r="T28" s="35"/>
       <c r="U28" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="3"/>
@@ -9088,10 +9097,13 @@
       <c r="J39" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
       <c r="L39" s="35"/>
       <c r="M39" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="0"/>
@@ -9108,7 +9120,7 @@
       <c r="T39" s="35"/>
       <c r="U39" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="3"/>
@@ -11584,10 +11596,13 @@
       <c r="J50" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K50" s="1">
+        <v>4</v>
+      </c>
       <c r="L50" s="35"/>
       <c r="M50" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="0"/>
@@ -11604,7 +11619,7 @@
       <c r="T50" s="35"/>
       <c r="U50" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="3"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B11812E-5A81-1649-81F2-BC0EEF98AC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96A3DE-0438-CC42-AE2A-88F5028A94C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="3840" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q4" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="27">
   <si>
     <t>總計</t>
   </si>
@@ -157,6 +157,14 @@
   </si>
   <si>
     <t>07/05-07/11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q4W3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>07/12-07/18</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -941,7 +949,9 @@
       </c>
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
-      <c r="Q1" s="26"/>
+      <c r="Q1" s="26" t="s">
+        <v>25</v>
+      </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
       <c r="Y1" s="26"/>
@@ -985,7 +995,9 @@
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
-      <c r="Q2" s="23"/>
+      <c r="Q2" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>
       <c r="W2" s="23"/>
@@ -1359,11 +1371,13 @@
       <c r="R5" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="40"/>
+      <c r="S5" s="40">
+        <v>6480</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="10">
         <f t="shared" ref="U5:U60" si="2">S5-K5</f>
-        <v>-4160</v>
+        <v>2320</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V60" si="3">T5-L5</f>
@@ -1382,7 +1396,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="10">
         <f t="shared" ref="AC5:AD60" si="5">AA5-S5</f>
-        <v>0</v>
+        <v>-6480</v>
       </c>
       <c r="AD5" s="12">
         <f t="shared" si="5"/>
@@ -1840,18 +1854,23 @@
       <c r="R7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="12"/>
+      <c r="S7" s="10">
+        <v>232</v>
+      </c>
+      <c r="T7" s="12">
+        <v>272942.85714200989</v>
+      </c>
       <c r="U7" s="10">
         <f t="shared" si="2"/>
-        <v>-159</v>
+        <v>73</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="3"/>
-        <v>-178482.85714225</v>
+        <v>94459.999999759893</v>
       </c>
       <c r="W7" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.52923850229759439</v>
       </c>
       <c r="Y7" s="14"/>
       <c r="Z7" s="13"/>
@@ -1860,15 +1879,15 @@
       </c>
       <c r="AC7" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-232</v>
       </c>
       <c r="AD7" s="12">
         <f t="shared" si="5"/>
-        <v>201242.85714209004</v>
-      </c>
-      <c r="AE7" s="11" t="e">
+        <v>-71699.999999919848</v>
+      </c>
+      <c r="AE7" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.26269234795404423</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="13" t="s">
@@ -2064,18 +2083,23 @@
       <c r="R8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T8" s="12"/>
+      <c r="S8" s="10">
+        <v>326</v>
+      </c>
+      <c r="T8" s="12">
+        <v>435428.57142646989</v>
+      </c>
       <c r="U8" s="10">
         <f t="shared" si="2"/>
-        <v>-189</v>
+        <v>137</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="3"/>
-        <v>-267975.23809503997</v>
+        <v>167453.33333142992</v>
       </c>
       <c r="W8" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.62488360686535149</v>
       </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13"/>
@@ -2084,15 +2108,15 @@
       </c>
       <c r="AC8" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-326</v>
       </c>
       <c r="AD8" s="12">
         <f t="shared" si="5"/>
-        <v>475849.52380930987</v>
-      </c>
-      <c r="AE8" s="11" t="e">
+        <v>40420.952382839983</v>
+      </c>
+      <c r="AE8" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>9.2830271220881069E-2</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
@@ -2288,18 +2312,23 @@
       <c r="R9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T9" s="12"/>
+      <c r="S9" s="10">
+        <v>74</v>
+      </c>
+      <c r="T9" s="12">
+        <v>490439.04761901998</v>
+      </c>
       <c r="U9" s="10">
         <f t="shared" si="2"/>
-        <v>-62</v>
+        <v>12</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="3"/>
-        <v>-412266.66666664998</v>
+        <v>78172.380952370004</v>
       </c>
       <c r="W9" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.18961605987800736</v>
       </c>
       <c r="Y9" s="14"/>
       <c r="Z9" s="13"/>
@@ -2308,15 +2337,15 @@
       </c>
       <c r="AC9" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-74</v>
       </c>
       <c r="AD9" s="12">
         <f t="shared" si="5"/>
-        <v>426009.52380950004</v>
-      </c>
-      <c r="AE9" s="11" t="e">
+        <v>-64429.523809519946</v>
+      </c>
+      <c r="AE9" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.13137111354063657</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="13" t="s">
@@ -2512,18 +2541,23 @@
       <c r="R10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="12"/>
+      <c r="S10" s="10">
+        <v>47</v>
+      </c>
+      <c r="T10" s="12">
+        <v>596476.19047609996</v>
+      </c>
       <c r="U10" s="10">
         <f t="shared" si="2"/>
-        <v>-25</v>
+        <v>22</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="3"/>
-        <v>-279147.61904757004</v>
+        <v>317328.57142852992</v>
       </c>
       <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>1.1367769229457529</v>
       </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="13"/>
@@ -2532,15 +2566,15 @@
       </c>
       <c r="AC10" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-47</v>
       </c>
       <c r="AD10" s="12">
         <f t="shared" si="5"/>
-        <v>787523.80952371005</v>
-      </c>
-      <c r="AE10" s="11" t="e">
+        <v>191047.61904761009</v>
+      </c>
+      <c r="AE10" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.32029378891908195</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="13" t="s">
@@ -2736,18 +2770,23 @@
       <c r="R11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T11" s="12"/>
+      <c r="S11" s="10">
+        <v>12</v>
+      </c>
+      <c r="T11" s="12">
+        <v>66680</v>
+      </c>
       <c r="U11" s="10">
         <f t="shared" si="2"/>
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="3"/>
-        <v>-35120</v>
+        <v>31560</v>
       </c>
       <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.89863325740318911</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="13"/>
@@ -2756,15 +2795,15 @@
       </c>
       <c r="AC11" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AD11" s="12">
         <f t="shared" si="5"/>
-        <v>26860</v>
-      </c>
-      <c r="AE11" s="11" t="e">
+        <v>-39820</v>
+      </c>
+      <c r="AE11" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.59718056388722252</v>
       </c>
       <c r="AG11" s="14"/>
       <c r="AH11" s="13" t="s">
@@ -2960,18 +2999,23 @@
       <c r="R12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T12" s="12"/>
+      <c r="S12" s="10">
+        <v>28</v>
+      </c>
+      <c r="T12" s="12">
+        <v>1271766.6666665294</v>
+      </c>
       <c r="U12" s="10">
         <f t="shared" si="2"/>
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="3"/>
-        <v>-1034838.0952380203</v>
+        <v>236928.57142850908</v>
       </c>
       <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.22895230907982159</v>
       </c>
       <c r="Y12" s="14"/>
       <c r="Z12" s="13"/>
@@ -2980,15 +3024,15 @@
       </c>
       <c r="AC12" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AD12" s="12">
         <f t="shared" si="5"/>
-        <v>1773776.1904760499</v>
-      </c>
-      <c r="AE12" s="11" t="e">
+        <v>502009.52380952053</v>
+      </c>
+      <c r="AE12" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.39473398459589659</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="13" t="s">
@@ -3184,18 +3228,23 @@
       <c r="R13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T13" s="12"/>
+      <c r="S13" s="10">
+        <v>65</v>
+      </c>
+      <c r="T13" s="12">
+        <v>1783619.0476188997</v>
+      </c>
       <c r="U13" s="10">
         <f t="shared" si="2"/>
-        <v>-60</v>
+        <v>5</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="3"/>
-        <v>-1410190.47619037</v>
+        <v>373428.57142852969</v>
       </c>
       <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.26480718579049484</v>
       </c>
       <c r="Y13" s="14"/>
       <c r="Z13" s="13"/>
@@ -3204,15 +3253,15 @@
       </c>
       <c r="AC13" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AD13" s="12">
         <f t="shared" si="5"/>
-        <v>1379619.0476189305</v>
-      </c>
-      <c r="AE13" s="11" t="e">
+        <v>-403999.99999996927</v>
+      </c>
+      <c r="AE13" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.22650576676634071</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="13" t="s">
@@ -3408,18 +3457,23 @@
       <c r="R14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T14" s="12"/>
+      <c r="S14" s="10">
+        <v>117</v>
+      </c>
+      <c r="T14" s="12">
+        <v>4160098.0952380095</v>
+      </c>
       <c r="U14" s="10">
         <f t="shared" si="2"/>
-        <v>-140</v>
+        <v>-23</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="3"/>
-        <v>-5139047.6190475598</v>
+        <v>-978949.52380955033</v>
       </c>
       <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.19049240177910298</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="13"/>
@@ -3428,15 +3482,15 @@
       </c>
       <c r="AC14" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-117</v>
       </c>
       <c r="AD14" s="12">
         <f t="shared" si="5"/>
-        <v>2842761.9047618099</v>
-      </c>
-      <c r="AE14" s="11" t="e">
+        <v>-1317336.1904761996</v>
+      </c>
+      <c r="AE14" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.31665988645415138</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="13" t="s">
@@ -3633,19 +3687,23 @@
         <v>18</v>
       </c>
       <c r="R15" s="9"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="7"/>
+      <c r="S15" s="8">
+        <v>901</v>
+      </c>
+      <c r="T15" s="7">
+        <v>9077450.4761870392</v>
+      </c>
       <c r="U15" s="27">
         <f t="shared" si="2"/>
-        <v>-671</v>
+        <v>230</v>
       </c>
       <c r="V15" s="28">
         <f t="shared" si="3"/>
-        <v>-8757068.5714274608</v>
+        <v>320381.90475957841</v>
       </c>
       <c r="W15" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>3.6585519702896883E-2</v>
       </c>
       <c r="Y15" s="9" t="s">
         <v>18</v>
@@ -3657,15 +3715,15 @@
       </c>
       <c r="AC15" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-901</v>
       </c>
       <c r="AD15" s="28">
         <f t="shared" si="5"/>
-        <v>7913642.8571413998</v>
-      </c>
-      <c r="AE15" s="29" t="e">
+        <v>-1163807.6190456394</v>
+      </c>
+      <c r="AE15" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.12820864427723036</v>
       </c>
       <c r="AG15" s="9" t="s">
         <v>18</v>
@@ -3872,10 +3930,13 @@
       <c r="R16" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="S16" s="1">
+        <v>4282</v>
+      </c>
       <c r="T16" s="35"/>
       <c r="U16" s="10">
         <f t="shared" si="2"/>
-        <v>-2903</v>
+        <v>1379</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="3"/>
@@ -3892,7 +3953,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4282</v>
       </c>
       <c r="AD16" s="12">
         <f t="shared" si="5"/>
@@ -4341,18 +4402,23 @@
       <c r="R18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T18" s="12"/>
+      <c r="S18" s="10">
+        <v>138</v>
+      </c>
+      <c r="T18" s="12">
+        <v>143140.95238040996</v>
+      </c>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>-99</v>
+        <v>39</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
-        <v>-104603.80952343997</v>
+        <v>38537.142856969993</v>
       </c>
       <c r="W18" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.3684105104062626</v>
       </c>
       <c r="Y18" s="14"/>
       <c r="Z18" s="13"/>
@@ -4361,15 +4427,15 @@
       </c>
       <c r="AC18" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-138</v>
       </c>
       <c r="AD18" s="12">
         <f t="shared" si="5"/>
-        <v>152445.71428508</v>
-      </c>
-      <c r="AE18" s="11" t="e">
+        <v>9304.761904670042</v>
+      </c>
+      <c r="AE18" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>6.5004191672148437E-2</v>
       </c>
       <c r="AG18" s="14"/>
       <c r="AH18" s="13" t="s">
@@ -4565,18 +4631,23 @@
       <c r="R19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T19" s="12"/>
+      <c r="S19" s="10">
+        <v>149</v>
+      </c>
+      <c r="T19" s="12">
+        <v>165923.80952371002</v>
+      </c>
       <c r="U19" s="10">
         <f t="shared" si="2"/>
-        <v>-133</v>
+        <v>16</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="3"/>
-        <v>-152373.33333323002</v>
+        <v>13550.476190479996</v>
       </c>
       <c r="W19" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>8.8929446472408885E-2</v>
       </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="13"/>
@@ -4585,15 +4656,15 @@
       </c>
       <c r="AC19" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-149</v>
       </c>
       <c r="AD19" s="12">
         <f t="shared" si="5"/>
-        <v>205209.52380940001</v>
-      </c>
-      <c r="AE19" s="11" t="e">
+        <v>39285.714285689988</v>
+      </c>
+      <c r="AE19" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.23676960165307787</v>
       </c>
       <c r="AG19" s="14"/>
       <c r="AH19" s="13" t="s">
@@ -4789,18 +4860,23 @@
       <c r="R20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T20" s="12"/>
+      <c r="S20" s="10">
+        <v>33</v>
+      </c>
+      <c r="T20" s="12">
+        <v>200758.09523808002</v>
+      </c>
       <c r="U20" s="10">
         <f t="shared" si="2"/>
-        <v>-33</v>
+        <v>0</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="3"/>
-        <v>-241114.28571425998</v>
+        <v>-40356.190476179967</v>
       </c>
       <c r="W20" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.16737370146539277</v>
       </c>
       <c r="Y20" s="14"/>
       <c r="Z20" s="13"/>
@@ -4809,15 +4885,15 @@
       </c>
       <c r="AC20" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="AD20" s="12">
         <f t="shared" si="5"/>
-        <v>269276.19047617004</v>
-      </c>
-      <c r="AE20" s="11" t="e">
+        <v>68518.095238090027</v>
+      </c>
+      <c r="AE20" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.34129679880073616</v>
       </c>
       <c r="AG20" s="14"/>
       <c r="AH20" s="13" t="s">
@@ -5013,18 +5089,23 @@
       <c r="R21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="12"/>
+      <c r="S21" s="10">
+        <v>30</v>
+      </c>
+      <c r="T21" s="12">
+        <v>344761.90476185002</v>
+      </c>
       <c r="U21" s="10">
         <f t="shared" si="2"/>
-        <v>-21</v>
+        <v>9</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="3"/>
-        <v>-262190.47619041003</v>
+        <v>82571.428571439988</v>
       </c>
       <c r="W21" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.3149291681802901</v>
       </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="13"/>
@@ -5033,15 +5114,15 @@
       </c>
       <c r="AC21" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AD21" s="12">
         <f t="shared" si="5"/>
-        <v>479142.85714278999</v>
-      </c>
-      <c r="AE21" s="11" t="e">
+        <v>134380.95238093997</v>
+      </c>
+      <c r="AE21" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.38977900552488776</v>
       </c>
       <c r="AG21" s="14"/>
       <c r="AH21" s="13" t="s">
@@ -5237,18 +5318,23 @@
       <c r="R22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T22" s="12"/>
+      <c r="S22" s="10">
+        <v>23</v>
+      </c>
+      <c r="T22" s="12">
+        <v>72780</v>
+      </c>
       <c r="U22" s="10">
         <f t="shared" si="2"/>
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="3"/>
-        <v>-43520</v>
+        <v>29260</v>
       </c>
       <c r="W22" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.67233455882352944</v>
       </c>
       <c r="Y22" s="14"/>
       <c r="Z22" s="13"/>
@@ -5257,15 +5343,15 @@
       </c>
       <c r="AC22" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="AD22" s="12">
         <f t="shared" si="5"/>
-        <v>59080</v>
-      </c>
-      <c r="AE22" s="11" t="e">
+        <v>-13700</v>
+      </c>
+      <c r="AE22" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.18823852706787578</v>
       </c>
       <c r="AG22" s="14"/>
       <c r="AH22" s="13" t="s">
@@ -5461,18 +5547,23 @@
       <c r="R23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="12"/>
+      <c r="S23" s="10">
+        <v>15</v>
+      </c>
+      <c r="T23" s="12">
+        <v>637985.71428566996</v>
+      </c>
       <c r="U23" s="10">
         <f t="shared" si="2"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="3"/>
-        <v>-544261.90476184001</v>
+        <v>93723.809523829957</v>
       </c>
       <c r="W23" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.17220350846499527</v>
       </c>
       <c r="Y23" s="14"/>
       <c r="Z23" s="13"/>
@@ -5481,15 +5572,15 @@
       </c>
       <c r="AC23" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AD23" s="12">
         <f t="shared" si="5"/>
-        <v>974552.38095230004</v>
-      </c>
-      <c r="AE23" s="11" t="e">
+        <v>336566.66666663007</v>
+      </c>
+      <c r="AE23" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.52754577278187464</v>
       </c>
       <c r="AG23" s="14"/>
       <c r="AH23" s="13" t="s">
@@ -5685,18 +5776,23 @@
       <c r="R24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="12"/>
+      <c r="S24" s="10">
+        <v>22</v>
+      </c>
+      <c r="T24" s="12">
+        <v>554285.71428562002</v>
+      </c>
       <c r="U24" s="10">
         <f t="shared" si="2"/>
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="3"/>
-        <v>-381904.76190469001</v>
+        <v>172380.95238093002</v>
       </c>
       <c r="W24" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.4513715710723456</v>
       </c>
       <c r="Y24" s="14"/>
       <c r="Z24" s="13"/>
@@ -5705,15 +5801,15 @@
       </c>
       <c r="AC24" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AD24" s="12">
         <f t="shared" si="5"/>
-        <v>385999.99999995006</v>
-      </c>
-      <c r="AE24" s="11" t="e">
+        <v>-168285.71428566996</v>
+      </c>
+      <c r="AE24" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.30360824742265208</v>
       </c>
       <c r="AG24" s="14"/>
       <c r="AH24" s="13" t="s">
@@ -5909,18 +6005,23 @@
       <c r="R25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T25" s="12"/>
+      <c r="S25" s="10">
+        <v>43</v>
+      </c>
+      <c r="T25" s="12">
+        <v>1493999.99999996</v>
+      </c>
       <c r="U25" s="10">
         <f t="shared" si="2"/>
-        <v>-28</v>
+        <v>15</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="3"/>
-        <v>-979238.09523806989</v>
+        <v>514761.90476189007</v>
       </c>
       <c r="W25" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.52567593853335792</v>
       </c>
       <c r="Y25" s="14"/>
       <c r="Z25" s="13"/>
@@ -5929,15 +6030,15 @@
       </c>
       <c r="AC25" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="AD25" s="12">
         <f t="shared" si="5"/>
-        <v>2358857.1428570701</v>
-      </c>
-      <c r="AE25" s="11" t="e">
+        <v>864857.14285711013</v>
+      </c>
+      <c r="AE25" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.57888697647733156</v>
       </c>
       <c r="AG25" s="14"/>
       <c r="AH25" s="13" t="s">
@@ -6134,19 +6235,23 @@
         <v>12</v>
       </c>
       <c r="R26" s="9"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="7"/>
+      <c r="S26" s="8">
+        <v>453</v>
+      </c>
+      <c r="T26" s="7">
+        <v>3613636.1904753</v>
+      </c>
       <c r="U26" s="27">
         <f t="shared" si="2"/>
-        <v>-359</v>
+        <v>94</v>
       </c>
       <c r="V26" s="28">
         <f t="shared" si="3"/>
-        <v>-2709206.6666659401</v>
+        <v>904429.52380935987</v>
       </c>
       <c r="W26" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.33383555966307571</v>
       </c>
       <c r="Y26" s="9" t="s">
         <v>12</v>
@@ -6158,15 +6263,15 @@
       </c>
       <c r="AC26" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-453</v>
       </c>
       <c r="AD26" s="28">
         <f t="shared" si="5"/>
-        <v>4884563.809522761</v>
-      </c>
-      <c r="AE26" s="29" t="e">
+        <v>1270927.6190474611</v>
+      </c>
+      <c r="AE26" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.35170325734431407</v>
       </c>
       <c r="AG26" s="9" t="s">
         <v>12</v>
@@ -6373,10 +6478,13 @@
       <c r="R27" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="S27" s="1">
+        <v>3621</v>
+      </c>
       <c r="T27" s="35"/>
       <c r="U27" s="10">
         <f t="shared" si="2"/>
-        <v>-2311</v>
+        <v>1310</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="3"/>
@@ -6393,7 +6501,7 @@
       <c r="AB27" s="35"/>
       <c r="AC27" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3621</v>
       </c>
       <c r="AD27" s="12">
         <f t="shared" si="5"/>
@@ -6842,18 +6950,23 @@
       <c r="R29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T29" s="12"/>
+      <c r="S29" s="10">
+        <v>103</v>
+      </c>
+      <c r="T29" s="12">
+        <v>95442.857142479974</v>
+      </c>
       <c r="U29" s="10">
         <f t="shared" si="2"/>
-        <v>-63</v>
+        <v>40</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="3"/>
-        <v>-74600.952380670016</v>
+        <v>20841.904761809958</v>
       </c>
       <c r="W29" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.27937853467954304</v>
       </c>
       <c r="Y29" s="14"/>
       <c r="Z29" s="13"/>
@@ -6862,15 +6975,15 @@
       </c>
       <c r="AC29" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-103</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="5"/>
-        <v>92987.619047320011</v>
-      </c>
-      <c r="AE29" s="11" t="e">
+        <v>-2455.2380951599625</v>
+      </c>
+      <c r="AE29" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-2.5724691911671389E-2</v>
       </c>
       <c r="AG29" s="14"/>
       <c r="AH29" s="13" t="s">
@@ -7066,18 +7179,23 @@
       <c r="R30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T30" s="12"/>
+      <c r="S30" s="10">
+        <v>76</v>
+      </c>
+      <c r="T30" s="12">
+        <v>58361.904761790014</v>
+      </c>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>-44</v>
+        <v>32</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
-        <v>-39866.666666610006</v>
+        <v>18495.238095180008</v>
       </c>
       <c r="W30" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.46392737697005754</v>
       </c>
       <c r="Y30" s="14"/>
       <c r="Z30" s="13"/>
@@ -7086,15 +7204,15 @@
       </c>
       <c r="AC30" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-76</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="5"/>
-        <v>37430.476190390007</v>
-      </c>
-      <c r="AE30" s="11" t="e">
+        <v>-20931.428571400007</v>
+      </c>
+      <c r="AE30" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.3586488250654899</v>
       </c>
       <c r="AG30" s="14"/>
       <c r="AH30" s="13" t="s">
@@ -7290,18 +7408,23 @@
       <c r="R31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T31" s="12"/>
+      <c r="S31" s="10">
+        <v>9</v>
+      </c>
+      <c r="T31" s="12">
+        <v>67773.333333319999</v>
+      </c>
       <c r="U31" s="10">
         <f t="shared" si="2"/>
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="3"/>
-        <v>-96999.999999989988</v>
+        <v>-29226.666666669989</v>
       </c>
       <c r="W31" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.30130584192446397</v>
       </c>
       <c r="Y31" s="14"/>
       <c r="Z31" s="13"/>
@@ -7310,15 +7433,15 @@
       </c>
       <c r="AC31" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AD31" s="12">
         <f t="shared" si="5"/>
-        <v>74076.190476179996</v>
-      </c>
-      <c r="AE31" s="11" t="e">
+        <v>6302.8571428599971</v>
+      </c>
+      <c r="AE31" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>9.2999072538774888E-2</v>
       </c>
       <c r="AG31" s="14"/>
       <c r="AH31" s="13" t="s">
@@ -7514,18 +7637,23 @@
       <c r="R32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T32" s="12"/>
+      <c r="S32" s="10">
+        <v>8</v>
+      </c>
+      <c r="T32" s="12">
+        <v>82761.904761879996</v>
+      </c>
       <c r="U32" s="10">
         <f t="shared" si="2"/>
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="3"/>
-        <v>-110571.4285714</v>
+        <v>-27809.523809520004</v>
       </c>
       <c r="W32" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.25150732127479369</v>
       </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="13"/>
@@ -7534,15 +7662,15 @@
       </c>
       <c r="AC32" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="5"/>
-        <v>142666.66666663002</v>
-      </c>
-      <c r="AE32" s="11" t="e">
+        <v>59904.761904750019</v>
+      </c>
+      <c r="AE32" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.72382048331422721</v>
       </c>
       <c r="AG32" s="14"/>
       <c r="AH32" s="13" t="s">
@@ -7738,18 +7866,23 @@
       <c r="R33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T33" s="12"/>
+      <c r="S33" s="10">
+        <v>3</v>
+      </c>
+      <c r="T33" s="12">
+        <v>13970</v>
+      </c>
       <c r="U33" s="10">
         <f t="shared" si="2"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="3"/>
-        <v>-3880</v>
+        <v>10090</v>
       </c>
       <c r="W33" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>2.6005154639175259</v>
       </c>
       <c r="Y33" s="14"/>
       <c r="Z33" s="13"/>
@@ -7758,15 +7891,15 @@
       </c>
       <c r="AC33" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD33" s="12">
         <f t="shared" si="5"/>
-        <v>2857.1428571400002</v>
-      </c>
-      <c r="AE33" s="11" t="e">
+        <v>-11112.857142860001</v>
+      </c>
+      <c r="AE33" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.79548011044094491</v>
       </c>
       <c r="AG33" s="14"/>
       <c r="AH33" s="13" t="s">
@@ -7962,18 +8095,23 @@
       <c r="R34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T34" s="12"/>
+      <c r="S34" s="10">
+        <v>6</v>
+      </c>
+      <c r="T34" s="12">
+        <v>195185.71428568999</v>
+      </c>
       <c r="U34" s="10">
         <f t="shared" si="2"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="3"/>
-        <v>-198380.95238093002</v>
+        <v>-3195.2380952400272</v>
       </c>
       <c r="W34" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-1.6106577052339928E-2</v>
       </c>
       <c r="Y34" s="14"/>
       <c r="Z34" s="13"/>
@@ -7982,15 +8120,15 @@
       </c>
       <c r="AC34" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="5"/>
-        <v>19650</v>
-      </c>
-      <c r="AE34" s="11" t="e">
+        <v>-175535.71428568999</v>
+      </c>
+      <c r="AE34" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.89932664861303002</v>
       </c>
       <c r="AG34" s="14"/>
       <c r="AH34" s="13" t="s">
@@ -8186,18 +8324,23 @@
       <c r="R35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T35" s="12"/>
+      <c r="S35" s="10">
+        <v>3</v>
+      </c>
+      <c r="T35" s="12">
+        <v>64952.380952359992</v>
+      </c>
       <c r="U35" s="10">
         <f t="shared" si="2"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="3"/>
-        <v>-116190.47619044999</v>
+        <v>-51238.095238089998</v>
       </c>
       <c r="W35" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.44098360655743141</v>
       </c>
       <c r="Y35" s="14"/>
       <c r="Z35" s="13"/>
@@ -8206,15 +8349,15 @@
       </c>
       <c r="AC35" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD35" s="12">
         <f t="shared" si="5"/>
-        <v>154952.38095235999</v>
-      </c>
-      <c r="AE35" s="11" t="e">
+        <v>90000</v>
+      </c>
+      <c r="AE35" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>1.3856304985341714</v>
       </c>
       <c r="AG35" s="14"/>
       <c r="AH35" s="13" t="s">
@@ -8410,18 +8553,23 @@
       <c r="R36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T36" s="12"/>
+      <c r="S36" s="10">
+        <v>20</v>
+      </c>
+      <c r="T36" s="12">
+        <v>598095.23809520993</v>
+      </c>
       <c r="U36" s="10">
         <f t="shared" si="2"/>
-        <v>-13</v>
+        <v>7</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="3"/>
-        <v>-416857.14285712998</v>
+        <v>181238.09523807996</v>
       </c>
       <c r="W36" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.43477267534838893</v>
       </c>
       <c r="Y36" s="14"/>
       <c r="Z36" s="13"/>
@@ -8430,15 +8578,15 @@
       </c>
       <c r="AC36" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AD36" s="12">
         <f t="shared" si="5"/>
-        <v>236571.42857142002</v>
-      </c>
-      <c r="AE36" s="11" t="e">
+        <v>-361523.80952378991</v>
+      </c>
+      <c r="AE36" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.6044585987261103</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="13" t="s">
@@ -8635,19 +8783,23 @@
         <v>11</v>
       </c>
       <c r="R37" s="9"/>
-      <c r="S37" s="8"/>
-      <c r="T37" s="7"/>
+      <c r="S37" s="8">
+        <v>228</v>
+      </c>
+      <c r="T37" s="7">
+        <v>1176543.33333273</v>
+      </c>
       <c r="U37" s="27">
         <f t="shared" si="2"/>
-        <v>-158</v>
+        <v>70</v>
       </c>
       <c r="V37" s="28">
         <f t="shared" si="3"/>
-        <v>-1057347.6190471801</v>
+        <v>119195.71428554994</v>
       </c>
       <c r="W37" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.11273086744448543</v>
       </c>
       <c r="Y37" s="9" t="s">
         <v>11</v>
@@ -8659,15 +8811,15 @@
       </c>
       <c r="AC37" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-228</v>
       </c>
       <c r="AD37" s="28">
         <f t="shared" si="5"/>
-        <v>761191.90476144012</v>
-      </c>
-      <c r="AE37" s="29" t="e">
+        <v>-415351.42857128987</v>
+      </c>
+      <c r="AE37" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.35302688545669336</v>
       </c>
       <c r="AG37" s="9" t="s">
         <v>11</v>
@@ -8874,10 +9026,13 @@
       <c r="R38" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="S38" s="1">
+        <v>1836</v>
+      </c>
       <c r="T38" s="35"/>
       <c r="U38" s="10">
         <f t="shared" si="2"/>
-        <v>-1271</v>
+        <v>565</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="3"/>
@@ -8894,7 +9049,7 @@
       <c r="AB38" s="35"/>
       <c r="AC38" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1836</v>
       </c>
       <c r="AD38" s="12">
         <f t="shared" si="5"/>
@@ -9343,18 +9498,23 @@
       <c r="R40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T40" s="12"/>
+      <c r="S40" s="10">
+        <v>97</v>
+      </c>
+      <c r="T40" s="12">
+        <v>114887.61904714999</v>
+      </c>
       <c r="U40" s="10">
         <f t="shared" si="2"/>
-        <v>-69</v>
+        <v>28</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="3"/>
-        <v>-62975.238094860004</v>
+        <v>51912.380952289983</v>
       </c>
       <c r="W40" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.82433004658265896</v>
       </c>
       <c r="Y40" s="14"/>
       <c r="Z40" s="13"/>
@@ -9363,15 +9523,15 @@
       </c>
       <c r="AC40" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-97</v>
       </c>
       <c r="AD40" s="12">
         <f t="shared" si="5"/>
-        <v>64970.47619015001</v>
-      </c>
-      <c r="AE40" s="11" t="e">
+        <v>-49917.142856999977</v>
+      </c>
+      <c r="AE40" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.43448670336282219</v>
       </c>
       <c r="AG40" s="14"/>
       <c r="AH40" s="13" t="s">
@@ -9567,18 +9727,23 @@
       <c r="R41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T41" s="12"/>
+      <c r="S41" s="10">
+        <v>85</v>
+      </c>
+      <c r="T41" s="12">
+        <v>77676.190476110016</v>
+      </c>
       <c r="U41" s="10">
         <f t="shared" si="2"/>
-        <v>-71</v>
+        <v>14</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="3"/>
-        <v>-59047.619047520013</v>
+        <v>18628.571428590003</v>
       </c>
       <c r="W41" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.31548387096858566</v>
       </c>
       <c r="Y41" s="14"/>
       <c r="Z41" s="13"/>
@@ -9587,15 +9752,15 @@
       </c>
       <c r="AC41" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-85</v>
       </c>
       <c r="AD41" s="12">
         <f t="shared" si="5"/>
-        <v>83323.809523720003</v>
-      </c>
-      <c r="AE41" s="11" t="e">
+        <v>5647.6190476099873</v>
+      </c>
+      <c r="AE41" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>7.270720941633925E-2</v>
       </c>
       <c r="AG41" s="14"/>
       <c r="AH41" s="13" t="s">
@@ -9791,18 +9956,23 @@
       <c r="R42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T42" s="12"/>
+      <c r="S42" s="10">
+        <v>15</v>
+      </c>
+      <c r="T42" s="12">
+        <v>102714.28571428001</v>
+      </c>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
-        <v>-92733.333333319999</v>
+        <v>9980.9523809600068</v>
       </c>
       <c r="W42" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.10763068707003712</v>
       </c>
       <c r="Y42" s="14"/>
       <c r="Z42" s="13"/>
@@ -9811,15 +9981,15 @@
       </c>
       <c r="AC42" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AD42" s="12">
         <f t="shared" si="5"/>
-        <v>100704.76190474999</v>
-      </c>
-      <c r="AE42" s="11" t="e">
+        <v>-2009.5238095300156</v>
+      </c>
+      <c r="AE42" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1.9564209550362852E-2</v>
       </c>
       <c r="AG42" s="14"/>
       <c r="AH42" s="13" t="s">
@@ -10015,18 +10185,23 @@
       <c r="R43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T43" s="12"/>
+      <c r="S43" s="10">
+        <v>4</v>
+      </c>
+      <c r="T43" s="12">
+        <v>42476.190476169999</v>
+      </c>
       <c r="U43" s="10">
         <f t="shared" si="2"/>
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="3"/>
-        <v>-116190.47619045002</v>
+        <v>-73714.28571428002</v>
       </c>
       <c r="W43" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.63442622950829064</v>
       </c>
       <c r="Y43" s="14"/>
       <c r="Z43" s="13"/>
@@ -10035,15 +10210,15 @@
       </c>
       <c r="AC43" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD43" s="12">
         <f t="shared" si="5"/>
-        <v>129333.33333331</v>
-      </c>
-      <c r="AE43" s="11" t="e">
+        <v>86857.142857140003</v>
+      </c>
+      <c r="AE43" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>2.0448430493282728</v>
       </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="13" t="s">
@@ -10239,18 +10414,23 @@
       <c r="R44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="12"/>
+      <c r="S44" s="10">
+        <v>3</v>
+      </c>
+      <c r="T44" s="12">
+        <v>4490</v>
+      </c>
       <c r="U44" s="10">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="3"/>
-        <v>-2590</v>
+        <v>1900</v>
       </c>
       <c r="W44" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.73359073359073357</v>
       </c>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13"/>
@@ -10259,15 +10439,15 @@
       </c>
       <c r="AC44" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD44" s="12">
         <f t="shared" si="5"/>
-        <v>12990</v>
-      </c>
-      <c r="AE44" s="11" t="e">
+        <v>8500</v>
+      </c>
+      <c r="AE44" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>1.8930957683741647</v>
       </c>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
@@ -10464,18 +10644,23 @@
       <c r="R45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T45" s="12"/>
+      <c r="S45" s="10">
+        <v>6</v>
+      </c>
+      <c r="T45" s="12">
+        <v>219084.76190473</v>
+      </c>
       <c r="U45" s="10">
         <f t="shared" si="2"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="3"/>
-        <v>-159523.80952377999</v>
+        <v>59560.95238095001</v>
       </c>
       <c r="W45" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.37336716417915877</v>
       </c>
       <c r="Y45" s="14"/>
       <c r="Z45" s="13"/>
@@ -10484,15 +10669,15 @@
       </c>
       <c r="AC45" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD45" s="12">
         <f t="shared" si="5"/>
-        <v>224006.66666664</v>
-      </c>
-      <c r="AE45" s="11" t="e">
+        <v>4921.904761910002</v>
+      </c>
+      <c r="AE45" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>2.2465755806651284E-2</v>
       </c>
       <c r="AG45" s="14"/>
       <c r="AH45" s="13" t="s">
@@ -10689,18 +10874,23 @@
       <c r="R46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="12"/>
+      <c r="S46" s="10">
+        <v>8</v>
+      </c>
+      <c r="T46" s="12">
+        <v>208761.90476187001</v>
+      </c>
       <c r="U46" s="10">
         <f t="shared" si="2"/>
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="3"/>
-        <v>-235238.09523804</v>
+        <v>-26476.190476169984</v>
       </c>
       <c r="W46" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.11255060728738871</v>
       </c>
       <c r="Y46" s="14"/>
       <c r="Z46" s="13"/>
@@ -10709,15 +10899,15 @@
       </c>
       <c r="AC46" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AD46" s="12">
         <f t="shared" si="5"/>
-        <v>330909.52380948002</v>
-      </c>
-      <c r="AE46" s="11" t="e">
+        <v>122147.61904761</v>
+      </c>
+      <c r="AE46" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.58510492700735328</v>
       </c>
       <c r="AG46" s="14"/>
       <c r="AH46" s="13" t="s">
@@ -10914,18 +11104,23 @@
       <c r="R47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T47" s="12"/>
+      <c r="S47" s="10">
+        <v>16</v>
+      </c>
+      <c r="T47" s="12">
+        <v>540380.95238092996</v>
+      </c>
       <c r="U47" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="V47" s="12">
         <f t="shared" si="3"/>
-        <v>-419809.52380949992</v>
+        <v>120571.42857143003</v>
       </c>
       <c r="W47" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.28720508166971132</v>
       </c>
       <c r="Y47" s="14"/>
       <c r="Z47" s="13"/>
@@ -10934,15 +11129,15 @@
       </c>
       <c r="AC47" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AD47" s="12">
         <f t="shared" si="5"/>
-        <v>396857.14285711991</v>
-      </c>
-      <c r="AE47" s="11" t="e">
+        <v>-143523.80952381005</v>
+      </c>
+      <c r="AE47" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.26559746210787238</v>
       </c>
       <c r="AG47" s="14"/>
       <c r="AH47" s="13" t="s">
@@ -11140,19 +11335,23 @@
         <v>10</v>
       </c>
       <c r="R48" s="9"/>
-      <c r="S48" s="8"/>
-      <c r="T48" s="7"/>
+      <c r="S48" s="8">
+        <v>234</v>
+      </c>
+      <c r="T48" s="7">
+        <v>1310471.9047612399</v>
+      </c>
       <c r="U48" s="27">
         <f t="shared" si="2"/>
-        <v>-191</v>
+        <v>43</v>
       </c>
       <c r="V48" s="28">
         <f t="shared" si="3"/>
-        <v>-1148108.0952374698</v>
+        <v>162363.80952377012</v>
       </c>
       <c r="W48" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.14141857391066256</v>
       </c>
       <c r="Y48" s="9" t="s">
         <v>10</v>
@@ -11164,15 +11363,15 @@
       </c>
       <c r="AC48" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-234</v>
       </c>
       <c r="AD48" s="28">
         <f t="shared" si="5"/>
-        <v>1345952.8571423099</v>
-      </c>
-      <c r="AE48" s="29" t="e">
+        <v>35480.952381070005</v>
+      </c>
+      <c r="AE48" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>2.7074943195775282E-2</v>
       </c>
       <c r="AG48" s="9" t="s">
         <v>10</v>
@@ -11842,18 +12041,23 @@
       <c r="R51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T51" s="12"/>
+      <c r="S51" s="10">
+        <v>106</v>
+      </c>
+      <c r="T51" s="12">
+        <v>92673.333332900031</v>
+      </c>
       <c r="U51" s="10">
         <f t="shared" si="2"/>
-        <v>-124</v>
+        <v>-18</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="3"/>
-        <v>-124930.47618994996</v>
+        <v>-32257.142857049927</v>
       </c>
       <c r="W51" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.25820075165650297</v>
       </c>
       <c r="Y51" s="14"/>
       <c r="Z51" s="13"/>
@@ -11862,15 +12066,15 @@
       </c>
       <c r="AC51" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="5"/>
-        <v>73125.714285359994</v>
-      </c>
-      <c r="AE51" s="11" t="e">
+        <v>-19547.619047540036</v>
+      </c>
+      <c r="AE51" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.21093035444534314</v>
       </c>
       <c r="AG51" s="14"/>
       <c r="AH51" s="13" t="s">
@@ -12066,18 +12270,23 @@
       <c r="R52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T52" s="12"/>
+      <c r="S52" s="10">
+        <v>91</v>
+      </c>
+      <c r="T52" s="12">
+        <v>83609.523809440012</v>
+      </c>
       <c r="U52" s="10">
         <f t="shared" si="2"/>
-        <v>-60</v>
+        <v>31</v>
       </c>
       <c r="V52" s="12">
         <f t="shared" si="3"/>
-        <v>-62190.476190410016</v>
+        <v>21419.047619029996</v>
       </c>
       <c r="W52" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.34441041347634649</v>
       </c>
       <c r="Y52" s="14"/>
       <c r="Z52" s="13"/>
@@ -12086,15 +12295,15 @@
       </c>
       <c r="AC52" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AD52" s="12">
         <f t="shared" si="5"/>
-        <v>79457.142857069994</v>
-      </c>
-      <c r="AE52" s="11" t="e">
+        <v>-4152.3809523700183</v>
+      </c>
+      <c r="AE52" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-4.966397083942236E-2</v>
       </c>
       <c r="AG52" s="14"/>
       <c r="AH52" s="13" t="s">
@@ -12290,18 +12499,23 @@
       <c r="R53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T53" s="12"/>
+      <c r="S53" s="10">
+        <v>11</v>
+      </c>
+      <c r="T53" s="12">
+        <v>101323.80952380001</v>
+      </c>
       <c r="U53" s="10">
         <f t="shared" si="2"/>
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="V53" s="12">
         <f t="shared" si="3"/>
-        <v>-72752.380952370004</v>
+        <v>28571.428571430006</v>
       </c>
       <c r="W53" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.39272156041374551</v>
       </c>
       <c r="Y53" s="14"/>
       <c r="Z53" s="13"/>
@@ -12310,15 +12524,15 @@
       </c>
       <c r="AC53" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AD53" s="12">
         <f t="shared" si="5"/>
-        <v>86152.380952370004</v>
-      </c>
-      <c r="AE53" s="11" t="e">
+        <v>-15171.428571430006</v>
+      </c>
+      <c r="AE53" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.14973211768026132</v>
       </c>
       <c r="AG53" s="14"/>
       <c r="AH53" s="13" t="s">
@@ -12514,18 +12728,23 @@
       <c r="R54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T54" s="12"/>
+      <c r="S54" s="10">
+        <v>9</v>
+      </c>
+      <c r="T54" s="12">
+        <v>112476.19047615</v>
+      </c>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>
-        <v>-89809.52380950001</v>
+        <v>22666.666666649995</v>
       </c>
       <c r="W54" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.252386002120772</v>
       </c>
       <c r="Y54" s="14"/>
       <c r="Z54" s="13"/>
@@ -12534,15 +12753,15 @@
       </c>
       <c r="AC54" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>
-        <v>118285.71428567999</v>
-      </c>
-      <c r="AE54" s="11" t="e">
+        <v>5809.5238095299865</v>
+      </c>
+      <c r="AE54" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>5.1651143099142087E-2</v>
       </c>
       <c r="AG54" s="14"/>
       <c r="AH54" s="13" t="s">
@@ -12738,18 +12957,23 @@
       <c r="R55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T55" s="12"/>
+      <c r="S55" s="10">
+        <v>4</v>
+      </c>
+      <c r="T55" s="12">
+        <v>12160</v>
+      </c>
       <c r="U55" s="10">
         <f t="shared" si="2"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="3"/>
-        <v>-25140</v>
+        <v>-12980</v>
       </c>
       <c r="W55" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.51630867143993631</v>
       </c>
       <c r="Y55" s="14"/>
       <c r="Z55" s="13"/>
@@ -12758,15 +12982,15 @@
       </c>
       <c r="AC55" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="5"/>
-        <v>5880</v>
-      </c>
-      <c r="AE55" s="11" t="e">
+        <v>-6280</v>
+      </c>
+      <c r="AE55" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.51644736842105265</v>
       </c>
       <c r="AG55" s="14"/>
       <c r="AH55" s="13" t="s">
@@ -12963,18 +13187,23 @@
       <c r="R56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T56" s="12"/>
+      <c r="S56" s="10">
+        <v>3</v>
+      </c>
+      <c r="T56" s="12">
+        <v>74814.285714270009</v>
+      </c>
       <c r="U56" s="10">
         <f t="shared" si="2"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="3"/>
-        <v>-156057.14285710998</v>
+        <v>-81242.857142839974</v>
       </c>
       <c r="W56" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.52059685097034014</v>
       </c>
       <c r="Y56" s="14"/>
       <c r="Z56" s="13"/>
@@ -12983,15 +13212,15 @@
       </c>
       <c r="AC56" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="5"/>
-        <v>55999.999999990003</v>
-      </c>
-      <c r="AE56" s="11" t="e">
+        <v>-18814.285714280006</v>
+      </c>
+      <c r="AE56" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.25147985487872387</v>
       </c>
       <c r="AG56" s="14"/>
       <c r="AH56" s="13" t="s">
@@ -13188,18 +13417,23 @@
       <c r="R57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="12"/>
+      <c r="S57" s="10">
+        <v>11</v>
+      </c>
+      <c r="T57" s="12">
+        <v>248952.38095232999</v>
+      </c>
       <c r="U57" s="10">
         <f t="shared" si="2"/>
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="3"/>
-        <v>-114761.90476188999</v>
+        <v>134190.47619044001</v>
       </c>
       <c r="W57" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>1.1692946058089637</v>
       </c>
       <c r="Y57" s="14"/>
       <c r="Z57" s="13"/>
@@ -13208,15 +13442,15 @@
       </c>
       <c r="AC57" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="5"/>
-        <v>321904.76190471998</v>
-      </c>
-      <c r="AE57" s="11" t="e">
+        <v>72952.380952389998</v>
+      </c>
+      <c r="AE57" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.29303749043620958</v>
       </c>
       <c r="AG57" s="14"/>
       <c r="AH57" s="13" t="s">
@@ -13413,18 +13647,23 @@
       <c r="R58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T58" s="12"/>
+      <c r="S58" s="10">
+        <v>16</v>
+      </c>
+      <c r="T58" s="12">
+        <v>535619.04761903</v>
+      </c>
       <c r="U58" s="10">
         <f t="shared" si="2"/>
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="3"/>
-        <v>-658095.23809521995</v>
+        <v>-122476.19047618995</v>
       </c>
       <c r="W58" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.18610709117221852</v>
       </c>
       <c r="Y58" s="14"/>
       <c r="Z58" s="13"/>
@@ -13433,15 +13672,15 @@
       </c>
       <c r="AC58" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="5"/>
-        <v>858761.90476186003</v>
-      </c>
-      <c r="AE58" s="11" t="e">
+        <v>323142.85714283003</v>
+      </c>
+      <c r="AE58" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.60330725462301338</v>
       </c>
       <c r="AG58" s="14"/>
       <c r="AH58" s="13" t="s">
@@ -13639,19 +13878,23 @@
         <v>1</v>
       </c>
       <c r="R59" s="9"/>
-      <c r="S59" s="8"/>
-      <c r="T59" s="7"/>
+      <c r="S59" s="8">
+        <v>251</v>
+      </c>
+      <c r="T59" s="7">
+        <v>1261628.5714279201</v>
+      </c>
       <c r="U59" s="27">
         <f t="shared" si="2"/>
-        <v>-238</v>
+        <v>13</v>
       </c>
       <c r="V59" s="28">
         <f t="shared" si="3"/>
-        <v>-1303737.1428564498</v>
+        <v>-42108.571428529685</v>
       </c>
       <c r="W59" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-3.2298359879715507E-2</v>
       </c>
       <c r="Y59" s="9" t="s">
         <v>1</v>
@@ -13663,15 +13906,15 @@
       </c>
       <c r="AC59" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-251</v>
       </c>
       <c r="AD59" s="28">
         <f t="shared" si="5"/>
-        <v>1599567.6190470499</v>
-      </c>
-      <c r="AE59" s="29" t="e">
+        <v>337939.04761912976</v>
+      </c>
+      <c r="AE59" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0.26785938054386954</v>
       </c>
       <c r="AG59" s="9" t="s">
         <v>1</v>
@@ -13876,19 +14119,23 @@
         <v>0</v>
       </c>
       <c r="R60" s="4"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="2"/>
+      <c r="S60" s="3">
+        <v>2067</v>
+      </c>
+      <c r="T60" s="2">
+        <v>16439730.47618423</v>
+      </c>
       <c r="U60" s="6">
         <f t="shared" si="2"/>
-        <v>-1617</v>
+        <v>450</v>
       </c>
       <c r="V60" s="5">
         <f t="shared" si="3"/>
-        <v>-14975468.095234502</v>
+        <v>1464262.3809497282</v>
       </c>
       <c r="W60" s="30">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>9.7777403126095688E-2</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>0</v>
@@ -13900,15 +14147,15 @@
       </c>
       <c r="AC60" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2067</v>
       </c>
       <c r="AD60" s="5">
         <f t="shared" si="5"/>
-        <v>16504919.047614958</v>
-      </c>
-      <c r="AE60" s="30" t="e">
+        <v>65188.571430727839</v>
+      </c>
+      <c r="AE60" s="30">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>3.9653065800053519E-3</v>
       </c>
       <c r="AG60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96A3DE-0438-CC42-AE2A-88F5028A94C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12587687-0CF8-FF41-A070-68E3E6A3EA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1632,10 +1632,13 @@
       <c r="R6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S6" s="15">
+        <v>17</v>
+      </c>
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>-8</v>
+        <v>9</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -1650,7 +1653,7 @@
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AD6" s="12">
         <f t="shared" si="5"/>
@@ -4176,10 +4179,13 @@
       <c r="R17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S17" s="1">
+        <v>7</v>
+      </c>
       <c r="T17" s="35"/>
       <c r="U17" s="10">
         <f t="shared" si="2"/>
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="3"/>
@@ -4194,7 +4200,7 @@
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AD17" s="12">
         <f t="shared" si="5"/>
@@ -6724,10 +6730,13 @@
       <c r="R28" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S28" s="1">
+        <v>1</v>
+      </c>
       <c r="T28" s="35"/>
       <c r="U28" s="10">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="3"/>
@@ -6742,7 +6751,7 @@
       <c r="AB28" s="35"/>
       <c r="AC28" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD28" s="12">
         <f t="shared" si="5"/>
@@ -9272,10 +9281,13 @@
       <c r="R39" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S39" s="1">
+        <v>4</v>
+      </c>
       <c r="T39" s="35"/>
       <c r="U39" s="10">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="3"/>
@@ -9290,7 +9302,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD39" s="12">
         <f t="shared" si="5"/>
@@ -11815,10 +11827,13 @@
       <c r="R50" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="S50" s="1">
+        <v>2</v>
+      </c>
       <c r="T50" s="35"/>
       <c r="U50" s="10">
         <f t="shared" si="2"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="3"/>
@@ -11833,7 +11848,7 @@
       <c r="AB50" s="35"/>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="5"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12587687-0CF8-FF41-A070-68E3E6A3EA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF89EB2-615D-4F44-8245-7BE67D4EE6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="29">
   <si>
     <t>總計</t>
   </si>
@@ -165,6 +165,14 @@
   </si>
   <si>
     <t>07/12-07/18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q4W4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>07/19-07/25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -954,7 +962,9 @@
       </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
-      <c r="Y1" s="26"/>
+      <c r="Y1" s="26" t="s">
+        <v>27</v>
+      </c>
       <c r="Z1" s="26"/>
       <c r="AB1" s="25"/>
       <c r="AG1" s="26"/>
@@ -1001,7 +1011,9 @@
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>
       <c r="W2" s="23"/>
-      <c r="Y2" s="23"/>
+      <c r="Y2" s="23" t="s">
+        <v>28</v>
+      </c>
       <c r="Z2" s="22"/>
       <c r="AB2" s="21"/>
       <c r="AG2" s="23"/>
@@ -1391,12 +1403,16 @@
       <c r="Y5" s="14">
         <v>75</v>
       </c>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="40"/>
+      <c r="Z5" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA5" s="40">
+        <v>5616</v>
+      </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="10">
         <f t="shared" ref="AC5:AD60" si="5">AA5-S5</f>
-        <v>-6480</v>
+        <v>-864</v>
       </c>
       <c r="AD5" s="12">
         <f t="shared" si="5"/>
@@ -1417,7 +1433,7 @@
       <c r="AJ5" s="43"/>
       <c r="AK5" s="10">
         <f t="shared" ref="AK5:AL60" si="7">AI5-AA5</f>
-        <v>0</v>
+        <v>-5616</v>
       </c>
       <c r="AL5" s="12">
         <f t="shared" si="7"/>
@@ -1649,7 +1665,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y6" s="14"/>
-      <c r="Z6" s="32"/>
+      <c r="Z6" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
@@ -1876,21 +1894,26 @@
         <v>0.52923850229759439</v>
       </c>
       <c r="Y7" s="14"/>
-      <c r="Z7" s="13"/>
+      <c r="Z7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>193</v>
+      </c>
       <c r="AB7" s="12">
-        <v>201242.85714209004</v>
+        <v>229125.71428494997</v>
       </c>
       <c r="AC7" s="10">
         <f t="shared" si="5"/>
-        <v>-232</v>
+        <v>-39</v>
       </c>
       <c r="AD7" s="12">
         <f t="shared" si="5"/>
-        <v>-71699.999999919848</v>
+        <v>-43817.142857059924</v>
       </c>
       <c r="AE7" s="11">
         <f t="shared" si="6"/>
-        <v>-0.26269234795404423</v>
+        <v>-0.16053595729109785</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="13" t="s">
@@ -1900,11 +1923,11 @@
       <c r="AJ7" s="45"/>
       <c r="AK7" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-193</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="7"/>
-        <v>-201242.85714209004</v>
+        <v>-229125.71428494997</v>
       </c>
       <c r="AM7" s="11">
         <f t="shared" si="8"/>
@@ -2105,21 +2128,26 @@
         <v>0.62488360686535149</v>
       </c>
       <c r="Y8" s="14"/>
-      <c r="Z8" s="13"/>
+      <c r="Z8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>240</v>
+      </c>
       <c r="AB8" s="12">
-        <v>475849.52380930987</v>
+        <v>398944.76190460991</v>
       </c>
       <c r="AC8" s="10">
         <f t="shared" si="5"/>
-        <v>-326</v>
+        <v>-86</v>
       </c>
       <c r="AD8" s="12">
         <f t="shared" si="5"/>
-        <v>40420.952382839983</v>
+        <v>-36483.809521859977</v>
       </c>
       <c r="AE8" s="11">
         <f t="shared" si="6"/>
-        <v>9.2830271220881069E-2</v>
+        <v>-8.378827646136891E-2</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
@@ -2129,11 +2157,11 @@
       <c r="AJ8" s="45"/>
       <c r="AK8" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-240</v>
       </c>
       <c r="AL8" s="12">
         <f t="shared" si="7"/>
-        <v>-475849.52380930987</v>
+        <v>-398944.76190460991</v>
       </c>
       <c r="AM8" s="11">
         <f t="shared" si="8"/>
@@ -2334,21 +2362,26 @@
         <v>0.18961605987800736</v>
       </c>
       <c r="Y9" s="14"/>
-      <c r="Z9" s="13"/>
+      <c r="Z9" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>62</v>
+      </c>
       <c r="AB9" s="12">
-        <v>426009.52380950004</v>
+        <v>427980.95238093997</v>
       </c>
       <c r="AC9" s="10">
         <f t="shared" si="5"/>
-        <v>-74</v>
+        <v>-12</v>
       </c>
       <c r="AD9" s="12">
         <f t="shared" si="5"/>
-        <v>-64429.523809519946</v>
+        <v>-62458.095238080015</v>
       </c>
       <c r="AE9" s="11">
         <f t="shared" si="6"/>
-        <v>-0.13137111354063657</v>
+        <v>-0.12735139165876194</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="13" t="s">
@@ -2358,11 +2391,11 @@
       <c r="AJ9" s="45"/>
       <c r="AK9" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="AL9" s="12">
         <f t="shared" si="7"/>
-        <v>-426009.52380950004</v>
+        <v>-427980.95238093997</v>
       </c>
       <c r="AM9" s="11">
         <f t="shared" si="8"/>
@@ -2563,21 +2596,26 @@
         <v>1.1367769229457529</v>
       </c>
       <c r="Y10" s="14"/>
-      <c r="Z10" s="13"/>
+      <c r="Z10" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>44</v>
+      </c>
       <c r="AB10" s="12">
-        <v>787523.80952371005</v>
+        <v>551714.28571422002</v>
       </c>
       <c r="AC10" s="10">
         <f t="shared" si="5"/>
-        <v>-47</v>
+        <v>-3</v>
       </c>
       <c r="AD10" s="12">
         <f t="shared" si="5"/>
-        <v>191047.61904761009</v>
+        <v>-44761.904761879938</v>
       </c>
       <c r="AE10" s="11">
         <f t="shared" si="6"/>
-        <v>0.32029378891908195</v>
+        <v>-7.5043908669936238E-2</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="13" t="s">
@@ -2587,11 +2625,11 @@
       <c r="AJ10" s="45"/>
       <c r="AK10" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="7"/>
-        <v>-787523.80952371005</v>
+        <v>-551714.28571422002</v>
       </c>
       <c r="AM10" s="11">
         <f t="shared" si="8"/>
@@ -2792,21 +2830,26 @@
         <v>0.89863325740318911</v>
       </c>
       <c r="Y11" s="14"/>
-      <c r="Z11" s="13"/>
+      <c r="Z11" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA11" s="10">
+        <v>12</v>
+      </c>
       <c r="AB11" s="12">
-        <v>26860</v>
+        <v>56600</v>
       </c>
       <c r="AC11" s="10">
         <f t="shared" si="5"/>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="12">
         <f t="shared" si="5"/>
-        <v>-39820</v>
+        <v>-10080</v>
       </c>
       <c r="AE11" s="11">
         <f t="shared" si="6"/>
-        <v>-0.59718056388722252</v>
+        <v>-0.15116976604679064</v>
       </c>
       <c r="AG11" s="14"/>
       <c r="AH11" s="13" t="s">
@@ -2816,11 +2859,11 @@
       <c r="AJ11" s="45"/>
       <c r="AK11" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="7"/>
-        <v>-26860</v>
+        <v>-56600</v>
       </c>
       <c r="AM11" s="11">
         <f t="shared" si="8"/>
@@ -3021,21 +3064,26 @@
         <v>0.22895230907982159</v>
       </c>
       <c r="Y12" s="14"/>
-      <c r="Z12" s="13"/>
+      <c r="Z12" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="10">
+        <v>33</v>
+      </c>
       <c r="AB12" s="12">
-        <v>1773776.1904760499</v>
+        <v>1467361.9047617998</v>
       </c>
       <c r="AC12" s="10">
         <f t="shared" si="5"/>
-        <v>-28</v>
+        <v>5</v>
       </c>
       <c r="AD12" s="12">
         <f t="shared" si="5"/>
-        <v>502009.52380952053</v>
+        <v>195595.23809527047</v>
       </c>
       <c r="AE12" s="11">
         <f t="shared" si="6"/>
-        <v>0.39473398459589659</v>
+        <v>0.15379805370111779</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="13" t="s">
@@ -3045,11 +3093,11 @@
       <c r="AJ12" s="45"/>
       <c r="AK12" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" si="7"/>
-        <v>-1773776.1904760499</v>
+        <v>-1467361.9047617998</v>
       </c>
       <c r="AM12" s="11">
         <f t="shared" si="8"/>
@@ -3250,21 +3298,26 @@
         <v>0.26480718579049484</v>
       </c>
       <c r="Y13" s="14"/>
-      <c r="Z13" s="13"/>
+      <c r="Z13" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA13" s="10">
+        <v>54</v>
+      </c>
       <c r="AB13" s="12">
-        <v>1379619.0476189305</v>
+        <v>1287619.0476189298</v>
       </c>
       <c r="AC13" s="10">
         <f t="shared" si="5"/>
-        <v>-65</v>
+        <v>-11</v>
       </c>
       <c r="AD13" s="12">
         <f t="shared" si="5"/>
-        <v>-403999.99999996927</v>
+        <v>-495999.99999996996</v>
       </c>
       <c r="AE13" s="11">
         <f t="shared" si="6"/>
-        <v>-0.22650576676634071</v>
+        <v>-0.27808628791115531</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="13" t="s">
@@ -3274,11 +3327,11 @@
       <c r="AJ13" s="45"/>
       <c r="AK13" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="AL13" s="12">
         <f t="shared" si="7"/>
-        <v>-1379619.0476189305</v>
+        <v>-1287619.0476189298</v>
       </c>
       <c r="AM13" s="11">
         <f t="shared" si="8"/>
@@ -3479,21 +3532,26 @@
         <v>-0.19049240177910298</v>
       </c>
       <c r="Y14" s="14"/>
-      <c r="Z14" s="13"/>
+      <c r="Z14" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="10">
+        <v>82</v>
+      </c>
       <c r="AB14" s="12">
-        <v>2842761.9047618099</v>
+        <v>3091659.9999999399</v>
       </c>
       <c r="AC14" s="10">
         <f t="shared" si="5"/>
-        <v>-117</v>
+        <v>-35</v>
       </c>
       <c r="AD14" s="12">
         <f t="shared" si="5"/>
-        <v>-1317336.1904761996</v>
+        <v>-1068438.0952380695</v>
       </c>
       <c r="AE14" s="11">
         <f t="shared" si="6"/>
-        <v>-0.31665988645415138</v>
+        <v>-0.25683002438358166</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="13" t="s">
@@ -3503,11 +3561,11 @@
       <c r="AJ14" s="45"/>
       <c r="AK14" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="7"/>
-        <v>-2842761.9047618099</v>
+        <v>-3091659.9999999399</v>
       </c>
       <c r="AM14" s="11">
         <f t="shared" si="8"/>
@@ -3712,21 +3770,23 @@
         <v>18</v>
       </c>
       <c r="Z15" s="9"/>
-      <c r="AA15" s="8"/>
+      <c r="AA15" s="8">
+        <v>720</v>
+      </c>
       <c r="AB15" s="7">
-        <v>7913642.8571413998</v>
+        <v>7511006.6666653901</v>
       </c>
       <c r="AC15" s="27">
         <f t="shared" si="5"/>
-        <v>-901</v>
+        <v>-181</v>
       </c>
       <c r="AD15" s="28">
         <f t="shared" si="5"/>
-        <v>-1163807.6190456394</v>
+        <v>-1566443.809521649</v>
       </c>
       <c r="AE15" s="29">
         <f t="shared" si="6"/>
-        <v>-0.12820864427723036</v>
+        <v>-0.17256429144184435</v>
       </c>
       <c r="AG15" s="9" t="s">
         <v>18</v>
@@ -3736,11 +3796,11 @@
       <c r="AJ15" s="46"/>
       <c r="AK15" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-720</v>
       </c>
       <c r="AL15" s="28">
         <f t="shared" si="7"/>
-        <v>-7913642.8571413998</v>
+        <v>-7511006.6666653901</v>
       </c>
       <c r="AM15" s="29">
         <f t="shared" si="8"/>
@@ -3952,11 +4012,16 @@
       <c r="Y16" s="14">
         <v>76</v>
       </c>
-      <c r="Z16" s="32"/>
+      <c r="Z16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>3776</v>
+      </c>
       <c r="AB16" s="35"/>
       <c r="AC16" s="10">
         <f t="shared" si="5"/>
-        <v>-4282</v>
+        <v>-506</v>
       </c>
       <c r="AD16" s="12">
         <f t="shared" si="5"/>
@@ -3976,7 +4041,7 @@
       <c r="AJ16" s="47"/>
       <c r="AK16" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3776</v>
       </c>
       <c r="AL16" s="12">
         <f t="shared" si="7"/>
@@ -4196,7 +4261,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y17" s="14"/>
-      <c r="Z17" s="32"/>
+      <c r="Z17" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
@@ -4427,21 +4494,26 @@
         <v>0.3684105104062626</v>
       </c>
       <c r="Y18" s="14"/>
-      <c r="Z18" s="13"/>
+      <c r="Z18" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="10">
+        <v>141</v>
+      </c>
       <c r="AB18" s="12">
-        <v>152445.71428508</v>
+        <v>127235.23809469998</v>
       </c>
       <c r="AC18" s="10">
         <f t="shared" si="5"/>
-        <v>-138</v>
+        <v>3</v>
       </c>
       <c r="AD18" s="12">
         <f t="shared" si="5"/>
-        <v>9304.761904670042</v>
+        <v>-15905.714285709983</v>
       </c>
       <c r="AE18" s="11">
         <f t="shared" si="6"/>
-        <v>6.5004191672148437E-2</v>
+        <v>-0.11111924310409166</v>
       </c>
       <c r="AG18" s="14"/>
       <c r="AH18" s="13" t="s">
@@ -4451,11 +4523,11 @@
       <c r="AJ18" s="45"/>
       <c r="AK18" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-141</v>
       </c>
       <c r="AL18" s="12">
         <f t="shared" si="7"/>
-        <v>-152445.71428508</v>
+        <v>-127235.23809469998</v>
       </c>
       <c r="AM18" s="11">
         <f t="shared" si="8"/>
@@ -4656,21 +4728,26 @@
         <v>8.8929446472408885E-2</v>
       </c>
       <c r="Y19" s="14"/>
-      <c r="Z19" s="13"/>
+      <c r="Z19" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA19" s="10">
+        <v>178</v>
+      </c>
       <c r="AB19" s="12">
-        <v>205209.52380940001</v>
+        <v>206676.19047605002</v>
       </c>
       <c r="AC19" s="10">
         <f t="shared" si="5"/>
-        <v>-149</v>
+        <v>29</v>
       </c>
       <c r="AD19" s="12">
         <f t="shared" si="5"/>
-        <v>39285.714285689988</v>
+        <v>40752.380952339998</v>
       </c>
       <c r="AE19" s="11">
         <f t="shared" si="6"/>
-        <v>0.23676960165307787</v>
+        <v>0.24560900011469786</v>
       </c>
       <c r="AG19" s="14"/>
       <c r="AH19" s="13" t="s">
@@ -4680,11 +4757,11 @@
       <c r="AJ19" s="45"/>
       <c r="AK19" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-178</v>
       </c>
       <c r="AL19" s="12">
         <f t="shared" si="7"/>
-        <v>-205209.52380940001</v>
+        <v>-206676.19047605002</v>
       </c>
       <c r="AM19" s="11">
         <f t="shared" si="8"/>
@@ -4885,21 +4962,26 @@
         <v>-0.16737370146539277</v>
       </c>
       <c r="Y20" s="14"/>
-      <c r="Z20" s="13"/>
+      <c r="Z20" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA20" s="10">
+        <v>22</v>
+      </c>
       <c r="AB20" s="12">
-        <v>269276.19047617004</v>
+        <v>141219.04761903</v>
       </c>
       <c r="AC20" s="10">
         <f t="shared" si="5"/>
-        <v>-33</v>
+        <v>-11</v>
       </c>
       <c r="AD20" s="12">
         <f t="shared" si="5"/>
-        <v>68518.095238090027</v>
+        <v>-59539.047619050019</v>
       </c>
       <c r="AE20" s="11">
         <f t="shared" si="6"/>
-        <v>0.34129679880073616</v>
+        <v>-0.29657109243063084</v>
       </c>
       <c r="AG20" s="14"/>
       <c r="AH20" s="13" t="s">
@@ -4909,11 +4991,11 @@
       <c r="AJ20" s="45"/>
       <c r="AK20" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AL20" s="12">
         <f t="shared" si="7"/>
-        <v>-269276.19047617004</v>
+        <v>-141219.04761903</v>
       </c>
       <c r="AM20" s="11">
         <f t="shared" si="8"/>
@@ -5114,21 +5196,26 @@
         <v>0.3149291681802901</v>
       </c>
       <c r="Y21" s="14"/>
-      <c r="Z21" s="13"/>
+      <c r="Z21" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA21" s="10">
+        <v>16</v>
+      </c>
       <c r="AB21" s="12">
-        <v>479142.85714278999</v>
+        <v>209904.76190470002</v>
       </c>
       <c r="AC21" s="10">
         <f t="shared" si="5"/>
-        <v>-30</v>
+        <v>-14</v>
       </c>
       <c r="AD21" s="12">
         <f t="shared" si="5"/>
-        <v>134380.95238093997</v>
+        <v>-134857.14285715</v>
       </c>
       <c r="AE21" s="11">
         <f t="shared" si="6"/>
-        <v>0.38977900552488776</v>
+        <v>-0.39116022099455799</v>
       </c>
       <c r="AG21" s="14"/>
       <c r="AH21" s="13" t="s">
@@ -5138,11 +5225,11 @@
       <c r="AJ21" s="45"/>
       <c r="AK21" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AL21" s="12">
         <f t="shared" si="7"/>
-        <v>-479142.85714278999</v>
+        <v>-209904.76190470002</v>
       </c>
       <c r="AM21" s="11">
         <f t="shared" si="8"/>
@@ -5343,21 +5430,26 @@
         <v>0.67233455882352944</v>
       </c>
       <c r="Y22" s="14"/>
-      <c r="Z22" s="13"/>
+      <c r="Z22" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="10">
+        <v>13</v>
+      </c>
       <c r="AB22" s="12">
-        <v>59080</v>
+        <v>41330</v>
       </c>
       <c r="AC22" s="10">
         <f t="shared" si="5"/>
-        <v>-23</v>
+        <v>-10</v>
       </c>
       <c r="AD22" s="12">
         <f t="shared" si="5"/>
-        <v>-13700</v>
+        <v>-31450</v>
       </c>
       <c r="AE22" s="11">
         <f t="shared" si="6"/>
-        <v>-0.18823852706787578</v>
+        <v>-0.43212420994778783</v>
       </c>
       <c r="AG22" s="14"/>
       <c r="AH22" s="13" t="s">
@@ -5367,11 +5459,11 @@
       <c r="AJ22" s="45"/>
       <c r="AK22" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AL22" s="12">
         <f t="shared" si="7"/>
-        <v>-59080</v>
+        <v>-41330</v>
       </c>
       <c r="AM22" s="11">
         <f t="shared" si="8"/>
@@ -5572,21 +5664,26 @@
         <v>0.17220350846499527</v>
       </c>
       <c r="Y23" s="14"/>
-      <c r="Z23" s="13"/>
+      <c r="Z23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="10">
+        <v>13</v>
+      </c>
       <c r="AB23" s="12">
-        <v>974552.38095230004</v>
+        <v>429095.23809519003</v>
       </c>
       <c r="AC23" s="10">
         <f t="shared" si="5"/>
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="AD23" s="12">
         <f t="shared" si="5"/>
-        <v>336566.66666663007</v>
+        <v>-208890.47619047994</v>
       </c>
       <c r="AE23" s="11">
         <f t="shared" si="6"/>
-        <v>0.52754577278187464</v>
+        <v>-0.32742187091817126</v>
       </c>
       <c r="AG23" s="14"/>
       <c r="AH23" s="13" t="s">
@@ -5596,11 +5693,11 @@
       <c r="AJ23" s="45"/>
       <c r="AK23" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AL23" s="12">
         <f t="shared" si="7"/>
-        <v>-974552.38095230004</v>
+        <v>-429095.23809519003</v>
       </c>
       <c r="AM23" s="11">
         <f t="shared" si="8"/>
@@ -5801,21 +5898,26 @@
         <v>0.4513715710723456</v>
       </c>
       <c r="Y24" s="14"/>
-      <c r="Z24" s="13"/>
+      <c r="Z24" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="10">
+        <v>23</v>
+      </c>
       <c r="AB24" s="12">
-        <v>385999.99999995006</v>
+        <v>567047.61904751998</v>
       </c>
       <c r="AC24" s="10">
         <f t="shared" si="5"/>
-        <v>-22</v>
+        <v>1</v>
       </c>
       <c r="AD24" s="12">
         <f t="shared" si="5"/>
-        <v>-168285.71428566996</v>
+        <v>12761.904761899961</v>
       </c>
       <c r="AE24" s="11">
         <f t="shared" si="6"/>
-        <v>-0.30360824742265208</v>
+        <v>2.3024054982813125E-2</v>
       </c>
       <c r="AG24" s="14"/>
       <c r="AH24" s="13" t="s">
@@ -5825,11 +5927,11 @@
       <c r="AJ24" s="45"/>
       <c r="AK24" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="AL24" s="12">
         <f t="shared" si="7"/>
-        <v>-385999.99999995006</v>
+        <v>-567047.61904751998</v>
       </c>
       <c r="AM24" s="11">
         <f t="shared" si="8"/>
@@ -6030,21 +6132,26 @@
         <v>0.52567593853335792</v>
       </c>
       <c r="Y25" s="14"/>
-      <c r="Z25" s="13"/>
+      <c r="Z25" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="10">
+        <v>40</v>
+      </c>
       <c r="AB25" s="12">
-        <v>2358857.1428570701</v>
+        <v>1429523.8095237699</v>
       </c>
       <c r="AC25" s="10">
         <f t="shared" si="5"/>
-        <v>-43</v>
+        <v>-3</v>
       </c>
       <c r="AD25" s="12">
         <f t="shared" si="5"/>
-        <v>864857.14285711013</v>
+        <v>-64476.190476190066</v>
       </c>
       <c r="AE25" s="11">
         <f t="shared" si="6"/>
-        <v>0.57888697647733156</v>
+        <v>-4.3156754000128375E-2</v>
       </c>
       <c r="AG25" s="14"/>
       <c r="AH25" s="13" t="s">
@@ -6054,11 +6161,11 @@
       <c r="AJ25" s="45"/>
       <c r="AK25" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AL25" s="12">
         <f t="shared" si="7"/>
-        <v>-2358857.1428570701</v>
+        <v>-1429523.8095237699</v>
       </c>
       <c r="AM25" s="11">
         <f t="shared" si="8"/>
@@ -6263,21 +6370,23 @@
         <v>12</v>
       </c>
       <c r="Z26" s="9"/>
-      <c r="AA26" s="8"/>
+      <c r="AA26" s="8">
+        <v>446</v>
+      </c>
       <c r="AB26" s="7">
-        <v>4884563.809522761</v>
+        <v>3152031.90476096</v>
       </c>
       <c r="AC26" s="27">
         <f t="shared" si="5"/>
-        <v>-453</v>
+        <v>-7</v>
       </c>
       <c r="AD26" s="28">
         <f t="shared" si="5"/>
-        <v>1270927.6190474611</v>
+        <v>-461604.28571433993</v>
       </c>
       <c r="AE26" s="29">
         <f t="shared" si="6"/>
-        <v>0.35170325734431407</v>
+        <v>-0.12773955688484107</v>
       </c>
       <c r="AG26" s="9" t="s">
         <v>12</v>
@@ -6287,11 +6396,11 @@
       <c r="AJ26" s="46"/>
       <c r="AK26" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-446</v>
       </c>
       <c r="AL26" s="28">
         <f t="shared" si="7"/>
-        <v>-4884563.809522761</v>
+        <v>-3152031.90476096</v>
       </c>
       <c r="AM26" s="29">
         <f t="shared" si="8"/>
@@ -6503,11 +6612,16 @@
       <c r="Y27" s="14">
         <v>77</v>
       </c>
-      <c r="Z27" s="32"/>
+      <c r="Z27" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>3036</v>
+      </c>
       <c r="AB27" s="35"/>
       <c r="AC27" s="10">
         <f t="shared" si="5"/>
-        <v>-3621</v>
+        <v>-585</v>
       </c>
       <c r="AD27" s="12">
         <f t="shared" si="5"/>
@@ -6527,7 +6641,7 @@
       <c r="AJ27" s="47"/>
       <c r="AK27" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3036</v>
       </c>
       <c r="AL27" s="12">
         <f t="shared" si="7"/>
@@ -6747,7 +6861,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y28" s="14"/>
-      <c r="Z28" s="32"/>
+      <c r="Z28" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="AB28" s="35"/>
       <c r="AC28" s="10">
         <f t="shared" si="5"/>
@@ -6978,21 +7094,26 @@
         <v>0.27937853467954304</v>
       </c>
       <c r="Y29" s="14"/>
-      <c r="Z29" s="13"/>
+      <c r="Z29" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="10">
+        <v>68</v>
+      </c>
       <c r="AB29" s="12">
-        <v>92987.619047320011</v>
+        <v>64845.71428546001</v>
       </c>
       <c r="AC29" s="10">
         <f t="shared" si="5"/>
-        <v>-103</v>
+        <v>-35</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="5"/>
-        <v>-2455.2380951599625</v>
+        <v>-30597.142857019964</v>
       </c>
       <c r="AE29" s="11">
         <f t="shared" si="6"/>
-        <v>-2.5724691911671389E-2</v>
+        <v>-0.32058075138450254</v>
       </c>
       <c r="AG29" s="14"/>
       <c r="AH29" s="13" t="s">
@@ -7002,11 +7123,11 @@
       <c r="AJ29" s="45"/>
       <c r="AK29" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="AL29" s="12">
         <f t="shared" si="7"/>
-        <v>-92987.619047320011</v>
+        <v>-64845.71428546001</v>
       </c>
       <c r="AM29" s="11">
         <f t="shared" si="8"/>
@@ -7207,21 +7328,26 @@
         <v>0.46392737697005754</v>
       </c>
       <c r="Y30" s="14"/>
-      <c r="Z30" s="13"/>
+      <c r="Z30" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA30" s="10">
+        <v>56</v>
+      </c>
       <c r="AB30" s="12">
-        <v>37430.476190390007</v>
+        <v>70249.523809409991</v>
       </c>
       <c r="AC30" s="10">
         <f t="shared" si="5"/>
-        <v>-76</v>
+        <v>-20</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="5"/>
-        <v>-20931.428571400007</v>
+        <v>11887.619047619977</v>
       </c>
       <c r="AE30" s="11">
         <f t="shared" si="6"/>
-        <v>-0.3586488250654899</v>
+        <v>0.20368798955655218</v>
       </c>
       <c r="AG30" s="14"/>
       <c r="AH30" s="13" t="s">
@@ -7231,11 +7357,11 @@
       <c r="AJ30" s="45"/>
       <c r="AK30" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="AL30" s="12">
         <f t="shared" si="7"/>
-        <v>-37430.476190390007</v>
+        <v>-70249.523809409991</v>
       </c>
       <c r="AM30" s="11">
         <f t="shared" si="8"/>
@@ -7436,21 +7562,26 @@
         <v>-0.30130584192446397</v>
       </c>
       <c r="Y31" s="14"/>
-      <c r="Z31" s="13"/>
+      <c r="Z31" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA31" s="10">
+        <v>10</v>
+      </c>
       <c r="AB31" s="12">
-        <v>74076.190476179996</v>
+        <v>72761.904761889993</v>
       </c>
       <c r="AC31" s="10">
         <f t="shared" si="5"/>
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="AD31" s="12">
         <f t="shared" si="5"/>
-        <v>6302.8571428599971</v>
+        <v>4988.5714285699942</v>
       </c>
       <c r="AE31" s="11">
         <f t="shared" si="6"/>
-        <v>9.2999072538774888E-2</v>
+        <v>7.3606700205158998E-2</v>
       </c>
       <c r="AG31" s="14"/>
       <c r="AH31" s="13" t="s">
@@ -7460,11 +7591,11 @@
       <c r="AJ31" s="45"/>
       <c r="AK31" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AL31" s="12">
         <f t="shared" si="7"/>
-        <v>-74076.190476179996</v>
+        <v>-72761.904761889993</v>
       </c>
       <c r="AM31" s="11">
         <f t="shared" si="8"/>
@@ -7665,21 +7796,26 @@
         <v>-0.25150732127479369</v>
       </c>
       <c r="Y32" s="14"/>
-      <c r="Z32" s="13"/>
+      <c r="Z32" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA32" s="10">
+        <v>13</v>
+      </c>
       <c r="AB32" s="12">
-        <v>142666.66666663002</v>
+        <v>151142.85714281999</v>
       </c>
       <c r="AC32" s="10">
         <f t="shared" si="5"/>
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="5"/>
-        <v>59904.761904750019</v>
+        <v>68380.952380939998</v>
       </c>
       <c r="AE32" s="11">
         <f t="shared" si="6"/>
-        <v>0.72382048331422721</v>
+        <v>0.82623705408525294</v>
       </c>
       <c r="AG32" s="14"/>
       <c r="AH32" s="13" t="s">
@@ -7689,11 +7825,11 @@
       <c r="AJ32" s="45"/>
       <c r="AK32" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AL32" s="12">
         <f t="shared" si="7"/>
-        <v>-142666.66666663002</v>
+        <v>-151142.85714281999</v>
       </c>
       <c r="AM32" s="11">
         <f t="shared" si="8"/>
@@ -7894,21 +8030,26 @@
         <v>2.6005154639175259</v>
       </c>
       <c r="Y33" s="14"/>
-      <c r="Z33" s="13"/>
+      <c r="Z33" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="10">
+        <v>1</v>
+      </c>
       <c r="AB33" s="12">
-        <v>2857.1428571400002</v>
+        <v>4890</v>
       </c>
       <c r="AC33" s="10">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AD33" s="12">
         <f t="shared" si="5"/>
-        <v>-11112.857142860001</v>
+        <v>-9080</v>
       </c>
       <c r="AE33" s="11">
         <f t="shared" si="6"/>
-        <v>-0.79548011044094491</v>
+        <v>-0.64996420901932717</v>
       </c>
       <c r="AG33" s="14"/>
       <c r="AH33" s="13" t="s">
@@ -7918,11 +8059,11 @@
       <c r="AJ33" s="45"/>
       <c r="AK33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL33" s="12">
         <f t="shared" si="7"/>
-        <v>-2857.1428571400002</v>
+        <v>-4890</v>
       </c>
       <c r="AM33" s="11">
         <f t="shared" si="8"/>
@@ -8123,21 +8264,26 @@
         <v>-1.6106577052339928E-2</v>
       </c>
       <c r="Y34" s="14"/>
-      <c r="Z34" s="13"/>
+      <c r="Z34" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA34" s="10">
+        <v>2</v>
+      </c>
       <c r="AB34" s="12">
-        <v>19650</v>
+        <v>122190.47619046</v>
       </c>
       <c r="AC34" s="10">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="5"/>
-        <v>-175535.71428568999</v>
+        <v>-72995.238095229986</v>
       </c>
       <c r="AE34" s="11">
         <f t="shared" si="6"/>
-        <v>-0.89932664861303002</v>
+        <v>-0.37397838444461212</v>
       </c>
       <c r="AG34" s="14"/>
       <c r="AH34" s="13" t="s">
@@ -8147,11 +8293,11 @@
       <c r="AJ34" s="45"/>
       <c r="AK34" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL34" s="12">
         <f t="shared" si="7"/>
-        <v>-19650</v>
+        <v>-122190.47619046</v>
       </c>
       <c r="AM34" s="11">
         <f t="shared" si="8"/>
@@ -8352,21 +8498,26 @@
         <v>-0.44098360655743141</v>
       </c>
       <c r="Y35" s="14"/>
-      <c r="Z35" s="13"/>
+      <c r="Z35" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="10">
+        <v>6</v>
+      </c>
       <c r="AB35" s="12">
-        <v>154952.38095235999</v>
+        <v>134666.66666663002</v>
       </c>
       <c r="AC35" s="10">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AD35" s="12">
         <f t="shared" si="5"/>
-        <v>90000</v>
+        <v>69714.285714270023</v>
       </c>
       <c r="AE35" s="11">
         <f t="shared" si="6"/>
-        <v>1.3856304985341714</v>
+        <v>1.0733137829913071</v>
       </c>
       <c r="AG35" s="14"/>
       <c r="AH35" s="13" t="s">
@@ -8376,11 +8527,11 @@
       <c r="AJ35" s="45"/>
       <c r="AK35" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL35" s="12">
         <f t="shared" si="7"/>
-        <v>-154952.38095235999</v>
+        <v>-134666.66666663002</v>
       </c>
       <c r="AM35" s="11">
         <f t="shared" si="8"/>
@@ -8581,21 +8732,26 @@
         <v>0.43477267534838893</v>
       </c>
       <c r="Y36" s="14"/>
-      <c r="Z36" s="13"/>
+      <c r="Z36" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA36" s="10">
+        <v>13</v>
+      </c>
       <c r="AB36" s="12">
-        <v>236571.42857142002</v>
+        <v>440666.66666664998</v>
       </c>
       <c r="AC36" s="10">
         <f t="shared" si="5"/>
-        <v>-20</v>
+        <v>-7</v>
       </c>
       <c r="AD36" s="12">
         <f t="shared" si="5"/>
-        <v>-361523.80952378991</v>
+        <v>-157428.57142855995</v>
       </c>
       <c r="AE36" s="11">
         <f t="shared" si="6"/>
-        <v>-0.6044585987261103</v>
+        <v>-0.26321656050954734</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="13" t="s">
@@ -8605,11 +8761,11 @@
       <c r="AJ36" s="45"/>
       <c r="AK36" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AL36" s="12">
         <f t="shared" si="7"/>
-        <v>-236571.42857142002</v>
+        <v>-440666.66666664998</v>
       </c>
       <c r="AM36" s="11">
         <f t="shared" si="8"/>
@@ -8814,21 +8970,23 @@
         <v>11</v>
       </c>
       <c r="Z37" s="9"/>
-      <c r="AA37" s="8"/>
+      <c r="AA37" s="8">
+        <v>169</v>
+      </c>
       <c r="AB37" s="7">
-        <v>761191.90476144012</v>
+        <v>1061413.8095233201</v>
       </c>
       <c r="AC37" s="27">
         <f t="shared" si="5"/>
-        <v>-228</v>
+        <v>-59</v>
       </c>
       <c r="AD37" s="28">
         <f t="shared" si="5"/>
-        <v>-415351.42857128987</v>
+        <v>-115129.52380940993</v>
       </c>
       <c r="AE37" s="29">
         <f t="shared" si="6"/>
-        <v>-0.35302688545669336</v>
+        <v>-9.7854044596291087E-2</v>
       </c>
       <c r="AG37" s="9" t="s">
         <v>11</v>
@@ -8838,11 +8996,11 @@
       <c r="AJ37" s="46"/>
       <c r="AK37" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-169</v>
       </c>
       <c r="AL37" s="28">
         <f t="shared" si="7"/>
-        <v>-761191.90476144012</v>
+        <v>-1061413.8095233201</v>
       </c>
       <c r="AM37" s="29">
         <f t="shared" si="8"/>
@@ -9054,11 +9212,16 @@
       <c r="Y38" s="14">
         <v>81</v>
       </c>
-      <c r="Z38" s="32"/>
+      <c r="Z38" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>1431</v>
+      </c>
       <c r="AB38" s="35"/>
       <c r="AC38" s="10">
         <f t="shared" si="5"/>
-        <v>-1836</v>
+        <v>-405</v>
       </c>
       <c r="AD38" s="12">
         <f t="shared" si="5"/>
@@ -9078,7 +9241,7 @@
       <c r="AJ38" s="47"/>
       <c r="AK38" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1431</v>
       </c>
       <c r="AL38" s="12">
         <f t="shared" si="7"/>
@@ -9298,7 +9461,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y39" s="14"/>
-      <c r="Z39" s="32"/>
+      <c r="Z39" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="AB39" s="35"/>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
@@ -9529,21 +9694,26 @@
         <v>0.82433004658265896</v>
       </c>
       <c r="Y40" s="14"/>
-      <c r="Z40" s="13"/>
+      <c r="Z40" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="10">
+        <v>78</v>
+      </c>
       <c r="AB40" s="12">
-        <v>64970.47619015001</v>
+        <v>66923.809523470001</v>
       </c>
       <c r="AC40" s="10">
         <f t="shared" si="5"/>
-        <v>-97</v>
+        <v>-19</v>
       </c>
       <c r="AD40" s="12">
         <f t="shared" si="5"/>
-        <v>-49917.142856999977</v>
+        <v>-47963.809523679985</v>
       </c>
       <c r="AE40" s="11">
         <f t="shared" si="6"/>
-        <v>-0.43448670336282219</v>
+        <v>-0.41748458120622722</v>
       </c>
       <c r="AG40" s="14"/>
       <c r="AH40" s="13" t="s">
@@ -9553,11 +9723,11 @@
       <c r="AJ40" s="45"/>
       <c r="AK40" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-78</v>
       </c>
       <c r="AL40" s="12">
         <f t="shared" si="7"/>
-        <v>-64970.47619015001</v>
+        <v>-66923.809523470001</v>
       </c>
       <c r="AM40" s="11">
         <f t="shared" si="8"/>
@@ -9758,21 +9928,26 @@
         <v>0.31548387096858566</v>
       </c>
       <c r="Y41" s="14"/>
-      <c r="Z41" s="13"/>
+      <c r="Z41" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA41" s="10">
+        <v>69</v>
+      </c>
       <c r="AB41" s="12">
-        <v>83323.809523720003</v>
+        <v>62904.76190468001</v>
       </c>
       <c r="AC41" s="10">
         <f t="shared" si="5"/>
-        <v>-85</v>
+        <v>-16</v>
       </c>
       <c r="AD41" s="12">
         <f t="shared" si="5"/>
-        <v>5647.6190476099873</v>
+        <v>-14771.428571430006</v>
       </c>
       <c r="AE41" s="11">
         <f t="shared" si="6"/>
-        <v>7.270720941633925E-2</v>
+        <v>-0.19016674840629685</v>
       </c>
       <c r="AG41" s="14"/>
       <c r="AH41" s="13" t="s">
@@ -9782,11 +9957,11 @@
       <c r="AJ41" s="45"/>
       <c r="AK41" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="AL41" s="12">
         <f t="shared" si="7"/>
-        <v>-83323.809523720003</v>
+        <v>-62904.76190468001</v>
       </c>
       <c r="AM41" s="11">
         <f t="shared" si="8"/>
@@ -9987,21 +10162,26 @@
         <v>0.10763068707003712</v>
       </c>
       <c r="Y42" s="14"/>
-      <c r="Z42" s="13"/>
+      <c r="Z42" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA42" s="10">
+        <v>9</v>
+      </c>
       <c r="AB42" s="12">
-        <v>100704.76190474999</v>
+        <v>55628.571428559997</v>
       </c>
       <c r="AC42" s="10">
         <f t="shared" si="5"/>
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="AD42" s="12">
         <f t="shared" si="5"/>
-        <v>-2009.5238095300156</v>
+        <v>-47085.714285720009</v>
       </c>
       <c r="AE42" s="11">
         <f t="shared" si="6"/>
-        <v>-1.9564209550362852E-2</v>
+        <v>-0.4584144645341563</v>
       </c>
       <c r="AG42" s="14"/>
       <c r="AH42" s="13" t="s">
@@ -10011,11 +10191,11 @@
       <c r="AJ42" s="45"/>
       <c r="AK42" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AL42" s="12">
         <f t="shared" si="7"/>
-        <v>-100704.76190474999</v>
+        <v>-55628.571428559997</v>
       </c>
       <c r="AM42" s="11">
         <f t="shared" si="8"/>
@@ -10216,21 +10396,26 @@
         <v>-0.63442622950829064</v>
       </c>
       <c r="Y43" s="14"/>
-      <c r="Z43" s="13"/>
+      <c r="Z43" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA43" s="10">
+        <v>14</v>
+      </c>
       <c r="AB43" s="12">
-        <v>129333.33333331</v>
+        <v>170095.23809520999</v>
       </c>
       <c r="AC43" s="10">
         <f t="shared" si="5"/>
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="AD43" s="12">
         <f t="shared" si="5"/>
-        <v>86857.142857140003</v>
+        <v>127619.04761903999</v>
       </c>
       <c r="AE43" s="11">
         <f t="shared" si="6"/>
-        <v>2.0448430493282728</v>
+        <v>3.0044843049340044</v>
       </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="13" t="s">
@@ -10240,11 +10425,11 @@
       <c r="AJ43" s="45"/>
       <c r="AK43" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AL43" s="12">
         <f t="shared" si="7"/>
-        <v>-129333.33333331</v>
+        <v>-170095.23809520999</v>
       </c>
       <c r="AM43" s="11">
         <f t="shared" si="8"/>
@@ -10445,21 +10630,26 @@
         <v>0.73359073359073357</v>
       </c>
       <c r="Y44" s="14"/>
-      <c r="Z44" s="13"/>
+      <c r="Z44" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="10">
+        <v>1</v>
+      </c>
       <c r="AB44" s="12">
-        <v>12990</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="10">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AD44" s="12">
         <f t="shared" si="5"/>
-        <v>8500</v>
+        <v>-4490</v>
       </c>
       <c r="AE44" s="11">
         <f t="shared" si="6"/>
-        <v>1.8930957683741647</v>
+        <v>-1</v>
       </c>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
@@ -10469,15 +10659,15 @@
       <c r="AJ44" s="45"/>
       <c r="AK44" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL44" s="12">
         <f t="shared" si="7"/>
-        <v>-12990</v>
-      </c>
-      <c r="AM44" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="11" t="e">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AO44" s="14"/>
       <c r="AP44" s="13" t="s">
@@ -10675,21 +10865,26 @@
         <v>0.37336716417915877</v>
       </c>
       <c r="Y45" s="14"/>
-      <c r="Z45" s="13"/>
+      <c r="Z45" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA45" s="10">
+        <v>4</v>
+      </c>
       <c r="AB45" s="12">
-        <v>224006.66666664</v>
+        <v>134825.7142857</v>
       </c>
       <c r="AC45" s="10">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="AD45" s="12">
         <f t="shared" si="5"/>
-        <v>4921.904761910002</v>
+        <v>-84259.047619029996</v>
       </c>
       <c r="AE45" s="11">
         <f t="shared" si="6"/>
-        <v>2.2465755806651284E-2</v>
+        <v>-0.38459565551925706</v>
       </c>
       <c r="AG45" s="14"/>
       <c r="AH45" s="13" t="s">
@@ -10699,11 +10894,11 @@
       <c r="AJ45" s="45"/>
       <c r="AK45" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AL45" s="12">
         <f t="shared" si="7"/>
-        <v>-224006.66666664</v>
+        <v>-134825.7142857</v>
       </c>
       <c r="AM45" s="11">
         <f t="shared" si="8"/>
@@ -10905,21 +11100,26 @@
         <v>-0.11255060728738871</v>
       </c>
       <c r="Y46" s="14"/>
-      <c r="Z46" s="13"/>
+      <c r="Z46" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="10">
+        <v>2</v>
+      </c>
       <c r="AB46" s="12">
-        <v>330909.52380948002</v>
+        <v>39619.04761904</v>
       </c>
       <c r="AC46" s="10">
         <f t="shared" si="5"/>
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AD46" s="12">
         <f t="shared" si="5"/>
-        <v>122147.61904761</v>
+        <v>-169142.85714283001</v>
       </c>
       <c r="AE46" s="11">
         <f t="shared" si="6"/>
-        <v>0.58510492700735328</v>
+        <v>-0.81021897810219468</v>
       </c>
       <c r="AG46" s="14"/>
       <c r="AH46" s="13" t="s">
@@ -10929,11 +11129,11 @@
       <c r="AJ46" s="45"/>
       <c r="AK46" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL46" s="12">
         <f t="shared" si="7"/>
-        <v>-330909.52380948002</v>
+        <v>-39619.04761904</v>
       </c>
       <c r="AM46" s="11">
         <f t="shared" si="8"/>
@@ -11135,21 +11335,26 @@
         <v>0.28720508166971132</v>
       </c>
       <c r="Y47" s="14"/>
-      <c r="Z47" s="13"/>
+      <c r="Z47" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA47" s="10">
+        <v>13</v>
+      </c>
       <c r="AB47" s="12">
-        <v>396857.14285711991</v>
+        <v>476857.14285711996</v>
       </c>
       <c r="AC47" s="10">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="AD47" s="12">
         <f t="shared" si="5"/>
-        <v>-143523.80952381005</v>
+        <v>-63523.809523809992</v>
       </c>
       <c r="AE47" s="11">
         <f t="shared" si="6"/>
-        <v>-0.26559746210787238</v>
+        <v>-0.11755375396546221</v>
       </c>
       <c r="AG47" s="14"/>
       <c r="AH47" s="13" t="s">
@@ -11159,11 +11364,11 @@
       <c r="AJ47" s="45"/>
       <c r="AK47" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AL47" s="12">
         <f t="shared" si="7"/>
-        <v>-396857.14285711991</v>
+        <v>-476857.14285711996</v>
       </c>
       <c r="AM47" s="11">
         <f t="shared" si="8"/>
@@ -11369,21 +11574,23 @@
         <v>10</v>
       </c>
       <c r="Z48" s="9"/>
-      <c r="AA48" s="8"/>
+      <c r="AA48" s="8">
+        <v>190</v>
+      </c>
       <c r="AB48" s="7">
-        <v>1345952.8571423099</v>
+        <v>1006854.28571378</v>
       </c>
       <c r="AC48" s="27">
         <f t="shared" si="5"/>
-        <v>-234</v>
+        <v>-44</v>
       </c>
       <c r="AD48" s="28">
         <f t="shared" si="5"/>
-        <v>35480.952381070005</v>
+        <v>-303617.61904745991</v>
       </c>
       <c r="AE48" s="29">
         <f t="shared" si="6"/>
-        <v>2.7074943195775282E-2</v>
+        <v>-0.23168571408845062</v>
       </c>
       <c r="AG48" s="9" t="s">
         <v>10</v>
@@ -11393,11 +11600,11 @@
       <c r="AJ48" s="46"/>
       <c r="AK48" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-190</v>
       </c>
       <c r="AL48" s="28">
         <f t="shared" si="7"/>
-        <v>-1345952.8571423099</v>
+        <v>-1006854.28571378</v>
       </c>
       <c r="AM48" s="29">
         <f t="shared" si="8"/>
@@ -11600,7 +11807,9 @@
       <c r="Y49" s="14">
         <v>84</v>
       </c>
-      <c r="Z49" s="32"/>
+      <c r="Z49" s="32" t="s">
+        <v>19</v>
+      </c>
       <c r="AB49" s="35"/>
       <c r="AC49" s="10">
         <f t="shared" si="5"/>
@@ -11844,7 +12053,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Y50" s="14"/>
-      <c r="Z50" s="32"/>
+      <c r="Z50" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="AB50" s="35"/>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
@@ -12075,21 +12286,26 @@
         <v>-0.25820075165650297</v>
       </c>
       <c r="Y51" s="14"/>
-      <c r="Z51" s="13"/>
+      <c r="Z51" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA51" s="10">
+        <v>111</v>
+      </c>
       <c r="AB51" s="12">
-        <v>73125.714285359994</v>
+        <v>95536.190475689975</v>
       </c>
       <c r="AC51" s="10">
         <f t="shared" si="5"/>
-        <v>-106</v>
+        <v>5</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="5"/>
-        <v>-19547.619047540036</v>
+        <v>2862.8571427899442</v>
       </c>
       <c r="AE51" s="11">
         <f t="shared" si="6"/>
-        <v>-0.21093035444534314</v>
+        <v>3.0891919388569129E-2</v>
       </c>
       <c r="AG51" s="14"/>
       <c r="AH51" s="13" t="s">
@@ -12099,11 +12315,11 @@
       <c r="AJ51" s="45"/>
       <c r="AK51" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-111</v>
       </c>
       <c r="AL51" s="12">
         <f t="shared" si="7"/>
-        <v>-73125.714285359994</v>
+        <v>-95536.190475689975</v>
       </c>
       <c r="AM51" s="11">
         <f t="shared" si="8"/>
@@ -12304,21 +12520,26 @@
         <v>0.34441041347634649</v>
       </c>
       <c r="Y52" s="14"/>
-      <c r="Z52" s="13"/>
+      <c r="Z52" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA52" s="10">
+        <v>54</v>
+      </c>
       <c r="AB52" s="12">
-        <v>79457.142857069994</v>
+        <v>96542.857142790002</v>
       </c>
       <c r="AC52" s="10">
         <f t="shared" si="5"/>
-        <v>-91</v>
+        <v>-37</v>
       </c>
       <c r="AD52" s="12">
         <f t="shared" si="5"/>
-        <v>-4152.3809523700183</v>
+        <v>12933.33333334999</v>
       </c>
       <c r="AE52" s="11">
         <f t="shared" si="6"/>
-        <v>-4.966397083942236E-2</v>
+        <v>0.15468732201880739</v>
       </c>
       <c r="AG52" s="14"/>
       <c r="AH52" s="13" t="s">
@@ -12328,11 +12549,11 @@
       <c r="AJ52" s="45"/>
       <c r="AK52" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="AL52" s="12">
         <f t="shared" si="7"/>
-        <v>-79457.142857069994</v>
+        <v>-96542.857142790002</v>
       </c>
       <c r="AM52" s="11">
         <f t="shared" si="8"/>
@@ -12533,21 +12754,26 @@
         <v>0.39272156041374551</v>
       </c>
       <c r="Y53" s="14"/>
-      <c r="Z53" s="13"/>
+      <c r="Z53" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA53" s="10">
+        <v>6</v>
+      </c>
       <c r="AB53" s="12">
-        <v>86152.380952370004</v>
+        <v>34228.571428559997</v>
       </c>
       <c r="AC53" s="10">
         <f t="shared" si="5"/>
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="AD53" s="12">
         <f t="shared" si="5"/>
-        <v>-15171.428571430006</v>
+        <v>-67095.238095240013</v>
       </c>
       <c r="AE53" s="11">
         <f t="shared" si="6"/>
-        <v>-0.14973211768026132</v>
+        <v>-0.66218629570456455</v>
       </c>
       <c r="AG53" s="14"/>
       <c r="AH53" s="13" t="s">
@@ -12557,11 +12783,11 @@
       <c r="AJ53" s="45"/>
       <c r="AK53" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL53" s="12">
         <f t="shared" si="7"/>
-        <v>-86152.380952370004</v>
+        <v>-34228.571428559997</v>
       </c>
       <c r="AM53" s="11">
         <f t="shared" si="8"/>
@@ -12762,21 +12988,26 @@
         <v>0.252386002120772</v>
       </c>
       <c r="Y54" s="14"/>
-      <c r="Z54" s="13"/>
+      <c r="Z54" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA54" s="10">
+        <v>11</v>
+      </c>
       <c r="AB54" s="12">
-        <v>118285.71428567999</v>
+        <v>144666.66666664003</v>
       </c>
       <c r="AC54" s="10">
         <f t="shared" si="5"/>
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>
-        <v>5809.5238095299865</v>
+        <v>32190.476190490022</v>
       </c>
       <c r="AE54" s="11">
         <f t="shared" si="6"/>
-        <v>5.1651143099142087E-2</v>
+        <v>0.28619813717211418</v>
       </c>
       <c r="AG54" s="14"/>
       <c r="AH54" s="13" t="s">
@@ -12786,11 +13017,11 @@
       <c r="AJ54" s="45"/>
       <c r="AK54" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AL54" s="12">
         <f t="shared" si="7"/>
-        <v>-118285.71428567999</v>
+        <v>-144666.66666664003</v>
       </c>
       <c r="AM54" s="11">
         <f t="shared" si="8"/>
@@ -12991,21 +13222,26 @@
         <v>-0.51630867143993631</v>
       </c>
       <c r="Y55" s="14"/>
-      <c r="Z55" s="13"/>
+      <c r="Z55" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA55" s="10">
+        <v>1</v>
+      </c>
       <c r="AB55" s="12">
-        <v>5880</v>
+        <v>990</v>
       </c>
       <c r="AC55" s="10">
         <f t="shared" si="5"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="5"/>
-        <v>-6280</v>
+        <v>-11170</v>
       </c>
       <c r="AE55" s="11">
         <f t="shared" si="6"/>
-        <v>-0.51644736842105265</v>
+        <v>-0.91858552631578949</v>
       </c>
       <c r="AG55" s="14"/>
       <c r="AH55" s="13" t="s">
@@ -13015,11 +13251,11 @@
       <c r="AJ55" s="45"/>
       <c r="AK55" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL55" s="12">
         <f t="shared" si="7"/>
-        <v>-5880</v>
+        <v>-990</v>
       </c>
       <c r="AM55" s="11">
         <f t="shared" si="8"/>
@@ -13221,21 +13457,26 @@
         <v>-0.52059685097034014</v>
       </c>
       <c r="Y56" s="14"/>
-      <c r="Z56" s="13"/>
+      <c r="Z56" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA56" s="10">
+        <v>5</v>
+      </c>
       <c r="AB56" s="12">
-        <v>55999.999999990003</v>
+        <v>214761.90476188</v>
       </c>
       <c r="AC56" s="10">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="5"/>
-        <v>-18814.285714280006</v>
+        <v>139947.61904760997</v>
       </c>
       <c r="AE56" s="11">
         <f t="shared" si="6"/>
-        <v>-0.25147985487872387</v>
+        <v>1.8706002164091569</v>
       </c>
       <c r="AG56" s="14"/>
       <c r="AH56" s="13" t="s">
@@ -13245,11 +13486,11 @@
       <c r="AJ56" s="45"/>
       <c r="AK56" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AL56" s="12">
         <f t="shared" si="7"/>
-        <v>-55999.999999990003</v>
+        <v>-214761.90476188</v>
       </c>
       <c r="AM56" s="11">
         <f t="shared" si="8"/>
@@ -13451,21 +13692,26 @@
         <v>1.1692946058089637</v>
       </c>
       <c r="Y57" s="14"/>
-      <c r="Z57" s="13"/>
+      <c r="Z57" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="10">
+        <v>8</v>
+      </c>
       <c r="AB57" s="12">
-        <v>321904.76190471998</v>
+        <v>192095.23809520996</v>
       </c>
       <c r="AC57" s="10">
         <f t="shared" si="5"/>
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="5"/>
-        <v>72952.380952389998</v>
+        <v>-56857.142857120023</v>
       </c>
       <c r="AE57" s="11">
         <f t="shared" si="6"/>
-        <v>0.29303749043620958</v>
+        <v>-0.2283856159142626</v>
       </c>
       <c r="AG57" s="14"/>
       <c r="AH57" s="13" t="s">
@@ -13475,11 +13721,11 @@
       <c r="AJ57" s="45"/>
       <c r="AK57" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AL57" s="12">
         <f t="shared" si="7"/>
-        <v>-321904.76190471998</v>
+        <v>-192095.23809520996</v>
       </c>
       <c r="AM57" s="11">
         <f t="shared" si="8"/>
@@ -13681,21 +13927,26 @@
         <v>-0.18610709117221852</v>
       </c>
       <c r="Y58" s="14"/>
-      <c r="Z58" s="13"/>
+      <c r="Z58" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA58" s="10">
+        <v>22</v>
+      </c>
       <c r="AB58" s="12">
-        <v>858761.90476186003</v>
+        <v>798955.23809519992</v>
       </c>
       <c r="AC58" s="10">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="5"/>
-        <v>323142.85714283003</v>
+        <v>263336.19047616993</v>
       </c>
       <c r="AE58" s="11">
         <f t="shared" si="6"/>
-        <v>0.60330725462301338</v>
+        <v>0.4916482930298498</v>
       </c>
       <c r="AG58" s="14"/>
       <c r="AH58" s="13" t="s">
@@ -13705,11 +13956,11 @@
       <c r="AJ58" s="45"/>
       <c r="AK58" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AL58" s="12">
         <f t="shared" si="7"/>
-        <v>-858761.90476186003</v>
+        <v>-798955.23809519992</v>
       </c>
       <c r="AM58" s="11">
         <f t="shared" si="8"/>
@@ -13915,21 +14166,23 @@
         <v>1</v>
       </c>
       <c r="Z59" s="9"/>
-      <c r="AA59" s="8"/>
+      <c r="AA59" s="8">
+        <v>218</v>
+      </c>
       <c r="AB59" s="7">
-        <v>1599567.6190470499</v>
+        <v>1577776.6666659699</v>
       </c>
       <c r="AC59" s="27">
         <f t="shared" si="5"/>
-        <v>-251</v>
+        <v>-33</v>
       </c>
       <c r="AD59" s="28">
         <f t="shared" si="5"/>
-        <v>337939.04761912976</v>
+        <v>316148.09523804975</v>
       </c>
       <c r="AE59" s="29">
         <f t="shared" si="6"/>
-        <v>0.26785938054386954</v>
+        <v>0.25058729835218546</v>
       </c>
       <c r="AG59" s="9" t="s">
         <v>1</v>
@@ -13939,11 +14192,11 @@
       <c r="AJ59" s="46"/>
       <c r="AK59" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-218</v>
       </c>
       <c r="AL59" s="28">
         <f t="shared" si="7"/>
-        <v>-1599567.6190470499</v>
+        <v>-1577776.6666659699</v>
       </c>
       <c r="AM59" s="29">
         <f t="shared" si="8"/>
@@ -14156,21 +14409,23 @@
         <v>0</v>
       </c>
       <c r="Z60" s="4"/>
-      <c r="AA60" s="3"/>
+      <c r="AA60" s="3">
+        <v>1743</v>
+      </c>
       <c r="AB60" s="2">
-        <v>16504919.047614958</v>
+        <v>14309083.333329419</v>
       </c>
       <c r="AC60" s="6">
         <f t="shared" si="5"/>
-        <v>-2067</v>
+        <v>-324</v>
       </c>
       <c r="AD60" s="5">
         <f t="shared" si="5"/>
-        <v>65188.571430727839</v>
+        <v>-2130647.1428548116</v>
       </c>
       <c r="AE60" s="30">
         <f t="shared" si="6"/>
-        <v>3.9653065800053519E-3</v>
+        <v>-0.12960353248743461</v>
       </c>
       <c r="AG60" s="4" t="s">
         <v>0</v>
@@ -14180,11 +14435,11 @@
       <c r="AJ60" s="48"/>
       <c r="AK60" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1743</v>
       </c>
       <c r="AL60" s="5">
         <f t="shared" si="7"/>
-        <v>-16504919.047614958</v>
+        <v>-14309083.333329419</v>
       </c>
       <c r="AM60" s="30">
         <f t="shared" si="8"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF89EB2-615D-4F44-8245-7BE67D4EE6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AAD3C7-1948-0244-916C-879681306F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1668,10 +1668,13 @@
       <c r="Z6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA6" s="15">
+        <v>9</v>
+      </c>
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="AD6" s="12">
         <f t="shared" si="5"/>
@@ -1689,7 +1692,7 @@
       <c r="AJ6" s="44"/>
       <c r="AK6" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="7"/>
@@ -4264,10 +4267,13 @@
       <c r="Z17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA17" s="1">
+        <v>6</v>
+      </c>
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="AD17" s="12">
         <f t="shared" si="5"/>
@@ -4285,7 +4291,7 @@
       <c r="AJ17" s="47"/>
       <c r="AK17" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL17" s="12">
         <f t="shared" si="7"/>
@@ -6864,10 +6870,13 @@
       <c r="Z28" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA28" s="1">
+        <v>5</v>
+      </c>
       <c r="AB28" s="35"/>
       <c r="AC28" s="10">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AD28" s="12">
         <f t="shared" si="5"/>
@@ -6885,7 +6894,7 @@
       <c r="AJ28" s="47"/>
       <c r="AK28" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AL28" s="12">
         <f t="shared" si="7"/>
@@ -9464,10 +9473,13 @@
       <c r="Z39" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA39" s="1">
+        <v>1</v>
+      </c>
       <c r="AB39" s="35"/>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="AD39" s="12">
         <f t="shared" si="5"/>
@@ -9485,7 +9497,7 @@
       <c r="AJ39" s="47"/>
       <c r="AK39" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL39" s="12">
         <f t="shared" si="7"/>
@@ -12056,10 +12068,13 @@
       <c r="Z50" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA50" s="1">
+        <v>2</v>
+      </c>
       <c r="AB50" s="35"/>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="5"/>
@@ -12077,7 +12092,7 @@
       <c r="AJ50" s="47"/>
       <c r="AK50" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL50" s="12">
         <f t="shared" si="7"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AAD3C7-1948-0244-916C-879681306F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F40180D-8800-3440-8DB9-8E783E40E78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="31">
   <si>
     <t>總計</t>
   </si>
@@ -175,6 +175,14 @@
     <t>07/19-07/25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>26Q4W5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>07/26-08/01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -183,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -317,6 +325,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -374,7 +387,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -529,6 +542,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -967,7 +983,9 @@
       </c>
       <c r="Z1" s="26"/>
       <c r="AB1" s="25"/>
-      <c r="AG1" s="26"/>
+      <c r="AG1" s="26" t="s">
+        <v>29</v>
+      </c>
       <c r="AH1" s="26"/>
       <c r="AJ1" s="41"/>
       <c r="AO1" s="26"/>
@@ -1016,7 +1034,9 @@
       </c>
       <c r="Z2" s="22"/>
       <c r="AB2" s="21"/>
-      <c r="AG2" s="23"/>
+      <c r="AG2" s="23" t="s">
+        <v>30</v>
+      </c>
       <c r="AJ2" s="42"/>
       <c r="AK2" s="22"/>
       <c r="AL2" s="22"/>
@@ -1429,11 +1449,13 @@
       <c r="AH5" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AI5" s="32"/>
+      <c r="AI5" s="32">
+        <v>5898</v>
+      </c>
       <c r="AJ5" s="43"/>
       <c r="AK5" s="10">
         <f t="shared" ref="AK5:AL60" si="7">AI5-AA5</f>
-        <v>-5616</v>
+        <v>282</v>
       </c>
       <c r="AL5" s="12">
         <f t="shared" si="7"/>
@@ -1454,7 +1476,7 @@
       <c r="AR5" s="1"/>
       <c r="AS5" s="10">
         <f t="shared" ref="AS5:AT60" si="9">AQ5-AI5</f>
-        <v>0</v>
+        <v>-5898</v>
       </c>
       <c r="AT5" s="12">
         <f t="shared" si="9"/>
@@ -1922,19 +1944,23 @@
       <c r="AH7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="45"/>
+      <c r="AI7" s="13">
+        <v>255</v>
+      </c>
+      <c r="AJ7" s="45">
+        <v>266492.38095159992</v>
+      </c>
       <c r="AK7" s="10">
         <f t="shared" si="7"/>
-        <v>-193</v>
+        <v>62</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="7"/>
-        <v>-229125.71428494997</v>
+        <v>37366.666666649951</v>
       </c>
       <c r="AM7" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.16308368872198806</v>
       </c>
       <c r="AO7" s="14"/>
       <c r="AP7" s="13" t="s">
@@ -1943,15 +1969,15 @@
       <c r="AR7" s="12"/>
       <c r="AS7" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-255</v>
       </c>
       <c r="AT7" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU7" s="11" t="e">
+        <v>-266492.38095159992</v>
+      </c>
+      <c r="AU7" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW7" s="14"/>
       <c r="AX7" s="13" t="s">
@@ -2156,19 +2182,23 @@
       <c r="AH8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI8" s="13"/>
-      <c r="AJ8" s="45"/>
+      <c r="AI8" s="13">
+        <v>247</v>
+      </c>
+      <c r="AJ8" s="45">
+        <v>337030.47619030991</v>
+      </c>
       <c r="AK8" s="10">
         <f t="shared" si="7"/>
-        <v>-240</v>
+        <v>7</v>
       </c>
       <c r="AL8" s="12">
         <f t="shared" si="7"/>
-        <v>-398944.76190460991</v>
+        <v>-61914.2857143</v>
       </c>
       <c r="AM8" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.15519513382933969</v>
       </c>
       <c r="AO8" s="14"/>
       <c r="AP8" s="13" t="s">
@@ -2177,15 +2207,15 @@
       <c r="AR8" s="12"/>
       <c r="AS8" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="AT8" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU8" s="11" t="e">
+        <v>-337030.47619030991</v>
+      </c>
+      <c r="AU8" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW8" s="14"/>
       <c r="AX8" s="13" t="s">
@@ -2390,19 +2420,23 @@
       <c r="AH9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI9" s="13"/>
-      <c r="AJ9" s="45"/>
+      <c r="AI9" s="13">
+        <v>72</v>
+      </c>
+      <c r="AJ9" s="45">
+        <v>503599.99999997998</v>
+      </c>
       <c r="AK9" s="10">
         <f t="shared" si="7"/>
-        <v>-62</v>
+        <v>10</v>
       </c>
       <c r="AL9" s="12">
         <f t="shared" si="7"/>
-        <v>-427980.95238093997</v>
+        <v>75619.047619040008</v>
       </c>
       <c r="AM9" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.17668788108058728</v>
       </c>
       <c r="AO9" s="14"/>
       <c r="AP9" s="13" t="s">
@@ -2411,15 +2445,15 @@
       <c r="AR9" s="12"/>
       <c r="AS9" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="AT9" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU9" s="11" t="e">
+        <v>-503599.99999997998</v>
+      </c>
+      <c r="AU9" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW9" s="14"/>
       <c r="AX9" s="13" t="s">
@@ -2624,19 +2658,23 @@
       <c r="AH10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI10" s="13"/>
-      <c r="AJ10" s="45"/>
+      <c r="AI10" s="13">
+        <v>38</v>
+      </c>
+      <c r="AJ10" s="45">
+        <v>474857.14285708999</v>
+      </c>
       <c r="AK10" s="10">
         <f t="shared" si="7"/>
-        <v>-44</v>
+        <v>-6</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="7"/>
-        <v>-551714.28571422002</v>
+        <v>-76857.142857130035</v>
       </c>
       <c r="AM10" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.13930605903676185</v>
       </c>
       <c r="AO10" s="14"/>
       <c r="AP10" s="13" t="s">
@@ -2645,15 +2683,15 @@
       <c r="AR10" s="12"/>
       <c r="AS10" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="AT10" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU10" s="11" t="e">
+        <v>-474857.14285708999</v>
+      </c>
+      <c r="AU10" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW10" s="14"/>
       <c r="AX10" s="13" t="s">
@@ -2858,19 +2896,23 @@
       <c r="AH11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="45"/>
+      <c r="AI11" s="13">
+        <v>11</v>
+      </c>
+      <c r="AJ11" s="45">
+        <v>53110</v>
+      </c>
       <c r="AK11" s="10">
         <f t="shared" si="7"/>
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="7"/>
-        <v>-56600</v>
+        <v>-3490</v>
       </c>
       <c r="AM11" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-6.1660777385159009E-2</v>
       </c>
       <c r="AO11" s="14"/>
       <c r="AP11" s="13" t="s">
@@ -2879,15 +2921,15 @@
       <c r="AR11" s="12"/>
       <c r="AS11" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AT11" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU11" s="11" t="e">
+        <v>-53110</v>
+      </c>
+      <c r="AU11" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW11" s="14"/>
       <c r="AX11" s="13" t="s">
@@ -3092,19 +3134,23 @@
       <c r="AH12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="45"/>
+      <c r="AI12" s="13">
+        <v>28</v>
+      </c>
+      <c r="AJ12" s="45">
+        <v>1397652.38095225</v>
+      </c>
       <c r="AK12" s="10">
         <f t="shared" si="7"/>
-        <v>-33</v>
+        <v>-5</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" si="7"/>
-        <v>-1467361.9047617998</v>
+        <v>-69709.523809549864</v>
       </c>
       <c r="AM12" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-4.7506701368852808E-2</v>
       </c>
       <c r="AO12" s="14"/>
       <c r="AP12" s="13" t="s">
@@ -3113,15 +3159,15 @@
       <c r="AR12" s="12"/>
       <c r="AS12" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AT12" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU12" s="11" t="e">
+        <v>-1397652.38095225</v>
+      </c>
+      <c r="AU12" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW12" s="14"/>
       <c r="AX12" s="13" t="s">
@@ -3326,19 +3372,23 @@
       <c r="AH13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI13" s="13"/>
-      <c r="AJ13" s="45"/>
+      <c r="AI13" s="13">
+        <v>115</v>
+      </c>
+      <c r="AJ13" s="45">
+        <v>2222285.7142855702</v>
+      </c>
       <c r="AK13" s="10">
         <f t="shared" si="7"/>
-        <v>-54</v>
+        <v>61</v>
       </c>
       <c r="AL13" s="12">
         <f t="shared" si="7"/>
-        <v>-1287619.0476189298</v>
+        <v>934666.66666664043</v>
       </c>
       <c r="AM13" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.72588757396454306</v>
       </c>
       <c r="AO13" s="14"/>
       <c r="AP13" s="13" t="s">
@@ -3347,15 +3397,15 @@
       <c r="AR13" s="12"/>
       <c r="AS13" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="AT13" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU13" s="11" t="e">
+        <v>-2222285.7142855702</v>
+      </c>
+      <c r="AU13" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW13" s="14"/>
       <c r="AX13" s="13" t="s">
@@ -3560,19 +3610,23 @@
       <c r="AH14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI14" s="13"/>
-      <c r="AJ14" s="45"/>
+      <c r="AI14" s="13">
+        <v>70</v>
+      </c>
+      <c r="AJ14" s="45">
+        <v>2648571.4285713602</v>
+      </c>
       <c r="AK14" s="10">
         <f t="shared" si="7"/>
-        <v>-82</v>
+        <v>-12</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="7"/>
-        <v>-3091659.9999999399</v>
+        <v>-443088.57142857974</v>
       </c>
       <c r="AM14" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.14331736718416266</v>
       </c>
       <c r="AO14" s="14"/>
       <c r="AP14" s="13" t="s">
@@ -3581,15 +3635,15 @@
       <c r="AR14" s="12"/>
       <c r="AS14" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="AT14" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU14" s="11" t="e">
+        <v>-2648571.4285713602</v>
+      </c>
+      <c r="AU14" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW14" s="14"/>
       <c r="AX14" s="13" t="s">
@@ -3795,19 +3849,23 @@
         <v>18</v>
       </c>
       <c r="AH15" s="9"/>
-      <c r="AI15" s="9"/>
-      <c r="AJ15" s="46"/>
+      <c r="AI15" s="9">
+        <v>836</v>
+      </c>
+      <c r="AJ15" s="46">
+        <v>7903599.5238081599</v>
+      </c>
       <c r="AK15" s="27">
         <f t="shared" si="7"/>
-        <v>-720</v>
+        <v>116</v>
       </c>
       <c r="AL15" s="28">
         <f t="shared" si="7"/>
-        <v>-7511006.6666653901</v>
+        <v>392592.85714276973</v>
       </c>
       <c r="AM15" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>5.22690066146708E-2</v>
       </c>
       <c r="AO15" s="9" t="s">
         <v>18</v>
@@ -3817,15 +3875,15 @@
       <c r="AR15" s="7"/>
       <c r="AS15" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-836</v>
       </c>
       <c r="AT15" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU15" s="29" t="e">
+        <v>-7903599.5238081599</v>
+      </c>
+      <c r="AU15" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW15" s="9" t="s">
         <v>18</v>
@@ -4040,11 +4098,13 @@
       <c r="AH16" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AI16" s="32"/>
+      <c r="AI16" s="32">
+        <v>3807</v>
+      </c>
       <c r="AJ16" s="47"/>
       <c r="AK16" s="10">
         <f t="shared" si="7"/>
-        <v>-3776</v>
+        <v>31</v>
       </c>
       <c r="AL16" s="12">
         <f t="shared" si="7"/>
@@ -4063,7 +4123,7 @@
       <c r="AR16" s="35"/>
       <c r="AS16" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-3807</v>
       </c>
       <c r="AT16" s="12">
         <f t="shared" si="9"/>
@@ -4525,19 +4585,23 @@
       <c r="AH18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI18" s="13"/>
-      <c r="AJ18" s="45"/>
+      <c r="AI18" s="13">
+        <v>104</v>
+      </c>
+      <c r="AJ18" s="45">
+        <v>102379.04761861001</v>
+      </c>
       <c r="AK18" s="10">
         <f t="shared" si="7"/>
-        <v>-141</v>
+        <v>-37</v>
       </c>
       <c r="AL18" s="12">
         <f t="shared" si="7"/>
-        <v>-127235.23809469998</v>
+        <v>-24856.190476089963</v>
       </c>
       <c r="AM18" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.19535618314786143</v>
       </c>
       <c r="AO18" s="14"/>
       <c r="AP18" s="13" t="s">
@@ -4546,15 +4610,15 @@
       <c r="AR18" s="12"/>
       <c r="AS18" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="AT18" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU18" s="11" t="e">
+        <v>-102379.04761861001</v>
+      </c>
+      <c r="AU18" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW18" s="14"/>
       <c r="AX18" s="13" t="s">
@@ -4759,19 +4823,23 @@
       <c r="AH19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI19" s="13"/>
-      <c r="AJ19" s="45"/>
+      <c r="AI19" s="13">
+        <v>138</v>
+      </c>
+      <c r="AJ19" s="45">
+        <v>136401.90476181998</v>
+      </c>
       <c r="AK19" s="10">
         <f t="shared" si="7"/>
-        <v>-178</v>
+        <v>-40</v>
       </c>
       <c r="AL19" s="12">
         <f t="shared" si="7"/>
-        <v>-206676.19047605002</v>
+        <v>-70274.285714230035</v>
       </c>
       <c r="AM19" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.34002119717981516</v>
       </c>
       <c r="AO19" s="14"/>
       <c r="AP19" s="13" t="s">
@@ -4780,15 +4848,15 @@
       <c r="AR19" s="12"/>
       <c r="AS19" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-138</v>
       </c>
       <c r="AT19" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU19" s="11" t="e">
+        <v>-136401.90476181998</v>
+      </c>
+      <c r="AU19" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW19" s="14"/>
       <c r="AX19" s="13" t="s">
@@ -4993,19 +5061,23 @@
       <c r="AH20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI20" s="13"/>
-      <c r="AJ20" s="45"/>
+      <c r="AI20" s="13">
+        <v>34</v>
+      </c>
+      <c r="AJ20" s="45">
+        <v>205390.47619046</v>
+      </c>
       <c r="AK20" s="10">
         <f t="shared" si="7"/>
-        <v>-22</v>
+        <v>12</v>
       </c>
       <c r="AL20" s="12">
         <f t="shared" si="7"/>
-        <v>-141219.04761903</v>
+        <v>64171.428571430006</v>
       </c>
       <c r="AM20" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.454410574588683</v>
       </c>
       <c r="AO20" s="14"/>
       <c r="AP20" s="13" t="s">
@@ -5014,15 +5086,15 @@
       <c r="AR20" s="12"/>
       <c r="AS20" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AT20" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU20" s="11" t="e">
+        <v>-205390.47619046</v>
+      </c>
+      <c r="AU20" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW20" s="14"/>
       <c r="AX20" s="13" t="s">
@@ -5227,19 +5299,23 @@
       <c r="AH21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI21" s="13"/>
-      <c r="AJ21" s="45"/>
+      <c r="AI21" s="13">
+        <v>19</v>
+      </c>
+      <c r="AJ21" s="45">
+        <v>193238.09523804003</v>
+      </c>
       <c r="AK21" s="10">
         <f t="shared" si="7"/>
-        <v>-16</v>
+        <v>3</v>
       </c>
       <c r="AL21" s="12">
         <f t="shared" si="7"/>
-        <v>-209904.76190470002</v>
+        <v>-16666.666666659992</v>
       </c>
       <c r="AM21" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-7.9401088929211217E-2</v>
       </c>
       <c r="AO21" s="14"/>
       <c r="AP21" s="13" t="s">
@@ -5248,15 +5324,15 @@
       <c r="AR21" s="12"/>
       <c r="AS21" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AT21" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU21" s="11" t="e">
+        <v>-193238.09523804003</v>
+      </c>
+      <c r="AU21" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW21" s="14"/>
       <c r="AX21" s="13" t="s">
@@ -5461,19 +5537,23 @@
       <c r="AH22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI22" s="13"/>
-      <c r="AJ22" s="45"/>
+      <c r="AI22" s="13">
+        <v>19</v>
+      </c>
+      <c r="AJ22" s="45">
+        <v>67390</v>
+      </c>
       <c r="AK22" s="10">
         <f t="shared" si="7"/>
-        <v>-13</v>
+        <v>6</v>
       </c>
       <c r="AL22" s="12">
         <f t="shared" si="7"/>
-        <v>-41330</v>
+        <v>26060</v>
       </c>
       <c r="AM22" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.63053472054197923</v>
       </c>
       <c r="AO22" s="14"/>
       <c r="AP22" s="13" t="s">
@@ -5482,15 +5562,15 @@
       <c r="AR22" s="12"/>
       <c r="AS22" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AT22" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU22" s="11" t="e">
+        <v>-67390</v>
+      </c>
+      <c r="AU22" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW22" s="14"/>
       <c r="AX22" s="13" t="s">
@@ -5695,19 +5775,23 @@
       <c r="AH23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI23" s="13"/>
-      <c r="AJ23" s="45"/>
+      <c r="AI23" s="13">
+        <v>13</v>
+      </c>
+      <c r="AJ23" s="45">
+        <v>600428.57142853003</v>
+      </c>
       <c r="AK23" s="10">
         <f t="shared" si="7"/>
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="AL23" s="12">
         <f t="shared" si="7"/>
-        <v>-429095.23809519003</v>
+        <v>171333.33333334001</v>
       </c>
       <c r="AM23" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.39928975696377128</v>
       </c>
       <c r="AO23" s="14"/>
       <c r="AP23" s="13" t="s">
@@ -5716,15 +5800,15 @@
       <c r="AR23" s="12"/>
       <c r="AS23" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AT23" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU23" s="11" t="e">
+        <v>-600428.57142853003</v>
+      </c>
+      <c r="AU23" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW23" s="14"/>
       <c r="AX23" s="13" t="s">
@@ -5929,19 +6013,23 @@
       <c r="AH24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI24" s="13"/>
-      <c r="AJ24" s="45"/>
+      <c r="AI24" s="13">
+        <v>22</v>
+      </c>
+      <c r="AJ24" s="45">
+        <v>390952.38095231005</v>
+      </c>
       <c r="AK24" s="10">
         <f t="shared" si="7"/>
-        <v>-23</v>
+        <v>-1</v>
       </c>
       <c r="AL24" s="12">
         <f t="shared" si="7"/>
-        <v>-567047.61904751998</v>
+        <v>-176095.23809520993</v>
       </c>
       <c r="AM24" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.31054753107155314</v>
       </c>
       <c r="AO24" s="14"/>
       <c r="AP24" s="13" t="s">
@@ -5950,15 +6038,15 @@
       <c r="AR24" s="12"/>
       <c r="AS24" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AT24" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU24" s="11" t="e">
+        <v>-390952.38095231005</v>
+      </c>
+      <c r="AU24" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW24" s="14"/>
       <c r="AX24" s="13" t="s">
@@ -6163,19 +6251,23 @@
       <c r="AH25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI25" s="13"/>
-      <c r="AJ25" s="45"/>
+      <c r="AI25" s="13">
+        <v>27</v>
+      </c>
+      <c r="AJ25" s="45">
+        <v>928857.14285710989</v>
+      </c>
       <c r="AK25" s="10">
         <f t="shared" si="7"/>
-        <v>-40</v>
+        <v>-13</v>
       </c>
       <c r="AL25" s="12">
         <f t="shared" si="7"/>
-        <v>-1429523.8095237699</v>
+        <v>-500666.66666665999</v>
       </c>
       <c r="AM25" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.35023317788141745</v>
       </c>
       <c r="AO25" s="14"/>
       <c r="AP25" s="13" t="s">
@@ -6184,15 +6276,15 @@
       <c r="AR25" s="12"/>
       <c r="AS25" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="AT25" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU25" s="11" t="e">
+        <v>-928857.14285710989</v>
+      </c>
+      <c r="AU25" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW25" s="14"/>
       <c r="AX25" s="13" t="s">
@@ -6398,19 +6490,23 @@
         <v>12</v>
       </c>
       <c r="AH26" s="9"/>
-      <c r="AI26" s="9"/>
-      <c r="AJ26" s="46"/>
+      <c r="AI26" s="9">
+        <v>376</v>
+      </c>
+      <c r="AJ26" s="46">
+        <v>2625037.6190468799</v>
+      </c>
       <c r="AK26" s="27">
         <f t="shared" si="7"/>
-        <v>-446</v>
+        <v>-70</v>
       </c>
       <c r="AL26" s="28">
         <f t="shared" si="7"/>
-        <v>-3152031.90476096</v>
+        <v>-526994.28571408009</v>
       </c>
       <c r="AM26" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.1671919262359261</v>
       </c>
       <c r="AO26" s="9" t="s">
         <v>12</v>
@@ -6420,15 +6516,15 @@
       <c r="AR26" s="7"/>
       <c r="AS26" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-376</v>
       </c>
       <c r="AT26" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU26" s="29" t="e">
+        <v>-2625037.6190468799</v>
+      </c>
+      <c r="AU26" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW26" s="9" t="s">
         <v>12</v>
@@ -6643,11 +6739,13 @@
       <c r="AH27" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AI27" s="32"/>
+      <c r="AI27" s="32">
+        <v>3211</v>
+      </c>
       <c r="AJ27" s="47"/>
       <c r="AK27" s="10">
         <f t="shared" si="7"/>
-        <v>-3036</v>
+        <v>175</v>
       </c>
       <c r="AL27" s="12">
         <f t="shared" si="7"/>
@@ -6666,7 +6764,7 @@
       <c r="AR27" s="35"/>
       <c r="AS27" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-3211</v>
       </c>
       <c r="AT27" s="12">
         <f t="shared" si="9"/>
@@ -7128,19 +7226,23 @@
       <c r="AH29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI29" s="13"/>
-      <c r="AJ29" s="45"/>
+      <c r="AI29" s="13">
+        <v>95</v>
+      </c>
+      <c r="AJ29" s="45">
+        <v>88453.333332949987</v>
+      </c>
       <c r="AK29" s="10">
         <f t="shared" si="7"/>
-        <v>-68</v>
+        <v>27</v>
       </c>
       <c r="AL29" s="12">
         <f t="shared" si="7"/>
-        <v>-64845.71428546001</v>
+        <v>23607.619047489978</v>
       </c>
       <c r="AM29" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.36405827752264242</v>
       </c>
       <c r="AO29" s="14"/>
       <c r="AP29" s="13" t="s">
@@ -7149,15 +7251,15 @@
       <c r="AR29" s="12"/>
       <c r="AS29" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="AT29" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU29" s="11" t="e">
+        <v>-88453.333332949987</v>
+      </c>
+      <c r="AU29" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW29" s="14"/>
       <c r="AX29" s="13" t="s">
@@ -7362,19 +7464,23 @@
       <c r="AH30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI30" s="13"/>
-      <c r="AJ30" s="45"/>
+      <c r="AI30" s="13">
+        <v>65</v>
+      </c>
+      <c r="AJ30" s="45">
+        <v>60828.571428500007</v>
+      </c>
       <c r="AK30" s="10">
         <f t="shared" si="7"/>
-        <v>-56</v>
+        <v>9</v>
       </c>
       <c r="AL30" s="12">
         <f t="shared" si="7"/>
-        <v>-70249.523809409991</v>
+        <v>-9420.9523809099846</v>
       </c>
       <c r="AM30" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.13410699276011376</v>
       </c>
       <c r="AO30" s="14"/>
       <c r="AP30" s="13" t="s">
@@ -7383,15 +7489,15 @@
       <c r="AR30" s="12"/>
       <c r="AS30" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AT30" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU30" s="11" t="e">
+        <v>-60828.571428500007</v>
+      </c>
+      <c r="AU30" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW30" s="14"/>
       <c r="AX30" s="13" t="s">
@@ -7596,19 +7702,23 @@
       <c r="AH31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI31" s="13"/>
-      <c r="AJ31" s="45"/>
+      <c r="AI31" s="13">
+        <v>11</v>
+      </c>
+      <c r="AJ31" s="45">
+        <v>62752.380952370004</v>
+      </c>
       <c r="AK31" s="10">
         <f t="shared" si="7"/>
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="AL31" s="12">
         <f t="shared" si="7"/>
-        <v>-72761.904761889993</v>
+        <v>-10009.523809519989</v>
       </c>
       <c r="AM31" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.13756544502615342</v>
       </c>
       <c r="AO31" s="14"/>
       <c r="AP31" s="13" t="s">
@@ -7617,15 +7727,15 @@
       <c r="AR31" s="12"/>
       <c r="AS31" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AT31" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU31" s="11" t="e">
+        <v>-62752.380952370004</v>
+      </c>
+      <c r="AU31" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW31" s="14"/>
       <c r="AX31" s="13" t="s">
@@ -7830,19 +7940,23 @@
       <c r="AH32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI32" s="13"/>
-      <c r="AJ32" s="45"/>
+      <c r="AI32" s="13">
+        <v>12</v>
+      </c>
+      <c r="AJ32" s="45">
+        <v>159809.52380948002</v>
+      </c>
       <c r="AK32" s="10">
         <f t="shared" si="7"/>
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="AL32" s="12">
         <f t="shared" si="7"/>
-        <v>-151142.85714281999</v>
+        <v>8666.6666666600213</v>
       </c>
       <c r="AM32" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>5.7340894769976426E-2</v>
       </c>
       <c r="AO32" s="14"/>
       <c r="AP32" s="13" t="s">
@@ -7851,15 +7965,15 @@
       <c r="AR32" s="12"/>
       <c r="AS32" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AT32" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU32" s="11" t="e">
+        <v>-159809.52380948002</v>
+      </c>
+      <c r="AU32" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW32" s="14"/>
       <c r="AX32" s="13" t="s">
@@ -8064,8 +8178,12 @@
       <c r="AH33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI33" s="13"/>
-      <c r="AJ33" s="45"/>
+      <c r="AI33" s="52">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="45">
+        <v>0</v>
+      </c>
       <c r="AK33" s="10">
         <f t="shared" si="7"/>
         <v>-1</v>
@@ -8298,19 +8416,23 @@
       <c r="AH34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI34" s="13"/>
-      <c r="AJ34" s="45"/>
+      <c r="AI34" s="13">
+        <v>2</v>
+      </c>
+      <c r="AJ34" s="45">
+        <v>56952.380952370004</v>
+      </c>
       <c r="AK34" s="10">
         <f t="shared" si="7"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL34" s="12">
         <f t="shared" si="7"/>
-        <v>-122190.47619046</v>
+        <v>-65238.095238089998</v>
       </c>
       <c r="AM34" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.53390491036635679</v>
       </c>
       <c r="AO34" s="14"/>
       <c r="AP34" s="13" t="s">
@@ -8319,15 +8441,15 @@
       <c r="AR34" s="12"/>
       <c r="AS34" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT34" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU34" s="11" t="e">
+        <v>-56952.380952370004</v>
+      </c>
+      <c r="AU34" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW34" s="14"/>
       <c r="AX34" s="13" t="s">
@@ -8532,19 +8654,23 @@
       <c r="AH35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI35" s="13"/>
-      <c r="AJ35" s="45"/>
+      <c r="AI35" s="13">
+        <v>7</v>
+      </c>
+      <c r="AJ35" s="45">
+        <v>134571.4285714</v>
+      </c>
       <c r="AK35" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="AL35" s="12">
         <f t="shared" si="7"/>
-        <v>-134666.66666663002</v>
+        <v>-95.23809523001546</v>
       </c>
       <c r="AM35" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-7.0721357844090134E-4</v>
       </c>
       <c r="AO35" s="14"/>
       <c r="AP35" s="13" t="s">
@@ -8553,15 +8679,15 @@
       <c r="AR35" s="12"/>
       <c r="AS35" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AT35" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU35" s="11" t="e">
+        <v>-134571.4285714</v>
+      </c>
+      <c r="AU35" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW35" s="14"/>
       <c r="AX35" s="13" t="s">
@@ -8766,19 +8892,23 @@
       <c r="AH36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI36" s="13"/>
-      <c r="AJ36" s="45"/>
+      <c r="AI36" s="13">
+        <v>19</v>
+      </c>
+      <c r="AJ36" s="45">
+        <v>767812.38095233997</v>
+      </c>
       <c r="AK36" s="10">
         <f t="shared" si="7"/>
-        <v>-13</v>
+        <v>6</v>
       </c>
       <c r="AL36" s="12">
         <f t="shared" si="7"/>
-        <v>-440666.66666664998</v>
+        <v>327145.71428568999</v>
       </c>
       <c r="AM36" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.74238815647284961</v>
       </c>
       <c r="AO36" s="14"/>
       <c r="AP36" s="13" t="s">
@@ -8787,15 +8917,15 @@
       <c r="AR36" s="12"/>
       <c r="AS36" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AT36" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU36" s="11" t="e">
+        <v>-767812.38095233997</v>
+      </c>
+      <c r="AU36" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW36" s="14"/>
       <c r="AX36" s="13" t="s">
@@ -9001,19 +9131,23 @@
         <v>11</v>
       </c>
       <c r="AH37" s="9"/>
-      <c r="AI37" s="9"/>
-      <c r="AJ37" s="46"/>
+      <c r="AI37" s="9">
+        <v>211</v>
+      </c>
+      <c r="AJ37" s="46">
+        <v>1331179.99999941</v>
+      </c>
       <c r="AK37" s="27">
         <f t="shared" si="7"/>
-        <v>-169</v>
+        <v>42</v>
       </c>
       <c r="AL37" s="28">
         <f t="shared" si="7"/>
-        <v>-1061413.8095233201</v>
+        <v>269766.19047608995</v>
       </c>
       <c r="AM37" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.25415741537906095</v>
       </c>
       <c r="AO37" s="9" t="s">
         <v>11</v>
@@ -9023,15 +9157,15 @@
       <c r="AR37" s="7"/>
       <c r="AS37" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-211</v>
       </c>
       <c r="AT37" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU37" s="29" t="e">
+        <v>-1331179.99999941</v>
+      </c>
+      <c r="AU37" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW37" s="9" t="s">
         <v>11</v>
@@ -9246,11 +9380,13 @@
       <c r="AH38" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AI38" s="32"/>
+      <c r="AI38" s="32">
+        <v>1633</v>
+      </c>
       <c r="AJ38" s="47"/>
       <c r="AK38" s="10">
         <f t="shared" si="7"/>
-        <v>-1431</v>
+        <v>202</v>
       </c>
       <c r="AL38" s="12">
         <f t="shared" si="7"/>
@@ -9269,7 +9405,7 @@
       <c r="AR38" s="35"/>
       <c r="AS38" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1633</v>
       </c>
       <c r="AT38" s="12">
         <f t="shared" si="9"/>
@@ -9731,19 +9867,23 @@
       <c r="AH40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI40" s="13"/>
-      <c r="AJ40" s="45"/>
+      <c r="AI40" s="13">
+        <v>91</v>
+      </c>
+      <c r="AJ40" s="45">
+        <v>82550.476190100031</v>
+      </c>
       <c r="AK40" s="10">
         <f t="shared" si="7"/>
-        <v>-78</v>
+        <v>13</v>
       </c>
       <c r="AL40" s="12">
         <f t="shared" si="7"/>
-        <v>-66923.809523470001</v>
+        <v>15626.66666663003</v>
       </c>
       <c r="AM40" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.23349935961355875</v>
       </c>
       <c r="AO40" s="14"/>
       <c r="AP40" s="13" t="s">
@@ -9752,15 +9892,15 @@
       <c r="AR40" s="12"/>
       <c r="AS40" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AT40" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU40" s="11" t="e">
+        <v>-82550.476190100031</v>
+      </c>
+      <c r="AU40" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW40" s="14"/>
       <c r="AX40" s="13" t="s">
@@ -9965,19 +10105,23 @@
       <c r="AH41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI41" s="13"/>
-      <c r="AJ41" s="45"/>
+      <c r="AI41" s="13">
+        <v>68</v>
+      </c>
+      <c r="AJ41" s="45">
+        <v>62773.333333250011</v>
+      </c>
       <c r="AK41" s="10">
         <f t="shared" si="7"/>
-        <v>-69</v>
+        <v>-1</v>
       </c>
       <c r="AL41" s="12">
         <f t="shared" si="7"/>
-        <v>-62904.76190468001</v>
+        <v>-131.42857142999856</v>
       </c>
       <c r="AM41" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-2.0893262680042111E-3</v>
       </c>
       <c r="AO41" s="14"/>
       <c r="AP41" s="13" t="s">
@@ -9986,15 +10130,15 @@
       <c r="AR41" s="12"/>
       <c r="AS41" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="AT41" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU41" s="11" t="e">
+        <v>-62773.333333250011</v>
+      </c>
+      <c r="AU41" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW41" s="14"/>
       <c r="AX41" s="13" t="s">
@@ -10199,19 +10343,23 @@
       <c r="AH42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI42" s="13"/>
-      <c r="AJ42" s="45"/>
+      <c r="AI42" s="13">
+        <v>11</v>
+      </c>
+      <c r="AJ42" s="45">
+        <v>61323.809523799995</v>
+      </c>
       <c r="AK42" s="10">
         <f t="shared" si="7"/>
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="AL42" s="12">
         <f t="shared" si="7"/>
-        <v>-55628.571428559997</v>
+        <v>5695.2380952399981</v>
       </c>
       <c r="AM42" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.10237972949842881</v>
       </c>
       <c r="AO42" s="14"/>
       <c r="AP42" s="13" t="s">
@@ -10220,15 +10368,15 @@
       <c r="AR42" s="12"/>
       <c r="AS42" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AT42" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU42" s="11" t="e">
+        <v>-61323.809523799995</v>
+      </c>
+      <c r="AU42" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW42" s="14"/>
       <c r="AX42" s="13" t="s">
@@ -10433,19 +10581,23 @@
       <c r="AH43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI43" s="13"/>
-      <c r="AJ43" s="45"/>
+      <c r="AI43" s="13">
+        <v>7</v>
+      </c>
+      <c r="AJ43" s="45">
+        <v>65047.619047600005</v>
+      </c>
       <c r="AK43" s="10">
         <f t="shared" si="7"/>
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="AL43" s="12">
         <f t="shared" si="7"/>
-        <v>-170095.23809520999</v>
+        <v>-105047.61904760999</v>
       </c>
       <c r="AM43" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.61758118701012721</v>
       </c>
       <c r="AO43" s="14"/>
       <c r="AP43" s="13" t="s">
@@ -10454,15 +10606,15 @@
       <c r="AR43" s="12"/>
       <c r="AS43" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AT43" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU43" s="11" t="e">
+        <v>-65047.619047600005</v>
+      </c>
+      <c r="AU43" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW43" s="14"/>
       <c r="AX43" s="13" t="s">
@@ -10667,11 +10819,15 @@
       <c r="AH44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI44" s="13"/>
-      <c r="AJ44" s="45"/>
+      <c r="AI44" s="13">
+        <v>1</v>
+      </c>
+      <c r="AJ44" s="45">
+        <v>0</v>
+      </c>
       <c r="AK44" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL44" s="12">
         <f t="shared" si="7"/>
@@ -10688,7 +10844,7 @@
       <c r="AR44" s="12"/>
       <c r="AS44" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AT44" s="12">
         <f t="shared" si="9"/>
@@ -10902,19 +11058,23 @@
       <c r="AH45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI45" s="13"/>
-      <c r="AJ45" s="45"/>
+      <c r="AI45" s="13">
+        <v>3</v>
+      </c>
+      <c r="AJ45" s="45">
+        <v>103228.57142856001</v>
+      </c>
       <c r="AK45" s="10">
         <f t="shared" si="7"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="AL45" s="12">
         <f t="shared" si="7"/>
-        <v>-134825.7142857</v>
+        <v>-31597.142857139988</v>
       </c>
       <c r="AM45" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.23435546419716816</v>
       </c>
       <c r="AO45" s="14"/>
       <c r="AP45" s="13" t="s">
@@ -10923,15 +11083,15 @@
       <c r="AR45" s="12"/>
       <c r="AS45" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AT45" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU45" s="11" t="e">
+        <v>-103228.57142856001</v>
+      </c>
+      <c r="AU45" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW45" s="14"/>
       <c r="AX45" s="13" t="s">
@@ -11137,19 +11297,23 @@
       <c r="AH46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI46" s="13"/>
-      <c r="AJ46" s="45"/>
+      <c r="AI46" s="13">
+        <v>7</v>
+      </c>
+      <c r="AJ46" s="45">
+        <v>145999.99999997998</v>
+      </c>
       <c r="AK46" s="10">
         <f t="shared" si="7"/>
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="AL46" s="12">
         <f t="shared" si="7"/>
-        <v>-39619.04761904</v>
+        <v>106380.95238093997</v>
       </c>
       <c r="AM46" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>2.6850961538463567</v>
       </c>
       <c r="AO46" s="14"/>
       <c r="AP46" s="13" t="s">
@@ -11158,15 +11322,15 @@
       <c r="AR46" s="12"/>
       <c r="AS46" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AT46" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU46" s="11" t="e">
+        <v>-145999.99999997998</v>
+      </c>
+      <c r="AU46" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW46" s="14"/>
       <c r="AX46" s="13" t="s">
@@ -11372,19 +11536,23 @@
       <c r="AH47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI47" s="13"/>
-      <c r="AJ47" s="45"/>
+      <c r="AI47" s="13">
+        <v>19</v>
+      </c>
+      <c r="AJ47" s="45">
+        <v>663904.76190473</v>
+      </c>
       <c r="AK47" s="10">
         <f t="shared" si="7"/>
-        <v>-13</v>
+        <v>6</v>
       </c>
       <c r="AL47" s="12">
         <f t="shared" si="7"/>
-        <v>-476857.14285711996</v>
+        <v>187047.61904761003</v>
       </c>
       <c r="AM47" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.39225084881166361</v>
       </c>
       <c r="AO47" s="14"/>
       <c r="AP47" s="13" t="s">
@@ -11393,15 +11561,15 @@
       <c r="AR47" s="12"/>
       <c r="AS47" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AT47" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU47" s="11" t="e">
+        <v>-663904.76190473</v>
+      </c>
+      <c r="AU47" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW47" s="14"/>
       <c r="AX47" s="13" t="s">
@@ -11608,19 +11776,23 @@
         <v>10</v>
       </c>
       <c r="AH48" s="9"/>
-      <c r="AI48" s="9"/>
-      <c r="AJ48" s="46"/>
+      <c r="AI48" s="9">
+        <v>207</v>
+      </c>
+      <c r="AJ48" s="46">
+        <v>1184828.57142802</v>
+      </c>
       <c r="AK48" s="27">
         <f t="shared" si="7"/>
-        <v>-190</v>
+        <v>17</v>
       </c>
       <c r="AL48" s="28">
         <f t="shared" si="7"/>
-        <v>-1006854.28571378</v>
+        <v>177974.28571424005</v>
       </c>
       <c r="AM48" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.17676270363995161</v>
       </c>
       <c r="AO48" s="9" t="s">
         <v>10</v>
@@ -11630,15 +11802,15 @@
       <c r="AR48" s="7"/>
       <c r="AS48" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-207</v>
       </c>
       <c r="AT48" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU48" s="29" t="e">
+        <v>-1184828.57142802</v>
+      </c>
+      <c r="AU48" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW48" s="9" t="s">
         <v>10</v>
@@ -12326,19 +12498,23 @@
       <c r="AH51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AI51" s="13"/>
-      <c r="AJ51" s="45"/>
+      <c r="AI51" s="13">
+        <v>122</v>
+      </c>
+      <c r="AJ51" s="45">
+        <v>110514.28571370998</v>
+      </c>
       <c r="AK51" s="10">
         <f t="shared" si="7"/>
-        <v>-111</v>
+        <v>11</v>
       </c>
       <c r="AL51" s="12">
         <f t="shared" si="7"/>
-        <v>-95536.190475689975</v>
+        <v>14978.095238020003</v>
       </c>
       <c r="AM51" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.15677928085097043</v>
       </c>
       <c r="AO51" s="14"/>
       <c r="AP51" s="13" t="s">
@@ -12347,15 +12523,15 @@
       <c r="AR51" s="12"/>
       <c r="AS51" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="AT51" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU51" s="11" t="e">
+        <v>-110514.28571370998</v>
+      </c>
+      <c r="AU51" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW51" s="14"/>
       <c r="AX51" s="13" t="s">
@@ -12560,19 +12736,23 @@
       <c r="AH52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AI52" s="13"/>
-      <c r="AJ52" s="45"/>
+      <c r="AI52" s="13">
+        <v>65</v>
+      </c>
+      <c r="AJ52" s="45">
+        <v>67476.190476090007</v>
+      </c>
       <c r="AK52" s="10">
         <f t="shared" si="7"/>
-        <v>-54</v>
+        <v>11</v>
       </c>
       <c r="AL52" s="12">
         <f t="shared" si="7"/>
-        <v>-96542.857142790002</v>
+        <v>-29066.666666699995</v>
       </c>
       <c r="AM52" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.30107526881775892</v>
       </c>
       <c r="AO52" s="14"/>
       <c r="AP52" s="13" t="s">
@@ -12581,15 +12761,15 @@
       <c r="AR52" s="12"/>
       <c r="AS52" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AT52" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU52" s="11" t="e">
+        <v>-67476.190476090007</v>
+      </c>
+      <c r="AU52" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW52" s="14"/>
       <c r="AX52" s="13" t="s">
@@ -12794,19 +12974,23 @@
       <c r="AH53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AI53" s="13"/>
-      <c r="AJ53" s="45"/>
+      <c r="AI53" s="13">
+        <v>17</v>
+      </c>
+      <c r="AJ53" s="45">
+        <v>128409.52380950001</v>
+      </c>
       <c r="AK53" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>11</v>
       </c>
       <c r="AL53" s="12">
         <f t="shared" si="7"/>
-        <v>-34228.571428559997</v>
+        <v>94180.952380940013</v>
       </c>
       <c r="AM53" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>2.7515303283255439</v>
       </c>
       <c r="AO53" s="14"/>
       <c r="AP53" s="13" t="s">
@@ -12815,15 +12999,15 @@
       <c r="AR53" s="12"/>
       <c r="AS53" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AT53" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU53" s="11" t="e">
+        <v>-128409.52380950001</v>
+      </c>
+      <c r="AU53" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW53" s="14"/>
       <c r="AX53" s="13" t="s">
@@ -13028,19 +13212,23 @@
       <c r="AH54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AI54" s="13"/>
-      <c r="AJ54" s="45"/>
+      <c r="AI54" s="13">
+        <v>10</v>
+      </c>
+      <c r="AJ54" s="45">
+        <v>139047.61904760002</v>
+      </c>
       <c r="AK54" s="10">
         <f t="shared" si="7"/>
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="AL54" s="12">
         <f t="shared" si="7"/>
-        <v>-144666.66666664003</v>
+        <v>-5619.0476190400077</v>
       </c>
       <c r="AM54" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-3.8841342988762968E-2</v>
       </c>
       <c r="AO54" s="14"/>
       <c r="AP54" s="13" t="s">
@@ -13049,15 +13237,15 @@
       <c r="AR54" s="12"/>
       <c r="AS54" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AT54" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU54" s="11" t="e">
+        <v>-139047.61904760002</v>
+      </c>
+      <c r="AU54" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW54" s="14"/>
       <c r="AX54" s="13" t="s">
@@ -13262,19 +13450,23 @@
       <c r="AH55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AI55" s="13"/>
-      <c r="AJ55" s="45"/>
+      <c r="AI55" s="13">
+        <v>7</v>
+      </c>
+      <c r="AJ55" s="45">
+        <v>30030</v>
+      </c>
       <c r="AK55" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AL55" s="12">
         <f t="shared" si="7"/>
-        <v>-990</v>
+        <v>29040</v>
       </c>
       <c r="AM55" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="AO55" s="14"/>
       <c r="AP55" s="13" t="s">
@@ -13283,15 +13475,15 @@
       <c r="AR55" s="12"/>
       <c r="AS55" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AT55" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU55" s="11" t="e">
+        <v>-30030</v>
+      </c>
+      <c r="AU55" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW55" s="14"/>
       <c r="AX55" s="13" t="s">
@@ -13497,19 +13689,23 @@
       <c r="AH56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AI56" s="13"/>
-      <c r="AJ56" s="45"/>
+      <c r="AI56" s="13">
+        <v>2</v>
+      </c>
+      <c r="AJ56" s="45">
+        <v>69814.285714269994</v>
+      </c>
       <c r="AK56" s="10">
         <f t="shared" si="7"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AL56" s="12">
         <f t="shared" si="7"/>
-        <v>-214761.90476188</v>
+        <v>-144947.61904761</v>
       </c>
       <c r="AM56" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.67492239467852799</v>
       </c>
       <c r="AO56" s="14"/>
       <c r="AP56" s="13" t="s">
@@ -13518,15 +13714,15 @@
       <c r="AR56" s="12"/>
       <c r="AS56" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT56" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU56" s="11" t="e">
+        <v>-69814.285714269994</v>
+      </c>
+      <c r="AU56" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW56" s="14"/>
       <c r="AX56" s="13" t="s">
@@ -13732,19 +13928,23 @@
       <c r="AH57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AI57" s="13"/>
-      <c r="AJ57" s="45"/>
+      <c r="AI57" s="13">
+        <v>8</v>
+      </c>
+      <c r="AJ57" s="45">
+        <v>183523.80952377</v>
+      </c>
       <c r="AK57" s="10">
         <f t="shared" si="7"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AL57" s="12">
         <f t="shared" si="7"/>
-        <v>-192095.23809520996</v>
+        <v>-8571.4285714399593</v>
       </c>
       <c r="AM57" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-4.4620723847363784E-2</v>
       </c>
       <c r="AO57" s="14"/>
       <c r="AP57" s="13" t="s">
@@ -13753,15 +13953,15 @@
       <c r="AR57" s="12"/>
       <c r="AS57" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AT57" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU57" s="11" t="e">
+        <v>-183523.80952377</v>
+      </c>
+      <c r="AU57" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW57" s="14"/>
       <c r="AX57" s="13" t="s">
@@ -13967,19 +14167,23 @@
       <c r="AH58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI58" s="13"/>
-      <c r="AJ58" s="45"/>
+      <c r="AI58" s="13">
+        <v>18</v>
+      </c>
+      <c r="AJ58" s="45">
+        <v>669714.28571425995</v>
+      </c>
       <c r="AK58" s="10">
         <f t="shared" si="7"/>
-        <v>-22</v>
+        <v>-4</v>
       </c>
       <c r="AL58" s="12">
         <f t="shared" si="7"/>
-        <v>-798955.23809519992</v>
+        <v>-129240.95238093997</v>
       </c>
       <c r="AM58" s="11">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.16176244452575977</v>
       </c>
       <c r="AO58" s="14"/>
       <c r="AP58" s="13" t="s">
@@ -13988,15 +14192,15 @@
       <c r="AR58" s="12"/>
       <c r="AS58" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AT58" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU58" s="11" t="e">
+        <v>-669714.28571425995</v>
+      </c>
+      <c r="AU58" s="11">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW58" s="14"/>
       <c r="AX58" s="13" t="s">
@@ -14203,19 +14407,23 @@
         <v>1</v>
       </c>
       <c r="AH59" s="9"/>
-      <c r="AI59" s="9"/>
-      <c r="AJ59" s="46"/>
+      <c r="AI59" s="9">
+        <v>249</v>
+      </c>
+      <c r="AJ59" s="46">
+        <v>1398529.9999992</v>
+      </c>
       <c r="AK59" s="27">
         <f t="shared" si="7"/>
-        <v>-218</v>
+        <v>31</v>
       </c>
       <c r="AL59" s="28">
         <f t="shared" si="7"/>
-        <v>-1577776.6666659699</v>
+        <v>-179246.66666676989</v>
       </c>
       <c r="AM59" s="29">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.1136071222586524</v>
       </c>
       <c r="AO59" s="9" t="s">
         <v>1</v>
@@ -14225,15 +14433,15 @@
       <c r="AR59" s="7"/>
       <c r="AS59" s="27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-249</v>
       </c>
       <c r="AT59" s="28">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU59" s="29" t="e">
+        <v>-1398529.9999992</v>
+      </c>
+      <c r="AU59" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW59" s="9" t="s">
         <v>1</v>
@@ -14446,19 +14654,23 @@
         <v>0</v>
       </c>
       <c r="AH60" s="4"/>
-      <c r="AI60" s="4"/>
-      <c r="AJ60" s="48"/>
+      <c r="AI60" s="4">
+        <v>1879</v>
+      </c>
+      <c r="AJ60" s="48">
+        <v>14443175.714281667</v>
+      </c>
       <c r="AK60" s="6">
         <f t="shared" si="7"/>
-        <v>-1743</v>
+        <v>136</v>
       </c>
       <c r="AL60" s="5">
         <f t="shared" si="7"/>
-        <v>-14309083.333329419</v>
+        <v>134092.38095224835</v>
       </c>
       <c r="AM60" s="30">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>9.3711370483050994E-3</v>
       </c>
       <c r="AO60" s="4" t="s">
         <v>0</v>
@@ -14468,15 +14680,15 @@
       <c r="AR60" s="2"/>
       <c r="AS60" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1879</v>
       </c>
       <c r="AT60" s="5">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AU60" s="30" t="e">
+        <v>-14443175.714281667</v>
+      </c>
+      <c r="AU60" s="30">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AW60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F40180D-8800-3440-8DB9-8E783E40E78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349AE0F8-2CA8-C547-9026-F33C45CCF3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1710,11 +1710,13 @@
       <c r="AH6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI6" s="32"/>
+      <c r="AI6" s="32">
+        <v>12</v>
+      </c>
       <c r="AJ6" s="44"/>
       <c r="AK6" s="10">
         <f t="shared" si="7"/>
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="7"/>
@@ -1731,7 +1733,7 @@
       <c r="AR6" s="33"/>
       <c r="AS6" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AT6" s="12">
         <f t="shared" si="9"/>
@@ -4347,11 +4349,13 @@
       <c r="AH17" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI17" s="32"/>
+      <c r="AI17" s="32">
+        <v>4</v>
+      </c>
       <c r="AJ17" s="47"/>
       <c r="AK17" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="AL17" s="12">
         <f t="shared" si="7"/>
@@ -4368,7 +4372,7 @@
       <c r="AR17" s="35"/>
       <c r="AS17" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AT17" s="12">
         <f t="shared" si="9"/>
@@ -6988,11 +6992,13 @@
       <c r="AH28" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI28" s="32"/>
+      <c r="AI28" s="32">
+        <v>2</v>
+      </c>
       <c r="AJ28" s="47"/>
       <c r="AK28" s="10">
         <f t="shared" si="7"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AL28" s="12">
         <f t="shared" si="7"/>
@@ -7009,7 +7015,7 @@
       <c r="AR28" s="35"/>
       <c r="AS28" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT28" s="12">
         <f t="shared" si="9"/>
@@ -9629,11 +9635,13 @@
       <c r="AH39" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI39" s="32"/>
+      <c r="AI39" s="32">
+        <v>5</v>
+      </c>
       <c r="AJ39" s="47"/>
       <c r="AK39" s="10">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AL39" s="12">
         <f t="shared" si="7"/>
@@ -9650,7 +9658,7 @@
       <c r="AR39" s="35"/>
       <c r="AS39" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AT39" s="12">
         <f t="shared" si="9"/>
@@ -12260,11 +12268,13 @@
       <c r="AH50" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AI50" s="32"/>
+      <c r="AI50" s="32">
+        <v>3</v>
+      </c>
       <c r="AJ50" s="47"/>
       <c r="AK50" s="10">
         <f t="shared" si="7"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AL50" s="12">
         <f t="shared" si="7"/>
@@ -12281,7 +12291,7 @@
       <c r="AR50" s="35"/>
       <c r="AS50" s="10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AT50" s="12">
         <f t="shared" si="9"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349AE0F8-2CA8-C547-9026-F33C45CCF3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DADFF45-D6DF-C34A-8798-93F585CD4B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="40">
   <si>
     <t>總計</t>
   </si>
@@ -182,6 +182,33 @@
   <si>
     <t>07/26-08/01</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q4W6</t>
+  </si>
+  <si>
+    <t>08/02-08/08</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>業績</t>
+  </si>
+  <si>
+    <t>Traffic</t>
+  </si>
+  <si>
+    <t>Trade in</t>
+  </si>
+  <si>
+    <t>75 合計</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1015,9 @@
       </c>
       <c r="AH1" s="26"/>
       <c r="AJ1" s="41"/>
-      <c r="AO1" s="26"/>
+      <c r="AO1" s="26" t="s">
+        <v>31</v>
+      </c>
       <c r="AP1" s="26"/>
       <c r="AR1" s="25"/>
       <c r="AW1" s="26"/>
@@ -1041,7 +1070,9 @@
       <c r="AK2" s="22"/>
       <c r="AL2" s="22"/>
       <c r="AN2" s="21"/>
-      <c r="AO2" s="23"/>
+      <c r="AO2" s="23" t="s">
+        <v>32</v>
+      </c>
       <c r="AQ2" s="22"/>
       <c r="AR2" s="22"/>
       <c r="AT2" s="21"/>
@@ -1191,16 +1222,16 @@
         <v>13</v>
       </c>
       <c r="AO4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="AP4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AQ4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AR4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AS4" s="16" t="s">
         <v>13</v>
@@ -1470,13 +1501,15 @@
         <v>75</v>
       </c>
       <c r="AP5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AQ5" s="40"/>
+        <v>37</v>
+      </c>
+      <c r="AQ5" s="40">
+        <v>6469</v>
+      </c>
       <c r="AR5" s="1"/>
       <c r="AS5" s="10">
         <f t="shared" ref="AS5:AT60" si="9">AQ5-AI5</f>
-        <v>-5898</v>
+        <v>571</v>
       </c>
       <c r="AT5" s="12">
         <f t="shared" si="9"/>
@@ -1497,7 +1530,7 @@
       <c r="AZ5" s="1"/>
       <c r="BA5" s="10">
         <f t="shared" ref="BA5:BA60" si="11">AY5-AQ5</f>
-        <v>0</v>
+        <v>-6469</v>
       </c>
       <c r="BB5" s="12">
         <f t="shared" ref="BB5:BB60" si="12">AZ5-AR5</f>
@@ -1728,7 +1761,7 @@
       </c>
       <c r="AO6" s="14"/>
       <c r="AP6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AR6" s="33"/>
       <c r="AS6" s="10">
@@ -1968,18 +2001,23 @@
       <c r="AP7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR7" s="12"/>
+      <c r="AQ7" s="10">
+        <v>240</v>
+      </c>
+      <c r="AR7" s="12">
+        <v>282545.71428457979</v>
+      </c>
       <c r="AS7" s="10">
         <f t="shared" si="9"/>
-        <v>-255</v>
+        <v>-15</v>
       </c>
       <c r="AT7" s="12">
         <f t="shared" si="9"/>
-        <v>-266492.38095159992</v>
+        <v>16053.333332979877</v>
       </c>
       <c r="AU7" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>6.0239370730435504E-2</v>
       </c>
       <c r="AW7" s="14"/>
       <c r="AX7" s="13" t="s">
@@ -1988,15 +2026,15 @@
       <c r="AZ7" s="12"/>
       <c r="BA7" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-240</v>
       </c>
       <c r="BB7" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="11" t="e">
+        <v>-282545.71428457979</v>
+      </c>
+      <c r="BC7" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE7" s="14"/>
       <c r="BF7" s="13" t="s">
@@ -2206,18 +2244,23 @@
       <c r="AP8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR8" s="12"/>
+      <c r="AQ8" s="10">
+        <v>253</v>
+      </c>
+      <c r="AR8" s="12">
+        <v>370535.23809472017</v>
+      </c>
       <c r="AS8" s="10">
         <f t="shared" si="9"/>
-        <v>-247</v>
+        <v>6</v>
       </c>
       <c r="AT8" s="12">
         <f t="shared" si="9"/>
-        <v>-337030.47619030991</v>
+        <v>33504.761904410261</v>
       </c>
       <c r="AU8" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>9.9411668295217415E-2</v>
       </c>
       <c r="AW8" s="14"/>
       <c r="AX8" s="13" t="s">
@@ -2226,15 +2269,15 @@
       <c r="AZ8" s="12"/>
       <c r="BA8" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-253</v>
       </c>
       <c r="BB8" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC8" s="11" t="e">
+        <v>-370535.23809472017</v>
+      </c>
+      <c r="BC8" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE8" s="14"/>
       <c r="BF8" s="13" t="s">
@@ -2444,18 +2487,23 @@
       <c r="AP9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR9" s="12"/>
+      <c r="AQ9" s="10">
+        <v>64</v>
+      </c>
+      <c r="AR9" s="12">
+        <v>456533.33333325997</v>
+      </c>
       <c r="AS9" s="10">
         <f t="shared" si="9"/>
-        <v>-72</v>
+        <v>-8</v>
       </c>
       <c r="AT9" s="12">
         <f t="shared" si="9"/>
-        <v>-503599.99999997998</v>
+        <v>-47066.666666720004</v>
       </c>
       <c r="AU9" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-9.3460418321528738E-2</v>
       </c>
       <c r="AW9" s="14"/>
       <c r="AX9" s="13" t="s">
@@ -2464,15 +2512,15 @@
       <c r="AZ9" s="12"/>
       <c r="BA9" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-64</v>
       </c>
       <c r="BB9" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC9" s="11" t="e">
+        <v>-456533.33333325997</v>
+      </c>
+      <c r="BC9" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE9" s="14"/>
       <c r="BF9" s="13" t="s">
@@ -2682,18 +2730,23 @@
       <c r="AP10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR10" s="12"/>
+      <c r="AQ10" s="10">
+        <v>54</v>
+      </c>
+      <c r="AR10" s="12">
+        <v>716761.90476172033</v>
+      </c>
       <c r="AS10" s="10">
         <f t="shared" si="9"/>
-        <v>-38</v>
+        <v>16</v>
       </c>
       <c r="AT10" s="12">
         <f t="shared" si="9"/>
-        <v>-474857.14285708999</v>
+        <v>241904.76190463034</v>
       </c>
       <c r="AU10" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.50942639390270783</v>
       </c>
       <c r="AW10" s="14"/>
       <c r="AX10" s="13" t="s">
@@ -2702,15 +2755,15 @@
       <c r="AZ10" s="12"/>
       <c r="BA10" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="BB10" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC10" s="11" t="e">
+        <v>-716761.90476172033</v>
+      </c>
+      <c r="BC10" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE10" s="14"/>
       <c r="BF10" s="13" t="s">
@@ -2920,18 +2973,23 @@
       <c r="AP11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR11" s="12"/>
+      <c r="AQ11" s="10">
+        <v>14</v>
+      </c>
+      <c r="AR11" s="12">
+        <v>67170</v>
+      </c>
       <c r="AS11" s="10">
         <f t="shared" si="9"/>
-        <v>-11</v>
+        <v>3</v>
       </c>
       <c r="AT11" s="12">
         <f t="shared" si="9"/>
-        <v>-53110</v>
+        <v>14060</v>
       </c>
       <c r="AU11" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.26473357183204671</v>
       </c>
       <c r="AW11" s="14"/>
       <c r="AX11" s="13" t="s">
@@ -2940,15 +2998,15 @@
       <c r="AZ11" s="12"/>
       <c r="BA11" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BB11" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="11" t="e">
+        <v>-67170</v>
+      </c>
+      <c r="BC11" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE11" s="14"/>
       <c r="BF11" s="13" t="s">
@@ -3158,18 +3216,23 @@
       <c r="AP12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR12" s="12"/>
+      <c r="AQ12" s="10">
+        <v>37</v>
+      </c>
+      <c r="AR12" s="12">
+        <v>1971285.7142855099</v>
+      </c>
       <c r="AS12" s="10">
         <f t="shared" si="9"/>
-        <v>-28</v>
+        <v>9</v>
       </c>
       <c r="AT12" s="12">
         <f t="shared" si="9"/>
-        <v>-1397652.38095225</v>
+        <v>573633.33333325991</v>
       </c>
       <c r="AU12" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.41042632714039484</v>
       </c>
       <c r="AW12" s="14"/>
       <c r="AX12" s="13" t="s">
@@ -3178,15 +3241,15 @@
       <c r="AZ12" s="12"/>
       <c r="BA12" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-37</v>
       </c>
       <c r="BB12" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="11" t="e">
+        <v>-1971285.7142855099</v>
+      </c>
+      <c r="BC12" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE12" s="14"/>
       <c r="BF12" s="13" t="s">
@@ -3396,18 +3459,23 @@
       <c r="AP13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR13" s="12"/>
+      <c r="AQ13" s="10">
+        <v>63</v>
+      </c>
+      <c r="AR13" s="12">
+        <v>1626095.23809503</v>
+      </c>
       <c r="AS13" s="10">
         <f t="shared" si="9"/>
-        <v>-115</v>
+        <v>-52</v>
       </c>
       <c r="AT13" s="12">
         <f t="shared" si="9"/>
-        <v>-2222285.7142855702</v>
+        <v>-596190.47619054024</v>
       </c>
       <c r="AU13" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.26827804919864057</v>
       </c>
       <c r="AW13" s="14"/>
       <c r="AX13" s="13" t="s">
@@ -3416,15 +3484,15 @@
       <c r="AZ13" s="12"/>
       <c r="BA13" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="BB13" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC13" s="11" t="e">
+        <v>-1626095.23809503</v>
+      </c>
+      <c r="BC13" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE13" s="14"/>
       <c r="BF13" s="13" t="s">
@@ -3634,18 +3702,23 @@
       <c r="AP14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR14" s="12"/>
+      <c r="AQ14" s="10">
+        <v>105</v>
+      </c>
+      <c r="AR14" s="12">
+        <v>4165238.0952379601</v>
+      </c>
       <c r="AS14" s="10">
         <f t="shared" si="9"/>
-        <v>-70</v>
+        <v>35</v>
       </c>
       <c r="AT14" s="12">
         <f t="shared" si="9"/>
-        <v>-2648571.4285713602</v>
+        <v>1516666.6666665999</v>
       </c>
       <c r="AU14" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.5726357425386448</v>
       </c>
       <c r="AW14" s="14"/>
       <c r="AX14" s="13" t="s">
@@ -3654,15 +3727,15 @@
       <c r="AZ14" s="12"/>
       <c r="BA14" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="BB14" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC14" s="11" t="e">
+        <v>-4165238.0952379601</v>
+      </c>
+      <c r="BC14" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE14" s="14"/>
       <c r="BF14" s="13" t="s">
@@ -3870,22 +3943,26 @@
         <v>5.22690066146708E-2</v>
       </c>
       <c r="AO15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="AP15" s="9"/>
-      <c r="AQ15" s="8"/>
-      <c r="AR15" s="7"/>
+      <c r="AQ15" s="8">
+        <v>830</v>
+      </c>
+      <c r="AR15" s="7">
+        <v>9656165.2380927801</v>
+      </c>
       <c r="AS15" s="27">
         <f t="shared" si="9"/>
-        <v>-836</v>
+        <v>-6</v>
       </c>
       <c r="AT15" s="28">
         <f t="shared" si="9"/>
-        <v>-7903599.5238081599</v>
+        <v>1752565.7142846202</v>
       </c>
       <c r="AU15" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.22174272734914438</v>
       </c>
       <c r="AW15" s="9" t="s">
         <v>18</v>
@@ -3895,15 +3972,15 @@
       <c r="AZ15" s="7"/>
       <c r="BA15" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-830</v>
       </c>
       <c r="BB15" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC15" s="29" t="e">
+        <v>-9656165.2380927801</v>
+      </c>
+      <c r="BC15" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE15" s="9" t="s">
         <v>18</v>
@@ -4120,12 +4197,15 @@
         <v>76</v>
       </c>
       <c r="AP16" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="AQ16" s="1">
+        <v>4138</v>
       </c>
       <c r="AR16" s="35"/>
       <c r="AS16" s="10">
         <f t="shared" si="9"/>
-        <v>-3807</v>
+        <v>331</v>
       </c>
       <c r="AT16" s="12">
         <f t="shared" si="9"/>
@@ -4144,7 +4224,7 @@
       <c r="AZ16" s="35"/>
       <c r="BA16" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-4138</v>
       </c>
       <c r="BB16" s="12">
         <f t="shared" si="12"/>
@@ -4367,7 +4447,7 @@
       </c>
       <c r="AO17" s="14"/>
       <c r="AP17" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AR17" s="35"/>
       <c r="AS17" s="10">
@@ -4611,18 +4691,23 @@
       <c r="AP18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR18" s="12"/>
+      <c r="AQ18" s="10">
+        <v>133</v>
+      </c>
+      <c r="AR18" s="12">
+        <v>128007.61904704</v>
+      </c>
       <c r="AS18" s="10">
         <f t="shared" si="9"/>
-        <v>-104</v>
+        <v>29</v>
       </c>
       <c r="AT18" s="12">
         <f t="shared" si="9"/>
-        <v>-102379.04761861001</v>
+        <v>25628.57142842999</v>
       </c>
       <c r="AU18" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.25033023870180388</v>
       </c>
       <c r="AW18" s="14"/>
       <c r="AX18" s="13" t="s">
@@ -4631,15 +4716,15 @@
       <c r="AZ18" s="12"/>
       <c r="BA18" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-133</v>
       </c>
       <c r="BB18" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC18" s="11" t="e">
+        <v>-128007.61904704</v>
+      </c>
+      <c r="BC18" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE18" s="14"/>
       <c r="BF18" s="13" t="s">
@@ -4849,18 +4934,23 @@
       <c r="AP19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR19" s="12"/>
+      <c r="AQ19" s="10">
+        <v>171</v>
+      </c>
+      <c r="AR19" s="12">
+        <v>165000.95238059</v>
+      </c>
       <c r="AS19" s="10">
         <f t="shared" si="9"/>
-        <v>-138</v>
+        <v>33</v>
       </c>
       <c r="AT19" s="12">
         <f t="shared" si="9"/>
-        <v>-136401.90476181998</v>
+        <v>28599.047618770011</v>
       </c>
       <c r="AU19" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.20966750917964541</v>
       </c>
       <c r="AW19" s="14"/>
       <c r="AX19" s="13" t="s">
@@ -4869,15 +4959,15 @@
       <c r="AZ19" s="12"/>
       <c r="BA19" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-171</v>
       </c>
       <c r="BB19" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC19" s="11" t="e">
+        <v>-165000.95238059</v>
+      </c>
+      <c r="BC19" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE19" s="14"/>
       <c r="BF19" s="13" t="s">
@@ -5087,18 +5177,23 @@
       <c r="AP20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR20" s="12"/>
+      <c r="AQ20" s="10">
+        <v>25</v>
+      </c>
+      <c r="AR20" s="12">
+        <v>161190.47619043</v>
+      </c>
       <c r="AS20" s="10">
         <f t="shared" si="9"/>
-        <v>-34</v>
+        <v>-9</v>
       </c>
       <c r="AT20" s="12">
         <f t="shared" si="9"/>
-        <v>-205390.47619046</v>
+        <v>-44200.000000030006</v>
       </c>
       <c r="AU20" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.21519985161845109</v>
       </c>
       <c r="AW20" s="14"/>
       <c r="AX20" s="13" t="s">
@@ -5107,15 +5202,15 @@
       <c r="AZ20" s="12"/>
       <c r="BA20" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="BB20" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC20" s="11" t="e">
+        <v>-161190.47619043</v>
+      </c>
+      <c r="BC20" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE20" s="14"/>
       <c r="BF20" s="13" t="s">
@@ -5325,18 +5420,23 @@
       <c r="AP21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR21" s="12"/>
+      <c r="AQ21" s="10">
+        <v>21</v>
+      </c>
+      <c r="AR21" s="12">
+        <v>262476.19047610002</v>
+      </c>
       <c r="AS21" s="10">
         <f t="shared" si="9"/>
-        <v>-19</v>
+        <v>2</v>
       </c>
       <c r="AT21" s="12">
         <f t="shared" si="9"/>
-        <v>-193238.09523804003</v>
+        <v>69238.095238059992</v>
       </c>
       <c r="AU21" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.358304583538609</v>
       </c>
       <c r="AW21" s="14"/>
       <c r="AX21" s="13" t="s">
@@ -5345,15 +5445,15 @@
       <c r="AZ21" s="12"/>
       <c r="BA21" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="BB21" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC21" s="11" t="e">
+        <v>-262476.19047610002</v>
+      </c>
+      <c r="BC21" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE21" s="14"/>
       <c r="BF21" s="13" t="s">
@@ -5563,18 +5663,23 @@
       <c r="AP22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR22" s="12"/>
+      <c r="AQ22" s="10">
+        <v>21</v>
+      </c>
+      <c r="AR22" s="12">
+        <v>73180</v>
+      </c>
       <c r="AS22" s="10">
         <f t="shared" si="9"/>
-        <v>-19</v>
+        <v>2</v>
       </c>
       <c r="AT22" s="12">
         <f t="shared" si="9"/>
-        <v>-67390</v>
+        <v>5790</v>
       </c>
       <c r="AU22" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>8.5917791957263692E-2</v>
       </c>
       <c r="AW22" s="14"/>
       <c r="AX22" s="13" t="s">
@@ -5583,15 +5688,15 @@
       <c r="AZ22" s="12"/>
       <c r="BA22" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="BB22" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC22" s="11" t="e">
+        <v>-73180</v>
+      </c>
+      <c r="BC22" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE22" s="14"/>
       <c r="BF22" s="13" t="s">
@@ -5801,18 +5906,23 @@
       <c r="AP23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR23" s="12"/>
+      <c r="AQ23" s="10">
+        <v>10</v>
+      </c>
+      <c r="AR23" s="12">
+        <v>327357.14285708999</v>
+      </c>
       <c r="AS23" s="10">
         <f t="shared" si="9"/>
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="AT23" s="12">
         <f t="shared" si="9"/>
-        <v>-600428.57142853003</v>
+        <v>-273071.42857144005</v>
       </c>
       <c r="AU23" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.45479419462293885</v>
       </c>
       <c r="AW23" s="14"/>
       <c r="AX23" s="13" t="s">
@@ -5821,15 +5931,15 @@
       <c r="AZ23" s="12"/>
       <c r="BA23" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BB23" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC23" s="11" t="e">
+        <v>-327357.14285708999</v>
+      </c>
+      <c r="BC23" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE23" s="14"/>
       <c r="BF23" s="13" t="s">
@@ -6039,18 +6149,23 @@
       <c r="AP24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR24" s="12"/>
+      <c r="AQ24" s="10">
+        <v>24</v>
+      </c>
+      <c r="AR24" s="12">
+        <v>609904.76190465991</v>
+      </c>
       <c r="AS24" s="10">
         <f t="shared" si="9"/>
-        <v>-22</v>
+        <v>2</v>
       </c>
       <c r="AT24" s="12">
         <f t="shared" si="9"/>
-        <v>-390952.38095231005</v>
+        <v>218952.38095234986</v>
       </c>
       <c r="AU24" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.56004872107188564</v>
       </c>
       <c r="AW24" s="14"/>
       <c r="AX24" s="13" t="s">
@@ -6059,15 +6174,15 @@
       <c r="AZ24" s="12"/>
       <c r="BA24" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="BB24" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC24" s="11" t="e">
+        <v>-609904.76190465991</v>
+      </c>
+      <c r="BC24" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE24" s="14"/>
       <c r="BF24" s="13" t="s">
@@ -6277,18 +6392,23 @@
       <c r="AP25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR25" s="12"/>
+      <c r="AQ25" s="10">
+        <v>57</v>
+      </c>
+      <c r="AR25" s="12">
+        <v>2140285.7142856</v>
+      </c>
       <c r="AS25" s="10">
         <f t="shared" si="9"/>
-        <v>-27</v>
+        <v>30</v>
       </c>
       <c r="AT25" s="12">
         <f t="shared" si="9"/>
-        <v>-928857.14285710989</v>
+        <v>1211428.5714284901</v>
       </c>
       <c r="AU25" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.3042140879728901</v>
       </c>
       <c r="AW25" s="14"/>
       <c r="AX25" s="13" t="s">
@@ -6297,15 +6417,15 @@
       <c r="AZ25" s="12"/>
       <c r="BA25" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-57</v>
       </c>
       <c r="BB25" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC25" s="11" t="e">
+        <v>-2140285.7142856</v>
+      </c>
+      <c r="BC25" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE25" s="14"/>
       <c r="BF25" s="13" t="s">
@@ -6516,19 +6636,23 @@
         <v>12</v>
       </c>
       <c r="AP26" s="9"/>
-      <c r="AQ26" s="8"/>
-      <c r="AR26" s="7"/>
+      <c r="AQ26" s="8">
+        <v>462</v>
+      </c>
+      <c r="AR26" s="7">
+        <v>3867402.8571415101</v>
+      </c>
       <c r="AS26" s="27">
         <f t="shared" si="9"/>
-        <v>-376</v>
+        <v>86</v>
       </c>
       <c r="AT26" s="28">
         <f t="shared" si="9"/>
-        <v>-2625037.6190468799</v>
+        <v>1242365.2380946302</v>
       </c>
       <c r="AU26" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.47327521292655544</v>
       </c>
       <c r="AW26" s="9" t="s">
         <v>12</v>
@@ -6538,15 +6662,15 @@
       <c r="AZ26" s="7"/>
       <c r="BA26" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-462</v>
       </c>
       <c r="BB26" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC26" s="29" t="e">
+        <v>-3867402.8571415101</v>
+      </c>
+      <c r="BC26" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE26" s="9" t="s">
         <v>12</v>
@@ -6763,12 +6887,15 @@
         <v>77</v>
       </c>
       <c r="AP27" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="AQ27" s="1">
+        <v>3328</v>
       </c>
       <c r="AR27" s="35"/>
       <c r="AS27" s="10">
         <f t="shared" si="9"/>
-        <v>-3211</v>
+        <v>117</v>
       </c>
       <c r="AT27" s="12">
         <f t="shared" si="9"/>
@@ -6787,7 +6914,7 @@
       <c r="AZ27" s="35"/>
       <c r="BA27" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3328</v>
       </c>
       <c r="BB27" s="12">
         <f t="shared" si="12"/>
@@ -7010,7 +7137,7 @@
       </c>
       <c r="AO28" s="14"/>
       <c r="AP28" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AR28" s="35"/>
       <c r="AS28" s="10">
@@ -7254,18 +7381,23 @@
       <c r="AP29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR29" s="12"/>
+      <c r="AQ29" s="10">
+        <v>96</v>
+      </c>
+      <c r="AR29" s="12">
+        <v>86227.619047240034</v>
+      </c>
       <c r="AS29" s="10">
         <f t="shared" si="9"/>
-        <v>-95</v>
+        <v>1</v>
       </c>
       <c r="AT29" s="12">
         <f t="shared" si="9"/>
-        <v>-88453.333332949987</v>
+        <v>-2225.7142857099534</v>
       </c>
       <c r="AU29" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-2.5162582367948442E-2</v>
       </c>
       <c r="AW29" s="14"/>
       <c r="AX29" s="13" t="s">
@@ -7274,15 +7406,15 @@
       <c r="AZ29" s="12"/>
       <c r="BA29" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="BB29" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC29" s="11" t="e">
+        <v>-86227.619047240034</v>
+      </c>
+      <c r="BC29" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE29" s="14"/>
       <c r="BF29" s="13" t="s">
@@ -7492,18 +7624,23 @@
       <c r="AP30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR30" s="12"/>
+      <c r="AQ30" s="10">
+        <v>88</v>
+      </c>
+      <c r="AR30" s="12">
+        <v>72116.190475950003</v>
+      </c>
       <c r="AS30" s="10">
         <f t="shared" si="9"/>
-        <v>-65</v>
+        <v>23</v>
       </c>
       <c r="AT30" s="12">
         <f t="shared" si="9"/>
-        <v>-60828.571428500007</v>
+        <v>11287.619047449996</v>
       </c>
       <c r="AU30" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.18556442774129345</v>
       </c>
       <c r="AW30" s="14"/>
       <c r="AX30" s="13" t="s">
@@ -7512,15 +7649,15 @@
       <c r="AZ30" s="12"/>
       <c r="BA30" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-88</v>
       </c>
       <c r="BB30" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC30" s="11" t="e">
+        <v>-72116.190475950003</v>
+      </c>
+      <c r="BC30" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE30" s="14"/>
       <c r="BF30" s="13" t="s">
@@ -7730,18 +7867,23 @@
       <c r="AP31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR31" s="12"/>
+      <c r="AQ31" s="10">
+        <v>24</v>
+      </c>
+      <c r="AR31" s="12">
+        <v>156914.28571423999</v>
+      </c>
       <c r="AS31" s="10">
         <f t="shared" si="9"/>
-        <v>-11</v>
+        <v>13</v>
       </c>
       <c r="AT31" s="12">
         <f t="shared" si="9"/>
-        <v>-62752.380952370004</v>
+        <v>94161.904761869984</v>
       </c>
       <c r="AU31" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.5005311883439176</v>
       </c>
       <c r="AW31" s="14"/>
       <c r="AX31" s="13" t="s">
@@ -7750,15 +7892,15 @@
       <c r="AZ31" s="12"/>
       <c r="BA31" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="BB31" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="11" t="e">
+        <v>-156914.28571423999</v>
+      </c>
+      <c r="BC31" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE31" s="14"/>
       <c r="BF31" s="13" t="s">
@@ -7968,18 +8110,23 @@
       <c r="AP32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR32" s="12"/>
+      <c r="AQ32" s="10">
+        <v>8</v>
+      </c>
+      <c r="AR32" s="12">
+        <v>99904.761904709987</v>
+      </c>
       <c r="AS32" s="10">
         <f t="shared" si="9"/>
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="AT32" s="12">
         <f t="shared" si="9"/>
-        <v>-159809.52380948002</v>
+        <v>-59904.761904770028</v>
       </c>
       <c r="AU32" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.37485101311099978</v>
       </c>
       <c r="AW32" s="14"/>
       <c r="AX32" s="13" t="s">
@@ -7988,15 +8135,15 @@
       <c r="AZ32" s="12"/>
       <c r="BA32" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BB32" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="11" t="e">
+        <v>-99904.761904709987</v>
+      </c>
+      <c r="BC32" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE32" s="14"/>
       <c r="BF32" s="13" t="s">
@@ -8206,7 +8353,12 @@
       <c r="AP33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR33" s="12"/>
+      <c r="AQ33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR33" s="12">
+        <v>0</v>
+      </c>
       <c r="AS33" s="10">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -8444,18 +8596,23 @@
       <c r="AP34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR34" s="12"/>
+      <c r="AQ34" s="10">
+        <v>2</v>
+      </c>
+      <c r="AR34" s="12">
+        <v>49333.333333319999</v>
+      </c>
       <c r="AS34" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AT34" s="12">
         <f t="shared" si="9"/>
-        <v>-56952.380952370004</v>
+        <v>-7619.0476190500049</v>
       </c>
       <c r="AU34" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.13377926421411443</v>
       </c>
       <c r="AW34" s="14"/>
       <c r="AX34" s="13" t="s">
@@ -8464,15 +8621,15 @@
       <c r="AZ34" s="12"/>
       <c r="BA34" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BB34" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="11" t="e">
+        <v>-49333.333333319999</v>
+      </c>
+      <c r="BC34" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE34" s="14"/>
       <c r="BF34" s="13" t="s">
@@ -8682,18 +8839,23 @@
       <c r="AP35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR35" s="12"/>
+      <c r="AQ35" s="10">
+        <v>13</v>
+      </c>
+      <c r="AR35" s="12">
+        <v>359714.28571423999</v>
+      </c>
       <c r="AS35" s="10">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="AT35" s="12">
         <f t="shared" si="9"/>
-        <v>-134571.4285714</v>
+        <v>225142.85714283999</v>
       </c>
       <c r="AU35" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.6730360934184867</v>
       </c>
       <c r="AW35" s="14"/>
       <c r="AX35" s="13" t="s">
@@ -8702,15 +8864,15 @@
       <c r="AZ35" s="12"/>
       <c r="BA35" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BB35" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC35" s="11" t="e">
+        <v>-359714.28571423999</v>
+      </c>
+      <c r="BC35" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE35" s="14"/>
       <c r="BF35" s="13" t="s">
@@ -8920,18 +9082,23 @@
       <c r="AP36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR36" s="12"/>
+      <c r="AQ36" s="10">
+        <v>10</v>
+      </c>
+      <c r="AR36" s="12">
+        <v>352479.04761903</v>
+      </c>
       <c r="AS36" s="10">
         <f t="shared" si="9"/>
-        <v>-19</v>
+        <v>-9</v>
       </c>
       <c r="AT36" s="12">
         <f t="shared" si="9"/>
-        <v>-767812.38095233997</v>
+        <v>-415333.33333330997</v>
       </c>
       <c r="AU36" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.54093075813411606</v>
       </c>
       <c r="AW36" s="14"/>
       <c r="AX36" s="13" t="s">
@@ -8940,15 +9107,15 @@
       <c r="AZ36" s="12"/>
       <c r="BA36" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BB36" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC36" s="11" t="e">
+        <v>-352479.04761903</v>
+      </c>
+      <c r="BC36" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE36" s="14"/>
       <c r="BF36" s="13" t="s">
@@ -9159,19 +9326,23 @@
         <v>11</v>
       </c>
       <c r="AP37" s="9"/>
-      <c r="AQ37" s="8"/>
-      <c r="AR37" s="7"/>
+      <c r="AQ37" s="8">
+        <v>241</v>
+      </c>
+      <c r="AR37" s="7">
+        <v>1176689.5238087301</v>
+      </c>
       <c r="AS37" s="27">
         <f t="shared" si="9"/>
-        <v>-211</v>
+        <v>30</v>
       </c>
       <c r="AT37" s="28">
         <f t="shared" si="9"/>
-        <v>-1331179.99999941</v>
+        <v>-154490.47619067994</v>
       </c>
       <c r="AU37" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.1160552864306468</v>
       </c>
       <c r="AW37" s="9" t="s">
         <v>11</v>
@@ -9181,15 +9352,15 @@
       <c r="AZ37" s="7"/>
       <c r="BA37" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-241</v>
       </c>
       <c r="BB37" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC37" s="29" t="e">
+        <v>-1176689.5238087301</v>
+      </c>
+      <c r="BC37" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE37" s="9" t="s">
         <v>11</v>
@@ -9406,12 +9577,15 @@
         <v>81</v>
       </c>
       <c r="AP38" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="AQ38" s="1">
+        <v>2066</v>
       </c>
       <c r="AR38" s="35"/>
       <c r="AS38" s="10">
         <f t="shared" si="9"/>
-        <v>-1633</v>
+        <v>433</v>
       </c>
       <c r="AT38" s="12">
         <f t="shared" si="9"/>
@@ -9430,7 +9604,7 @@
       <c r="AZ38" s="35"/>
       <c r="BA38" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2066</v>
       </c>
       <c r="BB38" s="12">
         <f t="shared" si="12"/>
@@ -9653,7 +9827,7 @@
       </c>
       <c r="AO39" s="14"/>
       <c r="AP39" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AR39" s="35"/>
       <c r="AS39" s="10">
@@ -9897,18 +10071,23 @@
       <c r="AP40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR40" s="12"/>
+      <c r="AQ40" s="10">
+        <v>109</v>
+      </c>
+      <c r="AR40" s="12">
+        <v>103550.4761899</v>
+      </c>
       <c r="AS40" s="10">
         <f t="shared" si="9"/>
-        <v>-91</v>
+        <v>18</v>
       </c>
       <c r="AT40" s="12">
         <f t="shared" si="9"/>
-        <v>-82550.476190100031</v>
+        <v>20999.999999799969</v>
       </c>
       <c r="AU40" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.25438981056197008</v>
       </c>
       <c r="AW40" s="14"/>
       <c r="AX40" s="13" t="s">
@@ -9917,15 +10096,15 @@
       <c r="AZ40" s="12"/>
       <c r="BA40" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="BB40" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC40" s="11" t="e">
+        <v>-103550.4761899</v>
+      </c>
+      <c r="BC40" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE40" s="14"/>
       <c r="BF40" s="13" t="s">
@@ -10135,18 +10314,23 @@
       <c r="AP41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR41" s="12"/>
+      <c r="AQ41" s="10">
+        <v>79</v>
+      </c>
+      <c r="AR41" s="12">
+        <v>104352.38095211</v>
+      </c>
       <c r="AS41" s="10">
         <f t="shared" si="9"/>
-        <v>-68</v>
+        <v>11</v>
       </c>
       <c r="AT41" s="12">
         <f t="shared" si="9"/>
-        <v>-62773.333333250011</v>
+        <v>41579.047618859993</v>
       </c>
       <c r="AU41" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.66236800582384003</v>
       </c>
       <c r="AW41" s="14"/>
       <c r="AX41" s="13" t="s">
@@ -10155,15 +10339,15 @@
       <c r="AZ41" s="12"/>
       <c r="BA41" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-79</v>
       </c>
       <c r="BB41" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC41" s="11" t="e">
+        <v>-104352.38095211</v>
+      </c>
+      <c r="BC41" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE41" s="14"/>
       <c r="BF41" s="13" t="s">
@@ -10373,18 +10557,23 @@
       <c r="AP42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR42" s="12"/>
+      <c r="AQ42" s="10">
+        <v>22</v>
+      </c>
+      <c r="AR42" s="12">
+        <v>154076.19047616</v>
+      </c>
       <c r="AS42" s="10">
         <f t="shared" si="9"/>
-        <v>-11</v>
+        <v>11</v>
       </c>
       <c r="AT42" s="12">
         <f t="shared" si="9"/>
-        <v>-61323.809523799995</v>
+        <v>92752.380952360007</v>
       </c>
       <c r="AU42" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.5125019412951257</v>
       </c>
       <c r="AW42" s="14"/>
       <c r="AX42" s="13" t="s">
@@ -10393,15 +10582,15 @@
       <c r="AZ42" s="12"/>
       <c r="BA42" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="BB42" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC42" s="11" t="e">
+        <v>-154076.19047616</v>
+      </c>
+      <c r="BC42" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE42" s="14"/>
       <c r="BF42" s="13" t="s">
@@ -10611,18 +10800,23 @@
       <c r="AP43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR43" s="12"/>
+      <c r="AQ43" s="10">
+        <v>12</v>
+      </c>
+      <c r="AR43" s="12">
+        <v>109333.33333331</v>
+      </c>
       <c r="AS43" s="10">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="AT43" s="12">
         <f t="shared" si="9"/>
-        <v>-65047.619047600005</v>
+        <v>44285.714285709997</v>
       </c>
       <c r="AU43" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.68081991215240278</v>
       </c>
       <c r="AW43" s="14"/>
       <c r="AX43" s="13" t="s">
@@ -10631,15 +10825,15 @@
       <c r="AZ43" s="12"/>
       <c r="BA43" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BB43" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC43" s="11" t="e">
+        <v>-109333.33333331</v>
+      </c>
+      <c r="BC43" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE43" s="14"/>
       <c r="BF43" s="13" t="s">
@@ -10849,14 +11043,19 @@
       <c r="AP44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR44" s="12"/>
+      <c r="AQ44" s="10">
+        <v>3</v>
+      </c>
+      <c r="AR44" s="12">
+        <v>9490</v>
+      </c>
       <c r="AS44" s="10">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AT44" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9490</v>
       </c>
       <c r="AU44" s="11" t="e">
         <f t="shared" si="10"/>
@@ -10869,15 +11068,15 @@
       <c r="AZ44" s="12"/>
       <c r="BA44" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB44" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC44" s="11" t="e">
+        <v>-9490</v>
+      </c>
+      <c r="BC44" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE44" s="14"/>
       <c r="BF44" s="13" t="s">
@@ -11088,18 +11287,23 @@
       <c r="AP45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR45" s="12"/>
+      <c r="AQ45" s="10">
+        <v>6</v>
+      </c>
+      <c r="AR45" s="12">
+        <v>261334.28571425</v>
+      </c>
       <c r="AS45" s="10">
         <f t="shared" si="9"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AT45" s="12">
         <f t="shared" si="9"/>
-        <v>-103228.57142856001</v>
+        <v>158105.71428568999</v>
       </c>
       <c r="AU45" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>1.5316080819263109</v>
       </c>
       <c r="AW45" s="14"/>
       <c r="AX45" s="13" t="s">
@@ -11108,15 +11312,15 @@
       <c r="AZ45" s="12"/>
       <c r="BA45" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BB45" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC45" s="11" t="e">
+        <v>-261334.28571425</v>
+      </c>
+      <c r="BC45" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE45" s="14"/>
       <c r="BF45" s="13" t="s">
@@ -11327,18 +11531,23 @@
       <c r="AP46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR46" s="12"/>
+      <c r="AQ46" s="10">
+        <v>8</v>
+      </c>
+      <c r="AR46" s="12">
+        <v>179333.33333329999</v>
+      </c>
       <c r="AS46" s="10">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="AT46" s="12">
         <f t="shared" si="9"/>
-        <v>-145999.99999997998</v>
+        <v>33333.333333320013</v>
       </c>
       <c r="AU46" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.22831050228304511</v>
       </c>
       <c r="AW46" s="14"/>
       <c r="AX46" s="13" t="s">
@@ -11347,15 +11556,15 @@
       <c r="AZ46" s="12"/>
       <c r="BA46" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BB46" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC46" s="11" t="e">
+        <v>-179333.33333329999</v>
+      </c>
+      <c r="BC46" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE46" s="14"/>
       <c r="BF46" s="13" t="s">
@@ -11566,18 +11775,23 @@
       <c r="AP47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR47" s="12"/>
+      <c r="AQ47" s="10">
+        <v>24</v>
+      </c>
+      <c r="AR47" s="12">
+        <v>922476.19047615991</v>
+      </c>
       <c r="AS47" s="10">
         <f t="shared" si="9"/>
-        <v>-19</v>
+        <v>5</v>
       </c>
       <c r="AT47" s="12">
         <f t="shared" si="9"/>
-        <v>-663904.76190473</v>
+        <v>258571.42857142992</v>
       </c>
       <c r="AU47" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.38947066418019577</v>
       </c>
       <c r="AW47" s="14"/>
       <c r="AX47" s="13" t="s">
@@ -11586,15 +11800,15 @@
       <c r="AZ47" s="12"/>
       <c r="BA47" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="BB47" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC47" s="11" t="e">
+        <v>-922476.19047615991</v>
+      </c>
+      <c r="BC47" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE47" s="14"/>
       <c r="BF47" s="13" t="s">
@@ -11806,19 +12020,23 @@
         <v>10</v>
       </c>
       <c r="AP48" s="9"/>
-      <c r="AQ48" s="8"/>
-      <c r="AR48" s="7"/>
+      <c r="AQ48" s="8">
+        <v>263</v>
+      </c>
+      <c r="AR48" s="7">
+        <v>1843946.1904751901</v>
+      </c>
       <c r="AS48" s="27">
         <f t="shared" si="9"/>
-        <v>-207</v>
+        <v>56</v>
       </c>
       <c r="AT48" s="28">
         <f t="shared" si="9"/>
-        <v>-1184828.57142802</v>
+        <v>659117.61904717004</v>
       </c>
       <c r="AU48" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.55629787712898038</v>
       </c>
       <c r="AW48" s="9" t="s">
         <v>10</v>
@@ -11828,15 +12046,15 @@
       <c r="AZ48" s="7"/>
       <c r="BA48" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-263</v>
       </c>
       <c r="BB48" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC48" s="29" t="e">
+        <v>-1843946.1904751901</v>
+      </c>
+      <c r="BC48" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE48" s="9" t="s">
         <v>10</v>
@@ -12039,7 +12257,7 @@
         <v>84</v>
       </c>
       <c r="AP49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="AR49" s="35"/>
       <c r="AS49" s="10">
@@ -12286,7 +12504,7 @@
       </c>
       <c r="AO50" s="14"/>
       <c r="AP50" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AR50" s="35"/>
       <c r="AS50" s="10">
@@ -12530,18 +12748,23 @@
       <c r="AP51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AR51" s="12"/>
+      <c r="AQ51" s="10">
+        <v>104</v>
+      </c>
+      <c r="AR51" s="12">
+        <v>107172.38095183999</v>
+      </c>
       <c r="AS51" s="10">
         <f t="shared" si="9"/>
-        <v>-122</v>
+        <v>-18</v>
       </c>
       <c r="AT51" s="12">
         <f t="shared" si="9"/>
-        <v>-110514.28571370998</v>
+        <v>-3341.9047618699842</v>
       </c>
       <c r="AU51" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-3.0239572561028646E-2</v>
       </c>
       <c r="AW51" s="14"/>
       <c r="AX51" s="13" t="s">
@@ -12550,15 +12773,15 @@
       <c r="AZ51" s="12"/>
       <c r="BA51" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="BB51" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC51" s="11" t="e">
+        <v>-107172.38095183999</v>
+      </c>
+      <c r="BC51" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE51" s="14"/>
       <c r="BF51" s="13" t="s">
@@ -12768,18 +12991,23 @@
       <c r="AP52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AR52" s="12"/>
+      <c r="AQ52" s="10">
+        <v>62</v>
+      </c>
+      <c r="AR52" s="12">
+        <v>71790.476190239991</v>
+      </c>
       <c r="AS52" s="10">
         <f t="shared" si="9"/>
-        <v>-65</v>
+        <v>-3</v>
       </c>
       <c r="AT52" s="12">
         <f t="shared" si="9"/>
-        <v>-67476.190476090007</v>
+        <v>4314.2857141499844</v>
       </c>
       <c r="AU52" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>6.3937896963503577E-2</v>
       </c>
       <c r="AW52" s="14"/>
       <c r="AX52" s="13" t="s">
@@ -12788,15 +13016,15 @@
       <c r="AZ52" s="12"/>
       <c r="BA52" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="BB52" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC52" s="11" t="e">
+        <v>-71790.476190239991</v>
+      </c>
+      <c r="BC52" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE52" s="14"/>
       <c r="BF52" s="13" t="s">
@@ -13006,18 +13234,23 @@
       <c r="AP53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AR53" s="12"/>
+      <c r="AQ53" s="10">
+        <v>16</v>
+      </c>
+      <c r="AR53" s="12">
+        <v>92704.761904729981</v>
+      </c>
       <c r="AS53" s="10">
         <f t="shared" si="9"/>
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="AT53" s="12">
         <f t="shared" si="9"/>
-        <v>-128409.52380950001</v>
+        <v>-35704.761904770028</v>
       </c>
       <c r="AU53" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.27805384558344193</v>
       </c>
       <c r="AW53" s="14"/>
       <c r="AX53" s="13" t="s">
@@ -13026,15 +13259,15 @@
       <c r="AZ53" s="12"/>
       <c r="BA53" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BB53" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC53" s="11" t="e">
+        <v>-92704.761904729981</v>
+      </c>
+      <c r="BC53" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE53" s="14"/>
       <c r="BF53" s="13" t="s">
@@ -13244,18 +13477,23 @@
       <c r="AP54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AR54" s="12"/>
+      <c r="AQ54" s="10">
+        <v>15</v>
+      </c>
+      <c r="AR54" s="12">
+        <v>187142.85714278999</v>
+      </c>
       <c r="AS54" s="10">
         <f t="shared" si="9"/>
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="AT54" s="12">
         <f t="shared" si="9"/>
-        <v>-139047.61904760002</v>
+        <v>48095.238095189969</v>
       </c>
       <c r="AU54" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.34589041095860534</v>
       </c>
       <c r="AW54" s="14"/>
       <c r="AX54" s="13" t="s">
@@ -13264,15 +13502,15 @@
       <c r="AZ54" s="12"/>
       <c r="BA54" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BB54" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC54" s="11" t="e">
+        <v>-187142.85714278999</v>
+      </c>
+      <c r="BC54" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE54" s="14"/>
       <c r="BF54" s="13" t="s">
@@ -13482,18 +13720,23 @@
       <c r="AP55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AR55" s="12"/>
+      <c r="AQ55" s="10">
+        <v>5</v>
+      </c>
+      <c r="AR55" s="12">
+        <v>27550</v>
+      </c>
       <c r="AS55" s="10">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="AT55" s="12">
         <f t="shared" si="9"/>
-        <v>-30030</v>
+        <v>-2480</v>
       </c>
       <c r="AU55" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-8.2584082584082591E-2</v>
       </c>
       <c r="AW55" s="14"/>
       <c r="AX55" s="13" t="s">
@@ -13502,15 +13745,15 @@
       <c r="AZ55" s="12"/>
       <c r="BA55" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BB55" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC55" s="11" t="e">
+        <v>-27550</v>
+      </c>
+      <c r="BC55" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE55" s="14"/>
       <c r="BF55" s="13" t="s">
@@ -13721,18 +13964,23 @@
       <c r="AP56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AR56" s="12"/>
+      <c r="AQ56" s="10">
+        <v>5</v>
+      </c>
+      <c r="AR56" s="12">
+        <v>217819.04761902001</v>
+      </c>
       <c r="AS56" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="AT56" s="12">
         <f t="shared" si="9"/>
-        <v>-69814.285714269994</v>
+        <v>148004.76190475002</v>
       </c>
       <c r="AU56" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>2.1199781733854786</v>
       </c>
       <c r="AW56" s="14"/>
       <c r="AX56" s="13" t="s">
@@ -13741,15 +13989,15 @@
       <c r="AZ56" s="12"/>
       <c r="BA56" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BB56" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC56" s="11" t="e">
+        <v>-217819.04761902001</v>
+      </c>
+      <c r="BC56" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE56" s="14"/>
       <c r="BF56" s="13" t="s">
@@ -13960,18 +14208,23 @@
       <c r="AP57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AR57" s="12"/>
+      <c r="AQ57" s="10">
+        <v>13</v>
+      </c>
+      <c r="AR57" s="12">
+        <v>341619.04761898</v>
+      </c>
       <c r="AS57" s="10">
         <f t="shared" si="9"/>
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="AT57" s="12">
         <f t="shared" si="9"/>
-        <v>-183523.80952377</v>
+        <v>158095.23809520999</v>
       </c>
       <c r="AU57" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.86144265697979361</v>
       </c>
       <c r="AW57" s="14"/>
       <c r="AX57" s="13" t="s">
@@ -13980,15 +14233,15 @@
       <c r="AZ57" s="12"/>
       <c r="BA57" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BB57" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC57" s="11" t="e">
+        <v>-341619.04761898</v>
+      </c>
+      <c r="BC57" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE57" s="14"/>
       <c r="BF57" s="13" t="s">
@@ -14199,18 +14452,23 @@
       <c r="AP58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AR58" s="12"/>
+      <c r="AQ58" s="10">
+        <v>10</v>
+      </c>
+      <c r="AR58" s="12">
+        <v>387619.04761901998</v>
+      </c>
       <c r="AS58" s="10">
         <f t="shared" si="9"/>
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AT58" s="12">
         <f t="shared" si="9"/>
-        <v>-669714.28571425995</v>
+        <v>-282095.23809523997</v>
       </c>
       <c r="AU58" s="11">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>-0.42121729237772093</v>
       </c>
       <c r="AW58" s="14"/>
       <c r="AX58" s="13" t="s">
@@ -14219,15 +14477,15 @@
       <c r="AZ58" s="12"/>
       <c r="BA58" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BB58" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC58" s="11" t="e">
+        <v>-387619.04761901998</v>
+      </c>
+      <c r="BC58" s="11">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE58" s="14"/>
       <c r="BF58" s="13" t="s">
@@ -14439,19 +14697,23 @@
         <v>1</v>
       </c>
       <c r="AP59" s="9"/>
-      <c r="AQ59" s="8"/>
-      <c r="AR59" s="7"/>
+      <c r="AQ59" s="8">
+        <v>230</v>
+      </c>
+      <c r="AR59" s="7">
+        <v>1433417.6190466201</v>
+      </c>
       <c r="AS59" s="27">
         <f t="shared" si="9"/>
-        <v>-249</v>
+        <v>-19</v>
       </c>
       <c r="AT59" s="28">
         <f t="shared" si="9"/>
-        <v>-1398529.9999992</v>
+        <v>34887.619047420099</v>
       </c>
       <c r="AU59" s="29">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>2.4945921108192215E-2</v>
       </c>
       <c r="AW59" s="9" t="s">
         <v>1</v>
@@ -14461,15 +14723,15 @@
       <c r="AZ59" s="7"/>
       <c r="BA59" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-230</v>
       </c>
       <c r="BB59" s="28">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC59" s="29" t="e">
+        <v>-1433417.6190466201</v>
+      </c>
+      <c r="BC59" s="29">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE59" s="9" t="s">
         <v>1</v>
@@ -14686,19 +14948,23 @@
         <v>0</v>
       </c>
       <c r="AP60" s="4"/>
-      <c r="AQ60" s="3"/>
-      <c r="AR60" s="2"/>
+      <c r="AQ60" s="3">
+        <v>2026</v>
+      </c>
+      <c r="AR60" s="2">
+        <v>17977621.428564832</v>
+      </c>
       <c r="AS60" s="6">
         <f t="shared" si="9"/>
-        <v>-1879</v>
+        <v>147</v>
       </c>
       <c r="AT60" s="5">
         <f t="shared" si="9"/>
-        <v>-14443175.714281667</v>
+        <v>3534445.7142831646</v>
       </c>
       <c r="AU60" s="30">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>0.24471389008916108</v>
       </c>
       <c r="AW60" s="4" t="s">
         <v>0</v>
@@ -14708,15 +14974,15 @@
       <c r="AZ60" s="2"/>
       <c r="BA60" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-2026</v>
       </c>
       <c r="BB60" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BC60" s="30" t="e">
+        <v>-17977621.428564832</v>
+      </c>
+      <c r="BC60" s="30">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BE60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DADFF45-D6DF-C34A-8798-93F585CD4B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26D1630-78CD-3D4D-9714-DACBFC55B095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1763,10 +1763,13 @@
       <c r="AP6" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AQ6" s="15">
+        <v>16</v>
+      </c>
       <c r="AR6" s="33"/>
       <c r="AS6" s="10">
         <f t="shared" si="9"/>
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="AT6" s="12">
         <f t="shared" si="9"/>
@@ -1783,7 +1786,7 @@
       <c r="AZ6" s="33"/>
       <c r="BA6" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BB6" s="12">
         <f t="shared" si="12"/>
@@ -4449,10 +4452,13 @@
       <c r="AP17" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AQ17" s="1">
+        <v>9</v>
+      </c>
       <c r="AR17" s="35"/>
       <c r="AS17" s="10">
         <f t="shared" si="9"/>
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="AT17" s="12">
         <f t="shared" si="9"/>
@@ -4469,7 +4475,7 @@
       <c r="AZ17" s="35"/>
       <c r="BA17" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BB17" s="12">
         <f t="shared" si="12"/>
@@ -7139,10 +7145,13 @@
       <c r="AP28" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AQ28" s="1">
+        <v>3</v>
+      </c>
       <c r="AR28" s="35"/>
       <c r="AS28" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT28" s="12">
         <f t="shared" si="9"/>
@@ -7159,7 +7168,7 @@
       <c r="AZ28" s="35"/>
       <c r="BA28" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB28" s="12">
         <f t="shared" si="12"/>
@@ -9829,10 +9838,13 @@
       <c r="AP39" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AQ39" s="1">
+        <v>7</v>
+      </c>
       <c r="AR39" s="35"/>
       <c r="AS39" s="10">
         <f t="shared" si="9"/>
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="AT39" s="12">
         <f t="shared" si="9"/>
@@ -9849,7 +9861,7 @@
       <c r="AZ39" s="35"/>
       <c r="BA39" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BB39" s="12">
         <f t="shared" si="12"/>
@@ -12506,10 +12518,13 @@
       <c r="AP50" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AQ50" s="1">
+        <v>3</v>
+      </c>
       <c r="AR50" s="35"/>
       <c r="AS50" s="10">
         <f t="shared" si="9"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AT50" s="12">
         <f t="shared" si="9"/>
@@ -12526,7 +12541,7 @@
       <c r="AZ50" s="35"/>
       <c r="BA50" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BB50" s="12">
         <f t="shared" si="12"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26D1630-78CD-3D4D-9714-DACBFC55B095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C20A83-1088-5E48-BB9E-60857A7BAE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12760" yWindow="3860" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q4" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="42">
   <si>
     <t>總計</t>
   </si>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t>75 合計</t>
+  </si>
+  <si>
+    <t>26Q4W7</t>
+  </si>
+  <si>
+    <t>08/09-08/15</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1026,9 @@
       </c>
       <c r="AP1" s="26"/>
       <c r="AR1" s="25"/>
-      <c r="AW1" s="26"/>
+      <c r="AW1" s="26" t="s">
+        <v>40</v>
+      </c>
       <c r="AX1" s="26"/>
       <c r="AZ1" s="25"/>
       <c r="BE1" s="26"/>
@@ -1076,6 +1084,9 @@
       <c r="AQ2" s="22"/>
       <c r="AR2" s="22"/>
       <c r="AT2" s="21"/>
+      <c r="AW2" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="AY2" s="22"/>
       <c r="AZ2" s="22"/>
       <c r="BB2" s="21"/>
@@ -1243,16 +1254,16 @@
         <v>13</v>
       </c>
       <c r="AW4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="AX4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AY4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AZ4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BA4" s="16" t="s">
         <v>13</v>
@@ -1524,13 +1535,15 @@
         <v>75</v>
       </c>
       <c r="AX5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AY5" s="40"/>
+        <v>37</v>
+      </c>
+      <c r="AY5" s="40">
+        <v>6235</v>
+      </c>
       <c r="AZ5" s="1"/>
       <c r="BA5" s="10">
         <f t="shared" ref="BA5:BA60" si="11">AY5-AQ5</f>
-        <v>-6469</v>
+        <v>-234</v>
       </c>
       <c r="BB5" s="12">
         <f t="shared" ref="BB5:BB60" si="12">AZ5-AR5</f>
@@ -1551,7 +1564,7 @@
       <c r="BH5" s="1"/>
       <c r="BI5" s="10">
         <f t="shared" ref="BI5:BI60" si="14">BG5-AY5</f>
-        <v>0</v>
+        <v>-6235</v>
       </c>
       <c r="BJ5" s="12">
         <f t="shared" ref="BJ5:BJ60" si="15">BH5-AZ5</f>
@@ -1781,7 +1794,7 @@
       </c>
       <c r="AW6" s="14"/>
       <c r="AX6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AZ6" s="33"/>
       <c r="BA6" s="10">
@@ -2026,18 +2039,23 @@
       <c r="AX7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ7" s="12"/>
+      <c r="AY7" s="10">
+        <v>200</v>
+      </c>
+      <c r="AZ7" s="12">
+        <v>235359.99999904991</v>
+      </c>
       <c r="BA7" s="10">
         <f t="shared" si="11"/>
-        <v>-240</v>
+        <v>-40</v>
       </c>
       <c r="BB7" s="12">
         <f t="shared" si="12"/>
-        <v>-282545.71428457979</v>
+        <v>-47185.714285529888</v>
       </c>
       <c r="BC7" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.16700205276518362</v>
       </c>
       <c r="BE7" s="14"/>
       <c r="BF7" s="13" t="s">
@@ -2046,15 +2064,15 @@
       <c r="BH7" s="12"/>
       <c r="BI7" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="BJ7" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK7" s="11" t="e">
+        <v>-235359.99999904991</v>
+      </c>
+      <c r="BK7" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM7" s="14"/>
       <c r="BN7" s="13" t="s">
@@ -2269,18 +2287,23 @@
       <c r="AX8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ8" s="12"/>
+      <c r="AY8" s="10">
+        <v>265</v>
+      </c>
+      <c r="AZ8" s="12">
+        <v>417266.66666615021</v>
+      </c>
       <c r="BA8" s="10">
         <f t="shared" si="11"/>
-        <v>-253</v>
+        <v>12</v>
       </c>
       <c r="BB8" s="12">
         <f t="shared" si="12"/>
-        <v>-370535.23809472017</v>
+        <v>46731.428571430035</v>
       </c>
       <c r="BC8" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.12611871629732568</v>
       </c>
       <c r="BE8" s="14"/>
       <c r="BF8" s="13" t="s">
@@ -2289,15 +2312,15 @@
       <c r="BH8" s="12"/>
       <c r="BI8" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-265</v>
       </c>
       <c r="BJ8" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK8" s="11" t="e">
+        <v>-417266.66666615021</v>
+      </c>
+      <c r="BK8" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM8" s="14"/>
       <c r="BN8" s="13" t="s">
@@ -2512,18 +2535,23 @@
       <c r="AX9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ9" s="12"/>
+      <c r="AY9" s="10">
+        <v>73</v>
+      </c>
+      <c r="AZ9" s="12">
+        <v>531685.71428561991</v>
+      </c>
       <c r="BA9" s="10">
         <f t="shared" si="11"/>
-        <v>-64</v>
+        <v>9</v>
       </c>
       <c r="BB9" s="12">
         <f t="shared" si="12"/>
-        <v>-456533.33333325997</v>
+        <v>75152.380952359934</v>
       </c>
       <c r="BC9" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.16461532042721672</v>
       </c>
       <c r="BE9" s="14"/>
       <c r="BF9" s="13" t="s">
@@ -2532,15 +2560,15 @@
       <c r="BH9" s="12"/>
       <c r="BI9" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-73</v>
       </c>
       <c r="BJ9" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK9" s="11" t="e">
+        <v>-531685.71428561991</v>
+      </c>
+      <c r="BK9" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM9" s="14"/>
       <c r="BN9" s="13" t="s">
@@ -2755,18 +2783,23 @@
       <c r="AX10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ10" s="12"/>
+      <c r="AY10" s="10">
+        <v>37</v>
+      </c>
+      <c r="AZ10" s="12">
+        <v>487333.33333317022</v>
+      </c>
       <c r="BA10" s="10">
         <f t="shared" si="11"/>
-        <v>-54</v>
+        <v>-17</v>
       </c>
       <c r="BB10" s="12">
         <f t="shared" si="12"/>
-        <v>-716761.90476172033</v>
+        <v>-229428.57142855012</v>
       </c>
       <c r="BC10" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.32009035344145575</v>
       </c>
       <c r="BE10" s="14"/>
       <c r="BF10" s="13" t="s">
@@ -2775,15 +2808,15 @@
       <c r="BH10" s="12"/>
       <c r="BI10" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-37</v>
       </c>
       <c r="BJ10" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK10" s="11" t="e">
+        <v>-487333.33333317022</v>
+      </c>
+      <c r="BK10" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM10" s="14"/>
       <c r="BN10" s="13" t="s">
@@ -2998,18 +3031,23 @@
       <c r="AX11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ11" s="12"/>
+      <c r="AY11" s="10">
+        <v>13</v>
+      </c>
+      <c r="AZ11" s="12">
+        <v>71080</v>
+      </c>
       <c r="BA11" s="10">
         <f t="shared" si="11"/>
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="BB11" s="12">
         <f t="shared" si="12"/>
-        <v>-67170</v>
+        <v>3910</v>
       </c>
       <c r="BC11" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>5.8210510644633021E-2</v>
       </c>
       <c r="BE11" s="14"/>
       <c r="BF11" s="13" t="s">
@@ -3018,15 +3056,15 @@
       <c r="BH11" s="12"/>
       <c r="BI11" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK11" s="11" t="e">
+        <v>-71080</v>
+      </c>
+      <c r="BK11" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM11" s="14"/>
       <c r="BN11" s="13" t="s">
@@ -3241,18 +3279,23 @@
       <c r="AX12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ12" s="12"/>
+      <c r="AY12" s="10">
+        <v>31</v>
+      </c>
+      <c r="AZ12" s="12">
+        <v>1534395.238095101</v>
+      </c>
       <c r="BA12" s="10">
         <f t="shared" si="11"/>
-        <v>-37</v>
+        <v>-6</v>
       </c>
       <c r="BB12" s="12">
         <f t="shared" si="12"/>
-        <v>-1971285.7142855099</v>
+        <v>-436890.47619040892</v>
       </c>
       <c r="BC12" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.22162717105103119</v>
       </c>
       <c r="BE12" s="14"/>
       <c r="BF12" s="13" t="s">
@@ -3261,15 +3304,15 @@
       <c r="BH12" s="12"/>
       <c r="BI12" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK12" s="11" t="e">
+        <v>-1534395.238095101</v>
+      </c>
+      <c r="BK12" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM12" s="14"/>
       <c r="BN12" s="13" t="s">
@@ -3484,18 +3527,23 @@
       <c r="AX13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ13" s="12"/>
+      <c r="AY13" s="10">
+        <v>53</v>
+      </c>
+      <c r="AZ13" s="12">
+        <v>1229714.2857141199</v>
+      </c>
       <c r="BA13" s="10">
         <f t="shared" si="11"/>
-        <v>-63</v>
+        <v>-10</v>
       </c>
       <c r="BB13" s="12">
         <f t="shared" si="12"/>
-        <v>-1626095.23809503</v>
+        <v>-396380.95238091005</v>
       </c>
       <c r="BC13" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.24376244582406514</v>
       </c>
       <c r="BE13" s="14"/>
       <c r="BF13" s="13" t="s">
@@ -3504,15 +3552,15 @@
       <c r="BH13" s="12"/>
       <c r="BI13" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="BJ13" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK13" s="11" t="e">
+        <v>-1229714.2857141199</v>
+      </c>
+      <c r="BK13" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM13" s="14"/>
       <c r="BN13" s="13" t="s">
@@ -3727,18 +3775,23 @@
       <c r="AX14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ14" s="12"/>
+      <c r="AY14" s="10">
+        <v>81</v>
+      </c>
+      <c r="AZ14" s="12">
+        <v>3206571.4285713299</v>
+      </c>
       <c r="BA14" s="10">
         <f t="shared" si="11"/>
-        <v>-105</v>
+        <v>-24</v>
       </c>
       <c r="BB14" s="12">
         <f t="shared" si="12"/>
-        <v>-4165238.0952379601</v>
+        <v>-958666.66666663019</v>
       </c>
       <c r="BC14" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.23015891162684221</v>
       </c>
       <c r="BE14" s="14"/>
       <c r="BF14" s="13" t="s">
@@ -3747,15 +3800,15 @@
       <c r="BH14" s="12"/>
       <c r="BI14" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-81</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK14" s="11" t="e">
+        <v>-3206571.4285713299</v>
+      </c>
+      <c r="BK14" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM14" s="14"/>
       <c r="BN14" s="13" t="s">
@@ -3968,22 +4021,26 @@
         <v>0.22174272734914438</v>
       </c>
       <c r="AW15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="AX15" s="9"/>
-      <c r="AY15" s="8"/>
-      <c r="AZ15" s="7"/>
+      <c r="AY15" s="8">
+        <v>753</v>
+      </c>
+      <c r="AZ15" s="7">
+        <v>7713406.6666645408</v>
+      </c>
       <c r="BA15" s="27">
         <f t="shared" si="11"/>
-        <v>-830</v>
+        <v>-77</v>
       </c>
       <c r="BB15" s="28">
         <f t="shared" si="12"/>
-        <v>-9656165.2380927801</v>
+        <v>-1942758.5714282393</v>
       </c>
       <c r="BC15" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.20119359223102523</v>
       </c>
       <c r="BE15" s="9" t="s">
         <v>18</v>
@@ -3993,15 +4050,15 @@
       <c r="BH15" s="7"/>
       <c r="BI15" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-753</v>
       </c>
       <c r="BJ15" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK15" s="29" t="e">
+        <v>-7713406.6666645408</v>
+      </c>
+      <c r="BK15" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM15" s="9" t="s">
         <v>18</v>
@@ -4222,7 +4279,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="AZ16" s="35"/>
       <c r="BA16" s="10">
@@ -4470,7 +4527,7 @@
       </c>
       <c r="AW17" s="14"/>
       <c r="AX17" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AZ17" s="35"/>
       <c r="BA17" s="10">
@@ -4719,18 +4776,23 @@
       <c r="AX18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ18" s="12"/>
+      <c r="AY18" s="10">
+        <v>111</v>
+      </c>
+      <c r="AZ18" s="12">
+        <v>115135.2380947101</v>
+      </c>
       <c r="BA18" s="10">
         <f t="shared" si="11"/>
-        <v>-133</v>
+        <v>-22</v>
       </c>
       <c r="BB18" s="12">
         <f t="shared" si="12"/>
-        <v>-128007.61904704</v>
+        <v>-12872.380952329899</v>
       </c>
       <c r="BC18" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.10055949050657352</v>
       </c>
       <c r="BE18" s="14"/>
       <c r="BF18" s="13" t="s">
@@ -4739,15 +4801,15 @@
       <c r="BH18" s="12"/>
       <c r="BI18" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-111</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK18" s="11" t="e">
+        <v>-115135.2380947101</v>
+      </c>
+      <c r="BK18" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM18" s="14"/>
       <c r="BN18" s="13" t="s">
@@ -4962,18 +5024,23 @@
       <c r="AX19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ19" s="12"/>
+      <c r="AY19" s="10">
+        <v>170</v>
+      </c>
+      <c r="AZ19" s="12">
+        <v>173704.76190436989</v>
+      </c>
       <c r="BA19" s="10">
         <f t="shared" si="11"/>
-        <v>-171</v>
+        <v>-1</v>
       </c>
       <c r="BB19" s="12">
         <f t="shared" si="12"/>
-        <v>-165000.95238059</v>
+        <v>8703.8095237798989</v>
       </c>
       <c r="BC19" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>5.2750056276667755E-2</v>
       </c>
       <c r="BE19" s="14"/>
       <c r="BF19" s="13" t="s">
@@ -4982,15 +5049,15 @@
       <c r="BH19" s="12"/>
       <c r="BI19" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK19" s="11" t="e">
+        <v>-173704.76190436989</v>
+      </c>
+      <c r="BK19" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM19" s="14"/>
       <c r="BN19" s="13" t="s">
@@ -5205,18 +5272,23 @@
       <c r="AX20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ20" s="12"/>
+      <c r="AY20" s="10">
+        <v>39</v>
+      </c>
+      <c r="AZ20" s="12">
+        <v>243914.28571423999</v>
+      </c>
       <c r="BA20" s="10">
         <f t="shared" si="11"/>
-        <v>-25</v>
+        <v>14</v>
       </c>
       <c r="BB20" s="12">
         <f t="shared" si="12"/>
-        <v>-161190.47619043</v>
+        <v>82723.809523809992</v>
       </c>
       <c r="BC20" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.51320531757769794</v>
       </c>
       <c r="BE20" s="14"/>
       <c r="BF20" s="13" t="s">
@@ -5225,15 +5297,15 @@
       <c r="BH20" s="12"/>
       <c r="BI20" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="BJ20" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK20" s="11" t="e">
+        <v>-243914.28571423999</v>
+      </c>
+      <c r="BK20" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM20" s="14"/>
       <c r="BN20" s="13" t="s">
@@ -5448,18 +5520,23 @@
       <c r="AX21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ21" s="12"/>
+      <c r="AY21" s="10">
+        <v>16</v>
+      </c>
+      <c r="AZ21" s="12">
+        <v>169904.76190467001</v>
+      </c>
       <c r="BA21" s="10">
         <f t="shared" si="11"/>
-        <v>-21</v>
+        <v>-5</v>
       </c>
       <c r="BB21" s="12">
         <f t="shared" si="12"/>
-        <v>-262476.19047610002</v>
+        <v>-92571.428571430006</v>
       </c>
       <c r="BC21" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.35268505079838536</v>
       </c>
       <c r="BE21" s="14"/>
       <c r="BF21" s="13" t="s">
@@ -5468,15 +5545,15 @@
       <c r="BH21" s="12"/>
       <c r="BI21" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK21" s="11" t="e">
+        <v>-169904.76190467001</v>
+      </c>
+      <c r="BK21" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM21" s="14"/>
       <c r="BN21" s="13" t="s">
@@ -5691,18 +5768,23 @@
       <c r="AX22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ22" s="12"/>
+      <c r="AY22" s="10">
+        <v>14</v>
+      </c>
+      <c r="AZ22" s="12">
+        <v>48220</v>
+      </c>
       <c r="BA22" s="10">
         <f t="shared" si="11"/>
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="BB22" s="12">
         <f t="shared" si="12"/>
-        <v>-73180</v>
+        <v>-24960</v>
       </c>
       <c r="BC22" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.34107679693905441</v>
       </c>
       <c r="BE22" s="14"/>
       <c r="BF22" s="13" t="s">
@@ -5711,15 +5793,15 @@
       <c r="BH22" s="12"/>
       <c r="BI22" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK22" s="11" t="e">
+        <v>-48220</v>
+      </c>
+      <c r="BK22" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM22" s="14"/>
       <c r="BN22" s="13" t="s">
@@ -5934,18 +6016,23 @@
       <c r="AX23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ23" s="12"/>
+      <c r="AY23" s="10">
+        <v>5</v>
+      </c>
+      <c r="AZ23" s="12">
+        <v>200395.23809520999</v>
+      </c>
       <c r="BA23" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="BB23" s="12">
         <f t="shared" si="12"/>
-        <v>-327357.14285708999</v>
+        <v>-126961.90476188</v>
       </c>
       <c r="BC23" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.3878391155720286</v>
       </c>
       <c r="BE23" s="14"/>
       <c r="BF23" s="13" t="s">
@@ -5954,15 +6041,15 @@
       <c r="BH23" s="12"/>
       <c r="BI23" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BJ23" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK23" s="11" t="e">
+        <v>-200395.23809520999</v>
+      </c>
+      <c r="BK23" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM23" s="14"/>
       <c r="BN23" s="13" t="s">
@@ -6177,18 +6264,23 @@
       <c r="AX24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ24" s="12"/>
+      <c r="AY24" s="10">
+        <v>13</v>
+      </c>
+      <c r="AZ24" s="12">
+        <v>258857.14285708999</v>
+      </c>
       <c r="BA24" s="10">
         <f t="shared" si="11"/>
-        <v>-24</v>
+        <v>-11</v>
       </c>
       <c r="BB24" s="12">
         <f t="shared" si="12"/>
-        <v>-609904.76190465991</v>
+        <v>-351047.61904756993</v>
       </c>
       <c r="BC24" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.57557776389757975</v>
       </c>
       <c r="BE24" s="14"/>
       <c r="BF24" s="13" t="s">
@@ -6197,15 +6289,15 @@
       <c r="BH24" s="12"/>
       <c r="BI24" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK24" s="11" t="e">
+        <v>-258857.14285708999</v>
+      </c>
+      <c r="BK24" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM24" s="14"/>
       <c r="BN24" s="13" t="s">
@@ -6420,18 +6512,23 @@
       <c r="AX25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ25" s="12"/>
+      <c r="AY25" s="10">
+        <v>40</v>
+      </c>
+      <c r="AZ25" s="12">
+        <v>1629523.80952367</v>
+      </c>
       <c r="BA25" s="10">
         <f t="shared" si="11"/>
-        <v>-57</v>
+        <v>-17</v>
       </c>
       <c r="BB25" s="12">
         <f t="shared" si="12"/>
-        <v>-2140285.7142856</v>
+        <v>-510761.90476193</v>
       </c>
       <c r="BC25" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.23864192586662</v>
       </c>
       <c r="BE25" s="14"/>
       <c r="BF25" s="13" t="s">
@@ -6440,15 +6537,15 @@
       <c r="BH25" s="12"/>
       <c r="BI25" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK25" s="11" t="e">
+        <v>-1629523.80952367</v>
+      </c>
+      <c r="BK25" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM25" s="14"/>
       <c r="BN25" s="13" t="s">
@@ -6664,19 +6761,23 @@
         <v>12</v>
       </c>
       <c r="AX26" s="9"/>
-      <c r="AY26" s="8"/>
-      <c r="AZ26" s="7"/>
+      <c r="AY26" s="8">
+        <v>408</v>
+      </c>
+      <c r="AZ26" s="7">
+        <v>2839655.2380939601</v>
+      </c>
       <c r="BA26" s="27">
         <f t="shared" si="11"/>
-        <v>-462</v>
+        <v>-54</v>
       </c>
       <c r="BB26" s="28">
         <f t="shared" si="12"/>
-        <v>-3867402.8571415101</v>
+        <v>-1027747.61904755</v>
       </c>
       <c r="BC26" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.26574620152377476</v>
       </c>
       <c r="BE26" s="9" t="s">
         <v>12</v>
@@ -6686,15 +6787,15 @@
       <c r="BH26" s="7"/>
       <c r="BI26" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-408</v>
       </c>
       <c r="BJ26" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK26" s="29" t="e">
+        <v>-2839655.2380939601</v>
+      </c>
+      <c r="BK26" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM26" s="9" t="s">
         <v>12</v>
@@ -6915,12 +7016,15 @@
         <v>77</v>
       </c>
       <c r="AX27" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="AY27" s="1">
+        <v>3174</v>
       </c>
       <c r="AZ27" s="35"/>
       <c r="BA27" s="10">
         <f t="shared" si="11"/>
-        <v>-3328</v>
+        <v>-154</v>
       </c>
       <c r="BB27" s="12">
         <f t="shared" si="12"/>
@@ -6939,7 +7043,7 @@
       <c r="BH27" s="35"/>
       <c r="BI27" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3174</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="15"/>
@@ -7163,7 +7267,7 @@
       </c>
       <c r="AW28" s="14"/>
       <c r="AX28" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AZ28" s="35"/>
       <c r="BA28" s="10">
@@ -7412,18 +7516,23 @@
       <c r="AX29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ29" s="12"/>
+      <c r="AY29" s="10">
+        <v>92</v>
+      </c>
+      <c r="AZ29" s="12">
+        <v>82476.19047580006</v>
+      </c>
       <c r="BA29" s="10">
         <f t="shared" si="11"/>
-        <v>-96</v>
+        <v>-4</v>
       </c>
       <c r="BB29" s="12">
         <f t="shared" si="12"/>
-        <v>-86227.619047240034</v>
+        <v>-3751.4285714399739</v>
       </c>
       <c r="BC29" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-4.3506113387924393E-2</v>
       </c>
       <c r="BE29" s="14"/>
       <c r="BF29" s="13" t="s">
@@ -7432,15 +7541,15 @@
       <c r="BH29" s="12"/>
       <c r="BI29" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK29" s="11" t="e">
+        <v>-82476.19047580006</v>
+      </c>
+      <c r="BK29" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM29" s="14"/>
       <c r="BN29" s="13" t="s">
@@ -7655,18 +7764,23 @@
       <c r="AX30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ30" s="12"/>
+      <c r="AY30" s="10">
+        <v>54</v>
+      </c>
+      <c r="AZ30" s="12">
+        <v>51580.952380770002</v>
+      </c>
       <c r="BA30" s="10">
         <f t="shared" si="11"/>
-        <v>-88</v>
+        <v>-34</v>
       </c>
       <c r="BB30" s="12">
         <f t="shared" si="12"/>
-        <v>-72116.190475950003</v>
+        <v>-20535.238095180001</v>
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.28475211959550595</v>
       </c>
       <c r="BE30" s="14"/>
       <c r="BF30" s="13" t="s">
@@ -7675,15 +7789,15 @@
       <c r="BH30" s="12"/>
       <c r="BI30" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK30" s="11" t="e">
+        <v>-51580.952380770002</v>
+      </c>
+      <c r="BK30" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM30" s="14"/>
       <c r="BN30" s="13" t="s">
@@ -7898,18 +8012,23 @@
       <c r="AX31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ31" s="12"/>
+      <c r="AY31" s="10">
+        <v>15</v>
+      </c>
+      <c r="AZ31" s="12">
+        <v>99024.761904739993</v>
+      </c>
       <c r="BA31" s="10">
         <f t="shared" si="11"/>
-        <v>-24</v>
+        <v>-9</v>
       </c>
       <c r="BB31" s="12">
         <f t="shared" si="12"/>
-        <v>-156914.28571423999</v>
+        <v>-57889.523809499995</v>
       </c>
       <c r="BC31" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.36892449623690643</v>
       </c>
       <c r="BE31" s="14"/>
       <c r="BF31" s="13" t="s">
@@ -7918,15 +8037,15 @@
       <c r="BH31" s="12"/>
       <c r="BI31" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK31" s="11" t="e">
+        <v>-99024.761904739993</v>
+      </c>
+      <c r="BK31" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM31" s="14"/>
       <c r="BN31" s="13" t="s">
@@ -8141,18 +8260,23 @@
       <c r="AX32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ32" s="12"/>
+      <c r="AY32" s="10">
+        <v>14</v>
+      </c>
+      <c r="AZ32" s="12">
+        <v>174285.71428565</v>
+      </c>
       <c r="BA32" s="10">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="BB32" s="12">
         <f t="shared" si="12"/>
-        <v>-99904.761904709987</v>
+        <v>74380.952380940013</v>
       </c>
       <c r="BC32" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.74451858913277025</v>
       </c>
       <c r="BE32" s="14"/>
       <c r="BF32" s="13" t="s">
@@ -8161,15 +8285,15 @@
       <c r="BH32" s="12"/>
       <c r="BI32" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK32" s="11" t="e">
+        <v>-174285.71428565</v>
+      </c>
+      <c r="BK32" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM32" s="14"/>
       <c r="BN32" s="13" t="s">
@@ -8384,14 +8508,19 @@
       <c r="AX33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ33" s="12"/>
+      <c r="AY33" s="10">
+        <v>2</v>
+      </c>
+      <c r="AZ33" s="12">
+        <v>18980</v>
+      </c>
       <c r="BA33" s="10">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB33" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>18980</v>
       </c>
       <c r="BC33" s="11" t="e">
         <f t="shared" si="13"/>
@@ -8404,15 +8533,15 @@
       <c r="BH33" s="12"/>
       <c r="BI33" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK33" s="11" t="e">
+        <v>-18980</v>
+      </c>
+      <c r="BK33" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM33" s="14"/>
       <c r="BN33" s="13" t="s">
@@ -8627,18 +8756,23 @@
       <c r="AX34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ34" s="12"/>
+      <c r="AY34" s="10">
+        <v>2</v>
+      </c>
+      <c r="AZ34" s="12">
+        <v>128735.23809523</v>
+      </c>
       <c r="BA34" s="10">
         <f t="shared" si="11"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BB34" s="12">
         <f t="shared" si="12"/>
-        <v>-49333.333333319999</v>
+        <v>79401.904761910002</v>
       </c>
       <c r="BC34" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>1.6094980694986107</v>
       </c>
       <c r="BE34" s="14"/>
       <c r="BF34" s="13" t="s">
@@ -8647,15 +8781,15 @@
       <c r="BH34" s="12"/>
       <c r="BI34" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ34" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK34" s="11" t="e">
+        <v>-128735.23809523</v>
+      </c>
+      <c r="BK34" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM34" s="14"/>
       <c r="BN34" s="13" t="s">
@@ -8870,18 +9004,23 @@
       <c r="AX35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ35" s="12"/>
+      <c r="AY35" s="10">
+        <v>3</v>
+      </c>
+      <c r="AZ35" s="12">
+        <v>52095.238095219996</v>
+      </c>
       <c r="BA35" s="10">
         <f t="shared" si="11"/>
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="BB35" s="12">
         <f t="shared" si="12"/>
-        <v>-359714.28571423999</v>
+        <v>-307619.04761901998</v>
       </c>
       <c r="BC35" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.85517606566060911</v>
       </c>
       <c r="BE35" s="14"/>
       <c r="BF35" s="13" t="s">
@@ -8890,15 +9029,15 @@
       <c r="BH35" s="12"/>
       <c r="BI35" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BJ35" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK35" s="11" t="e">
+        <v>-52095.238095219996</v>
+      </c>
+      <c r="BK35" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM35" s="14"/>
       <c r="BN35" s="13" t="s">
@@ -9113,18 +9252,23 @@
       <c r="AX36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ36" s="12"/>
+      <c r="AY36" s="10">
+        <v>16</v>
+      </c>
+      <c r="AZ36" s="12">
+        <v>648098.09523805999</v>
+      </c>
       <c r="BA36" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="BB36" s="12">
         <f t="shared" si="12"/>
-        <v>-352479.04761903</v>
+        <v>295619.04761903</v>
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.83868544702419867</v>
       </c>
       <c r="BE36" s="14"/>
       <c r="BF36" s="13" t="s">
@@ -9133,15 +9277,15 @@
       <c r="BH36" s="12"/>
       <c r="BI36" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK36" s="11" t="e">
+        <v>-648098.09523805999</v>
+      </c>
+      <c r="BK36" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM36" s="14"/>
       <c r="BN36" s="13" t="s">
@@ -9357,19 +9501,23 @@
         <v>11</v>
       </c>
       <c r="AX37" s="9"/>
-      <c r="AY37" s="8"/>
-      <c r="AZ37" s="7"/>
+      <c r="AY37" s="8">
+        <v>198</v>
+      </c>
+      <c r="AZ37" s="7">
+        <v>1255276.1904754699</v>
+      </c>
       <c r="BA37" s="27">
         <f t="shared" si="11"/>
-        <v>-241</v>
+        <v>-43</v>
       </c>
       <c r="BB37" s="28">
         <f t="shared" si="12"/>
-        <v>-1176689.5238087301</v>
+        <v>78586.666666739853</v>
       </c>
       <c r="BC37" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>6.6786238065899575E-2</v>
       </c>
       <c r="BE37" s="9" t="s">
         <v>11</v>
@@ -9379,15 +9527,15 @@
       <c r="BH37" s="7"/>
       <c r="BI37" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-198</v>
       </c>
       <c r="BJ37" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK37" s="29" t="e">
+        <v>-1255276.1904754699</v>
+      </c>
+      <c r="BK37" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM37" s="9" t="s">
         <v>11</v>
@@ -9608,12 +9756,15 @@
         <v>81</v>
       </c>
       <c r="AX38" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="AY38" s="1">
+        <v>1711</v>
       </c>
       <c r="AZ38" s="35"/>
       <c r="BA38" s="10">
         <f t="shared" si="11"/>
-        <v>-2066</v>
+        <v>-355</v>
       </c>
       <c r="BB38" s="12">
         <f t="shared" si="12"/>
@@ -9632,7 +9783,7 @@
       <c r="BH38" s="35"/>
       <c r="BI38" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-1711</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="15"/>
@@ -9856,7 +10007,7 @@
       </c>
       <c r="AW39" s="14"/>
       <c r="AX39" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AZ39" s="35"/>
       <c r="BA39" s="10">
@@ -10105,18 +10256,23 @@
       <c r="AX40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ40" s="12"/>
+      <c r="AY40" s="10">
+        <v>97</v>
+      </c>
+      <c r="AZ40" s="12">
+        <v>90916.190475729993</v>
+      </c>
       <c r="BA40" s="10">
         <f t="shared" si="11"/>
-        <v>-109</v>
+        <v>-12</v>
       </c>
       <c r="BB40" s="12">
         <f t="shared" si="12"/>
-        <v>-103550.4761899</v>
+        <v>-12634.285714170008</v>
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.12201088955882868</v>
       </c>
       <c r="BE40" s="14"/>
       <c r="BF40" s="13" t="s">
@@ -10125,15 +10281,15 @@
       <c r="BH40" s="12"/>
       <c r="BI40" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-97</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK40" s="11" t="e">
+        <v>-90916.190475729993</v>
+      </c>
+      <c r="BK40" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM40" s="14"/>
       <c r="BN40" s="13" t="s">
@@ -10348,18 +10504,23 @@
       <c r="AX41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ41" s="12"/>
+      <c r="AY41" s="10">
+        <v>64</v>
+      </c>
+      <c r="AZ41" s="12">
+        <v>71868.571428339987</v>
+      </c>
       <c r="BA41" s="10">
         <f t="shared" si="11"/>
-        <v>-79</v>
+        <v>-15</v>
       </c>
       <c r="BB41" s="12">
         <f t="shared" si="12"/>
-        <v>-104352.38095211</v>
+        <v>-32483.809523770018</v>
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.31128958656609546</v>
       </c>
       <c r="BE41" s="14"/>
       <c r="BF41" s="13" t="s">
@@ -10368,15 +10529,15 @@
       <c r="BH41" s="12"/>
       <c r="BI41" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-64</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK41" s="11" t="e">
+        <v>-71868.571428339987</v>
+      </c>
+      <c r="BK41" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM41" s="14"/>
       <c r="BN41" s="13" t="s">
@@ -10591,18 +10752,23 @@
       <c r="AX42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ42" s="12"/>
+      <c r="AY42" s="10">
+        <v>12</v>
+      </c>
+      <c r="AZ42" s="12">
+        <v>94171.4285714</v>
+      </c>
       <c r="BA42" s="10">
         <f t="shared" si="11"/>
-        <v>-22</v>
+        <v>-10</v>
       </c>
       <c r="BB42" s="12">
         <f t="shared" si="12"/>
-        <v>-154076.19047616</v>
+        <v>-59904.761904760002</v>
       </c>
       <c r="BC42" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.38879960440110301</v>
       </c>
       <c r="BE42" s="14"/>
       <c r="BF42" s="13" t="s">
@@ -10611,15 +10777,15 @@
       <c r="BH42" s="12"/>
       <c r="BI42" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK42" s="11" t="e">
+        <v>-94171.4285714</v>
+      </c>
+      <c r="BK42" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM42" s="14"/>
       <c r="BN42" s="13" t="s">
@@ -10834,18 +11000,23 @@
       <c r="AX43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ43" s="12"/>
+      <c r="AY43" s="10">
+        <v>5</v>
+      </c>
+      <c r="AZ43" s="12">
+        <v>54761.904761880003</v>
+      </c>
       <c r="BA43" s="10">
         <f t="shared" si="11"/>
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="BB43" s="12">
         <f t="shared" si="12"/>
-        <v>-109333.33333331</v>
+        <v>-54571.428571429999</v>
       </c>
       <c r="BC43" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.49912891986074676</v>
       </c>
       <c r="BE43" s="14"/>
       <c r="BF43" s="13" t="s">
@@ -10854,15 +11025,15 @@
       <c r="BH43" s="12"/>
       <c r="BI43" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK43" s="11" t="e">
+        <v>-54761.904761880003</v>
+      </c>
+      <c r="BK43" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM43" s="14"/>
       <c r="BN43" s="13" t="s">
@@ -11077,7 +11248,12 @@
       <c r="AX44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ44" s="12"/>
+      <c r="AY44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="12">
+        <v>0</v>
+      </c>
       <c r="BA44" s="10">
         <f t="shared" si="11"/>
         <v>-3</v>
@@ -11321,18 +11497,23 @@
       <c r="AX45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ45" s="12"/>
+      <c r="AY45" s="10">
+        <v>2</v>
+      </c>
+      <c r="AZ45" s="12">
+        <v>46476.190476180003</v>
+      </c>
       <c r="BA45" s="10">
         <f t="shared" si="11"/>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="BB45" s="12">
         <f t="shared" si="12"/>
-        <v>-261334.28571425</v>
+        <v>-214858.09523807</v>
       </c>
       <c r="BC45" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.82215808251429234</v>
       </c>
       <c r="BE45" s="14"/>
       <c r="BF45" s="13" t="s">
@@ -11341,15 +11522,15 @@
       <c r="BH45" s="12"/>
       <c r="BI45" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK45" s="11" t="e">
+        <v>-46476.190476180003</v>
+      </c>
+      <c r="BK45" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM45" s="14"/>
       <c r="BN45" s="13" t="s">
@@ -11565,18 +11746,23 @@
       <c r="AX46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ46" s="12"/>
+      <c r="AY46" s="10">
+        <v>7</v>
+      </c>
+      <c r="AZ46" s="12">
+        <v>201142.85714281999</v>
+      </c>
       <c r="BA46" s="10">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="BB46" s="12">
         <f t="shared" si="12"/>
-        <v>-179333.33333329999</v>
+        <v>21809.523809520004</v>
       </c>
       <c r="BC46" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.12161444503452078</v>
       </c>
       <c r="BE46" s="14"/>
       <c r="BF46" s="13" t="s">
@@ -11585,15 +11771,15 @@
       <c r="BH46" s="12"/>
       <c r="BI46" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BJ46" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK46" s="11" t="e">
+        <v>-201142.85714281999</v>
+      </c>
+      <c r="BK46" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM46" s="14"/>
       <c r="BN46" s="13" t="s">
@@ -11809,18 +11995,23 @@
       <c r="AX47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ47" s="12"/>
+      <c r="AY47" s="10">
+        <v>16</v>
+      </c>
+      <c r="AZ47" s="12">
+        <v>650857.14285712002</v>
+      </c>
       <c r="BA47" s="10">
         <f t="shared" si="11"/>
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="BB47" s="12">
         <f t="shared" si="12"/>
-        <v>-922476.19047615991</v>
+        <v>-271619.04761903989</v>
       </c>
       <c r="BC47" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.29444559157547112</v>
       </c>
       <c r="BE47" s="14"/>
       <c r="BF47" s="13" t="s">
@@ -11829,15 +12020,15 @@
       <c r="BH47" s="12"/>
       <c r="BI47" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BJ47" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK47" s="11" t="e">
+        <v>-650857.14285712002</v>
+      </c>
+      <c r="BK47" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM47" s="14"/>
       <c r="BN47" s="13" t="s">
@@ -12054,19 +12245,23 @@
         <v>10</v>
       </c>
       <c r="AX48" s="9"/>
-      <c r="AY48" s="8"/>
-      <c r="AZ48" s="7"/>
+      <c r="AY48" s="8">
+        <v>203</v>
+      </c>
+      <c r="AZ48" s="7">
+        <v>1210194.2857134701</v>
+      </c>
       <c r="BA48" s="27">
         <f t="shared" si="11"/>
-        <v>-263</v>
+        <v>-60</v>
       </c>
       <c r="BB48" s="28">
         <f t="shared" si="12"/>
-        <v>-1843946.1904751901</v>
+        <v>-633751.90476171998</v>
       </c>
       <c r="BC48" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.34369327480125672</v>
       </c>
       <c r="BE48" s="9" t="s">
         <v>10</v>
@@ -12076,15 +12271,15 @@
       <c r="BH48" s="7"/>
       <c r="BI48" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-203</v>
       </c>
       <c r="BJ48" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK48" s="29" t="e">
+        <v>-1210194.2857134701</v>
+      </c>
+      <c r="BK48" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM48" s="9" t="s">
         <v>10</v>
@@ -12288,7 +12483,7 @@
         <v>84</v>
       </c>
       <c r="AX49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="AZ49" s="35"/>
       <c r="BA49" s="10">
@@ -12536,7 +12731,7 @@
       </c>
       <c r="AW50" s="14"/>
       <c r="AX50" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AZ50" s="35"/>
       <c r="BA50" s="10">
@@ -12785,18 +12980,23 @@
       <c r="AX51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AZ51" s="12"/>
+      <c r="AY51" s="10">
+        <v>112</v>
+      </c>
+      <c r="AZ51" s="12">
+        <v>111609.52380893</v>
+      </c>
       <c r="BA51" s="10">
         <f t="shared" si="11"/>
-        <v>-104</v>
+        <v>8</v>
       </c>
       <c r="BB51" s="12">
         <f t="shared" si="12"/>
-        <v>-107172.38095183999</v>
+        <v>4437.1428570900025</v>
       </c>
       <c r="BC51" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>4.1401924802658994E-2</v>
       </c>
       <c r="BE51" s="14"/>
       <c r="BF51" s="13" t="s">
@@ -12805,15 +13005,15 @@
       <c r="BH51" s="12"/>
       <c r="BI51" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-112</v>
       </c>
       <c r="BJ51" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK51" s="11" t="e">
+        <v>-111609.52380893</v>
+      </c>
+      <c r="BK51" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM51" s="14"/>
       <c r="BN51" s="13" t="s">
@@ -13028,18 +13228,23 @@
       <c r="AX52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AZ52" s="12"/>
+      <c r="AY52" s="10">
+        <v>68</v>
+      </c>
+      <c r="AZ52" s="12">
+        <v>67161.904761679994</v>
+      </c>
       <c r="BA52" s="10">
         <f t="shared" si="11"/>
-        <v>-62</v>
+        <v>6</v>
       </c>
       <c r="BB52" s="12">
         <f t="shared" si="12"/>
-        <v>-71790.476190239991</v>
+        <v>-4628.571428559997</v>
       </c>
       <c r="BC52" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-6.4473335102202003E-2</v>
       </c>
       <c r="BE52" s="14"/>
       <c r="BF52" s="13" t="s">
@@ -13048,15 +13253,15 @@
       <c r="BH52" s="12"/>
       <c r="BI52" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="BJ52" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK52" s="11" t="e">
+        <v>-67161.904761679994</v>
+      </c>
+      <c r="BK52" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM52" s="14"/>
       <c r="BN52" s="13" t="s">
@@ -13271,18 +13476,23 @@
       <c r="AX53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AZ53" s="12"/>
+      <c r="AY53" s="10">
+        <v>11</v>
+      </c>
+      <c r="AZ53" s="12">
+        <v>62752.380952359992</v>
+      </c>
       <c r="BA53" s="10">
         <f t="shared" si="11"/>
-        <v>-16</v>
+        <v>-5</v>
       </c>
       <c r="BB53" s="12">
         <f t="shared" si="12"/>
-        <v>-92704.761904729981</v>
+        <v>-29952.380952369989</v>
       </c>
       <c r="BC53" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.32309430860899241</v>
       </c>
       <c r="BE53" s="14"/>
       <c r="BF53" s="13" t="s">
@@ -13291,15 +13501,15 @@
       <c r="BH53" s="12"/>
       <c r="BI53" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BJ53" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK53" s="11" t="e">
+        <v>-62752.380952359992</v>
+      </c>
+      <c r="BK53" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM53" s="14"/>
       <c r="BN53" s="13" t="s">
@@ -13514,18 +13724,23 @@
       <c r="AX54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AZ54" s="12"/>
+      <c r="AY54" s="10">
+        <v>8</v>
+      </c>
+      <c r="AZ54" s="12">
+        <v>92571.428571390003</v>
+      </c>
       <c r="BA54" s="10">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="BB54" s="12">
         <f t="shared" si="12"/>
-        <v>-187142.85714278999</v>
+        <v>-94571.428571399985</v>
       </c>
       <c r="BC54" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.50534351145041023</v>
       </c>
       <c r="BE54" s="14"/>
       <c r="BF54" s="13" t="s">
@@ -13534,15 +13749,15 @@
       <c r="BH54" s="12"/>
       <c r="BI54" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BJ54" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK54" s="11" t="e">
+        <v>-92571.428571390003</v>
+      </c>
+      <c r="BK54" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM54" s="14"/>
       <c r="BN54" s="13" t="s">
@@ -13757,18 +13972,23 @@
       <c r="AX55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AZ55" s="12"/>
+      <c r="AY55" s="10">
+        <v>6</v>
+      </c>
+      <c r="AZ55" s="12">
+        <v>14840</v>
+      </c>
       <c r="BA55" s="10">
         <f t="shared" si="11"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="BB55" s="12">
         <f t="shared" si="12"/>
-        <v>-27550</v>
+        <v>-12710</v>
       </c>
       <c r="BC55" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.46134301270417422</v>
       </c>
       <c r="BE55" s="14"/>
       <c r="BF55" s="13" t="s">
@@ -13777,15 +13997,15 @@
       <c r="BH55" s="12"/>
       <c r="BI55" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BJ55" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK55" s="11" t="e">
+        <v>-14840</v>
+      </c>
+      <c r="BK55" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM55" s="14"/>
       <c r="BN55" s="13" t="s">
@@ -14001,18 +14221,23 @@
       <c r="AX56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AZ56" s="12"/>
+      <c r="AY56" s="10">
+        <v>6</v>
+      </c>
+      <c r="AZ56" s="12">
+        <v>383238.09523805999</v>
+      </c>
       <c r="BA56" s="10">
         <f t="shared" si="11"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="BB56" s="12">
         <f t="shared" si="12"/>
-        <v>-217819.04761902001</v>
+        <v>165419.04761903998</v>
       </c>
       <c r="BC56" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.75943334353554282</v>
       </c>
       <c r="BE56" s="14"/>
       <c r="BF56" s="13" t="s">
@@ -14021,15 +14246,15 @@
       <c r="BH56" s="12"/>
       <c r="BI56" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BJ56" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK56" s="11" t="e">
+        <v>-383238.09523805999</v>
+      </c>
+      <c r="BK56" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM56" s="14"/>
       <c r="BN56" s="13" t="s">
@@ -14245,18 +14470,23 @@
       <c r="AX57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AZ57" s="12"/>
+      <c r="AY57" s="10">
+        <v>8</v>
+      </c>
+      <c r="AZ57" s="12">
+        <v>200666.66666662</v>
+      </c>
       <c r="BA57" s="10">
         <f t="shared" si="11"/>
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="BB57" s="12">
         <f t="shared" si="12"/>
-        <v>-341619.04761898</v>
+        <v>-140952.38095235999</v>
       </c>
       <c r="BC57" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.41260105938111874</v>
       </c>
       <c r="BE57" s="14"/>
       <c r="BF57" s="13" t="s">
@@ -14265,15 +14495,15 @@
       <c r="BH57" s="12"/>
       <c r="BI57" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BJ57" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK57" s="11" t="e">
+        <v>-200666.66666662</v>
+      </c>
+      <c r="BK57" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM57" s="14"/>
       <c r="BN57" s="13" t="s">
@@ -14489,18 +14719,23 @@
       <c r="AX58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AZ58" s="12"/>
+      <c r="AY58" s="10">
+        <v>19</v>
+      </c>
+      <c r="AZ58" s="12">
+        <v>773428.57142853003</v>
+      </c>
       <c r="BA58" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="BB58" s="12">
         <f t="shared" si="12"/>
-        <v>-387619.04761901998</v>
+        <v>385809.52380951005</v>
       </c>
       <c r="BC58" s="11">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.99533169533173083</v>
       </c>
       <c r="BE58" s="14"/>
       <c r="BF58" s="13" t="s">
@@ -14509,15 +14744,15 @@
       <c r="BH58" s="12"/>
       <c r="BI58" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="BJ58" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK58" s="11" t="e">
+        <v>-773428.57142853003</v>
+      </c>
+      <c r="BK58" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM58" s="14"/>
       <c r="BN58" s="13" t="s">
@@ -14734,19 +14969,23 @@
         <v>1</v>
       </c>
       <c r="AX59" s="9"/>
-      <c r="AY59" s="8"/>
-      <c r="AZ59" s="7"/>
+      <c r="AY59" s="8">
+        <v>238</v>
+      </c>
+      <c r="AZ59" s="7">
+        <v>1706268.57142757</v>
+      </c>
       <c r="BA59" s="27">
         <f t="shared" si="11"/>
-        <v>-230</v>
+        <v>8</v>
       </c>
       <c r="BB59" s="28">
         <f t="shared" si="12"/>
-        <v>-1433417.6190466201</v>
+        <v>272850.95238094986</v>
       </c>
       <c r="BC59" s="29">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>0.19034993623311652</v>
       </c>
       <c r="BE59" s="9" t="s">
         <v>1</v>
@@ -14756,15 +14995,15 @@
       <c r="BH59" s="7"/>
       <c r="BI59" s="27">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-238</v>
       </c>
       <c r="BJ59" s="28">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK59" s="29" t="e">
+        <v>-1706268.57142757</v>
+      </c>
+      <c r="BK59" s="29">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM59" s="9" t="s">
         <v>1</v>
@@ -14985,19 +15224,23 @@
         <v>0</v>
       </c>
       <c r="AX60" s="4"/>
-      <c r="AY60" s="3"/>
-      <c r="AZ60" s="2"/>
+      <c r="AY60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AZ60" s="2">
+        <v>14724800.95237501</v>
+      </c>
       <c r="BA60" s="6">
         <f t="shared" si="11"/>
-        <v>-2026</v>
+        <v>-226</v>
       </c>
       <c r="BB60" s="5">
         <f t="shared" si="12"/>
-        <v>-17977621.428564832</v>
+        <v>-3252820.476189822</v>
       </c>
       <c r="BC60" s="30">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>-0.18093719956864712</v>
       </c>
       <c r="BE60" s="4" t="s">
         <v>0</v>
@@ -15007,15 +15250,15 @@
       <c r="BH60" s="2"/>
       <c r="BI60" s="6">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="BJ60" s="5">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BK60" s="30" t="e">
+        <v>-14724800.95237501</v>
+      </c>
+      <c r="BK60" s="30">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BM60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C20A83-1088-5E48-BB9E-60857A7BAE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E6CAB1-E858-8642-91D0-DB316993965C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -4281,10 +4281,13 @@
       <c r="AX16" s="32" t="s">
         <v>37</v>
       </c>
+      <c r="AY16" s="1">
+        <v>3746</v>
+      </c>
       <c r="AZ16" s="35"/>
       <c r="BA16" s="10">
         <f t="shared" si="11"/>
-        <v>-4138</v>
+        <v>-392</v>
       </c>
       <c r="BB16" s="12">
         <f t="shared" si="12"/>
@@ -4303,7 +4306,7 @@
       <c r="BH16" s="35"/>
       <c r="BI16" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3746</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="15"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E6CAB1-E858-8642-91D0-DB316993965C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6270E07E-922E-874E-B476-F1917C1254AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1796,10 +1796,13 @@
       <c r="AX6" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AY6" s="15">
+        <v>18</v>
+      </c>
       <c r="AZ6" s="33"/>
       <c r="BA6" s="10">
         <f t="shared" si="11"/>
-        <v>-16</v>
+        <v>2</v>
       </c>
       <c r="BB6" s="12">
         <f t="shared" si="12"/>
@@ -1816,7 +1819,7 @@
       <c r="BH6" s="33"/>
       <c r="BI6" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="BJ6" s="12">
         <f t="shared" si="15"/>
@@ -4532,10 +4535,13 @@
       <c r="AX17" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AY17" s="1">
+        <v>10</v>
+      </c>
       <c r="AZ17" s="35"/>
       <c r="BA17" s="10">
         <f t="shared" si="11"/>
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="BB17" s="12">
         <f t="shared" si="12"/>
@@ -4552,7 +4558,7 @@
       <c r="BH17" s="35"/>
       <c r="BI17" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="15"/>
@@ -7272,10 +7278,13 @@
       <c r="AX28" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AY28" s="1">
+        <v>4</v>
+      </c>
       <c r="AZ28" s="35"/>
       <c r="BA28" s="10">
         <f t="shared" si="11"/>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="BB28" s="12">
         <f t="shared" si="12"/>
@@ -7292,7 +7301,7 @@
       <c r="BH28" s="35"/>
       <c r="BI28" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="15"/>
@@ -10012,10 +10021,13 @@
       <c r="AX39" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AY39" s="1">
+        <v>2</v>
+      </c>
       <c r="AZ39" s="35"/>
       <c r="BA39" s="10">
         <f t="shared" si="11"/>
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="BB39" s="12">
         <f t="shared" si="12"/>
@@ -10032,7 +10044,7 @@
       <c r="BH39" s="35"/>
       <c r="BI39" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BJ39" s="12">
         <f t="shared" si="15"/>
@@ -12736,10 +12748,13 @@
       <c r="AX50" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="AY50" s="1">
+        <v>3</v>
+      </c>
       <c r="AZ50" s="35"/>
       <c r="BA50" s="10">
         <f t="shared" si="11"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="BB50" s="12">
         <f t="shared" si="12"/>
@@ -12756,7 +12771,7 @@
       <c r="BH50" s="35"/>
       <c r="BI50" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BJ50" s="12">
         <f t="shared" si="15"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6270E07E-922E-874E-B476-F1917C1254AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B71B2F5-EE14-4E44-B717-75C55BE76F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="44">
   <si>
     <t>總計</t>
   </si>
@@ -216,6 +216,12 @@
   <si>
     <t>08/09-08/15</t>
   </si>
+  <si>
+    <t>26Q4W8</t>
+  </si>
+  <si>
+    <t>08/16-08/22</t>
+  </si>
 </sst>
 </file>
 
@@ -224,7 +230,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -363,6 +369,19 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -420,7 +439,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -578,6 +597,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1031,7 +1056,9 @@
       </c>
       <c r="AX1" s="26"/>
       <c r="AZ1" s="25"/>
-      <c r="BE1" s="26"/>
+      <c r="BE1" s="53" t="s">
+        <v>42</v>
+      </c>
       <c r="BF1" s="26"/>
       <c r="BH1" s="25"/>
       <c r="BM1" s="26"/>
@@ -1090,6 +1117,9 @@
       <c r="AY2" s="22"/>
       <c r="AZ2" s="22"/>
       <c r="BB2" s="21"/>
+      <c r="BE2" s="54" t="s">
+        <v>43</v>
+      </c>
       <c r="BG2" s="22"/>
       <c r="BH2" s="22"/>
       <c r="BJ2" s="21"/>
@@ -1560,11 +1590,13 @@
       <c r="BF5" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="BG5" s="40"/>
+      <c r="BG5" s="40">
+        <v>5656</v>
+      </c>
       <c r="BH5" s="1"/>
       <c r="BI5" s="10">
         <f t="shared" ref="BI5:BI60" si="14">BG5-AY5</f>
-        <v>-6235</v>
+        <v>-579</v>
       </c>
       <c r="BJ5" s="12">
         <f t="shared" ref="BJ5:BJ60" si="15">BH5-AZ5</f>
@@ -1585,7 +1617,7 @@
       <c r="BP5" s="1"/>
       <c r="BQ5" s="10">
         <f t="shared" ref="BQ5:BQ60" si="17">BO5-BG5</f>
-        <v>0</v>
+        <v>-5656</v>
       </c>
       <c r="BR5" s="12">
         <f t="shared" ref="BR5:BR60" si="18">BP5-BH5</f>
@@ -2064,18 +2096,23 @@
       <c r="BF7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH7" s="12"/>
+      <c r="BG7" s="10">
+        <v>170</v>
+      </c>
+      <c r="BH7" s="12">
+        <v>174014.28571349999</v>
+      </c>
       <c r="BI7" s="10">
         <f t="shared" si="14"/>
-        <v>-200</v>
+        <v>-30</v>
       </c>
       <c r="BJ7" s="12">
         <f t="shared" si="15"/>
-        <v>-235359.99999904991</v>
+        <v>-61345.714285549911</v>
       </c>
       <c r="BK7" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.26064630474930978</v>
       </c>
       <c r="BM7" s="14"/>
       <c r="BN7" s="13" t="s">
@@ -2084,15 +2121,15 @@
       <c r="BP7" s="12"/>
       <c r="BQ7" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="BR7" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS7" s="11" t="e">
+        <v>-174014.28571349999</v>
+      </c>
+      <c r="BS7" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU7" s="14"/>
       <c r="BV7" s="13" t="s">
@@ -2312,18 +2349,23 @@
       <c r="BF8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH8" s="12"/>
+      <c r="BG8" s="10">
+        <v>263</v>
+      </c>
+      <c r="BH8" s="12">
+        <v>314315.23809473001</v>
+      </c>
       <c r="BI8" s="10">
         <f t="shared" si="14"/>
-        <v>-265</v>
+        <v>-2</v>
       </c>
       <c r="BJ8" s="12">
         <f t="shared" si="15"/>
-        <v>-417266.66666615021</v>
+        <v>-102951.4285714202</v>
       </c>
       <c r="BK8" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.24672814005004223</v>
       </c>
       <c r="BM8" s="14"/>
       <c r="BN8" s="13" t="s">
@@ -2332,15 +2374,15 @@
       <c r="BP8" s="12"/>
       <c r="BQ8" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-263</v>
       </c>
       <c r="BR8" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS8" s="11" t="e">
+        <v>-314315.23809473001</v>
+      </c>
+      <c r="BS8" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU8" s="14"/>
       <c r="BV8" s="13" t="s">
@@ -2560,18 +2602,23 @@
       <c r="BF9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH9" s="12"/>
+      <c r="BG9" s="10">
+        <v>68</v>
+      </c>
+      <c r="BH9" s="12">
+        <v>467447.61904753</v>
+      </c>
       <c r="BI9" s="10">
         <f t="shared" si="14"/>
-        <v>-73</v>
+        <v>-5</v>
       </c>
       <c r="BJ9" s="12">
         <f t="shared" si="15"/>
-        <v>-531685.71428561991</v>
+        <v>-64238.095238089911</v>
       </c>
       <c r="BK9" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.12081967506763104</v>
       </c>
       <c r="BM9" s="14"/>
       <c r="BN9" s="13" t="s">
@@ -2580,15 +2627,15 @@
       <c r="BP9" s="12"/>
       <c r="BQ9" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="BR9" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS9" s="11" t="e">
+        <v>-467447.61904753</v>
+      </c>
+      <c r="BS9" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="13" t="s">
@@ -2808,18 +2855,23 @@
       <c r="BF10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BH10" s="12"/>
+      <c r="BG10" s="10">
+        <v>20</v>
+      </c>
+      <c r="BH10" s="12">
+        <v>222857.14285706001</v>
+      </c>
       <c r="BI10" s="10">
         <f t="shared" si="14"/>
-        <v>-37</v>
+        <v>-17</v>
       </c>
       <c r="BJ10" s="12">
         <f t="shared" si="15"/>
-        <v>-487333.33333317022</v>
+        <v>-264476.19047611021</v>
       </c>
       <c r="BK10" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.54270080125074982</v>
       </c>
       <c r="BM10" s="14"/>
       <c r="BN10" s="13" t="s">
@@ -2828,15 +2880,15 @@
       <c r="BP10" s="12"/>
       <c r="BQ10" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BR10" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS10" s="11" t="e">
+        <v>-222857.14285706001</v>
+      </c>
+      <c r="BS10" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU10" s="14"/>
       <c r="BV10" s="13" t="s">
@@ -3056,18 +3108,23 @@
       <c r="BF11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH11" s="12"/>
+      <c r="BG11" s="10">
+        <v>8</v>
+      </c>
+      <c r="BH11" s="12">
+        <v>58120</v>
+      </c>
       <c r="BI11" s="10">
         <f t="shared" si="14"/>
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" si="15"/>
-        <v>-71080</v>
+        <v>-12960</v>
       </c>
       <c r="BK11" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.18232976927405739</v>
       </c>
       <c r="BM11" s="14"/>
       <c r="BN11" s="13" t="s">
@@ -3076,15 +3133,15 @@
       <c r="BP11" s="12"/>
       <c r="BQ11" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BR11" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS11" s="11" t="e">
+        <v>-58120</v>
+      </c>
+      <c r="BS11" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU11" s="14"/>
       <c r="BV11" s="13" t="s">
@@ -3304,18 +3361,23 @@
       <c r="BF12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH12" s="12"/>
+      <c r="BG12" s="10">
+        <v>21</v>
+      </c>
+      <c r="BH12" s="12">
+        <v>943204.76190464001</v>
+      </c>
       <c r="BI12" s="10">
         <f t="shared" si="14"/>
-        <v>-31</v>
+        <v>-10</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="15"/>
-        <v>-1534395.238095101</v>
+        <v>-591190.47619046096</v>
       </c>
       <c r="BK12" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.38529217343270933</v>
       </c>
       <c r="BM12" s="14"/>
       <c r="BN12" s="13" t="s">
@@ -3324,15 +3386,15 @@
       <c r="BP12" s="12"/>
       <c r="BQ12" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="BR12" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS12" s="11" t="e">
+        <v>-943204.76190464001</v>
+      </c>
+      <c r="BS12" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU12" s="14"/>
       <c r="BV12" s="13" t="s">
@@ -3552,18 +3614,23 @@
       <c r="BF13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH13" s="12"/>
+      <c r="BG13" s="10">
+        <v>29</v>
+      </c>
+      <c r="BH13" s="12">
+        <v>671523.80952368001</v>
+      </c>
       <c r="BI13" s="10">
         <f t="shared" si="14"/>
-        <v>-53</v>
+        <v>-24</v>
       </c>
       <c r="BJ13" s="12">
         <f t="shared" si="15"/>
-        <v>-1229714.2857141199</v>
+        <v>-558190.47619043989</v>
       </c>
       <c r="BK13" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.45391883519210108</v>
       </c>
       <c r="BM13" s="14"/>
       <c r="BN13" s="13" t="s">
@@ -3572,15 +3639,15 @@
       <c r="BP13" s="12"/>
       <c r="BQ13" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="BR13" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS13" s="11" t="e">
+        <v>-671523.80952368001</v>
+      </c>
+      <c r="BS13" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU13" s="14"/>
       <c r="BV13" s="13" t="s">
@@ -3800,18 +3867,23 @@
       <c r="BF14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH14" s="12"/>
+      <c r="BG14" s="10">
+        <v>41</v>
+      </c>
+      <c r="BH14" s="12">
+        <v>1441809.52380946</v>
+      </c>
       <c r="BI14" s="10">
         <f t="shared" si="14"/>
-        <v>-81</v>
+        <v>-40</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="15"/>
-        <v>-3206571.4285713299</v>
+        <v>-1764761.9047618699</v>
       </c>
       <c r="BK14" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.55035789598741292</v>
       </c>
       <c r="BM14" s="14"/>
       <c r="BN14" s="13" t="s">
@@ -3820,15 +3892,15 @@
       <c r="BP14" s="12"/>
       <c r="BQ14" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="BR14" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS14" s="11" t="e">
+        <v>-1441809.52380946</v>
+      </c>
+      <c r="BS14" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU14" s="14"/>
       <c r="BV14" s="13" t="s">
@@ -4049,19 +4121,23 @@
         <v>18</v>
       </c>
       <c r="BF15" s="9"/>
-      <c r="BG15" s="8"/>
-      <c r="BH15" s="7"/>
+      <c r="BG15" s="8">
+        <v>620</v>
+      </c>
+      <c r="BH15" s="7">
+        <v>4293292.3809505999</v>
+      </c>
       <c r="BI15" s="27">
         <f t="shared" si="14"/>
-        <v>-753</v>
+        <v>-133</v>
       </c>
       <c r="BJ15" s="28">
         <f t="shared" si="15"/>
-        <v>-7713406.6666645408</v>
+        <v>-3420114.2857139409</v>
       </c>
       <c r="BK15" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.44339867370079672</v>
       </c>
       <c r="BM15" s="9" t="s">
         <v>18</v>
@@ -4071,15 +4147,15 @@
       <c r="BP15" s="7"/>
       <c r="BQ15" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-620</v>
       </c>
       <c r="BR15" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS15" s="29" t="e">
+        <v>-4293292.3809505999</v>
+      </c>
+      <c r="BS15" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU15" s="9" t="s">
         <v>18</v>
@@ -4306,10 +4382,13 @@
       <c r="BF16" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="BG16" s="1">
+        <v>3813</v>
+      </c>
       <c r="BH16" s="35"/>
       <c r="BI16" s="10">
         <f t="shared" si="14"/>
-        <v>-3746</v>
+        <v>67</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="15"/>
@@ -4328,7 +4407,7 @@
       <c r="BP16" s="35"/>
       <c r="BQ16" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3813</v>
       </c>
       <c r="BR16" s="12">
         <f t="shared" si="18"/>
@@ -4807,18 +4886,23 @@
       <c r="BF18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH18" s="12"/>
+      <c r="BG18" s="10">
+        <v>124</v>
+      </c>
+      <c r="BH18" s="12">
+        <v>122476.19047563001</v>
+      </c>
       <c r="BI18" s="10">
         <f t="shared" si="14"/>
-        <v>-111</v>
+        <v>13</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="15"/>
-        <v>-115135.2380947101</v>
+        <v>7340.9523809199018</v>
       </c>
       <c r="BK18" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>6.375938854515803E-2</v>
       </c>
       <c r="BM18" s="14"/>
       <c r="BN18" s="13" t="s">
@@ -4827,15 +4911,15 @@
       <c r="BP18" s="12"/>
       <c r="BQ18" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="BR18" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS18" s="11" t="e">
+        <v>-122476.19047563001</v>
+      </c>
+      <c r="BS18" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU18" s="14"/>
       <c r="BV18" s="13" t="s">
@@ -5055,18 +5139,23 @@
       <c r="BF19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH19" s="12"/>
+      <c r="BG19" s="10">
+        <v>115</v>
+      </c>
+      <c r="BH19" s="12">
+        <v>115704.76190441</v>
+      </c>
       <c r="BI19" s="10">
         <f t="shared" si="14"/>
-        <v>-170</v>
+        <v>-55</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="15"/>
-        <v>-173704.76190436989</v>
+        <v>-57999.999999959895</v>
       </c>
       <c r="BK19" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.33389988486263134</v>
       </c>
       <c r="BM19" s="14"/>
       <c r="BN19" s="13" t="s">
@@ -5075,15 +5164,15 @@
       <c r="BP19" s="12"/>
       <c r="BQ19" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="BR19" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS19" s="11" t="e">
+        <v>-115704.76190441</v>
+      </c>
+      <c r="BS19" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU19" s="14"/>
       <c r="BV19" s="13" t="s">
@@ -5303,18 +5392,23 @@
       <c r="BF20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH20" s="12"/>
+      <c r="BG20" s="10">
+        <v>42</v>
+      </c>
+      <c r="BH20" s="12">
+        <v>253409.52380945001</v>
+      </c>
       <c r="BI20" s="10">
         <f t="shared" si="14"/>
-        <v>-39</v>
+        <v>3</v>
       </c>
       <c r="BJ20" s="12">
         <f t="shared" si="15"/>
-        <v>-243914.28571423999</v>
+        <v>9495.2380952100211</v>
       </c>
       <c r="BK20" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>3.8928585373364535E-2</v>
       </c>
       <c r="BM20" s="14"/>
       <c r="BN20" s="13" t="s">
@@ -5323,15 +5417,15 @@
       <c r="BP20" s="12"/>
       <c r="BQ20" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="BR20" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS20" s="11" t="e">
+        <v>-253409.52380945001</v>
+      </c>
+      <c r="BS20" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU20" s="14"/>
       <c r="BV20" s="13" t="s">
@@ -5551,18 +5645,23 @@
       <c r="BF21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BH21" s="12"/>
+      <c r="BG21" s="10">
+        <v>12</v>
+      </c>
+      <c r="BH21" s="12">
+        <v>101428.5714285</v>
+      </c>
       <c r="BI21" s="10">
         <f t="shared" si="14"/>
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="15"/>
-        <v>-169904.76190467001</v>
+        <v>-68476.190476170013</v>
       </c>
       <c r="BK21" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.40302690582969397</v>
       </c>
       <c r="BM21" s="14"/>
       <c r="BN21" s="13" t="s">
@@ -5571,15 +5670,15 @@
       <c r="BP21" s="12"/>
       <c r="BQ21" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BR21" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS21" s="11" t="e">
+        <v>-101428.5714285</v>
+      </c>
+      <c r="BS21" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU21" s="14"/>
       <c r="BV21" s="13" t="s">
@@ -5799,18 +5898,23 @@
       <c r="BF22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH22" s="12"/>
+      <c r="BG22" s="10">
+        <v>10</v>
+      </c>
+      <c r="BH22" s="12">
+        <v>39648</v>
+      </c>
       <c r="BI22" s="10">
         <f t="shared" si="14"/>
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="15"/>
-        <v>-48220</v>
+        <v>-8572</v>
       </c>
       <c r="BK22" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.1777685607631688</v>
       </c>
       <c r="BM22" s="14"/>
       <c r="BN22" s="13" t="s">
@@ -5819,15 +5923,15 @@
       <c r="BP22" s="12"/>
       <c r="BQ22" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BR22" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS22" s="11" t="e">
+        <v>-39648</v>
+      </c>
+      <c r="BS22" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU22" s="14"/>
       <c r="BV22" s="13" t="s">
@@ -6047,18 +6151,23 @@
       <c r="BF23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH23" s="12"/>
+      <c r="BG23" s="10">
+        <v>11</v>
+      </c>
+      <c r="BH23" s="12">
+        <v>431752.38095234003</v>
+      </c>
       <c r="BI23" s="10">
         <f t="shared" si="14"/>
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="BJ23" s="12">
         <f t="shared" si="15"/>
-        <v>-200395.23809520999</v>
+        <v>231357.14285713003</v>
       </c>
       <c r="BK23" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>1.1545041940927243</v>
       </c>
       <c r="BM23" s="14"/>
       <c r="BN23" s="13" t="s">
@@ -6067,15 +6176,15 @@
       <c r="BP23" s="12"/>
       <c r="BQ23" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BR23" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS23" s="11" t="e">
+        <v>-431752.38095234003</v>
+      </c>
+      <c r="BS23" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU23" s="14"/>
       <c r="BV23" s="13" t="s">
@@ -6295,18 +6404,23 @@
       <c r="BF24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH24" s="12"/>
+      <c r="BG24" s="10">
+        <v>16</v>
+      </c>
+      <c r="BH24" s="12">
+        <v>330571.42857133999</v>
+      </c>
       <c r="BI24" s="10">
         <f t="shared" si="14"/>
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="15"/>
-        <v>-258857.14285708999</v>
+        <v>71714.28571425</v>
       </c>
       <c r="BK24" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.2770419426047751</v>
       </c>
       <c r="BM24" s="14"/>
       <c r="BN24" s="13" t="s">
@@ -6315,15 +6429,15 @@
       <c r="BP24" s="12"/>
       <c r="BQ24" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BR24" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS24" s="11" t="e">
+        <v>-330571.42857133999</v>
+      </c>
+      <c r="BS24" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU24" s="14"/>
       <c r="BV24" s="13" t="s">
@@ -6543,18 +6657,23 @@
       <c r="BF25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH25" s="12"/>
+      <c r="BG25" s="10">
+        <v>33</v>
+      </c>
+      <c r="BH25" s="12">
+        <v>1169238.0952380199</v>
+      </c>
       <c r="BI25" s="10">
         <f t="shared" si="14"/>
-        <v>-40</v>
+        <v>-7</v>
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="15"/>
-        <v>-1629523.80952367</v>
+        <v>-460285.71428565006</v>
       </c>
       <c r="BK25" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.282466393921668</v>
       </c>
       <c r="BM25" s="14"/>
       <c r="BN25" s="13" t="s">
@@ -6563,15 +6682,15 @@
       <c r="BP25" s="12"/>
       <c r="BQ25" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="BR25" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS25" s="11" t="e">
+        <v>-1169238.0952380199</v>
+      </c>
+      <c r="BS25" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU25" s="14"/>
       <c r="BV25" s="13" t="s">
@@ -6792,19 +6911,23 @@
         <v>12</v>
       </c>
       <c r="BF26" s="9"/>
-      <c r="BG26" s="8"/>
-      <c r="BH26" s="7"/>
+      <c r="BG26" s="8">
+        <v>363</v>
+      </c>
+      <c r="BH26" s="7">
+        <v>2564228.95237969</v>
+      </c>
       <c r="BI26" s="27">
         <f t="shared" si="14"/>
-        <v>-408</v>
+        <v>-45</v>
       </c>
       <c r="BJ26" s="28">
         <f t="shared" si="15"/>
-        <v>-2839655.2380939601</v>
+        <v>-275426.28571427008</v>
       </c>
       <c r="BK26" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-9.6992860971088293E-2</v>
       </c>
       <c r="BM26" s="9" t="s">
         <v>12</v>
@@ -6814,15 +6937,15 @@
       <c r="BP26" s="7"/>
       <c r="BQ26" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-363</v>
       </c>
       <c r="BR26" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS26" s="29" t="e">
+        <v>-2564228.95237969</v>
+      </c>
+      <c r="BS26" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU26" s="9" t="s">
         <v>12</v>
@@ -7049,10 +7172,13 @@
       <c r="BF27" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="BG27" s="1">
+        <v>3534</v>
+      </c>
       <c r="BH27" s="35"/>
       <c r="BI27" s="10">
         <f t="shared" si="14"/>
-        <v>-3174</v>
+        <v>360</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="15"/>
@@ -7071,7 +7197,7 @@
       <c r="BP27" s="35"/>
       <c r="BQ27" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3534</v>
       </c>
       <c r="BR27" s="12">
         <f t="shared" si="18"/>
@@ -7550,18 +7676,23 @@
       <c r="BF29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH29" s="12"/>
+      <c r="BG29" s="10">
+        <v>99</v>
+      </c>
+      <c r="BH29" s="12">
+        <v>102610.47619004</v>
+      </c>
       <c r="BI29" s="10">
         <f t="shared" si="14"/>
-        <v>-92</v>
+        <v>7</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="15"/>
-        <v>-82476.19047580006</v>
+        <v>20134.285714239944</v>
       </c>
       <c r="BK29" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.24412240184817571</v>
       </c>
       <c r="BM29" s="14"/>
       <c r="BN29" s="13" t="s">
@@ -7570,15 +7701,15 @@
       <c r="BP29" s="12"/>
       <c r="BQ29" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="BR29" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS29" s="11" t="e">
+        <v>-102610.47619004</v>
+      </c>
+      <c r="BS29" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU29" s="14"/>
       <c r="BV29" s="13" t="s">
@@ -7798,18 +7929,23 @@
       <c r="BF30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH30" s="12"/>
+      <c r="BG30" s="10">
+        <v>90</v>
+      </c>
+      <c r="BH30" s="12">
+        <v>91561.904761619997</v>
+      </c>
       <c r="BI30" s="10">
         <f t="shared" si="14"/>
-        <v>-54</v>
+        <v>36</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="15"/>
-        <v>-51580.952380770002</v>
+        <v>39980.952380849994</v>
       </c>
       <c r="BK30" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.77511078286633905</v>
       </c>
       <c r="BM30" s="14"/>
       <c r="BN30" s="13" t="s">
@@ -7818,15 +7954,15 @@
       <c r="BP30" s="12"/>
       <c r="BQ30" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="BR30" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS30" s="11" t="e">
+        <v>-91561.904761619997</v>
+      </c>
+      <c r="BS30" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU30" s="14"/>
       <c r="BV30" s="13" t="s">
@@ -8046,18 +8182,23 @@
       <c r="BF31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH31" s="12"/>
+      <c r="BG31" s="10">
+        <v>28</v>
+      </c>
+      <c r="BH31" s="12">
+        <v>235447.61904753</v>
+      </c>
       <c r="BI31" s="10">
         <f t="shared" si="14"/>
-        <v>-15</v>
+        <v>13</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="15"/>
-        <v>-99024.761904739993</v>
+        <v>136422.85714278999</v>
       </c>
       <c r="BK31" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>1.3776640763249326</v>
       </c>
       <c r="BM31" s="14"/>
       <c r="BN31" s="13" t="s">
@@ -8066,15 +8207,15 @@
       <c r="BP31" s="12"/>
       <c r="BQ31" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="BR31" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS31" s="11" t="e">
+        <v>-235447.61904753</v>
+      </c>
+      <c r="BS31" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU31" s="14"/>
       <c r="BV31" s="13" t="s">
@@ -8294,18 +8435,23 @@
       <c r="BF32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BH32" s="12"/>
+      <c r="BG32" s="10">
+        <v>8</v>
+      </c>
+      <c r="BH32" s="12">
+        <v>91619.047619010002</v>
+      </c>
       <c r="BI32" s="10">
         <f t="shared" si="14"/>
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="15"/>
-        <v>-174285.71428565</v>
+        <v>-82666.666666639998</v>
       </c>
       <c r="BK32" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.47431693989073231</v>
       </c>
       <c r="BM32" s="14"/>
       <c r="BN32" s="13" t="s">
@@ -8314,15 +8460,15 @@
       <c r="BP32" s="12"/>
       <c r="BQ32" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BR32" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS32" s="11" t="e">
+        <v>-91619.047619010002</v>
+      </c>
+      <c r="BS32" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU32" s="14"/>
       <c r="BV32" s="13" t="s">
@@ -8542,18 +8688,23 @@
       <c r="BF33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH33" s="12"/>
+      <c r="BG33" s="10">
+        <v>2</v>
+      </c>
+      <c r="BH33" s="12">
+        <v>11280</v>
+      </c>
       <c r="BI33" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="15"/>
-        <v>-18980</v>
+        <v>-7700</v>
       </c>
       <c r="BK33" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.40569020021074814</v>
       </c>
       <c r="BM33" s="14"/>
       <c r="BN33" s="13" t="s">
@@ -8562,15 +8713,15 @@
       <c r="BP33" s="12"/>
       <c r="BQ33" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BR33" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS33" s="11" t="e">
+        <v>-11280</v>
+      </c>
+      <c r="BS33" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU33" s="14"/>
       <c r="BV33" s="13" t="s">
@@ -8790,18 +8941,23 @@
       <c r="BF34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH34" s="12"/>
+      <c r="BG34" s="10">
+        <v>5</v>
+      </c>
+      <c r="BH34" s="12">
+        <v>210856.19047617001</v>
+      </c>
       <c r="BI34" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="BJ34" s="12">
         <f t="shared" si="15"/>
-        <v>-128735.23809523</v>
+        <v>82120.952380940013</v>
       </c>
       <c r="BK34" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.63790577930335002</v>
       </c>
       <c r="BM34" s="14"/>
       <c r="BN34" s="13" t="s">
@@ -8810,15 +8966,15 @@
       <c r="BP34" s="12"/>
       <c r="BQ34" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BR34" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS34" s="11" t="e">
+        <v>-210856.19047617001</v>
+      </c>
+      <c r="BS34" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU34" s="14"/>
       <c r="BV34" s="13" t="s">
@@ -9038,18 +9194,23 @@
       <c r="BF35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH35" s="12"/>
+      <c r="BG35" s="10">
+        <v>9</v>
+      </c>
+      <c r="BH35" s="12">
+        <v>225619.04761899999</v>
+      </c>
       <c r="BI35" s="10">
         <f t="shared" si="14"/>
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="BJ35" s="12">
         <f t="shared" si="15"/>
-        <v>-52095.238095219996</v>
+        <v>173523.80952377999</v>
       </c>
       <c r="BK35" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>3.330895795247391</v>
       </c>
       <c r="BM35" s="14"/>
       <c r="BN35" s="13" t="s">
@@ -9058,15 +9219,15 @@
       <c r="BP35" s="12"/>
       <c r="BQ35" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BR35" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS35" s="11" t="e">
+        <v>-225619.04761899999</v>
+      </c>
+      <c r="BS35" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU35" s="14"/>
       <c r="BV35" s="13" t="s">
@@ -9286,18 +9447,23 @@
       <c r="BF36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH36" s="12"/>
+      <c r="BG36" s="10">
+        <v>8</v>
+      </c>
+      <c r="BH36" s="12">
+        <v>314476.19047615997</v>
+      </c>
       <c r="BI36" s="10">
         <f t="shared" si="14"/>
-        <v>-16</v>
+        <v>-8</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="15"/>
-        <v>-648098.09523805999</v>
+        <v>-333621.90476190002</v>
       </c>
       <c r="BK36" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.51477069167955769</v>
       </c>
       <c r="BM36" s="14"/>
       <c r="BN36" s="13" t="s">
@@ -9306,15 +9472,15 @@
       <c r="BP36" s="12"/>
       <c r="BQ36" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BR36" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS36" s="11" t="e">
+        <v>-314476.19047615997</v>
+      </c>
+      <c r="BS36" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU36" s="14"/>
       <c r="BV36" s="13" t="s">
@@ -9535,19 +9701,23 @@
         <v>11</v>
       </c>
       <c r="BF37" s="9"/>
-      <c r="BG37" s="8"/>
-      <c r="BH37" s="7"/>
+      <c r="BG37" s="8">
+        <v>249</v>
+      </c>
+      <c r="BH37" s="7">
+        <v>1283470.47618953</v>
+      </c>
       <c r="BI37" s="27">
         <f t="shared" si="14"/>
-        <v>-198</v>
+        <v>51</v>
       </c>
       <c r="BJ37" s="28">
         <f t="shared" si="15"/>
-        <v>-1255276.1904754699</v>
+        <v>28194.285714060068</v>
       </c>
       <c r="BK37" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>2.2460623349655599E-2</v>
       </c>
       <c r="BM37" s="9" t="s">
         <v>11</v>
@@ -9557,15 +9727,15 @@
       <c r="BP37" s="7"/>
       <c r="BQ37" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-249</v>
       </c>
       <c r="BR37" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS37" s="29" t="e">
+        <v>-1283470.47618953</v>
+      </c>
+      <c r="BS37" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU37" s="9" t="s">
         <v>11</v>
@@ -9792,10 +9962,13 @@
       <c r="BF38" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="BG38" s="1">
+        <v>1804</v>
+      </c>
       <c r="BH38" s="35"/>
       <c r="BI38" s="10">
         <f t="shared" si="14"/>
-        <v>-1711</v>
+        <v>93</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="15"/>
@@ -9814,7 +9987,7 @@
       <c r="BP38" s="35"/>
       <c r="BQ38" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1804</v>
       </c>
       <c r="BR38" s="12">
         <f t="shared" si="18"/>
@@ -10293,18 +10466,23 @@
       <c r="BF40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH40" s="12"/>
+      <c r="BG40" s="10">
+        <v>101</v>
+      </c>
+      <c r="BH40" s="12">
+        <v>96915.23809472</v>
+      </c>
       <c r="BI40" s="10">
         <f t="shared" si="14"/>
-        <v>-97</v>
+        <v>4</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="15"/>
-        <v>-90916.190475729993</v>
+        <v>5999.0476189900073</v>
       </c>
       <c r="BK40" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>6.5984370744080492E-2</v>
       </c>
       <c r="BM40" s="14"/>
       <c r="BN40" s="13" t="s">
@@ -10313,15 +10491,15 @@
       <c r="BP40" s="12"/>
       <c r="BQ40" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-101</v>
       </c>
       <c r="BR40" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS40" s="11" t="e">
+        <v>-96915.23809472</v>
+      </c>
+      <c r="BS40" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU40" s="14"/>
       <c r="BV40" s="13" t="s">
@@ -10541,18 +10719,23 @@
       <c r="BF41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH41" s="12"/>
+      <c r="BG41" s="10">
+        <v>83</v>
+      </c>
+      <c r="BH41" s="12">
+        <v>102161.90476165</v>
+      </c>
       <c r="BI41" s="10">
         <f t="shared" si="14"/>
-        <v>-64</v>
+        <v>19</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="15"/>
-        <v>-71868.571428339987</v>
+        <v>30293.333333310016</v>
       </c>
       <c r="BK41" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.42151016405711417</v>
       </c>
       <c r="BM41" s="14"/>
       <c r="BN41" s="13" t="s">
@@ -10561,15 +10744,15 @@
       <c r="BP41" s="12"/>
       <c r="BQ41" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="BR41" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS41" s="11" t="e">
+        <v>-102161.90476165</v>
+      </c>
+      <c r="BS41" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU41" s="14"/>
       <c r="BV41" s="13" t="s">
@@ -10789,18 +10972,23 @@
       <c r="BF42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH42" s="12"/>
+      <c r="BG42" s="10">
+        <v>11</v>
+      </c>
+      <c r="BH42" s="12">
+        <v>77038.095238080001</v>
+      </c>
       <c r="BI42" s="10">
         <f t="shared" si="14"/>
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="15"/>
-        <v>-94171.4285714</v>
+        <v>-17133.333333319999</v>
       </c>
       <c r="BK42" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.18193770226528577</v>
       </c>
       <c r="BM42" s="14"/>
       <c r="BN42" s="13" t="s">
@@ -10809,15 +10997,15 @@
       <c r="BP42" s="12"/>
       <c r="BQ42" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BR42" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS42" s="11" t="e">
+        <v>-77038.095238080001</v>
+      </c>
+      <c r="BS42" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU42" s="14"/>
       <c r="BV42" s="13" t="s">
@@ -11037,18 +11225,23 @@
       <c r="BF43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BH43" s="12"/>
+      <c r="BG43" s="10">
+        <v>5</v>
+      </c>
+      <c r="BH43" s="12">
+        <v>54761.904761880003</v>
+      </c>
       <c r="BI43" s="10">
         <f t="shared" si="14"/>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="15"/>
-        <v>-54761.904761880003</v>
+        <v>0</v>
       </c>
       <c r="BK43" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BM43" s="14"/>
       <c r="BN43" s="13" t="s">
@@ -11057,15 +11250,15 @@
       <c r="BP43" s="12"/>
       <c r="BQ43" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BR43" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS43" s="11" t="e">
+        <v>-54761.904761880003</v>
+      </c>
+      <c r="BS43" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU43" s="14"/>
       <c r="BV43" s="13" t="s">
@@ -11285,14 +11478,19 @@
       <c r="BF44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH44" s="12"/>
+      <c r="BG44" s="10">
+        <v>3</v>
+      </c>
+      <c r="BH44" s="12">
+        <v>15270</v>
+      </c>
       <c r="BI44" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>15270</v>
       </c>
       <c r="BK44" s="11" t="e">
         <f t="shared" si="16"/>
@@ -11305,15 +11503,15 @@
       <c r="BP44" s="12"/>
       <c r="BQ44" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BR44" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS44" s="11" t="e">
+        <v>-15270</v>
+      </c>
+      <c r="BS44" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU44" s="14"/>
       <c r="BV44" s="13" t="s">
@@ -11534,18 +11732,23 @@
       <c r="BF45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH45" s="12"/>
+      <c r="BG45" s="10">
+        <v>4</v>
+      </c>
+      <c r="BH45" s="12">
+        <v>129160.95238094</v>
+      </c>
       <c r="BI45" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="15"/>
-        <v>-46476.190476180003</v>
+        <v>82684.761904760002</v>
       </c>
       <c r="BK45" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>1.779077868852819</v>
       </c>
       <c r="BM45" s="14"/>
       <c r="BN45" s="13" t="s">
@@ -11554,15 +11757,15 @@
       <c r="BP45" s="12"/>
       <c r="BQ45" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BR45" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS45" s="11" t="e">
+        <v>-129160.95238094</v>
+      </c>
+      <c r="BS45" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU45" s="14"/>
       <c r="BV45" s="13" t="s">
@@ -11783,18 +11986,23 @@
       <c r="BF46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH46" s="12"/>
+      <c r="BG46" s="10">
+        <v>9</v>
+      </c>
+      <c r="BH46" s="12">
+        <v>215809.52380947</v>
+      </c>
       <c r="BI46" s="10">
         <f t="shared" si="14"/>
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="BJ46" s="12">
         <f t="shared" si="15"/>
-        <v>-201142.85714281999</v>
+        <v>14666.66666665001</v>
       </c>
       <c r="BK46" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>7.2916666666597324E-2</v>
       </c>
       <c r="BM46" s="14"/>
       <c r="BN46" s="13" t="s">
@@ -11803,15 +12011,15 @@
       <c r="BP46" s="12"/>
       <c r="BQ46" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BR46" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS46" s="11" t="e">
+        <v>-215809.52380947</v>
+      </c>
+      <c r="BS46" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU46" s="14"/>
       <c r="BV46" s="13" t="s">
@@ -12032,18 +12240,23 @@
       <c r="BF47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH47" s="12"/>
+      <c r="BG47" s="10">
+        <v>15</v>
+      </c>
+      <c r="BH47" s="12">
+        <v>490952.38095235999</v>
+      </c>
       <c r="BI47" s="10">
         <f t="shared" si="14"/>
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="BJ47" s="12">
         <f t="shared" si="15"/>
-        <v>-650857.14285712002</v>
+        <v>-159904.76190476003</v>
       </c>
       <c r="BK47" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.24568334796605784</v>
       </c>
       <c r="BM47" s="14"/>
       <c r="BN47" s="13" t="s">
@@ -12052,15 +12265,15 @@
       <c r="BP47" s="12"/>
       <c r="BQ47" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BR47" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS47" s="11" t="e">
+        <v>-490952.38095235999</v>
+      </c>
+      <c r="BS47" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU47" s="14"/>
       <c r="BV47" s="13" t="s">
@@ -12282,19 +12495,23 @@
         <v>10</v>
       </c>
       <c r="BF48" s="9"/>
-      <c r="BG48" s="8"/>
-      <c r="BH48" s="7"/>
+      <c r="BG48" s="8">
+        <v>231</v>
+      </c>
+      <c r="BH48" s="7">
+        <v>1182069.9999991001</v>
+      </c>
       <c r="BI48" s="27">
         <f t="shared" si="14"/>
-        <v>-203</v>
+        <v>28</v>
       </c>
       <c r="BJ48" s="28">
         <f t="shared" si="15"/>
-        <v>-1210194.2857134701</v>
+        <v>-28124.285714369966</v>
       </c>
       <c r="BK48" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-2.3239479847476964E-2</v>
       </c>
       <c r="BM48" s="9" t="s">
         <v>10</v>
@@ -12304,15 +12521,15 @@
       <c r="BP48" s="7"/>
       <c r="BQ48" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-231</v>
       </c>
       <c r="BR48" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS48" s="29" t="e">
+        <v>-1182069.9999991001</v>
+      </c>
+      <c r="BS48" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU48" s="9" t="s">
         <v>10</v>
@@ -13020,18 +13237,23 @@
       <c r="BF51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BH51" s="12"/>
+      <c r="BG51" s="10">
+        <v>114</v>
+      </c>
+      <c r="BH51" s="12">
+        <v>109647.61904706</v>
+      </c>
       <c r="BI51" s="10">
         <f t="shared" si="14"/>
-        <v>-112</v>
+        <v>2</v>
       </c>
       <c r="BJ51" s="12">
         <f t="shared" si="15"/>
-        <v>-111609.52380893</v>
+        <v>-1961.9047618699988</v>
       </c>
       <c r="BK51" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-1.757829166289324E-2</v>
       </c>
       <c r="BM51" s="14"/>
       <c r="BN51" s="13" t="s">
@@ -13040,15 +13262,15 @@
       <c r="BP51" s="12"/>
       <c r="BQ51" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-114</v>
       </c>
       <c r="BR51" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS51" s="11" t="e">
+        <v>-109647.61904706</v>
+      </c>
+      <c r="BS51" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU51" s="14"/>
       <c r="BV51" s="13" t="s">
@@ -13268,18 +13490,23 @@
       <c r="BF52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BH52" s="12"/>
+      <c r="BG52" s="10">
+        <v>71</v>
+      </c>
+      <c r="BH52" s="12">
+        <v>81323.809523529999</v>
+      </c>
       <c r="BI52" s="10">
         <f t="shared" si="14"/>
-        <v>-68</v>
+        <v>3</v>
       </c>
       <c r="BJ52" s="12">
         <f t="shared" si="15"/>
-        <v>-67161.904761679994</v>
+        <v>14161.904761850004</v>
       </c>
       <c r="BK52" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.21086216676109287</v>
       </c>
       <c r="BM52" s="14"/>
       <c r="BN52" s="13" t="s">
@@ -13288,15 +13515,15 @@
       <c r="BP52" s="12"/>
       <c r="BQ52" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="BR52" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS52" s="11" t="e">
+        <v>-81323.809523529999</v>
+      </c>
+      <c r="BS52" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU52" s="14"/>
       <c r="BV52" s="13" t="s">
@@ -13516,18 +13743,23 @@
       <c r="BF53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BH53" s="12"/>
+      <c r="BG53" s="10">
+        <v>15</v>
+      </c>
+      <c r="BH53" s="12">
+        <v>112238.09523806001</v>
+      </c>
       <c r="BI53" s="10">
         <f t="shared" si="14"/>
-        <v>-11</v>
+        <v>4</v>
       </c>
       <c r="BJ53" s="12">
         <f t="shared" si="15"/>
-        <v>-62752.380952359992</v>
+        <v>49485.714285700014</v>
       </c>
       <c r="BK53" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.78858703900443727</v>
       </c>
       <c r="BM53" s="14"/>
       <c r="BN53" s="13" t="s">
@@ -13536,15 +13768,15 @@
       <c r="BP53" s="12"/>
       <c r="BQ53" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="BR53" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS53" s="11" t="e">
+        <v>-112238.09523806001</v>
+      </c>
+      <c r="BS53" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU53" s="14"/>
       <c r="BV53" s="13" t="s">
@@ -13764,18 +13996,23 @@
       <c r="BF54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BH54" s="12"/>
+      <c r="BG54" s="10">
+        <v>11</v>
+      </c>
+      <c r="BH54" s="12">
+        <v>124666.66666662</v>
+      </c>
       <c r="BI54" s="10">
         <f t="shared" si="14"/>
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="BJ54" s="12">
         <f t="shared" si="15"/>
-        <v>-92571.428571390003</v>
+        <v>32095.238095230001</v>
       </c>
       <c r="BK54" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.34670781893009817</v>
       </c>
       <c r="BM54" s="14"/>
       <c r="BN54" s="13" t="s">
@@ -13784,15 +14021,15 @@
       <c r="BP54" s="12"/>
       <c r="BQ54" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="BR54" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS54" s="11" t="e">
+        <v>-124666.66666662</v>
+      </c>
+      <c r="BS54" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU54" s="14"/>
       <c r="BV54" s="13" t="s">
@@ -14012,18 +14249,23 @@
       <c r="BF55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BH55" s="12"/>
+      <c r="BG55" s="10">
+        <v>3</v>
+      </c>
+      <c r="BH55" s="12">
+        <v>11370</v>
+      </c>
       <c r="BI55" s="10">
         <f t="shared" si="14"/>
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="BJ55" s="12">
         <f t="shared" si="15"/>
-        <v>-14840</v>
+        <v>-3470</v>
       </c>
       <c r="BK55" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.23382749326145552</v>
       </c>
       <c r="BM55" s="14"/>
       <c r="BN55" s="13" t="s">
@@ -14032,15 +14274,15 @@
       <c r="BP55" s="12"/>
       <c r="BQ55" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BR55" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS55" s="11" t="e">
+        <v>-11370</v>
+      </c>
+      <c r="BS55" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU55" s="14"/>
       <c r="BV55" s="13" t="s">
@@ -14261,18 +14503,23 @@
       <c r="BF56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BH56" s="12"/>
+      <c r="BG56" s="10">
+        <v>6</v>
+      </c>
+      <c r="BH56" s="12">
+        <v>191647.61904758</v>
+      </c>
       <c r="BI56" s="10">
         <f t="shared" si="14"/>
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="BJ56" s="12">
         <f t="shared" si="15"/>
-        <v>-383238.09523805999</v>
+        <v>-191590.47619048</v>
       </c>
       <c r="BK56" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.49992544731615929</v>
       </c>
       <c r="BM56" s="14"/>
       <c r="BN56" s="13" t="s">
@@ -14281,15 +14528,15 @@
       <c r="BP56" s="12"/>
       <c r="BQ56" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BR56" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS56" s="11" t="e">
+        <v>-191647.61904758</v>
+      </c>
+      <c r="BS56" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU56" s="14"/>
       <c r="BV56" s="13" t="s">
@@ -14510,18 +14757,23 @@
       <c r="BF57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BH57" s="12"/>
+      <c r="BG57" s="10">
+        <v>17</v>
+      </c>
+      <c r="BH57" s="12">
+        <v>399809.52380944003</v>
+      </c>
       <c r="BI57" s="10">
         <f t="shared" si="14"/>
-        <v>-8</v>
+        <v>9</v>
       </c>
       <c r="BJ57" s="12">
         <f t="shared" si="15"/>
-        <v>-200666.66666662</v>
+        <v>199142.85714282002</v>
       </c>
       <c r="BK57" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>0.9924062648315598</v>
       </c>
       <c r="BM57" s="14"/>
       <c r="BN57" s="13" t="s">
@@ -14530,15 +14782,15 @@
       <c r="BP57" s="12"/>
       <c r="BQ57" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="BR57" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS57" s="11" t="e">
+        <v>-399809.52380944003</v>
+      </c>
+      <c r="BS57" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU57" s="14"/>
       <c r="BV57" s="13" t="s">
@@ -14759,18 +15011,23 @@
       <c r="BF58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BH58" s="12"/>
+      <c r="BG58" s="10">
+        <v>17</v>
+      </c>
+      <c r="BH58" s="12">
+        <v>645047.61904757994</v>
+      </c>
       <c r="BI58" s="10">
         <f t="shared" si="14"/>
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="BJ58" s="12">
         <f t="shared" si="15"/>
-        <v>-773428.57142853003</v>
+        <v>-128380.9523809501</v>
       </c>
       <c r="BK58" s="11">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.16598941017116711</v>
       </c>
       <c r="BM58" s="14"/>
       <c r="BN58" s="13" t="s">
@@ -14779,15 +15036,15 @@
       <c r="BP58" s="12"/>
       <c r="BQ58" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="BR58" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS58" s="11" t="e">
+        <v>-645047.61904757994</v>
+      </c>
+      <c r="BS58" s="11">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU58" s="14"/>
       <c r="BV58" s="13" t="s">
@@ -15009,19 +15266,23 @@
         <v>1</v>
       </c>
       <c r="BF59" s="9"/>
-      <c r="BG59" s="8"/>
-      <c r="BH59" s="7"/>
+      <c r="BG59" s="8">
+        <v>254</v>
+      </c>
+      <c r="BH59" s="7">
+        <v>1675750.95237987</v>
+      </c>
       <c r="BI59" s="27">
         <f t="shared" si="14"/>
-        <v>-238</v>
+        <v>16</v>
       </c>
       <c r="BJ59" s="28">
         <f t="shared" si="15"/>
-        <v>-1706268.57142757</v>
+        <v>-30517.619047699962</v>
       </c>
       <c r="BK59" s="29">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-1.7885589384188817E-2</v>
       </c>
       <c r="BM59" s="9" t="s">
         <v>1</v>
@@ -15031,15 +15292,15 @@
       <c r="BP59" s="7"/>
       <c r="BQ59" s="27">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-254</v>
       </c>
       <c r="BR59" s="28">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS59" s="29" t="e">
+        <v>-1675750.95237987</v>
+      </c>
+      <c r="BS59" s="29">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU59" s="9" t="s">
         <v>1</v>
@@ -15264,19 +15525,23 @@
         <v>0</v>
       </c>
       <c r="BF60" s="4"/>
-      <c r="BG60" s="3"/>
-      <c r="BH60" s="2"/>
+      <c r="BG60" s="3">
+        <v>1717</v>
+      </c>
+      <c r="BH60" s="2">
+        <v>10998812.76189879</v>
+      </c>
       <c r="BI60" s="6">
         <f t="shared" si="14"/>
-        <v>-1800</v>
+        <v>-83</v>
       </c>
       <c r="BJ60" s="5">
         <f t="shared" si="15"/>
-        <v>-14724800.95237501</v>
+        <v>-3725988.1904762201</v>
       </c>
       <c r="BK60" s="30">
         <f t="shared" si="16"/>
-        <v>-1</v>
+        <v>-0.2530416677636137</v>
       </c>
       <c r="BM60" s="4" t="s">
         <v>0</v>
@@ -15286,15 +15551,15 @@
       <c r="BP60" s="2"/>
       <c r="BQ60" s="6">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1717</v>
       </c>
       <c r="BR60" s="5">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BS60" s="30" t="e">
+        <v>-10998812.76189879</v>
+      </c>
+      <c r="BS60" s="30">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="BU60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B71B2F5-EE14-4E44-B717-75C55BE76F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A93268-D1A0-6C43-B14F-2A7C850AFFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1848,10 +1848,13 @@
       <c r="BF6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG6" s="15">
+        <v>10</v>
+      </c>
       <c r="BH6" s="33"/>
       <c r="BI6" s="10">
         <f t="shared" si="14"/>
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="BJ6" s="12">
         <f t="shared" si="15"/>
@@ -1868,7 +1871,7 @@
       <c r="BP6" s="33"/>
       <c r="BQ6" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BR6" s="12">
         <f t="shared" si="18"/>
@@ -4634,10 +4637,13 @@
       <c r="BF17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG17" s="1">
+        <v>7</v>
+      </c>
       <c r="BH17" s="35"/>
       <c r="BI17" s="10">
         <f t="shared" si="14"/>
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="15"/>
@@ -4654,7 +4660,7 @@
       <c r="BP17" s="35"/>
       <c r="BQ17" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BR17" s="12">
         <f t="shared" si="18"/>
@@ -7424,10 +7430,13 @@
       <c r="BF28" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG28" s="1">
+        <v>5</v>
+      </c>
       <c r="BH28" s="35"/>
       <c r="BI28" s="10">
         <f t="shared" si="14"/>
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="15"/>
@@ -7444,7 +7453,7 @@
       <c r="BP28" s="35"/>
       <c r="BQ28" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BR28" s="12">
         <f t="shared" si="18"/>
@@ -10214,10 +10223,13 @@
       <c r="BF39" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG39" s="1">
+        <v>1</v>
+      </c>
       <c r="BH39" s="35"/>
       <c r="BI39" s="10">
         <f t="shared" si="14"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BJ39" s="12">
         <f t="shared" si="15"/>
@@ -10234,7 +10246,7 @@
       <c r="BP39" s="35"/>
       <c r="BQ39" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BR39" s="12">
         <f t="shared" si="18"/>
@@ -12985,10 +12997,13 @@
       <c r="BF50" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="BG50" s="1">
+        <v>2</v>
+      </c>
       <c r="BH50" s="35"/>
       <c r="BI50" s="10">
         <f t="shared" si="14"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BJ50" s="12">
         <f t="shared" si="15"/>
@@ -13005,7 +13020,7 @@
       <c r="BP50" s="35"/>
       <c r="BQ50" s="10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BR50" s="12">
         <f t="shared" si="18"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A93268-D1A0-6C43-B14F-2A7C850AFFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5049159E-2551-4044-BDEA-9D17C425CE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="46">
   <si>
     <t>總計</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>08/16-08/22</t>
+  </si>
+  <si>
+    <t>26Q4W9</t>
+  </si>
+  <si>
+    <t>08/23-08/29</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1067,9 @@
       </c>
       <c r="BF1" s="26"/>
       <c r="BH1" s="25"/>
-      <c r="BM1" s="26"/>
+      <c r="BM1" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="BU1" s="26"/>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
@@ -1123,6 +1131,9 @@
       <c r="BG2" s="22"/>
       <c r="BH2" s="22"/>
       <c r="BJ2" s="21"/>
+      <c r="BM2" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="BN2" s="21"/>
       <c r="BP2" s="21"/>
       <c r="BQ2" s="21"/>
@@ -1326,16 +1337,16 @@
         <v>13</v>
       </c>
       <c r="BM4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="BN4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="BO4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="BP4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BQ4" s="16" t="s">
         <v>13</v>
@@ -1611,13 +1622,15 @@
         <v>75</v>
       </c>
       <c r="BN5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="BO5" s="40"/>
+        <v>37</v>
+      </c>
+      <c r="BO5" s="40">
+        <v>6262</v>
+      </c>
       <c r="BP5" s="1"/>
       <c r="BQ5" s="10">
         <f t="shared" ref="BQ5:BQ60" si="17">BO5-BG5</f>
-        <v>-5656</v>
+        <v>606</v>
       </c>
       <c r="BR5" s="12">
         <f t="shared" ref="BR5:BR60" si="18">BP5-BH5</f>
@@ -1638,7 +1651,7 @@
       <c r="BX5" s="33"/>
       <c r="BY5" s="10">
         <f t="shared" ref="BY5:BY33" si="20">BW5-BO5</f>
-        <v>0</v>
+        <v>-6262</v>
       </c>
       <c r="BZ5" s="12">
         <f t="shared" ref="BZ5:BZ60" si="21">BX5-BP5</f>
@@ -1866,7 +1879,7 @@
       </c>
       <c r="BM6" s="14"/>
       <c r="BN6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BP6" s="33"/>
       <c r="BQ6" s="10">
@@ -2121,18 +2134,23 @@
       <c r="BN7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP7" s="12"/>
+      <c r="BO7" s="10">
+        <v>209</v>
+      </c>
+      <c r="BP7" s="12">
+        <v>210267.61904672001</v>
+      </c>
       <c r="BQ7" s="10">
         <f t="shared" si="17"/>
-        <v>-170</v>
+        <v>39</v>
       </c>
       <c r="BR7" s="12">
         <f t="shared" si="18"/>
-        <v>-174014.28571349999</v>
+        <v>36253.333333220013</v>
       </c>
       <c r="BS7" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.20833538571027496</v>
       </c>
       <c r="BU7" s="14"/>
       <c r="BV7" s="13" t="s">
@@ -2141,15 +2159,15 @@
       <c r="BX7" s="12"/>
       <c r="BY7" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-209</v>
       </c>
       <c r="BZ7" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA7" s="11" t="e">
+        <v>-210267.61904672001</v>
+      </c>
+      <c r="CA7" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC7" s="14"/>
       <c r="CD7" s="13" t="s">
@@ -2374,18 +2392,23 @@
       <c r="BN8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP8" s="12"/>
+      <c r="BO8" s="10">
+        <v>271</v>
+      </c>
+      <c r="BP8" s="12">
+        <v>337086.66666618001</v>
+      </c>
       <c r="BQ8" s="10">
         <f t="shared" si="17"/>
-        <v>-263</v>
+        <v>8</v>
       </c>
       <c r="BR8" s="12">
         <f t="shared" si="18"/>
-        <v>-314315.23809473001</v>
+        <v>22771.42857145</v>
       </c>
       <c r="BS8" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>7.2447739757965618E-2</v>
       </c>
       <c r="BU8" s="14"/>
       <c r="BV8" s="13" t="s">
@@ -2394,15 +2417,15 @@
       <c r="BX8" s="12"/>
       <c r="BY8" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-271</v>
       </c>
       <c r="BZ8" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA8" s="11" t="e">
+        <v>-337086.66666618001</v>
+      </c>
+      <c r="CA8" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC8" s="14"/>
       <c r="CD8" s="13" t="s">
@@ -2627,18 +2650,23 @@
       <c r="BN9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP9" s="12"/>
+      <c r="BO9" s="10">
+        <v>53</v>
+      </c>
+      <c r="BP9" s="12">
+        <v>376638.09523803002</v>
+      </c>
       <c r="BQ9" s="10">
         <f t="shared" si="17"/>
-        <v>-68</v>
+        <v>-15</v>
       </c>
       <c r="BR9" s="12">
         <f t="shared" si="18"/>
-        <v>-467447.61904753</v>
+        <v>-90809.52380949998</v>
       </c>
       <c r="BS9" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.1942667372967547</v>
       </c>
       <c r="BU9" s="14"/>
       <c r="BV9" s="13" t="s">
@@ -2647,15 +2675,15 @@
       <c r="BX9" s="12"/>
       <c r="BY9" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="BZ9" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA9" s="11" t="e">
+        <v>-376638.09523803002</v>
+      </c>
+      <c r="CA9" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC9" s="14"/>
       <c r="CD9" s="13" t="s">
@@ -2880,18 +2908,23 @@
       <c r="BN10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BP10" s="12"/>
+      <c r="BO10" s="10">
+        <v>5</v>
+      </c>
+      <c r="BP10" s="12">
+        <v>40476.190476169999</v>
+      </c>
       <c r="BQ10" s="10">
         <f t="shared" si="17"/>
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="BR10" s="12">
         <f t="shared" si="18"/>
-        <v>-222857.14285706001</v>
+        <v>-182380.95238089003</v>
       </c>
       <c r="BS10" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.81837606837609278</v>
       </c>
       <c r="BU10" s="14"/>
       <c r="BV10" s="13" t="s">
@@ -2900,15 +2933,15 @@
       <c r="BX10" s="12"/>
       <c r="BY10" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BZ10" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA10" s="11" t="e">
+        <v>-40476.190476169999</v>
+      </c>
+      <c r="CA10" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC10" s="14"/>
       <c r="CD10" s="13" t="s">
@@ -3133,18 +3166,23 @@
       <c r="BN11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP11" s="12"/>
+      <c r="BO11" s="10">
+        <v>5</v>
+      </c>
+      <c r="BP11" s="12">
+        <v>21150</v>
+      </c>
       <c r="BQ11" s="10">
         <f t="shared" si="17"/>
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="BR11" s="12">
         <f t="shared" si="18"/>
-        <v>-58120</v>
+        <v>-36970</v>
       </c>
       <c r="BS11" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.6360977288368892</v>
       </c>
       <c r="BU11" s="14"/>
       <c r="BV11" s="13" t="s">
@@ -3153,15 +3191,15 @@
       <c r="BX11" s="12"/>
       <c r="BY11" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BZ11" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA11" s="11" t="e">
+        <v>-21150</v>
+      </c>
+      <c r="CA11" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC11" s="14"/>
       <c r="CD11" s="13" t="s">
@@ -3386,18 +3424,23 @@
       <c r="BN12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP12" s="12"/>
+      <c r="BO12" s="10">
+        <v>24</v>
+      </c>
+      <c r="BP12" s="12">
+        <v>798423.80952372996</v>
+      </c>
       <c r="BQ12" s="10">
         <f t="shared" si="17"/>
-        <v>-21</v>
+        <v>3</v>
       </c>
       <c r="BR12" s="12">
         <f t="shared" si="18"/>
-        <v>-943204.76190464001</v>
+        <v>-144780.95238091005</v>
       </c>
       <c r="BS12" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.15349896250369832</v>
       </c>
       <c r="BU12" s="14"/>
       <c r="BV12" s="13" t="s">
@@ -3406,15 +3449,15 @@
       <c r="BX12" s="12"/>
       <c r="BY12" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="BZ12" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA12" s="11" t="e">
+        <v>-798423.80952372996</v>
+      </c>
+      <c r="CA12" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC12" s="14"/>
       <c r="CD12" s="13" t="s">
@@ -3639,18 +3682,23 @@
       <c r="BN13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP13" s="12"/>
+      <c r="BO13" s="10">
+        <v>45</v>
+      </c>
+      <c r="BP13" s="12">
+        <v>981238.09523791994</v>
+      </c>
       <c r="BQ13" s="10">
         <f t="shared" si="17"/>
-        <v>-29</v>
+        <v>16</v>
       </c>
       <c r="BR13" s="12">
         <f t="shared" si="18"/>
-        <v>-671523.80952368001</v>
+        <v>309714.28571423993</v>
       </c>
       <c r="BS13" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.46121117571977682</v>
       </c>
       <c r="BU13" s="14"/>
       <c r="BV13" s="13" t="s">
@@ -3659,15 +3707,15 @@
       <c r="BX13" s="12"/>
       <c r="BY13" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="BZ13" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA13" s="11" t="e">
+        <v>-981238.09523791994</v>
+      </c>
+      <c r="CA13" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC13" s="14"/>
       <c r="CD13" s="13" t="s">
@@ -3892,18 +3940,23 @@
       <c r="BN14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP14" s="12"/>
+      <c r="BO14" s="10">
+        <v>32</v>
+      </c>
+      <c r="BP14" s="12">
+        <v>1143619.0476189801</v>
+      </c>
       <c r="BQ14" s="10">
         <f t="shared" si="17"/>
-        <v>-41</v>
+        <v>-9</v>
       </c>
       <c r="BR14" s="12">
         <f t="shared" si="18"/>
-        <v>-1441809.52380946</v>
+        <v>-298190.47619047994</v>
       </c>
       <c r="BS14" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.20681683070217174</v>
       </c>
       <c r="BU14" s="14"/>
       <c r="BV14" s="13" t="s">
@@ -3912,15 +3965,15 @@
       <c r="BX14" s="12"/>
       <c r="BY14" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="BZ14" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA14" s="11" t="e">
+        <v>-1143619.0476189801</v>
+      </c>
+      <c r="CA14" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC14" s="14"/>
       <c r="CD14" s="13" t="s">
@@ -4143,22 +4196,26 @@
         <v>-0.44339867370079672</v>
       </c>
       <c r="BM15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="BN15" s="9"/>
-      <c r="BO15" s="8"/>
-      <c r="BP15" s="7"/>
+      <c r="BO15" s="8">
+        <v>644</v>
+      </c>
+      <c r="BP15" s="7">
+        <v>3908899.5238077301</v>
+      </c>
       <c r="BQ15" s="27">
         <f t="shared" si="17"/>
-        <v>-620</v>
+        <v>24</v>
       </c>
       <c r="BR15" s="28">
         <f t="shared" si="18"/>
-        <v>-4293292.3809505999</v>
+        <v>-384392.85714286985</v>
       </c>
       <c r="BS15" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-8.9533351804416225E-2</v>
       </c>
       <c r="BU15" s="9" t="s">
         <v>18</v>
@@ -4168,15 +4225,15 @@
       <c r="BX15" s="7"/>
       <c r="BY15" s="27">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-644</v>
       </c>
       <c r="BZ15" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA15" s="29" t="e">
+        <v>-3908899.5238077301</v>
+      </c>
+      <c r="CA15" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC15" s="9" t="s">
         <v>18</v>
@@ -4405,12 +4462,15 @@
         <v>76</v>
       </c>
       <c r="BN16" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="BO16" s="1">
+        <v>3936</v>
       </c>
       <c r="BP16" s="35"/>
       <c r="BQ16" s="10">
         <f t="shared" si="17"/>
-        <v>-3813</v>
+        <v>123</v>
       </c>
       <c r="BR16" s="12">
         <f t="shared" si="18"/>
@@ -4430,7 +4490,7 @@
       <c r="BX16" s="33"/>
       <c r="BY16" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-3936</v>
       </c>
       <c r="BZ16" s="12">
         <f t="shared" si="21"/>
@@ -4655,7 +4715,7 @@
       </c>
       <c r="BM17" s="14"/>
       <c r="BN17" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BP17" s="35"/>
       <c r="BQ17" s="10">
@@ -4914,18 +4974,23 @@
       <c r="BN18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP18" s="12"/>
+      <c r="BO18" s="10">
+        <v>129</v>
+      </c>
+      <c r="BP18" s="12">
+        <v>116457.14285663</v>
+      </c>
       <c r="BQ18" s="10">
         <f t="shared" si="17"/>
-        <v>-124</v>
+        <v>5</v>
       </c>
       <c r="BR18" s="12">
         <f t="shared" si="18"/>
-        <v>-122476.19047563001</v>
+        <v>-6019.0476190000045</v>
       </c>
       <c r="BS18" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-4.914463452549709E-2</v>
       </c>
       <c r="BU18" s="14"/>
       <c r="BV18" s="13" t="s">
@@ -4934,15 +4999,15 @@
       <c r="BX18" s="12"/>
       <c r="BY18" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="BZ18" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA18" s="11" t="e">
+        <v>-116457.14285663</v>
+      </c>
+      <c r="CA18" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC18" s="14"/>
       <c r="CD18" s="13" t="s">
@@ -5167,18 +5232,23 @@
       <c r="BN19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP19" s="12"/>
+      <c r="BO19" s="10">
+        <v>164</v>
+      </c>
+      <c r="BP19" s="12">
+        <v>177323.80952340999</v>
+      </c>
       <c r="BQ19" s="10">
         <f t="shared" si="17"/>
-        <v>-115</v>
+        <v>49</v>
       </c>
       <c r="BR19" s="12">
         <f t="shared" si="18"/>
-        <v>-115704.76190441</v>
+        <v>61619.04761899999</v>
       </c>
       <c r="BS19" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.53255411968184019</v>
       </c>
       <c r="BU19" s="14"/>
       <c r="BV19" s="13" t="s">
@@ -5187,15 +5257,15 @@
       <c r="BX19" s="12"/>
       <c r="BY19" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-164</v>
       </c>
       <c r="BZ19" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA19" s="11" t="e">
+        <v>-177323.80952340999</v>
+      </c>
+      <c r="CA19" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC19" s="14"/>
       <c r="CD19" s="13" t="s">
@@ -5420,18 +5490,23 @@
       <c r="BN20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP20" s="12"/>
+      <c r="BO20" s="10">
+        <v>36</v>
+      </c>
+      <c r="BP20" s="12">
+        <v>221085.71428565</v>
+      </c>
       <c r="BQ20" s="10">
         <f t="shared" si="17"/>
-        <v>-42</v>
+        <v>-6</v>
       </c>
       <c r="BR20" s="12">
         <f t="shared" si="18"/>
-        <v>-253409.52380945001</v>
+        <v>-32323.80952380001</v>
       </c>
       <c r="BS20" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.12755562236921186</v>
       </c>
       <c r="BU20" s="14"/>
       <c r="BV20" s="13" t="s">
@@ -5440,15 +5515,15 @@
       <c r="BX20" s="12"/>
       <c r="BY20" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="BZ20" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA20" s="11" t="e">
+        <v>-221085.71428565</v>
+      </c>
+      <c r="CA20" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC20" s="14"/>
       <c r="CD20" s="13" t="s">
@@ -5673,18 +5748,23 @@
       <c r="BN21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BP21" s="12"/>
+      <c r="BO21" s="10">
+        <v>8</v>
+      </c>
+      <c r="BP21" s="12">
+        <v>67809.523809480001</v>
+      </c>
       <c r="BQ21" s="10">
         <f t="shared" si="17"/>
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="BR21" s="12">
         <f t="shared" si="18"/>
-        <v>-101428.5714285</v>
+        <v>-33619.047619019999</v>
       </c>
       <c r="BS21" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.33145539906099397</v>
       </c>
       <c r="BU21" s="14"/>
       <c r="BV21" s="13" t="s">
@@ -5693,15 +5773,15 @@
       <c r="BX21" s="12"/>
       <c r="BY21" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BZ21" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA21" s="11" t="e">
+        <v>-67809.523809480001</v>
+      </c>
+      <c r="CA21" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC21" s="14"/>
       <c r="CD21" s="13" t="s">
@@ -5926,18 +6006,23 @@
       <c r="BN22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP22" s="12"/>
+      <c r="BO22" s="10">
+        <v>14</v>
+      </c>
+      <c r="BP22" s="12">
+        <v>78308</v>
+      </c>
       <c r="BQ22" s="10">
         <f t="shared" si="17"/>
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="BR22" s="12">
         <f t="shared" si="18"/>
-        <v>-39648</v>
+        <v>38660</v>
       </c>
       <c r="BS22" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.97508071025020182</v>
       </c>
       <c r="BU22" s="14"/>
       <c r="BV22" s="13" t="s">
@@ -5946,15 +6031,15 @@
       <c r="BX22" s="12"/>
       <c r="BY22" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="BZ22" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA22" s="11" t="e">
+        <v>-78308</v>
+      </c>
+      <c r="CA22" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC22" s="14"/>
       <c r="CD22" s="13" t="s">
@@ -6179,18 +6264,23 @@
       <c r="BN23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP23" s="12"/>
+      <c r="BO23" s="10">
+        <v>16</v>
+      </c>
+      <c r="BP23" s="12">
+        <v>555333.33333324001</v>
+      </c>
       <c r="BQ23" s="10">
         <f t="shared" si="17"/>
-        <v>-11</v>
+        <v>5</v>
       </c>
       <c r="BR23" s="12">
         <f t="shared" si="18"/>
-        <v>-431752.38095234003</v>
+        <v>123580.95238089998</v>
       </c>
       <c r="BS23" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.28623108483689347</v>
       </c>
       <c r="BU23" s="14"/>
       <c r="BV23" s="13" t="s">
@@ -6199,15 +6289,15 @@
       <c r="BX23" s="12"/>
       <c r="BY23" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="BZ23" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA23" s="11" t="e">
+        <v>-555333.33333324001</v>
+      </c>
+      <c r="CA23" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC23" s="14"/>
       <c r="CD23" s="13" t="s">
@@ -6432,18 +6522,23 @@
       <c r="BN24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP24" s="12"/>
+      <c r="BO24" s="10">
+        <v>28</v>
+      </c>
+      <c r="BP24" s="12">
+        <v>591904.76190464001</v>
+      </c>
       <c r="BQ24" s="10">
         <f t="shared" si="17"/>
-        <v>-16</v>
+        <v>12</v>
       </c>
       <c r="BR24" s="12">
         <f t="shared" si="18"/>
-        <v>-330571.42857133999</v>
+        <v>261333.33333330002</v>
       </c>
       <c r="BS24" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.79055027369645214</v>
       </c>
       <c r="BU24" s="14"/>
       <c r="BV24" s="13" t="s">
@@ -6452,15 +6547,15 @@
       <c r="BX24" s="12"/>
       <c r="BY24" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="BZ24" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA24" s="11" t="e">
+        <v>-591904.76190464001</v>
+      </c>
+      <c r="CA24" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC24" s="14"/>
       <c r="CD24" s="13" t="s">
@@ -6685,18 +6780,23 @@
       <c r="BN25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP25" s="12"/>
+      <c r="BO25" s="10">
+        <v>34</v>
+      </c>
+      <c r="BP25" s="12">
+        <v>1225333.3333332599</v>
+      </c>
       <c r="BQ25" s="10">
         <f t="shared" si="17"/>
-        <v>-33</v>
+        <v>1</v>
       </c>
       <c r="BR25" s="12">
         <f t="shared" si="18"/>
-        <v>-1169238.0952380199</v>
+        <v>56095.238095239969</v>
       </c>
       <c r="BS25" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>4.7975889875381414E-2</v>
       </c>
       <c r="BU25" s="14"/>
       <c r="BV25" s="13" t="s">
@@ -6705,15 +6805,15 @@
       <c r="BX25" s="12"/>
       <c r="BY25" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="BZ25" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA25" s="11" t="e">
+        <v>-1225333.3333332599</v>
+      </c>
+      <c r="CA25" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC25" s="14"/>
       <c r="CD25" s="13" t="s">
@@ -6939,19 +7039,23 @@
         <v>12</v>
       </c>
       <c r="BN26" s="9"/>
-      <c r="BO26" s="8"/>
-      <c r="BP26" s="7"/>
+      <c r="BO26" s="8">
+        <v>429</v>
+      </c>
+      <c r="BP26" s="7">
+        <v>3033555.61904631</v>
+      </c>
       <c r="BQ26" s="27">
         <f t="shared" si="17"/>
-        <v>-363</v>
+        <v>66</v>
       </c>
       <c r="BR26" s="28">
         <f t="shared" si="18"/>
-        <v>-2564228.95237969</v>
+        <v>469326.66666661995</v>
       </c>
       <c r="BS26" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.18302837826983787</v>
       </c>
       <c r="BU26" s="9" t="s">
         <v>12</v>
@@ -6961,15 +7065,15 @@
       <c r="BX26" s="7"/>
       <c r="BY26" s="27">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-429</v>
       </c>
       <c r="BZ26" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA26" s="29" t="e">
+        <v>-3033555.61904631</v>
+      </c>
+      <c r="CA26" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC26" s="9" t="s">
         <v>12</v>
@@ -7198,12 +7302,15 @@
         <v>77</v>
       </c>
       <c r="BN27" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="BO27" s="1">
+        <v>3175</v>
       </c>
       <c r="BP27" s="35"/>
       <c r="BQ27" s="10">
         <f t="shared" si="17"/>
-        <v>-3534</v>
+        <v>-359</v>
       </c>
       <c r="BR27" s="12">
         <f t="shared" si="18"/>
@@ -7223,7 +7330,7 @@
       <c r="BX27" s="33"/>
       <c r="BY27" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-3175</v>
       </c>
       <c r="BZ27" s="12">
         <f t="shared" si="21"/>
@@ -7448,7 +7555,7 @@
       </c>
       <c r="BM28" s="14"/>
       <c r="BN28" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BP28" s="35"/>
       <c r="BQ28" s="10">
@@ -7707,18 +7814,23 @@
       <c r="BN29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP29" s="12"/>
+      <c r="BO29" s="10">
+        <v>66</v>
+      </c>
+      <c r="BP29" s="12">
+        <v>56596.190475900003</v>
+      </c>
       <c r="BQ29" s="10">
         <f t="shared" si="17"/>
-        <v>-99</v>
+        <v>-33</v>
       </c>
       <c r="BR29" s="12">
         <f t="shared" si="18"/>
-        <v>-102610.47619004</v>
+        <v>-46014.285714140002</v>
       </c>
       <c r="BS29" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.44843652834160053</v>
       </c>
       <c r="BU29" s="14"/>
       <c r="BV29" s="13" t="s">
@@ -7727,15 +7839,15 @@
       <c r="BX29" s="12"/>
       <c r="BY29" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="BZ29" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA29" s="11" t="e">
+        <v>-56596.190475900003</v>
+      </c>
+      <c r="CA29" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC29" s="14"/>
       <c r="CD29" s="13" t="s">
@@ -7960,18 +8072,23 @@
       <c r="BN30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP30" s="12"/>
+      <c r="BO30" s="10">
+        <v>66</v>
+      </c>
+      <c r="BP30" s="12">
+        <v>72428.571428359995</v>
+      </c>
       <c r="BQ30" s="10">
         <f t="shared" si="17"/>
-        <v>-90</v>
+        <v>-24</v>
       </c>
       <c r="BR30" s="12">
         <f t="shared" si="18"/>
-        <v>-91561.904761619997</v>
+        <v>-19133.333333260001</v>
       </c>
       <c r="BS30" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.20896609111696987</v>
       </c>
       <c r="BU30" s="14"/>
       <c r="BV30" s="13" t="s">
@@ -7980,15 +8097,15 @@
       <c r="BX30" s="12"/>
       <c r="BY30" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="BZ30" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA30" s="11" t="e">
+        <v>-72428.571428359995</v>
+      </c>
+      <c r="CA30" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC30" s="14"/>
       <c r="CD30" s="13" t="s">
@@ -8213,18 +8330,23 @@
       <c r="BN31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP31" s="12"/>
+      <c r="BO31" s="10">
+        <v>17</v>
+      </c>
+      <c r="BP31" s="12">
+        <v>130314.28571421999</v>
+      </c>
       <c r="BQ31" s="10">
         <f t="shared" si="17"/>
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="BR31" s="12">
         <f t="shared" si="18"/>
-        <v>-235447.61904753</v>
+        <v>-105133.33333331</v>
       </c>
       <c r="BS31" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.44652536202579585</v>
       </c>
       <c r="BU31" s="14"/>
       <c r="BV31" s="13" t="s">
@@ -8233,15 +8355,15 @@
       <c r="BX31" s="12"/>
       <c r="BY31" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="BZ31" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA31" s="11" t="e">
+        <v>-130314.28571421999</v>
+      </c>
+      <c r="CA31" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC31" s="14"/>
       <c r="CD31" s="13" t="s">
@@ -8466,18 +8588,23 @@
       <c r="BN32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BP32" s="12"/>
+      <c r="BO32" s="10">
+        <v>8</v>
+      </c>
+      <c r="BP32" s="12">
+        <v>83999.999999959997</v>
+      </c>
       <c r="BQ32" s="10">
         <f t="shared" si="17"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="BR32" s="12">
         <f t="shared" si="18"/>
-        <v>-91619.047619010002</v>
+        <v>-7619.0476190500049</v>
       </c>
       <c r="BS32" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-8.3160083160143339E-2</v>
       </c>
       <c r="BU32" s="14"/>
       <c r="BV32" s="13" t="s">
@@ -8486,15 +8613,15 @@
       <c r="BX32" s="12"/>
       <c r="BY32" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BZ32" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA32" s="11" t="e">
+        <v>-83999.999999959997</v>
+      </c>
+      <c r="CA32" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC32" s="14"/>
       <c r="CD32" s="13" t="s">
@@ -8719,18 +8846,23 @@
       <c r="BN33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP33" s="12"/>
+      <c r="BO33" s="10">
+        <v>1</v>
+      </c>
+      <c r="BP33" s="12">
+        <v>990</v>
+      </c>
       <c r="BQ33" s="10">
         <f t="shared" si="17"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BR33" s="12">
         <f t="shared" si="18"/>
-        <v>-11280</v>
+        <v>-10290</v>
       </c>
       <c r="BS33" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.91223404255319152</v>
       </c>
       <c r="BU33" s="14"/>
       <c r="BV33" s="13" t="s">
@@ -8739,15 +8871,15 @@
       <c r="BX33" s="12"/>
       <c r="BY33" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BZ33" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA33" s="11" t="e">
+        <v>-990</v>
+      </c>
+      <c r="CA33" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC33" s="14"/>
       <c r="CD33" s="13" t="s">
@@ -8972,18 +9104,23 @@
       <c r="BN34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP34" s="12"/>
+      <c r="BO34" s="10">
+        <v>3</v>
+      </c>
+      <c r="BP34" s="12">
+        <v>70190.476190460002</v>
+      </c>
       <c r="BQ34" s="10">
         <f t="shared" si="17"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="BR34" s="12">
         <f t="shared" si="18"/>
-        <v>-210856.19047617001</v>
+        <v>-140665.71428571001</v>
       </c>
       <c r="BS34" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.66711683431275592</v>
       </c>
       <c r="BU34" s="14"/>
       <c r="BV34" s="13" t="s">
@@ -8992,15 +9129,15 @@
       <c r="BX34" s="12"/>
       <c r="BY34" s="10">
         <f t="shared" ref="BY34:BY60" si="32">BW34-BO34</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BZ34" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA34" s="11" t="e">
+        <v>-70190.476190460002</v>
+      </c>
+      <c r="CA34" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC34" s="14"/>
       <c r="CD34" s="13" t="s">
@@ -9225,18 +9362,23 @@
       <c r="BN35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP35" s="12"/>
+      <c r="BO35" s="10">
+        <v>5</v>
+      </c>
+      <c r="BP35" s="12">
+        <v>160476.19047617001</v>
+      </c>
       <c r="BQ35" s="10">
         <f t="shared" si="17"/>
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="BR35" s="12">
         <f t="shared" si="18"/>
-        <v>-225619.04761899999</v>
+        <v>-65142.857142829977</v>
       </c>
       <c r="BS35" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.28872942169685906</v>
       </c>
       <c r="BU35" s="14"/>
       <c r="BV35" s="13" t="s">
@@ -9245,15 +9387,15 @@
       <c r="BX35" s="12"/>
       <c r="BY35" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="BZ35" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA35" s="11" t="e">
+        <v>-160476.19047617001</v>
+      </c>
+      <c r="CA35" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC35" s="14"/>
       <c r="CD35" s="13" t="s">
@@ -9478,18 +9620,23 @@
       <c r="BN36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP36" s="12"/>
+      <c r="BO36" s="10">
+        <v>8</v>
+      </c>
+      <c r="BP36" s="12">
+        <v>280190.47619045997</v>
+      </c>
       <c r="BQ36" s="10">
         <f t="shared" si="17"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="BR36" s="12">
         <f t="shared" si="18"/>
-        <v>-314476.19047615997</v>
+        <v>-34285.7142857</v>
       </c>
       <c r="BS36" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.1090248334342474</v>
       </c>
       <c r="BU36" s="14"/>
       <c r="BV36" s="13" t="s">
@@ -9498,15 +9645,15 @@
       <c r="BX36" s="12"/>
       <c r="BY36" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BZ36" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA36" s="11" t="e">
+        <v>-280190.47619045997</v>
+      </c>
+      <c r="CA36" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC36" s="14"/>
       <c r="CD36" s="13" t="s">
@@ -9732,19 +9879,23 @@
         <v>11</v>
       </c>
       <c r="BN37" s="9"/>
-      <c r="BO37" s="8"/>
-      <c r="BP37" s="7"/>
+      <c r="BO37" s="8">
+        <v>174</v>
+      </c>
+      <c r="BP37" s="7">
+        <v>855186.19047552999</v>
+      </c>
       <c r="BQ37" s="27">
         <f t="shared" si="17"/>
-        <v>-249</v>
+        <v>-75</v>
       </c>
       <c r="BR37" s="28">
         <f t="shared" si="18"/>
-        <v>-1283470.47618953</v>
+        <v>-428284.285714</v>
       </c>
       <c r="BS37" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.33369235495429916</v>
       </c>
       <c r="BU37" s="9" t="s">
         <v>11</v>
@@ -9754,15 +9905,15 @@
       <c r="BX37" s="7"/>
       <c r="BY37" s="27">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-174</v>
       </c>
       <c r="BZ37" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA37" s="29" t="e">
+        <v>-855186.19047552999</v>
+      </c>
+      <c r="CA37" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC37" s="9" t="s">
         <v>11</v>
@@ -9991,12 +10142,15 @@
         <v>81</v>
       </c>
       <c r="BN38" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="BO38" s="1">
+        <v>1672</v>
       </c>
       <c r="BP38" s="35"/>
       <c r="BQ38" s="10">
         <f t="shared" si="17"/>
-        <v>-1804</v>
+        <v>-132</v>
       </c>
       <c r="BR38" s="12">
         <f t="shared" si="18"/>
@@ -10016,7 +10170,7 @@
       <c r="BX38" s="33"/>
       <c r="BY38" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-1672</v>
       </c>
       <c r="BZ38" s="12">
         <f t="shared" si="21"/>
@@ -10241,7 +10395,7 @@
       </c>
       <c r="BM39" s="14"/>
       <c r="BN39" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BP39" s="35"/>
       <c r="BQ39" s="10">
@@ -10500,18 +10654,23 @@
       <c r="BN40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP40" s="12"/>
+      <c r="BO40" s="10">
+        <v>104</v>
+      </c>
+      <c r="BP40" s="12">
+        <v>76006.666666129997</v>
+      </c>
       <c r="BQ40" s="10">
         <f t="shared" si="17"/>
-        <v>-101</v>
+        <v>3</v>
       </c>
       <c r="BR40" s="12">
         <f t="shared" si="18"/>
-        <v>-96915.23809472</v>
+        <v>-20908.571428590003</v>
       </c>
       <c r="BS40" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.21574080443526367</v>
       </c>
       <c r="BU40" s="14"/>
       <c r="BV40" s="13" t="s">
@@ -10520,15 +10679,15 @@
       <c r="BX40" s="12"/>
       <c r="BY40" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="BZ40" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA40" s="11" t="e">
+        <v>-76006.666666129997</v>
+      </c>
+      <c r="CA40" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC40" s="14"/>
       <c r="CD40" s="13" t="s">
@@ -10753,18 +10912,23 @@
       <c r="BN41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP41" s="12"/>
+      <c r="BO41" s="10">
+        <v>66</v>
+      </c>
+      <c r="BP41" s="12">
+        <v>85561.90476166</v>
+      </c>
       <c r="BQ41" s="10">
         <f t="shared" si="17"/>
-        <v>-83</v>
+        <v>-17</v>
       </c>
       <c r="BR41" s="12">
         <f t="shared" si="18"/>
-        <v>-102161.90476165</v>
+        <v>-16599.999999990003</v>
       </c>
       <c r="BS41" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.16248718187781269</v>
       </c>
       <c r="BU41" s="14"/>
       <c r="BV41" s="13" t="s">
@@ -10773,15 +10937,15 @@
       <c r="BX41" s="12"/>
       <c r="BY41" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="BZ41" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA41" s="11" t="e">
+        <v>-85561.90476166</v>
+      </c>
+      <c r="CA41" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC41" s="14"/>
       <c r="CD41" s="13" t="s">
@@ -11006,18 +11170,23 @@
       <c r="BN42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP42" s="12"/>
+      <c r="BO42" s="10">
+        <v>4</v>
+      </c>
+      <c r="BP42" s="12">
+        <v>27104.761904750001</v>
+      </c>
       <c r="BQ42" s="10">
         <f t="shared" si="17"/>
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="BR42" s="12">
         <f t="shared" si="18"/>
-        <v>-77038.095238080001</v>
+        <v>-49933.333333329996</v>
       </c>
       <c r="BS42" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.64816417356912925</v>
       </c>
       <c r="BU42" s="14"/>
       <c r="BV42" s="13" t="s">
@@ -11026,15 +11195,15 @@
       <c r="BX42" s="12"/>
       <c r="BY42" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BZ42" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA42" s="11" t="e">
+        <v>-27104.761904750001</v>
+      </c>
+      <c r="CA42" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC42" s="14"/>
       <c r="CD42" s="13" t="s">
@@ -11259,18 +11428,23 @@
       <c r="BN43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BP43" s="12"/>
+      <c r="BO43" s="10">
+        <v>2</v>
+      </c>
+      <c r="BP43" s="12">
+        <v>16952.380952380001</v>
+      </c>
       <c r="BQ43" s="10">
         <f t="shared" si="17"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="BR43" s="12">
         <f t="shared" si="18"/>
-        <v>-54761.904761880003</v>
+        <v>-37809.523809500002</v>
       </c>
       <c r="BS43" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.69043478260857305</v>
       </c>
       <c r="BU43" s="14"/>
       <c r="BV43" s="13" t="s">
@@ -11279,15 +11453,15 @@
       <c r="BX43" s="12"/>
       <c r="BY43" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BZ43" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA43" s="11" t="e">
+        <v>-16952.380952380001</v>
+      </c>
+      <c r="CA43" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC43" s="14"/>
       <c r="CD43" s="13" t="s">
@@ -11512,18 +11686,23 @@
       <c r="BN44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP44" s="12"/>
+      <c r="BO44" s="10">
+        <v>2</v>
+      </c>
+      <c r="BP44" s="12">
+        <v>4608</v>
+      </c>
       <c r="BQ44" s="10">
         <f t="shared" si="17"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BR44" s="12">
         <f t="shared" si="18"/>
-        <v>-15270</v>
+        <v>-10662</v>
       </c>
       <c r="BS44" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.69823182711198428</v>
       </c>
       <c r="BU44" s="14"/>
       <c r="BV44" s="13" t="s">
@@ -11532,15 +11711,15 @@
       <c r="BX44" s="12"/>
       <c r="BY44" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BZ44" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA44" s="11" t="e">
+        <v>-4608</v>
+      </c>
+      <c r="CA44" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC44" s="14"/>
       <c r="CD44" s="13" t="s">
@@ -11766,18 +11945,23 @@
       <c r="BN45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP45" s="12"/>
+      <c r="BO45" s="10">
+        <v>7</v>
+      </c>
+      <c r="BP45" s="12">
+        <v>214542.85714281001</v>
+      </c>
       <c r="BQ45" s="10">
         <f t="shared" si="17"/>
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="BR45" s="12">
         <f t="shared" si="18"/>
-        <v>-129160.95238094</v>
+        <v>85381.904761870013</v>
       </c>
       <c r="BS45" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.66105044278435998</v>
       </c>
       <c r="BU45" s="14"/>
       <c r="BV45" s="13" t="s">
@@ -11786,15 +11970,15 @@
       <c r="BX45" s="12"/>
       <c r="BY45" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BZ45" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA45" s="11" t="e">
+        <v>-214542.85714281001</v>
+      </c>
+      <c r="CA45" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC45" s="14"/>
       <c r="CD45" s="13" t="s">
@@ -12020,18 +12204,23 @@
       <c r="BN46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP46" s="12"/>
+      <c r="BO46" s="10">
+        <v>13</v>
+      </c>
+      <c r="BP46" s="12">
+        <v>245238.09523802</v>
+      </c>
       <c r="BQ46" s="10">
         <f t="shared" si="17"/>
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="BR46" s="12">
         <f t="shared" si="18"/>
-        <v>-215809.52380947</v>
+        <v>29428.57142855</v>
       </c>
       <c r="BS46" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.13636363636357107</v>
       </c>
       <c r="BU46" s="14"/>
       <c r="BV46" s="13" t="s">
@@ -12040,15 +12229,15 @@
       <c r="BX46" s="12"/>
       <c r="BY46" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="BZ46" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA46" s="11" t="e">
+        <v>-245238.09523802</v>
+      </c>
+      <c r="CA46" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC46" s="14"/>
       <c r="CD46" s="13" t="s">
@@ -12274,18 +12463,23 @@
       <c r="BN47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP47" s="12"/>
+      <c r="BO47" s="10">
+        <v>22</v>
+      </c>
+      <c r="BP47" s="12">
+        <v>702493.33333330997</v>
+      </c>
       <c r="BQ47" s="10">
         <f t="shared" si="17"/>
-        <v>-15</v>
+        <v>7</v>
       </c>
       <c r="BR47" s="12">
         <f t="shared" si="18"/>
-        <v>-490952.38095235999</v>
+        <v>211540.95238094998</v>
       </c>
       <c r="BS47" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.43087875848691942</v>
       </c>
       <c r="BU47" s="14"/>
       <c r="BV47" s="13" t="s">
@@ -12294,15 +12488,15 @@
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="BZ47" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA47" s="11" t="e">
+        <v>-702493.33333330997</v>
+      </c>
+      <c r="CA47" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC47" s="14"/>
       <c r="CD47" s="13" t="s">
@@ -12529,19 +12723,23 @@
         <v>10</v>
       </c>
       <c r="BN48" s="9"/>
-      <c r="BO48" s="8"/>
-      <c r="BP48" s="7"/>
+      <c r="BO48" s="8">
+        <v>220</v>
+      </c>
+      <c r="BP48" s="7">
+        <v>1372507.9999990601</v>
+      </c>
       <c r="BQ48" s="27">
         <f t="shared" si="17"/>
-        <v>-231</v>
+        <v>-11</v>
       </c>
       <c r="BR48" s="28">
         <f t="shared" si="18"/>
-        <v>-1182069.9999991001</v>
+        <v>190437.99999995995</v>
       </c>
       <c r="BS48" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.16110551828580788</v>
       </c>
       <c r="BU48" s="9" t="s">
         <v>10</v>
@@ -12551,15 +12749,15 @@
       <c r="BX48" s="7"/>
       <c r="BY48" s="27">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-220</v>
       </c>
       <c r="BZ48" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA48" s="29" t="e">
+        <v>-1372507.9999990601</v>
+      </c>
+      <c r="CA48" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC48" s="9" t="s">
         <v>10</v>
@@ -12765,7 +12963,7 @@
         <v>84</v>
       </c>
       <c r="BN49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="BP49" s="35"/>
       <c r="BQ49" s="10">
@@ -13015,7 +13213,7 @@
       </c>
       <c r="BM50" s="14"/>
       <c r="BN50" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BP50" s="35"/>
       <c r="BQ50" s="10">
@@ -13274,18 +13472,23 @@
       <c r="BN51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BP51" s="12"/>
+      <c r="BO51" s="10">
+        <v>109</v>
+      </c>
+      <c r="BP51" s="12">
+        <v>108975.23809471</v>
+      </c>
       <c r="BQ51" s="10">
         <f t="shared" si="17"/>
-        <v>-114</v>
+        <v>-5</v>
       </c>
       <c r="BR51" s="12">
         <f t="shared" si="18"/>
-        <v>-109647.61904706</v>
+        <v>-672.38095234999491</v>
       </c>
       <c r="BS51" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-6.1321983841839166E-3</v>
       </c>
       <c r="BU51" s="14"/>
       <c r="BV51" s="13" t="s">
@@ -13294,15 +13497,15 @@
       <c r="BX51" s="12"/>
       <c r="BY51" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="BZ51" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA51" s="11" t="e">
+        <v>-108975.23809471</v>
+      </c>
+      <c r="CA51" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC51" s="14"/>
       <c r="CD51" s="13" t="s">
@@ -13527,18 +13730,23 @@
       <c r="BN52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BP52" s="12"/>
+      <c r="BO52" s="10">
+        <v>76</v>
+      </c>
+      <c r="BP52" s="12">
+        <v>76523.809523589996</v>
+      </c>
       <c r="BQ52" s="10">
         <f t="shared" si="17"/>
-        <v>-71</v>
+        <v>5</v>
       </c>
       <c r="BR52" s="12">
         <f t="shared" si="18"/>
-        <v>-81323.809523529999</v>
+        <v>-4799.9999999400025</v>
       </c>
       <c r="BS52" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-5.9023304836097037E-2</v>
       </c>
       <c r="BU52" s="14"/>
       <c r="BV52" s="13" t="s">
@@ -13547,15 +13755,15 @@
       <c r="BX52" s="12"/>
       <c r="BY52" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-76</v>
       </c>
       <c r="BZ52" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA52" s="11" t="e">
+        <v>-76523.809523589996</v>
+      </c>
+      <c r="CA52" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC52" s="14"/>
       <c r="CD52" s="13" t="s">
@@ -13780,18 +13988,23 @@
       <c r="BN53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BP53" s="12"/>
+      <c r="BO53" s="10">
+        <v>7</v>
+      </c>
+      <c r="BP53" s="12">
+        <v>51958.095238069996</v>
+      </c>
       <c r="BQ53" s="10">
         <f t="shared" si="17"/>
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="BR53" s="12">
         <f t="shared" si="18"/>
-        <v>-112238.09523806001</v>
+        <v>-60279.99999999001</v>
       </c>
       <c r="BS53" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.5370725498515857</v>
       </c>
       <c r="BU53" s="14"/>
       <c r="BV53" s="13" t="s">
@@ -13800,15 +14013,15 @@
       <c r="BX53" s="12"/>
       <c r="BY53" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="BZ53" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA53" s="11" t="e">
+        <v>-51958.095238069996</v>
+      </c>
+      <c r="CA53" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC53" s="14"/>
       <c r="CD53" s="13" t="s">
@@ -14033,18 +14246,23 @@
       <c r="BN54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BP54" s="12"/>
+      <c r="BO54" s="10">
+        <v>3</v>
+      </c>
+      <c r="BP54" s="12">
+        <v>22571.4285714</v>
+      </c>
       <c r="BQ54" s="10">
         <f t="shared" si="17"/>
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="BR54" s="12">
         <f t="shared" si="18"/>
-        <v>-124666.66666662</v>
+        <v>-102095.23809522</v>
       </c>
       <c r="BS54" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.81894576012239217</v>
       </c>
       <c r="BU54" s="14"/>
       <c r="BV54" s="13" t="s">
@@ -14053,15 +14271,15 @@
       <c r="BX54" s="12"/>
       <c r="BY54" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BZ54" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA54" s="11" t="e">
+        <v>-22571.4285714</v>
+      </c>
+      <c r="CA54" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC54" s="14"/>
       <c r="CD54" s="13" t="s">
@@ -14286,18 +14504,23 @@
       <c r="BN55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BP55" s="12"/>
+      <c r="BO55" s="10">
+        <v>2</v>
+      </c>
+      <c r="BP55" s="12">
+        <v>9680</v>
+      </c>
       <c r="BQ55" s="10">
         <f t="shared" si="17"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BR55" s="12">
         <f t="shared" si="18"/>
-        <v>-11370</v>
+        <v>-1690</v>
       </c>
       <c r="BS55" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.14863676341248899</v>
       </c>
       <c r="BU55" s="14"/>
       <c r="BV55" s="13" t="s">
@@ -14306,15 +14529,15 @@
       <c r="BX55" s="12"/>
       <c r="BY55" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BZ55" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA55" s="11" t="e">
+        <v>-9680</v>
+      </c>
+      <c r="CA55" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC55" s="14"/>
       <c r="CD55" s="13" t="s">
@@ -14540,18 +14763,23 @@
       <c r="BN56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BP56" s="12"/>
+      <c r="BO56" s="10">
+        <v>8</v>
+      </c>
+      <c r="BP56" s="12">
+        <v>273257.1428571</v>
+      </c>
       <c r="BQ56" s="10">
         <f t="shared" si="17"/>
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="BR56" s="12">
         <f t="shared" si="18"/>
-        <v>-191647.61904758</v>
+        <v>81609.523809520004</v>
       </c>
       <c r="BS56" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0.42583113849830279</v>
       </c>
       <c r="BU56" s="14"/>
       <c r="BV56" s="13" t="s">
@@ -14560,15 +14788,15 @@
       <c r="BX56" s="12"/>
       <c r="BY56" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BZ56" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA56" s="11" t="e">
+        <v>-273257.1428571</v>
+      </c>
+      <c r="CA56" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC56" s="14"/>
       <c r="CD56" s="13" t="s">
@@ -14794,18 +15022,23 @@
       <c r="BN57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BP57" s="12"/>
+      <c r="BO57" s="10">
+        <v>12</v>
+      </c>
+      <c r="BP57" s="12">
+        <v>318857.14285708999</v>
+      </c>
       <c r="BQ57" s="10">
         <f t="shared" si="17"/>
-        <v>-17</v>
+        <v>-5</v>
       </c>
       <c r="BR57" s="12">
         <f t="shared" si="18"/>
-        <v>-399809.52380944003</v>
+        <v>-80952.380952350039</v>
       </c>
       <c r="BS57" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.20247737017623951</v>
       </c>
       <c r="BU57" s="14"/>
       <c r="BV57" s="13" t="s">
@@ -14814,15 +15047,15 @@
       <c r="BX57" s="12"/>
       <c r="BY57" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="BZ57" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA57" s="11" t="e">
+        <v>-318857.14285708999</v>
+      </c>
+      <c r="CA57" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC57" s="14"/>
       <c r="CD57" s="13" t="s">
@@ -15048,18 +15281,23 @@
       <c r="BN58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BP58" s="12"/>
+      <c r="BO58" s="10">
+        <v>9</v>
+      </c>
+      <c r="BP58" s="12">
+        <v>284857.14285712998</v>
+      </c>
       <c r="BQ58" s="10">
         <f t="shared" si="17"/>
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="BR58" s="12">
         <f t="shared" si="18"/>
-        <v>-645047.61904757994</v>
+        <v>-360190.47619044996</v>
       </c>
       <c r="BS58" s="11">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.55839362173334617</v>
       </c>
       <c r="BU58" s="14"/>
       <c r="BV58" s="13" t="s">
@@ -15068,15 +15306,15 @@
       <c r="BX58" s="12"/>
       <c r="BY58" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="BZ58" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA58" s="11" t="e">
+        <v>-284857.14285712998</v>
+      </c>
+      <c r="CA58" s="11">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC58" s="14"/>
       <c r="CD58" s="13" t="s">
@@ -15303,19 +15541,23 @@
         <v>1</v>
       </c>
       <c r="BN59" s="9"/>
-      <c r="BO59" s="8"/>
-      <c r="BP59" s="7"/>
+      <c r="BO59" s="8">
+        <v>226</v>
+      </c>
+      <c r="BP59" s="7">
+        <v>1146679.9999990901</v>
+      </c>
       <c r="BQ59" s="27">
         <f t="shared" si="17"/>
-        <v>-254</v>
+        <v>-28</v>
       </c>
       <c r="BR59" s="28">
         <f t="shared" si="18"/>
-        <v>-1675750.95237987</v>
+        <v>-529070.9523807799</v>
       </c>
       <c r="BS59" s="29">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-0.31572170770925312</v>
       </c>
       <c r="BU59" s="9" t="s">
         <v>1</v>
@@ -15325,15 +15567,15 @@
       <c r="BX59" s="7"/>
       <c r="BY59" s="27">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-226</v>
       </c>
       <c r="BZ59" s="28">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA59" s="29" t="e">
+        <v>-1146679.9999990901</v>
+      </c>
+      <c r="CA59" s="29">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC59" s="9" t="s">
         <v>1</v>
@@ -15562,19 +15804,23 @@
         <v>0</v>
       </c>
       <c r="BN60" s="4"/>
-      <c r="BO60" s="3"/>
-      <c r="BP60" s="2"/>
+      <c r="BO60" s="3">
+        <v>1693</v>
+      </c>
+      <c r="BP60" s="2">
+        <v>10316829.33332772</v>
+      </c>
       <c r="BQ60" s="6">
         <f t="shared" si="17"/>
-        <v>-1717</v>
+        <v>-24</v>
       </c>
       <c r="BR60" s="5">
         <f t="shared" si="18"/>
-        <v>-10998812.76189879</v>
+        <v>-681983.42857106961</v>
       </c>
       <c r="BS60" s="30">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>-6.2005185771826413E-2</v>
       </c>
       <c r="BU60" s="4" t="s">
         <v>0</v>
@@ -15584,15 +15830,15 @@
       <c r="BX60" s="2"/>
       <c r="BY60" s="6">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-1693</v>
       </c>
       <c r="BZ60" s="5">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="CA60" s="30" t="e">
+        <v>-10316829.33332772</v>
+      </c>
+      <c r="CA60" s="30">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CC60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5049159E-2551-4044-BDEA-9D17C425CE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17533084-75FC-EB43-9DB4-249428C1C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3280" yWindow="4020" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="15640" yWindow="3220" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q4" sheetId="2" r:id="rId1"/>
@@ -1881,10 +1881,13 @@
       <c r="BN6" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="BO6" s="15">
+        <v>10</v>
+      </c>
       <c r="BP6" s="33"/>
       <c r="BQ6" s="10">
         <f t="shared" si="17"/>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="BR6" s="12">
         <f t="shared" si="18"/>
@@ -1901,7 +1904,7 @@
       <c r="BX6" s="33"/>
       <c r="BY6" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BZ6" s="12">
         <f t="shared" si="21"/>
@@ -4717,10 +4720,13 @@
       <c r="BN17" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="BO17" s="1">
+        <v>6</v>
+      </c>
       <c r="BP17" s="35"/>
       <c r="BQ17" s="10">
         <f t="shared" si="17"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="BR17" s="12">
         <f t="shared" si="18"/>
@@ -4738,7 +4744,7 @@
       <c r="BX17" s="33"/>
       <c r="BY17" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="BZ17" s="12">
         <f t="shared" si="21"/>
@@ -7557,6 +7563,9 @@
       <c r="BN28" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="BO28" s="1">
+        <v>0</v>
+      </c>
       <c r="BP28" s="35"/>
       <c r="BQ28" s="10">
         <f t="shared" si="17"/>
@@ -10397,10 +10406,13 @@
       <c r="BN39" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="BO39" s="1">
+        <v>2</v>
+      </c>
       <c r="BP39" s="35"/>
       <c r="BQ39" s="10">
         <f t="shared" si="17"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BR39" s="12">
         <f t="shared" si="18"/>
@@ -10418,7 +10430,7 @@
       <c r="BX39" s="33"/>
       <c r="BY39" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BZ39" s="12">
         <f t="shared" si="21"/>
@@ -13215,10 +13227,13 @@
       <c r="BN50" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="BO50" s="1">
+        <v>2</v>
+      </c>
       <c r="BP50" s="35"/>
       <c r="BQ50" s="10">
         <f t="shared" si="17"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BR50" s="12">
         <f t="shared" si="18"/>
@@ -13236,7 +13251,7 @@
       <c r="BX50" s="33"/>
       <c r="BY50" s="10">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="BZ50" s="12">
         <f t="shared" si="21"/>
